--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_branch.xlsx
@@ -955,127 +955,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3557435144184714</v>
+        <v>0.3557435144214025</v>
       </c>
       <c r="D2">
-        <v>0.3557435144184714</v>
+        <v>0.355743514423176</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3557435144184714</v>
+        <v>0.3557435144214032</v>
       </c>
       <c r="G2">
-        <v>0.3557435144184714</v>
+        <v>0.3557435144231753</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.08215544674899872</v>
+        <v>0.08215544674967563</v>
       </c>
       <c r="J2">
-        <v>0.08215544674899873</v>
+        <v>0.08215544675008522</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.08215544674899872</v>
+        <v>0.08215544674967579</v>
       </c>
       <c r="M2">
-        <v>0.08215544674899873</v>
+        <v>0.08215544675008504</v>
       </c>
       <c r="N2">
-        <v>-2.544261153244686E-18</v>
+        <v>-8.112554785401425E-13</v>
       </c>
       <c r="O2">
-        <v>0.09010973163428015</v>
+        <v>0.0901097316350289</v>
       </c>
       <c r="P2">
-        <v>0.03935444973466317</v>
+        <v>0.03935444973556931</v>
       </c>
       <c r="Q2">
-        <v>5.088522306489369E-18</v>
+        <v>8.112529342919924E-13</v>
       </c>
       <c r="R2">
-        <v>-0.02537764094980933</v>
+        <v>-0.02537764094899424</v>
       </c>
       <c r="S2">
-        <v>0.0253776409498077</v>
+        <v>0.02537764095011651</v>
       </c>
       <c r="T2">
-        <v>5.088522306489372E-18</v>
+        <v>1.423259689123289E-14</v>
       </c>
       <c r="U2">
-        <v>0.006347849100821007</v>
+        <v>0.006347849100782066</v>
       </c>
       <c r="V2">
-        <v>0.08111962054068335</v>
+        <v>0.08111962054156635</v>
       </c>
       <c r="W2">
-        <v>-5.088522306489369E-18</v>
+        <v>-1.447175743614143E-14</v>
       </c>
       <c r="X2">
-        <v>0.03738588571993093</v>
+        <v>0.03738588571998035</v>
       </c>
       <c r="Y2">
-        <v>-0.03738588571993143</v>
+        <v>-0.03738588571894726</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-124.1687674797839</v>
+        <v>-124.168767479727</v>
       </c>
       <c r="AB2">
-        <v>55.83123252020882</v>
+        <v>55.8312325204807</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>55.83123252020884</v>
+        <v>55.83123252026577</v>
       </c>
       <c r="AE2">
-        <v>-124.1687674797839</v>
+        <v>-124.1687674795121</v>
       </c>
       <c r="AF2">
-        <v>1.100000023841855</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="AG2">
-        <v>1.099538107887551</v>
+        <v>1.099538107887549</v>
       </c>
       <c r="AH2">
-        <v>1.097454749634821</v>
+        <v>1.097454749634792</v>
       </c>
       <c r="AI2">
-        <v>1.100000023841855</v>
+        <v>1.100000023859399</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119209313</v>
+        <v>0.5500000119113241</v>
       </c>
       <c r="AK2">
-        <v>0.550000011920925</v>
+        <v>0.5500000119058521</v>
       </c>
       <c r="AL2">
-        <v>1.250975106659675E-15</v>
+        <v>1.264851143932793E-12</v>
       </c>
       <c r="AM2">
-        <v>-120.1391793376201</v>
+        <v>-120.1391793376213</v>
       </c>
       <c r="AN2">
-        <v>119.9513097268558</v>
+        <v>119.9513097268545</v>
       </c>
       <c r="AO2">
-        <v>1.181816298246187E-15</v>
+        <v>2.645052840876529E-10</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999999916</v>
+        <v>179.9999999991604</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999999917</v>
+        <v>-179.9999999986971</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -1119,40 +1119,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.124219233306085E-23</v>
+        <v>6.66962795766812E-13</v>
       </c>
       <c r="O3">
-        <v>-4.070821374148507E-17</v>
+        <v>2.791181703351831E-20</v>
       </c>
       <c r="P3">
-        <v>4.579666624442903E-17</v>
+        <v>4.343628794092517E-20</v>
       </c>
       <c r="Q3">
-        <v>1.124219233306085E-23</v>
+        <v>-6.669627957654743E-13</v>
       </c>
       <c r="R3">
-        <v>1.577218284516093E-16</v>
+        <v>1.169934726769811E-16</v>
       </c>
       <c r="S3">
-        <v>7.121694926396706E-17</v>
+        <v>1.169504879764412E-16</v>
       </c>
       <c r="T3">
-        <v>-9.151354021381658E-26</v>
+        <v>3.079025807300905E-24</v>
       </c>
       <c r="U3">
-        <v>1.921133041081558E-09</v>
+        <v>1.921353073841052E-09</v>
       </c>
       <c r="V3">
-        <v>-1.921133051258581E-09</v>
+        <v>-1.920852851725132E-09</v>
       </c>
       <c r="W3">
-        <v>9.151354021381658E-26</v>
+        <v>-2.557079240098857E-24</v>
       </c>
       <c r="X3">
-        <v>-1.921132962025833E-09</v>
+        <v>-1.921352994780761E-09</v>
       </c>
       <c r="Y3">
-        <v>1.921133130314307E-09</v>
+        <v>1.920852930757135E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1173,40 +1173,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.100000023841855</v>
+        <v>1.100000023859399</v>
       </c>
       <c r="AG3">
-        <v>0.5500000119209313</v>
+        <v>0.5500000119113241</v>
       </c>
       <c r="AH3">
-        <v>0.550000011920925</v>
+        <v>0.5500000119058521</v>
       </c>
       <c r="AI3">
-        <v>1.100000023841855</v>
+        <v>1.100000023857193</v>
       </c>
       <c r="AJ3">
-        <v>0.5499999892881174</v>
+        <v>0.5499999892797947</v>
       </c>
       <c r="AK3">
-        <v>0.5500000345537409</v>
+        <v>0.5500000345351774</v>
       </c>
       <c r="AL3">
-        <v>1.181816298246187E-15</v>
+        <v>2.645052840876529E-10</v>
       </c>
       <c r="AM3">
-        <v>-179.9999999999916</v>
+        <v>179.9999999991604</v>
       </c>
       <c r="AN3">
-        <v>179.9999999999917</v>
+        <v>-179.9999999986971</v>
       </c>
       <c r="AO3">
-        <v>1.181819705995724E-15</v>
+        <v>2.196671977333139E-10</v>
       </c>
       <c r="AP3">
-        <v>-179.9999965101831</v>
+        <v>-179.9999965111844</v>
       </c>
       <c r="AQ3">
-        <v>179.9999965101833</v>
+        <v>179.9999965115584</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1250,40 +1250,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.12421924053731E-23</v>
+        <v>-3.079025807300905E-24</v>
       </c>
       <c r="O4">
-        <v>-1.526560220903871E-17</v>
+        <v>-3.334813699725587E-13</v>
       </c>
       <c r="P4">
-        <v>4.070814393793904E-17</v>
+        <v>4.344382896313714E-20</v>
       </c>
       <c r="Q4">
-        <v>1.12421924053731E-23</v>
+        <v>4.17909662934156E-24</v>
       </c>
       <c r="R4">
-        <v>8.547377343038407E-17</v>
+        <v>3.335515398983665E-13</v>
       </c>
       <c r="S4">
-        <v>2.950002857833142E-17</v>
+        <v>7.015274939498083E-17</v>
       </c>
       <c r="T4">
-        <v>-9.151343174543977E-26</v>
+        <v>6.66962795766812E-13</v>
       </c>
       <c r="U4">
-        <v>1.921133076701215E-09</v>
+        <v>1.920519370346376E-09</v>
       </c>
       <c r="V4">
-        <v>-1.921133086878237E-09</v>
+        <v>-1.921186333123001E-09</v>
       </c>
       <c r="W4">
-        <v>9.151343174543977E-26</v>
+        <v>-6.669627957653841E-13</v>
       </c>
       <c r="X4">
-        <v>-1.921133029267777E-09</v>
+        <v>-1.920519322920671E-09</v>
       </c>
       <c r="Y4">
-        <v>1.921133134311674E-09</v>
+        <v>1.921186380544761E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1304,40 +1304,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.100000023841855</v>
+        <v>1.100000023859399</v>
       </c>
       <c r="AG4">
-        <v>0.5500000119209313</v>
+        <v>0.5500000119113241</v>
       </c>
       <c r="AH4">
-        <v>0.550000011920925</v>
+        <v>0.5500000119058521</v>
       </c>
       <c r="AI4">
-        <v>1.100000023841855</v>
+        <v>1.100000023857044</v>
       </c>
       <c r="AJ4">
-        <v>0.5499999983412421</v>
+        <v>0.5499999983329995</v>
       </c>
       <c r="AK4">
-        <v>0.5500000255006147</v>
+        <v>0.5500000254818225</v>
       </c>
       <c r="AL4">
-        <v>1.181816298246187E-15</v>
+        <v>2.645052840876529E-10</v>
       </c>
       <c r="AM4">
-        <v>-179.9999999999916</v>
+        <v>179.9999999991604</v>
       </c>
       <c r="AN4">
-        <v>179.9999999999917</v>
+        <v>-179.9999999986971</v>
       </c>
       <c r="AO4">
-        <v>1.181818342895962E-15</v>
+        <v>3.59007429738013E-10</v>
       </c>
       <c r="AP4">
-        <v>-179.9999979061065</v>
+        <v>-179.9999979071662</v>
       </c>
       <c r="AQ4">
-        <v>179.9999979061066</v>
+        <v>179.9999979078186</v>
       </c>
     </row>
   </sheetData>
@@ -1489,127 +1489,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.05066944729275168</v>
+        <v>0.05066944729294589</v>
       </c>
       <c r="D2">
-        <v>0.05066944729275168</v>
+        <v>0.05066944729320973</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.05066944729275168</v>
+        <v>0.05066944729294586</v>
       </c>
       <c r="G2">
-        <v>0.05066944729275168</v>
+        <v>0.05066944729320977</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01170160778803144</v>
+        <v>0.01170160778807629</v>
       </c>
       <c r="J2">
-        <v>0.01170160778803144</v>
+        <v>0.01170160778813722</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01170160778803144</v>
+        <v>0.01170160778807628</v>
       </c>
       <c r="M2">
-        <v>0.01170160778803144</v>
+        <v>0.01170160778813723</v>
       </c>
       <c r="N2">
-        <v>1.099977162972809E-36</v>
+        <v>-3.47947349563122E-14</v>
       </c>
       <c r="O2">
-        <v>0.01195213586575931</v>
+        <v>0.01195213586582431</v>
       </c>
       <c r="P2">
-        <v>0.003511272021138653</v>
+        <v>0.003511272021260142</v>
       </c>
       <c r="Q2">
-        <v>-1.93179787004859E-36</v>
+        <v>3.478866342451929E-14</v>
       </c>
       <c r="R2">
-        <v>-0.01063891436235429</v>
+        <v>-0.0106389143624084</v>
       </c>
       <c r="S2">
-        <v>-0.002198050517733626</v>
+        <v>-0.002198050517832185</v>
       </c>
       <c r="T2">
-        <v>-3.035765945095988E-19</v>
+        <v>8.854813181634305E-14</v>
       </c>
       <c r="U2">
-        <v>0.002841561563922337</v>
+        <v>0.002841561563852629</v>
       </c>
       <c r="V2">
-        <v>0.01176985984605268</v>
+        <v>0.01176985984613227</v>
       </c>
       <c r="W2">
-        <v>3.035765945095988E-19</v>
+        <v>-8.854357816734298E-14</v>
       </c>
       <c r="X2">
-        <v>-0.001954334218357825</v>
+        <v>-0.001954334218276918</v>
       </c>
       <c r="Y2">
-        <v>-0.01088263250048817</v>
+        <v>-0.01088263250055613</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-133.3925184285223</v>
+        <v>-133.392518428136</v>
       </c>
       <c r="AB2">
-        <v>46.60748157147039</v>
+        <v>46.60748157190714</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>46.60748157147042</v>
+        <v>46.6074815718567</v>
       </c>
       <c r="AE2">
-        <v>-133.3925184285223</v>
+        <v>-133.3925184280856</v>
       </c>
       <c r="AF2">
-        <v>1.049999952316288</v>
+        <v>1.049999952316286</v>
       </c>
       <c r="AG2">
-        <v>1.049879378451201</v>
+        <v>1.049879378451203</v>
       </c>
       <c r="AH2">
-        <v>1.049638000241888</v>
+        <v>1.049638000241886</v>
       </c>
       <c r="AI2">
-        <v>1.049999952316288</v>
+        <v>1.049999952315831</v>
       </c>
       <c r="AJ2">
-        <v>0.9243966914073701</v>
+        <v>0.9243966914071265</v>
       </c>
       <c r="AK2">
-        <v>0.9487920434344531</v>
+        <v>0.9487920434332352</v>
       </c>
       <c r="AL2">
-        <v>2.076050991379067E-16</v>
+        <v>7.130907144390266E-14</v>
       </c>
       <c r="AM2">
-        <v>-120.019008133439</v>
+        <v>-120.0190081334391</v>
       </c>
       <c r="AN2">
-        <v>119.9961963746865</v>
+        <v>119.9961963746863</v>
       </c>
       <c r="AO2">
-        <v>3.645994679034516E-16</v>
+        <v>7.2754296277823E-11</v>
       </c>
       <c r="AP2">
-        <v>-122.9835155918942</v>
+        <v>-122.9835155919812</v>
       </c>
       <c r="AQ2">
-        <v>125.1886277533084</v>
+        <v>125.188627753316</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -1653,40 +1653,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.449354072788632E-23</v>
+        <v>-7.958078279098861E-14</v>
       </c>
       <c r="O3">
-        <v>-4.209025870336179E-10</v>
+        <v>-4.209092355811138E-10</v>
       </c>
       <c r="P3">
-        <v>-3.371245645935736E-10</v>
+        <v>-3.370295330142179E-10</v>
       </c>
       <c r="Q3">
-        <v>-1.449354072788632E-23</v>
+        <v>7.958078279098437E-14</v>
       </c>
       <c r="R3">
-        <v>4.209025894070821E-10</v>
+        <v>4.209092379547537E-10</v>
       </c>
       <c r="S3">
-        <v>3.37124566967038E-10</v>
+        <v>3.370295353872489E-10</v>
       </c>
       <c r="T3">
-        <v>-2.572397888128923E-26</v>
+        <v>-7.958078279119072E-14</v>
       </c>
       <c r="U3">
-        <v>1.852373033288513E-10</v>
+        <v>1.852618209050096E-10</v>
       </c>
       <c r="V3">
-        <v>-3.303450918265923E-10</v>
+        <v>-3.303887849610429E-10</v>
       </c>
       <c r="W3">
-        <v>2.572397888128923E-26</v>
+        <v>7.958078279117127E-14</v>
       </c>
       <c r="X3">
-        <v>-1.852373017253119E-10</v>
+        <v>-1.852618193016929E-10</v>
       </c>
       <c r="Y3">
-        <v>3.303450934301317E-10</v>
+        <v>3.30388786564702E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,40 +1707,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.049999952316288</v>
+        <v>1.049999952315831</v>
       </c>
       <c r="AG3">
-        <v>0.9243966914073701</v>
+        <v>0.9243966914071265</v>
       </c>
       <c r="AH3">
-        <v>0.9487920434344531</v>
+        <v>0.9487920434332352</v>
       </c>
       <c r="AI3">
-        <v>1.049999952316288</v>
+        <v>1.049999952315675</v>
       </c>
       <c r="AJ3">
-        <v>0.9243966944758226</v>
+        <v>0.9243966944757667</v>
       </c>
       <c r="AK3">
-        <v>0.9487920490981999</v>
+        <v>0.9487920490967608</v>
       </c>
       <c r="AL3">
-        <v>3.645994679034516E-16</v>
+        <v>7.2754296277823E-11</v>
       </c>
       <c r="AM3">
-        <v>-122.9835155918942</v>
+        <v>-122.9835155919812</v>
       </c>
       <c r="AN3">
-        <v>125.1886277533084</v>
+        <v>125.188627753316</v>
       </c>
       <c r="AO3">
-        <v>3.64594574603633E-16</v>
+        <v>6.728118408410087E-11</v>
       </c>
       <c r="AP3">
-        <v>-122.9835152899099</v>
+        <v>-122.9835152900158</v>
       </c>
       <c r="AQ3">
-        <v>125.1886276906917</v>
+        <v>125.1886276906708</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1784,40 +1784,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.449354079691164E-23</v>
+        <v>-7.958078279124124E-14</v>
       </c>
       <c r="O4">
-        <v>-4.20902593673137E-10</v>
+        <v>-4.208107677346515E-10</v>
       </c>
       <c r="P4">
-        <v>-3.371245759868557E-10</v>
+        <v>-3.369707638073338E-10</v>
       </c>
       <c r="Q4">
-        <v>-1.449354079691164E-23</v>
+        <v>7.95807827912427E-14</v>
       </c>
       <c r="R4">
-        <v>4.209025950972156E-10</v>
+        <v>4.208107691581386E-10</v>
       </c>
       <c r="S4">
-        <v>3.371245774109343E-10</v>
+        <v>3.369707652306346E-10</v>
       </c>
       <c r="T4">
-        <v>-2.572415144460441E-26</v>
+        <v>1.193711741865334E-13</v>
       </c>
       <c r="U4">
-        <v>1.852373127357143E-10</v>
+        <v>1.851561540323438E-10</v>
       </c>
       <c r="V4">
-        <v>-3.303450985176716E-10</v>
+        <v>-3.303473453128637E-10</v>
       </c>
       <c r="W4">
-        <v>2.572415144460441E-26</v>
+        <v>-1.193711741864858E-13</v>
       </c>
       <c r="X4">
-        <v>-1.852373117735906E-10</v>
+        <v>-1.851561530704607E-10</v>
       </c>
       <c r="Y4">
-        <v>3.303450994797953E-10</v>
+        <v>3.303473462748289E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1838,40 +1838,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.049999952316288</v>
+        <v>1.049999952315831</v>
       </c>
       <c r="AG4">
-        <v>0.9243966914073701</v>
+        <v>0.9243966914071265</v>
       </c>
       <c r="AH4">
-        <v>0.9487920434344531</v>
+        <v>0.9487920434332352</v>
       </c>
       <c r="AI4">
-        <v>1.049999952316288</v>
+        <v>1.049999952315547</v>
       </c>
       <c r="AJ4">
-        <v>0.9243966932484416</v>
+        <v>0.9243966932480089</v>
       </c>
       <c r="AK4">
-        <v>0.9487920468327014</v>
+        <v>0.9487920468307789</v>
       </c>
       <c r="AL4">
-        <v>3.645994679034516E-16</v>
+        <v>7.2754296277823E-11</v>
       </c>
       <c r="AM4">
-        <v>-122.9835155918942</v>
+        <v>-122.9835155919812</v>
       </c>
       <c r="AN4">
-        <v>125.1886277533084</v>
+        <v>125.188627753316</v>
       </c>
       <c r="AO4">
-        <v>3.645965319234853E-16</v>
+        <v>8.37806879477124E-11</v>
       </c>
       <c r="AP4">
-        <v>-122.9835154107036</v>
+        <v>-122.983515410811</v>
       </c>
       <c r="AQ4">
-        <v>125.1886277157384</v>
+        <v>125.1886277157422</v>
       </c>
     </row>
   </sheetData>
@@ -2023,127 +2023,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.05308150717890439</v>
+        <v>0.05308150717911422</v>
       </c>
       <c r="D2">
-        <v>0.05308150717890438</v>
+        <v>0.05308150717936843</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.05308150717890441</v>
+        <v>0.05308150717911431</v>
       </c>
       <c r="G2">
-        <v>0.05308150717890437</v>
+        <v>0.05308150717936835</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01225864916616071</v>
+        <v>0.01225864916620916</v>
       </c>
       <c r="J2">
-        <v>0.0122586491661607</v>
+        <v>0.01225864916626787</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01225864916616071</v>
+        <v>0.01225864916620919</v>
       </c>
       <c r="M2">
-        <v>0.0122586491661607</v>
+        <v>0.01225864916626785</v>
       </c>
       <c r="N2">
-        <v>3.180326441555863E-19</v>
+        <v>-1.234593183632662E-13</v>
       </c>
       <c r="O2">
-        <v>0.01311728534338952</v>
+        <v>0.0131172853434581</v>
       </c>
       <c r="P2">
-        <v>0.003853399517110012</v>
+        <v>0.00385339951724745</v>
       </c>
       <c r="Q2">
-        <v>-1.589700269777241E-35</v>
+        <v>1.234574101676672E-13</v>
       </c>
       <c r="R2">
-        <v>-0.01167605916287374</v>
+        <v>-0.01167605916291939</v>
       </c>
       <c r="S2">
-        <v>-0.002412173336594232</v>
+        <v>-0.002412173336718006</v>
       </c>
       <c r="T2">
-        <v>-3.180326441555863E-19</v>
+        <v>1.101919505470233E-14</v>
       </c>
       <c r="U2">
-        <v>0.003118526389838118</v>
+        <v>0.003118526389780176</v>
       </c>
       <c r="V2">
-        <v>0.01291712564322495</v>
+        <v>0.01291712564330688</v>
       </c>
       <c r="W2">
-        <v>3.180326441555863E-19</v>
+        <v>-1.104749995995255E-14</v>
       </c>
       <c r="X2">
-        <v>-0.002144817632266303</v>
+        <v>-0.00214481763221125</v>
       </c>
       <c r="Y2">
-        <v>-0.01194341688565314</v>
+        <v>-0.01194341688570744</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-133.3932424906505</v>
+        <v>-133.3932424903436</v>
       </c>
       <c r="AB2">
-        <v>46.60675750934223</v>
+        <v>46.60675750980228</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>46.60675750934224</v>
+        <v>46.60675750964917</v>
       </c>
       <c r="AE2">
-        <v>-133.3932424906505</v>
+        <v>-133.3932424901905</v>
       </c>
       <c r="AF2">
         <v>1.100000023841857</v>
       </c>
       <c r="AG2">
-        <v>1.099867693450841</v>
+        <v>1.099867693450843</v>
       </c>
       <c r="AH2">
-        <v>1.099602784311816</v>
+        <v>1.099602784311813</v>
       </c>
       <c r="AI2">
-        <v>1.100000023841857</v>
+        <v>1.100000023844145</v>
       </c>
       <c r="AJ2">
-        <v>0.9684117156664244</v>
+        <v>0.9684117156654458</v>
       </c>
       <c r="AK2">
-        <v>0.9939571251563319</v>
+        <v>0.9939571251539845</v>
       </c>
       <c r="AL2">
-        <v>2.192535806754925E-16</v>
+        <v>1.938939491032897E-13</v>
       </c>
       <c r="AM2">
-        <v>-120.0199130138825</v>
+        <v>-120.0199130138827</v>
       </c>
       <c r="AN2">
-        <v>119.9960155039708</v>
+        <v>119.9960155039706</v>
       </c>
       <c r="AO2">
-        <v>2.86395493742087E-15</v>
+        <v>4.781261750552918E-11</v>
       </c>
       <c r="AP2">
-        <v>-122.9844140436503</v>
+        <v>-122.9844140436445</v>
       </c>
       <c r="AQ2">
-        <v>125.1885126247582</v>
+        <v>125.1885126246982</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -2187,40 +2187,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.999408649157294E-24</v>
+        <v>-8.337034946973016E-14</v>
       </c>
       <c r="O3">
-        <v>-4.619519336343917E-10</v>
+        <v>-4.618283171082641E-10</v>
       </c>
       <c r="P3">
-        <v>-3.700478120097041E-10</v>
+        <v>-3.699888718097138E-10</v>
       </c>
       <c r="Q3">
-        <v>1.999408649157294E-24</v>
+        <v>8.337034946970324E-14</v>
       </c>
       <c r="R3">
-        <v>4.619519362396388E-10</v>
+        <v>4.618283197134625E-10</v>
       </c>
       <c r="S3">
-        <v>3.700478146149512E-10</v>
+        <v>3.699888744147381E-10</v>
       </c>
       <c r="T3">
-        <v>-2.217687983687673E-25</v>
+        <v>4.168517473477812E-14</v>
       </c>
       <c r="U3">
-        <v>2.033593580601177E-10</v>
+        <v>2.034418634336968E-10</v>
       </c>
       <c r="V3">
-        <v>-3.62541964925171E-10</v>
+        <v>-3.626515946175774E-10</v>
       </c>
       <c r="W3">
-        <v>2.217687983687673E-25</v>
+        <v>-4.168517473477523E-14</v>
       </c>
       <c r="X3">
-        <v>-2.033593562999832E-10</v>
+        <v>-2.03441861674629E-10</v>
       </c>
       <c r="Y3">
-        <v>3.625419666853054E-10</v>
+        <v>3.626515963781447E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2241,40 +2241,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.100000023841857</v>
+        <v>1.100000023844145</v>
       </c>
       <c r="AG3">
-        <v>0.9684117156664244</v>
+        <v>0.9684117156654458</v>
       </c>
       <c r="AH3">
-        <v>0.9939571251563319</v>
+        <v>0.9939571251539845</v>
       </c>
       <c r="AI3">
-        <v>1.100000023841857</v>
+        <v>1.100000023843845</v>
       </c>
       <c r="AJ3">
-        <v>0.9684117188806912</v>
+        <v>0.9684117188796934</v>
       </c>
       <c r="AK3">
-        <v>0.9939571310902834</v>
+        <v>0.9939571310875647</v>
       </c>
       <c r="AL3">
-        <v>2.86395493742087E-15</v>
+        <v>4.781261750552918E-11</v>
       </c>
       <c r="AM3">
-        <v>-122.9844140436503</v>
+        <v>-122.9844140436445</v>
       </c>
       <c r="AN3">
-        <v>125.1885126247582</v>
+        <v>125.1885126246982</v>
       </c>
       <c r="AO3">
-        <v>2.863955450163008E-15</v>
+        <v>4.200137175881051E-11</v>
       </c>
       <c r="AP3">
-        <v>-122.9844137416246</v>
+        <v>-122.9844137416368</v>
       </c>
       <c r="AQ3">
-        <v>125.1885125621666</v>
+        <v>125.1885125620833</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -2318,40 +2318,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.999408671754873E-24</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>-4.619519399801827E-10</v>
+        <v>-4.617867293325862E-10</v>
       </c>
       <c r="P4">
-        <v>-3.700478217894609E-10</v>
+        <v>-3.699273049415146E-10</v>
       </c>
       <c r="Q4">
-        <v>1.999408671754873E-24</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>4.61951941543331E-10</v>
+        <v>4.617867308952758E-10</v>
       </c>
       <c r="S4">
-        <v>3.700478233526092E-10</v>
+        <v>3.699273065040236E-10</v>
       </c>
       <c r="T4">
-        <v>-2.217687848102202E-25</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.033593688544321E-10</v>
+        <v>2.033711218145542E-10</v>
       </c>
       <c r="V4">
-        <v>-3.625419690080528E-10</v>
+        <v>-3.626081824531511E-10</v>
       </c>
       <c r="W4">
-        <v>2.217687848102202E-25</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>-2.033593677983514E-10</v>
+        <v>-2.033711207591422E-10</v>
       </c>
       <c r="Y4">
-        <v>3.625419700641335E-10</v>
+        <v>3.626081835092544E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2372,40 +2372,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.100000023841857</v>
+        <v>1.100000023844145</v>
       </c>
       <c r="AG4">
-        <v>0.9684117156664244</v>
+        <v>0.9684117156654458</v>
       </c>
       <c r="AH4">
-        <v>0.9939571251563319</v>
+        <v>0.9939571251539845</v>
       </c>
       <c r="AI4">
-        <v>1.100000023841857</v>
+        <v>1.100000023843847</v>
       </c>
       <c r="AJ4">
-        <v>0.9684117175949843</v>
+        <v>0.9684117175938077</v>
       </c>
       <c r="AK4">
-        <v>0.9939571287167029</v>
+        <v>0.9939571287136172</v>
       </c>
       <c r="AL4">
-        <v>2.86395493742087E-15</v>
+        <v>4.781261750552918E-11</v>
       </c>
       <c r="AM4">
-        <v>-122.9844140436503</v>
+        <v>-122.9844140436445</v>
       </c>
       <c r="AN4">
-        <v>125.1885126247582</v>
+        <v>125.1885126246982</v>
       </c>
       <c r="AO4">
-        <v>2.863955245066162E-15</v>
+        <v>5.884150004763327E-11</v>
       </c>
       <c r="AP4">
-        <v>-122.9844138624349</v>
+        <v>-122.9844138624495</v>
       </c>
       <c r="AQ4">
-        <v>125.1885125872032</v>
+        <v>125.1885125871395</v>
       </c>
     </row>
   </sheetData>
@@ -2557,127 +2557,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1823566808252606</v>
+        <v>0.182356680823795</v>
       </c>
       <c r="D2">
-        <v>0.1823566808252605</v>
+        <v>0.1823566808242454</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1823566808252606</v>
+        <v>0.1823566808237947</v>
       </c>
       <c r="G2">
-        <v>0.1823566808252605</v>
+        <v>0.1823566808242458</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.04211347213273597</v>
+        <v>0.04211347213239751</v>
       </c>
       <c r="J2">
-        <v>0.04211347213273595</v>
+        <v>0.04211347213250154</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.04211347213273597</v>
+        <v>0.04211347213239744</v>
       </c>
       <c r="M2">
-        <v>0.04211347213273595</v>
+        <v>0.04211347213250163</v>
       </c>
       <c r="N2">
-        <v>1.098658187665618E-18</v>
+        <v>-2.093169072431486E-13</v>
       </c>
       <c r="O2">
-        <v>0.03932910800624996</v>
+        <v>0.03932910800588477</v>
       </c>
       <c r="P2">
-        <v>0.02598699020949711</v>
+        <v>0.02598699020898061</v>
       </c>
       <c r="Q2">
-        <v>-1.098658187665618E-18</v>
+        <v>2.095240043218687E-13</v>
       </c>
       <c r="R2">
-        <v>-0.006671058898376393</v>
+        <v>-0.00667105889906958</v>
       </c>
       <c r="S2">
-        <v>0.006671058898376373</v>
+        <v>0.00667105889906255</v>
       </c>
       <c r="T2">
-        <v>-1.098658187665618E-18</v>
+        <v>-5.167692597831628E-13</v>
       </c>
       <c r="U2">
-        <v>-0.007367019191465275</v>
+        <v>-0.007367019191670315</v>
       </c>
       <c r="V2">
-        <v>0.03035050717801045</v>
+        <v>0.0303505071781597</v>
       </c>
       <c r="W2">
-        <v>1.098658187665618E-18</v>
+        <v>5.169252692413449E-13</v>
       </c>
       <c r="X2">
-        <v>0.0188587631847376</v>
+        <v>0.01885876318492715</v>
       </c>
       <c r="Y2">
-        <v>-0.01885876318473813</v>
+        <v>-0.0188587631851847</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-109.4806160309473</v>
+        <v>-109.4806160305616</v>
       </c>
       <c r="AB2">
-        <v>70.51938396904544</v>
+        <v>70.51938396834485</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>70.51938396904544</v>
+        <v>70.51938396943071</v>
       </c>
       <c r="AE2">
-        <v>-109.4806160309473</v>
+        <v>-109.4806160316475</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880790568</v>
+        <v>0.9499999880790769</v>
       </c>
       <c r="AG2">
-        <v>0.9501269348783331</v>
+        <v>0.9501269348783421</v>
       </c>
       <c r="AH2">
-        <v>0.9487685420882901</v>
+        <v>0.9487685420882864</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880790571</v>
+        <v>0.9499999880786455</v>
       </c>
       <c r="AJ2">
-        <v>0.4749999940395219</v>
+        <v>0.4749999940530728</v>
       </c>
       <c r="AK2">
-        <v>0.474999994039534</v>
+        <v>0.4749999940576076</v>
       </c>
       <c r="AL2">
-        <v>5.243448782065525E-16</v>
+        <v>3.552890384816676E-13</v>
       </c>
       <c r="AM2">
-        <v>-120.0901541408788</v>
+        <v>-120.090154140878</v>
       </c>
       <c r="AN2">
-        <v>119.9482807313187</v>
+        <v>119.9482807313199</v>
       </c>
       <c r="AO2">
-        <v>2.992290340933839E-14</v>
+        <v>-1.1568458813415E-09</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999999925</v>
+        <v>-179.9999999979165</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999999924</v>
+        <v>-179.999999999267</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -2721,40 +2721,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-4.871303872876352E-23</v>
+        <v>-1.440033259678304E-13</v>
       </c>
       <c r="O3">
-        <v>-3.405840850645732E-17</v>
+        <v>3.60007795735809E-14</v>
       </c>
       <c r="P3">
-        <v>3.405839477490325E-17</v>
+        <v>1.81526688788354E-20</v>
       </c>
       <c r="Q3">
-        <v>4.871303872876352E-23</v>
+        <v>1.440033259677207E-13</v>
       </c>
       <c r="R3">
-        <v>2.016296178400791E-16</v>
+        <v>-3.58332073992297E-14</v>
       </c>
       <c r="S3">
-        <v>1.335128148156829E-16</v>
+        <v>1.675985154426536E-16</v>
       </c>
       <c r="T3">
-        <v>-1.728223793184694E-24</v>
+        <v>2.880066519501986E-13</v>
       </c>
       <c r="U3">
-        <v>1.432911065209952E-09</v>
+        <v>1.432833093479251E-09</v>
       </c>
       <c r="V3">
-        <v>-1.432911067407305E-09</v>
+        <v>-1.433193101807877E-09</v>
       </c>
       <c r="W3">
-        <v>1.728223793184694E-24</v>
+        <v>-2.880066519509516E-13</v>
       </c>
       <c r="X3">
-        <v>-1.432911006244843E-09</v>
+        <v>-1.432833034520377E-09</v>
       </c>
       <c r="Y3">
-        <v>1.432911126372415E-09</v>
+        <v>1.433193160791336E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2775,40 +2775,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9499999880790571</v>
+        <v>0.9499999880786455</v>
       </c>
       <c r="AG3">
-        <v>0.4749999940395219</v>
+        <v>0.4749999940530728</v>
       </c>
       <c r="AH3">
-        <v>0.474999994039534</v>
+        <v>0.4749999940576076</v>
       </c>
       <c r="AI3">
-        <v>0.9499999880790571</v>
+        <v>0.9499999880804879</v>
       </c>
       <c r="AJ3">
-        <v>0.4749999744930052</v>
+        <v>0.4749999745061622</v>
       </c>
       <c r="AK3">
-        <v>0.4750000135860572</v>
+        <v>0.4750000136063672</v>
       </c>
       <c r="AL3">
-        <v>2.992290340933839E-14</v>
+        <v>-1.1568458813415E-09</v>
       </c>
       <c r="AM3">
-        <v>-179.9999999999925</v>
+        <v>-179.9999999979165</v>
       </c>
       <c r="AN3">
-        <v>179.9999999999924</v>
+        <v>-179.999999999267</v>
       </c>
       <c r="AO3">
-        <v>2.992292142746984E-14</v>
+        <v>-1.234230370059394E-09</v>
       </c>
       <c r="AP3">
-        <v>-179.9999932995603</v>
+        <v>-179.9999932971403</v>
       </c>
       <c r="AQ3">
-        <v>179.9999932995606</v>
+        <v>179.999993299788</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -2852,40 +2852,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-4.871304035250219E-23</v>
+        <v>1.440033259736455E-13</v>
       </c>
       <c r="O4">
-        <v>-1.977585206680462E-17</v>
+        <v>-1.440033779143412E-13</v>
       </c>
       <c r="P4">
-        <v>2.417047108591226E-17</v>
+        <v>-1.440033078274319E-13</v>
       </c>
       <c r="Q4">
-        <v>4.871304035250219E-23</v>
+        <v>-1.440033259738012E-13</v>
       </c>
       <c r="R4">
-        <v>1.20318583762306E-16</v>
+        <v>1.441039484872089E-13</v>
       </c>
       <c r="S4">
-        <v>7.637226145271441E-17</v>
+        <v>1.441038748118746E-13</v>
       </c>
       <c r="T4">
-        <v>-1.728223574604487E-24</v>
+        <v>-2.907537971694035E-24</v>
       </c>
       <c r="U4">
-        <v>1.432911106958963E-09</v>
+        <v>1.433265103457178E-09</v>
       </c>
       <c r="V4">
-        <v>-1.432911115748266E-09</v>
+        <v>-1.433121100144889E-09</v>
       </c>
       <c r="W4">
-        <v>1.728223574604487E-24</v>
+        <v>2.877640643519706E-24</v>
       </c>
       <c r="X4">
-        <v>-1.432911071579896E-09</v>
+        <v>-1.43326506805718E-09</v>
       </c>
       <c r="Y4">
-        <v>1.432911151127334E-09</v>
+        <v>1.433121135524223E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9499999880790571</v>
+        <v>0.9499999880786455</v>
       </c>
       <c r="AG4">
-        <v>0.4749999940395219</v>
+        <v>0.4749999940530728</v>
       </c>
       <c r="AH4">
-        <v>0.474999994039534</v>
+        <v>0.4749999940576076</v>
       </c>
       <c r="AI4">
-        <v>0.9499999880790571</v>
+        <v>0.949999988079673</v>
       </c>
       <c r="AJ4">
-        <v>0.4749999823116104</v>
+        <v>0.4749999823244697</v>
       </c>
       <c r="AK4">
-        <v>0.4750000057674478</v>
+        <v>0.4750000057872406</v>
       </c>
       <c r="AL4">
-        <v>2.992290340933839E-14</v>
+        <v>-1.1568458813415E-09</v>
       </c>
       <c r="AM4">
-        <v>-179.9999999999925</v>
+        <v>-179.9999999979165</v>
       </c>
       <c r="AN4">
-        <v>179.9999999999924</v>
+        <v>-179.999999999267</v>
       </c>
       <c r="AO4">
-        <v>2.992291422021784E-14</v>
+        <v>-1.144950387180494E-09</v>
       </c>
       <c r="AP4">
-        <v>-179.9999959797331</v>
+        <v>-179.9999959773949</v>
       </c>
       <c r="AQ4">
-        <v>179.9999959797331</v>
+        <v>179.9999959802209</v>
       </c>
     </row>
   </sheetData>
@@ -3091,127 +3091,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1727660155207067</v>
+        <v>0.1727660155210032</v>
       </c>
       <c r="D2">
-        <v>0.1727660155207066</v>
+        <v>0.1727660155203913</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1727660155207067</v>
+        <v>0.1727660155210027</v>
       </c>
       <c r="G2">
-        <v>0.1727660155207066</v>
+        <v>0.1727660155203917</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.03989860282161513</v>
+        <v>0.03989860282168359</v>
       </c>
       <c r="J2">
-        <v>0.03989860282161511</v>
+        <v>0.03989860282154229</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.03989860282161513</v>
+        <v>0.03989860282168349</v>
       </c>
       <c r="M2">
-        <v>0.03989860282161511</v>
+        <v>0.03989860282154239</v>
       </c>
       <c r="N2">
-        <v>-5.204170290066909E-19</v>
+        <v>-6.595869509036617E-14</v>
       </c>
       <c r="O2">
-        <v>0.03529931497983594</v>
+        <v>0.03529931497988932</v>
       </c>
       <c r="P2">
-        <v>0.02332712331029338</v>
+        <v>0.02332712330998936</v>
       </c>
       <c r="Q2">
-        <v>5.204170290066906E-19</v>
+        <v>6.596806259743581E-14</v>
       </c>
       <c r="R2">
-        <v>-0.005986095834771259</v>
+        <v>-0.005986095834817829</v>
       </c>
       <c r="S2">
-        <v>0.005986095834771261</v>
+        <v>0.005986095835062072</v>
       </c>
       <c r="T2">
-        <v>-1.040834058013382E-18</v>
+        <v>-1.82974464062522E-13</v>
       </c>
       <c r="U2">
-        <v>-0.006612319288387273</v>
+        <v>-0.00661231928843742</v>
       </c>
       <c r="V2">
-        <v>0.02724184366206226</v>
+        <v>0.02724184366223613</v>
       </c>
       <c r="W2">
-        <v>1.040834058013382E-18</v>
+        <v>1.830785474674413E-13</v>
       </c>
       <c r="X2">
-        <v>0.01692708147522465</v>
+        <v>0.01692708147551594</v>
       </c>
       <c r="Y2">
-        <v>-0.01692708147522488</v>
+        <v>-0.01692708147564225</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-109.4756397444799</v>
+        <v>-109.4756397444171</v>
       </c>
       <c r="AB2">
-        <v>70.52436025551279</v>
+        <v>70.52436025496397</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>70.52436025551278</v>
+        <v>70.52436025557553</v>
       </c>
       <c r="AE2">
-        <v>-109.4756397444799</v>
+        <v>-109.4756397450287</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761581288</v>
+        <v>0.8999999761581358</v>
       </c>
       <c r="AG2">
-        <v>0.9001139774548345</v>
+        <v>0.9001139774548361</v>
       </c>
       <c r="AH2">
-        <v>0.8988947482999384</v>
+        <v>0.8988947482999331</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761581289</v>
+        <v>0.8999999761551563</v>
       </c>
       <c r="AJ2">
-        <v>0.4499999880790613</v>
+        <v>0.4499999880855623</v>
       </c>
       <c r="AK2">
-        <v>0.4499999880790669</v>
+        <v>0.4499999880921794</v>
       </c>
       <c r="AL2">
-        <v>5.095719068657533E-16</v>
+        <v>1.137305199592748E-13</v>
       </c>
       <c r="AM2">
-        <v>-120.085412641423</v>
+        <v>-120.0854126414232</v>
       </c>
       <c r="AN2">
-        <v>119.9509980239249</v>
+        <v>119.9509980239257</v>
       </c>
       <c r="AO2">
-        <v>1.670260853488846E-14</v>
+        <v>-2.395860923618548E-10</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999999926</v>
+        <v>179.9999999998857</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999999926</v>
+        <v>179.9999999998747</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -3255,40 +3255,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-4.360346831831073E-23</v>
+        <v>1.364242016509089E-13</v>
       </c>
       <c r="O3">
-        <v>-3.12250233268453E-17</v>
+        <v>-6.821209842534727E-14</v>
       </c>
       <c r="P3">
-        <v>3.018418419221129E-17</v>
+        <v>-6.821210347753951E-14</v>
       </c>
       <c r="Q3">
-        <v>4.360346831831073E-23</v>
+        <v>-1.364242016508455E-13</v>
       </c>
       <c r="R3">
-        <v>1.816213406807545E-16</v>
+        <v>6.836249643144399E-14</v>
       </c>
       <c r="S3">
-        <v>1.202121326438002E-16</v>
+        <v>6.836249896980611E-14</v>
       </c>
       <c r="T3">
-        <v>-8.658019573592802E-25</v>
+        <v>-1.364242016520499E-13</v>
       </c>
       <c r="U3">
-        <v>1.286047571839792E-09</v>
+        <v>1.286070948991314E-09</v>
       </c>
       <c r="V3">
-        <v>-1.28604756975814E-09</v>
+        <v>-1.286002736909398E-09</v>
       </c>
       <c r="W3">
-        <v>8.658019573592802E-25</v>
+        <v>1.364242016519705E-13</v>
       </c>
       <c r="X3">
-        <v>-1.286047518918199E-09</v>
+        <v>-1.28607089605942E-09</v>
       </c>
       <c r="Y3">
-        <v>1.286047622679733E-09</v>
+        <v>1.286002789821185E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3309,40 +3309,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8999999761581289</v>
+        <v>0.8999999761551563</v>
       </c>
       <c r="AG3">
-        <v>0.4499999880790613</v>
+        <v>0.4499999880855623</v>
       </c>
       <c r="AH3">
-        <v>0.4499999880790669</v>
+        <v>0.4499999880921794</v>
       </c>
       <c r="AI3">
-        <v>0.8999999761581289</v>
+        <v>0.8999999761546853</v>
       </c>
       <c r="AJ3">
-        <v>0.4499999695613089</v>
+        <v>0.4499999695673319</v>
       </c>
       <c r="AK3">
-        <v>0.4500000065968255</v>
+        <v>0.4500000066099451</v>
       </c>
       <c r="AL3">
-        <v>1.670260853488846E-14</v>
+        <v>-2.395860923618548E-10</v>
       </c>
       <c r="AM3">
-        <v>-179.9999999999926</v>
+        <v>179.9999999998857</v>
       </c>
       <c r="AN3">
-        <v>179.9999999999926</v>
+        <v>179.9999999998747</v>
       </c>
       <c r="AO3">
-        <v>1.670262739208523E-14</v>
+        <v>-2.362350423465078E-10</v>
       </c>
       <c r="AP3">
-        <v>-179.9999932995604</v>
+        <v>-179.999993299589</v>
       </c>
       <c r="AQ3">
-        <v>179.9999932995608</v>
+        <v>179.9999932993712</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -3386,40 +3386,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-4.360346973826032E-23</v>
+        <v>2.728484033006769E-13</v>
       </c>
       <c r="O4">
-        <v>-2.081668274671161E-17</v>
+        <v>-6.821209842509251E-14</v>
       </c>
       <c r="P4">
-        <v>2.081667767009068E-17</v>
+        <v>-1.364242043053519E-13</v>
       </c>
       <c r="Q4">
-        <v>4.360346973826032E-23</v>
+        <v>-2.728484033010853E-13</v>
       </c>
       <c r="R4">
-        <v>1.110544786469613E-16</v>
+        <v>6.830235163282717E-14</v>
       </c>
       <c r="S4">
-        <v>6.942111852228678E-17</v>
+        <v>1.365144428858153E-13</v>
       </c>
       <c r="T4">
-        <v>-8.658016023718823E-25</v>
+        <v>-5.456968066070585E-13</v>
       </c>
       <c r="U4">
-        <v>1.286047609309818E-09</v>
+        <v>1.286207373192969E-09</v>
       </c>
       <c r="V4">
-        <v>-1.28604761347317E-09</v>
+        <v>-1.28593452480857E-09</v>
       </c>
       <c r="W4">
-        <v>8.658016023718823E-25</v>
+        <v>5.456968066075921E-13</v>
       </c>
       <c r="X4">
-        <v>-1.286047577556861E-09</v>
+        <v>-1.286207341429408E-09</v>
       </c>
       <c r="Y4">
-        <v>1.286047645226128E-09</v>
+        <v>1.285934556553815E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3440,40 +3440,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.8999999761581289</v>
+        <v>0.8999999761551563</v>
       </c>
       <c r="AG4">
-        <v>0.4499999880790613</v>
+        <v>0.4499999880855623</v>
       </c>
       <c r="AH4">
-        <v>0.4499999880790669</v>
+        <v>0.4499999880921794</v>
       </c>
       <c r="AI4">
-        <v>0.8999999761581289</v>
+        <v>0.8999999761561297</v>
       </c>
       <c r="AJ4">
-        <v>0.4499999769684085</v>
+        <v>0.4499999769742542</v>
       </c>
       <c r="AK4">
-        <v>0.4499999991897219</v>
+        <v>0.4499999992044632</v>
       </c>
       <c r="AL4">
-        <v>1.670260853488846E-14</v>
+        <v>-2.395860923618548E-10</v>
       </c>
       <c r="AM4">
-        <v>-179.9999999999926</v>
+        <v>179.9999999998857</v>
       </c>
       <c r="AN4">
-        <v>179.9999999999926</v>
+        <v>179.9999999998747</v>
       </c>
       <c r="AO4">
-        <v>1.670261984920712E-14</v>
+        <v>-2.276905978372536E-10</v>
       </c>
       <c r="AP4">
-        <v>-179.9999959797332</v>
+        <v>-179.9999959795781</v>
       </c>
       <c r="AQ4">
-        <v>179.9999959797333</v>
+        <v>179.9999959793771</v>
       </c>
     </row>
   </sheetData>
@@ -3625,127 +3625,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.04223863540419828</v>
+        <v>0.04223863540422783</v>
       </c>
       <c r="D2">
-        <v>0.04223863540419828</v>
+        <v>0.04223863540440475</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.04223863540419828</v>
+        <v>0.04223863540422796</v>
       </c>
       <c r="G2">
-        <v>0.04223863540419828</v>
+        <v>0.04223863540440462</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.009754595153681328</v>
+        <v>0.00975459515368815</v>
       </c>
       <c r="J2">
-        <v>0.009754595153681328</v>
+        <v>0.009754595153729008</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.009754595153681326</v>
+        <v>0.009754595153688182</v>
       </c>
       <c r="M2">
-        <v>0.009754595153681328</v>
+        <v>0.009754595153728979</v>
       </c>
       <c r="N2">
-        <v>2.746645469164075E-19</v>
+        <v>-5.094148418749238E-14</v>
       </c>
       <c r="O2">
-        <v>0.009145426051980472</v>
+        <v>0.009145426051986837</v>
       </c>
       <c r="P2">
-        <v>0.003279349243070329</v>
+        <v>0.003279349242978402</v>
       </c>
       <c r="Q2">
-        <v>-2.746645469164075E-19</v>
+        <v>5.099614243339696E-14</v>
       </c>
       <c r="R2">
-        <v>-0.007393294790450208</v>
+        <v>-0.007393294790477599</v>
       </c>
       <c r="S2">
-        <v>-0.001527217981540056</v>
+        <v>-0.001527217981407577</v>
       </c>
       <c r="T2">
-        <v>9.736126157428184E-37</v>
+        <v>-1.645921804105645E-13</v>
       </c>
       <c r="U2">
-        <v>0.001489880146368682</v>
+        <v>0.001489880146369924</v>
       </c>
       <c r="V2">
-        <v>0.008663716984792322</v>
+        <v>0.008663716984875506</v>
       </c>
       <c r="W2">
-        <v>-2.746645469164075E-19</v>
+        <v>1.645993216887803E-13</v>
       </c>
       <c r="X2">
-        <v>-0.0008733386060701011</v>
+        <v>-0.0008733386060848104</v>
       </c>
       <c r="Y2">
-        <v>-0.008047175444493753</v>
+        <v>-0.008047175444556588</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-129.2730122327422</v>
+        <v>-129.2730122327434</v>
       </c>
       <c r="AB2">
-        <v>50.72698776725052</v>
+        <v>50.72698776653687</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>50.72698776725052</v>
+        <v>50.72698776724896</v>
       </c>
       <c r="AE2">
-        <v>-129.2730122327422</v>
+        <v>-129.2730122334556</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880790674</v>
+        <v>0.9499999880790737</v>
       </c>
       <c r="AG2">
-        <v>0.9499102019017732</v>
+        <v>0.9499102019017731</v>
       </c>
       <c r="AH2">
-        <v>0.9496643516854993</v>
+        <v>0.9496643516854965</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880790674</v>
+        <v>0.9499999880807952</v>
       </c>
       <c r="AJ2">
-        <v>0.7631990742675668</v>
+        <v>0.7631990742699961</v>
       </c>
       <c r="AK2">
-        <v>0.8396877029729445</v>
+        <v>0.8396877029726389</v>
       </c>
       <c r="AL2">
-        <v>2.030982680110189E-16</v>
+        <v>7.780433048820096E-14</v>
       </c>
       <c r="AM2">
         <v>-120.0202479590293</v>
       </c>
       <c r="AN2">
-        <v>119.9945677925551</v>
+        <v>119.9945677925553</v>
       </c>
       <c r="AO2">
-        <v>2.132484936059895E-16</v>
+        <v>-3.395880090024672E-10</v>
       </c>
       <c r="AP2">
-        <v>-122.5361235042045</v>
+        <v>-122.5361235041184</v>
       </c>
       <c r="AQ2">
-        <v>129.9810150645925</v>
+        <v>129.9810150648715</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -3789,40 +3789,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.288846870899803E-23</v>
+        <v>-6.401231012059596E-25</v>
       </c>
       <c r="O3">
-        <v>-5.201390904855484E-10</v>
+        <v>-5.20172227952566E-10</v>
       </c>
       <c r="P3">
-        <v>-2.953676383197859E-10</v>
+        <v>-2.954659654021549E-10</v>
       </c>
       <c r="Q3">
-        <v>1.288846870899803E-23</v>
+        <v>6.773868157876789E-25</v>
       </c>
       <c r="R3">
-        <v>5.201390994758819E-10</v>
+        <v>5.201722369431974E-10</v>
       </c>
       <c r="S3">
-        <v>2.953676473101193E-10</v>
+        <v>2.954659743943405E-10</v>
       </c>
       <c r="T3">
-        <v>-1.231665114814419E-26</v>
+        <v>-1.080024944804785E-13</v>
       </c>
       <c r="U3">
-        <v>1.176355892276271E-10</v>
+        <v>1.175712132713588E-10</v>
       </c>
       <c r="V3">
-        <v>-5.069511604102293E-10</v>
+        <v>-5.069710187941089E-10</v>
       </c>
       <c r="W3">
-        <v>1.231665114814419E-26</v>
+        <v>1.080024944805734E-13</v>
       </c>
       <c r="X3">
-        <v>-1.176355860641003E-10</v>
+        <v>-1.175712101064159E-10</v>
       </c>
       <c r="Y3">
-        <v>5.069511635737561E-10</v>
+        <v>5.069710219575997E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3843,40 +3843,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9499999880790674</v>
+        <v>0.9499999880807952</v>
       </c>
       <c r="AG3">
-        <v>0.7631990742675668</v>
+        <v>0.7631990742699961</v>
       </c>
       <c r="AH3">
-        <v>0.8396877029729445</v>
+        <v>0.8396877029726389</v>
       </c>
       <c r="AI3">
-        <v>0.9499999880790674</v>
+        <v>0.94999998808163</v>
       </c>
       <c r="AJ3">
-        <v>0.7631990858184422</v>
+        <v>0.7631990858214011</v>
       </c>
       <c r="AK3">
-        <v>0.8396877133621731</v>
+        <v>0.8396877133631061</v>
       </c>
       <c r="AL3">
-        <v>2.132484936059895E-16</v>
+        <v>-3.395880090024672E-10</v>
       </c>
       <c r="AM3">
-        <v>-122.5361235042045</v>
+        <v>-122.5361235041184</v>
       </c>
       <c r="AN3">
-        <v>129.9810150645925</v>
+        <v>129.9810150648715</v>
       </c>
       <c r="AO3">
-        <v>2.132537809740354E-16</v>
+        <v>-3.593565669857676E-10</v>
       </c>
       <c r="AP3">
-        <v>-122.5361229596084</v>
+        <v>-122.5361229594993</v>
       </c>
       <c r="AQ3">
-        <v>129.9810144615353</v>
+        <v>129.9810144618154</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -3920,40 +3920,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.288846902125547E-23</v>
+        <v>-1.440033259735446E-13</v>
       </c>
       <c r="O4">
-        <v>-5.201391082798662E-10</v>
+        <v>-5.200856248772989E-10</v>
       </c>
       <c r="P4">
-        <v>-2.953676541861837E-10</v>
+        <v>-2.954250739378964E-10</v>
       </c>
       <c r="Q4">
-        <v>1.288846902125547E-23</v>
+        <v>1.440033259735589E-13</v>
       </c>
       <c r="R4">
-        <v>5.201391136740668E-10</v>
+        <v>5.200856302713825E-10</v>
       </c>
       <c r="S4">
-        <v>2.953676595803842E-10</v>
+        <v>2.954250793332278E-10</v>
       </c>
       <c r="T4">
-        <v>-1.231654185804099E-26</v>
+        <v>7.200166298783919E-14</v>
       </c>
       <c r="U4">
-        <v>1.176355974388134E-10</v>
+        <v>1.176531888832339E-10</v>
       </c>
       <c r="V4">
-        <v>-5.069511762493771E-10</v>
+        <v>-5.070197841497282E-10</v>
       </c>
       <c r="W4">
-        <v>1.231654185804099E-26</v>
+        <v>-7.200166298785517E-14</v>
       </c>
       <c r="X4">
-        <v>-1.176355955406972E-10</v>
+        <v>-1.176531869852059E-10</v>
       </c>
       <c r="Y4">
-        <v>5.069511781474933E-10</v>
+        <v>5.070197860484561E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3974,40 +3974,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9499999880790674</v>
+        <v>0.9499999880807952</v>
       </c>
       <c r="AG4">
-        <v>0.7631990742675668</v>
+        <v>0.7631990742699961</v>
       </c>
       <c r="AH4">
-        <v>0.8396877029729445</v>
+        <v>0.8396877029726389</v>
       </c>
       <c r="AI4">
-        <v>0.9499999880790674</v>
+        <v>0.9499999880809129</v>
       </c>
       <c r="AJ4">
-        <v>0.7631990811980922</v>
+        <v>0.7631990812007773</v>
       </c>
       <c r="AK4">
-        <v>0.8396877092064819</v>
+        <v>0.8396877092069469</v>
       </c>
       <c r="AL4">
-        <v>2.132484936059895E-16</v>
+        <v>-3.395880090024672E-10</v>
       </c>
       <c r="AM4">
-        <v>-122.5361235042045</v>
+        <v>-122.5361235041184</v>
       </c>
       <c r="AN4">
-        <v>129.9810150645925</v>
+        <v>129.9810150648715</v>
       </c>
       <c r="AO4">
-        <v>2.132516660269813E-16</v>
+        <v>-3.423982909531318E-10</v>
       </c>
       <c r="AP4">
-        <v>-122.5361231774468</v>
+        <v>-122.5361231773148</v>
       </c>
       <c r="AQ4">
-        <v>129.9810147027582</v>
+        <v>129.9810147030372</v>
       </c>
     </row>
   </sheetData>
@@ -4159,127 +4159,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.04001617762540317</v>
+        <v>0.04001617762586085</v>
       </c>
       <c r="D2">
-        <v>0.04001617762540315</v>
+        <v>0.0400161776258431</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.04001617762540317</v>
+        <v>0.04001617762586087</v>
       </c>
       <c r="G2">
-        <v>0.04001617762540315</v>
+        <v>0.04001617762584307</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.009241340507293264</v>
+        <v>0.009241340507398959</v>
       </c>
       <c r="J2">
-        <v>0.009241340507293258</v>
+        <v>0.009241340507394861</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.009241340507293264</v>
+        <v>0.009241340507398966</v>
       </c>
       <c r="M2">
-        <v>0.009241340507293258</v>
+        <v>0.009241340507394854</v>
       </c>
       <c r="N2">
-        <v>-2.602085145033483E-19</v>
+        <v>2.441796700099391E-15</v>
       </c>
       <c r="O2">
-        <v>0.008208248980439439</v>
+        <v>0.008208248980527336</v>
       </c>
       <c r="P2">
-        <v>0.002943423073839462</v>
+        <v>0.002943423073778492</v>
       </c>
       <c r="Q2">
-        <v>4.095122551746376E-35</v>
+        <v>-2.419418767564721E-15</v>
       </c>
       <c r="R2">
-        <v>-0.006635649656879884</v>
+        <v>-0.006635649656944657</v>
       </c>
       <c r="S2">
-        <v>-0.001370823750279901</v>
+        <v>-0.001370823750171524</v>
       </c>
       <c r="T2">
-        <v>-8.884439216273526E-37</v>
+        <v>-8.58245743386397E-14</v>
       </c>
       <c r="U2">
-        <v>0.001337228939277349</v>
+        <v>0.001337228939329231</v>
       </c>
       <c r="V2">
-        <v>0.007775980972802931</v>
+        <v>0.007775980972923708</v>
       </c>
       <c r="W2">
-        <v>-2.602085145033484E-19</v>
+        <v>8.583706434733287E-14</v>
       </c>
       <c r="X2">
-        <v>-0.0007838612604351147</v>
+        <v>-0.0007838612604767001</v>
       </c>
       <c r="Y2">
-        <v>-0.007222613293960712</v>
+        <v>-0.007222613294066976</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-129.2721112936844</v>
+        <v>-129.27211129394</v>
       </c>
       <c r="AB2">
-        <v>50.7278887063083</v>
+        <v>50.72788870562088</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>50.72788870630832</v>
+        <v>50.72788870605252</v>
       </c>
       <c r="AE2">
-        <v>-129.2721112936844</v>
+        <v>-129.2721112943717</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761581389</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="AG2">
-        <v>0.8999193931135896</v>
+        <v>0.8999193931135874</v>
       </c>
       <c r="AH2">
-        <v>0.8996987365102961</v>
+        <v>0.8996987365102919</v>
       </c>
       <c r="AI2">
-        <v>0.899999976158139</v>
+        <v>0.899999976158026</v>
       </c>
       <c r="AJ2">
-        <v>0.7230322855558015</v>
+        <v>0.7230322855550202</v>
       </c>
       <c r="AK2">
-        <v>0.7955069817295959</v>
+        <v>0.7955069817299606</v>
       </c>
       <c r="AL2">
-        <v>1.956280605976938E-16</v>
+        <v>-2.5991852122724E-14</v>
       </c>
       <c r="AM2">
-        <v>-120.0191825636721</v>
+        <v>-120.0191825636723</v>
       </c>
       <c r="AN2">
-        <v>119.9948534113831</v>
+        <v>119.9948534113833</v>
       </c>
       <c r="AO2">
-        <v>9.017123795957977E-15</v>
+        <v>-1.916429492746603E-10</v>
       </c>
       <c r="AP2">
-        <v>-122.5350516916008</v>
+        <v>-122.5350516915676</v>
       </c>
       <c r="AQ2">
-        <v>129.9811982497753</v>
+        <v>129.9811982500723</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -4323,40 +4323,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.043678752815433E-23</v>
+        <v>-2.28155865747889E-25</v>
       </c>
       <c r="O3">
-        <v>-4.668272015194709E-10</v>
+        <v>-4.66859726940392E-10</v>
       </c>
       <c r="P3">
-        <v>-2.650584706291991E-10</v>
+        <v>-2.650735966853063E-10</v>
       </c>
       <c r="Q3">
-        <v>1.043678752815433E-23</v>
+        <v>2.392952378823636E-25</v>
       </c>
       <c r="R3">
-        <v>4.668272095879518E-10</v>
+        <v>4.66859735009228E-10</v>
       </c>
       <c r="S3">
-        <v>2.650584786976799E-10</v>
+        <v>2.650736047541914E-10</v>
       </c>
       <c r="T3">
-        <v>-4.674143252264891E-25</v>
+        <v>-6.82121008259572E-14</v>
       </c>
       <c r="U3">
-        <v>1.055343962454156E-10</v>
+        <v>1.055201058679385E-10</v>
       </c>
       <c r="V3">
-        <v>-4.55008083986829E-10</v>
+        <v>-4.55023839015811E-10</v>
       </c>
       <c r="W3">
-        <v>4.674143252264891E-25</v>
+        <v>6.821210082597039E-14</v>
       </c>
       <c r="X3">
-        <v>-1.055343934062713E-10</v>
+        <v>-1.055201030282822E-10</v>
       </c>
       <c r="Y3">
-        <v>4.550080868259734E-10</v>
+        <v>4.55023841855119E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4377,40 +4377,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.899999976158139</v>
+        <v>0.899999976158026</v>
       </c>
       <c r="AG3">
-        <v>0.7230322855558015</v>
+        <v>0.7230322855550202</v>
       </c>
       <c r="AH3">
-        <v>0.7955069817295959</v>
+        <v>0.7955069817299606</v>
       </c>
       <c r="AI3">
-        <v>0.899999976158139</v>
+        <v>0.8999999761582</v>
       </c>
       <c r="AJ3">
-        <v>0.7230322964990781</v>
+        <v>0.7230322964982995</v>
       </c>
       <c r="AK3">
-        <v>0.7955069915711531</v>
+        <v>0.7955069915717237</v>
       </c>
       <c r="AL3">
-        <v>9.017123795957977E-15</v>
+        <v>-1.916429492746603E-10</v>
       </c>
       <c r="AM3">
-        <v>-122.5350516916008</v>
+        <v>-122.5350516915676</v>
       </c>
       <c r="AN3">
-        <v>129.9811982497753</v>
+        <v>129.9811982500723</v>
       </c>
       <c r="AO3">
-        <v>9.017127970667553E-15</v>
+        <v>-2.009996323558165E-10</v>
       </c>
       <c r="AP3">
-        <v>-122.5350511470975</v>
+        <v>-122.535051147066</v>
       </c>
       <c r="AQ3">
-        <v>129.9811976466908</v>
+        <v>129.98119764699</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -4454,40 +4454,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.043678782397716E-23</v>
+        <v>-1.364242016515722E-13</v>
       </c>
       <c r="O4">
-        <v>-4.668272169675341E-10</v>
+        <v>-4.668449909303072E-10</v>
       </c>
       <c r="P4">
-        <v>-2.650584833182462E-10</v>
+        <v>-2.65142895801016E-10</v>
       </c>
       <c r="Q4">
-        <v>1.043678782397716E-23</v>
+        <v>1.36424201651584E-13</v>
       </c>
       <c r="R4">
-        <v>4.668272218086229E-10</v>
+        <v>4.668449957718487E-10</v>
       </c>
       <c r="S4">
-        <v>2.65058488159335E-10</v>
+        <v>2.651429006434413E-10</v>
       </c>
       <c r="T4">
-        <v>-4.67414258666352E-25</v>
+        <v>1.023181512393921E-13</v>
       </c>
       <c r="U4">
-        <v>1.055344031247212E-10</v>
+        <v>1.05543205573175E-10</v>
       </c>
       <c r="V4">
-        <v>-4.550080946271099E-10</v>
+        <v>-4.550819491367961E-10</v>
       </c>
       <c r="W4">
-        <v>4.67414258666352E-25</v>
+        <v>-1.023181512394115E-13</v>
       </c>
       <c r="X4">
-        <v>-1.055344014212344E-10</v>
+        <v>-1.055432038693288E-10</v>
       </c>
       <c r="Y4">
-        <v>4.550080963305966E-10</v>
+        <v>4.550819508407154E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -4508,40 +4508,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.899999976158139</v>
+        <v>0.899999976158026</v>
       </c>
       <c r="AG4">
-        <v>0.7230322855558015</v>
+        <v>0.7230322855550202</v>
       </c>
       <c r="AH4">
-        <v>0.7955069817295959</v>
+        <v>0.7955069817299606</v>
       </c>
       <c r="AI4">
-        <v>0.899999976158139</v>
+        <v>0.8999999761581374</v>
       </c>
       <c r="AJ4">
-        <v>0.7230322921217676</v>
+        <v>0.7230322921212288</v>
       </c>
       <c r="AK4">
-        <v>0.7955069876345304</v>
+        <v>0.7955069876356251</v>
       </c>
       <c r="AL4">
-        <v>9.017123795957977E-15</v>
+        <v>-1.916429492746603E-10</v>
       </c>
       <c r="AM4">
-        <v>-122.5350516916008</v>
+        <v>-122.5350516915676</v>
       </c>
       <c r="AN4">
-        <v>129.9811982497753</v>
+        <v>129.9811982500723</v>
       </c>
       <c r="AO4">
-        <v>9.017126300783862E-15</v>
+        <v>-1.944542947341415E-10</v>
       </c>
       <c r="AP4">
-        <v>-122.5350513648988</v>
+        <v>-122.5350513648198</v>
       </c>
       <c r="AQ4">
-        <v>129.9811978879246</v>
+        <v>129.9811978882215</v>
       </c>
     </row>
   </sheetData>
@@ -4693,16 +4693,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.1961699758851258</v>
+        <v>0.1961699758751887</v>
       </c>
       <c r="C2">
-        <v>4.668407857659386E-05</v>
+        <v>4.668407731738846E-05</v>
       </c>
       <c r="D2">
-        <v>4.668407857650866E-05</v>
+        <v>4.668408495978257E-05</v>
       </c>
       <c r="E2">
-        <v>0.1961438285542146</v>
+        <v>0.1961438285442765</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4711,16 +4711,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.04530351602875489</v>
+        <v>0.04530351602646002</v>
       </c>
       <c r="I2">
-        <v>1.078122629387923E-05</v>
+        <v>1.07812260030782E-05</v>
       </c>
       <c r="J2">
-        <v>1.078122629385956E-05</v>
+        <v>1.078122776801354E-05</v>
       </c>
       <c r="K2">
-        <v>0.04529747756124886</v>
+        <v>0.04529747755895373</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4729,52 +4729,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.03939106662789152</v>
+        <v>0.03939106662759952</v>
       </c>
       <c r="O2">
-        <v>9.808226519159631E-06</v>
+        <v>9.808225390188018E-06</v>
       </c>
       <c r="P2">
-        <v>-9.799079482928837E-06</v>
+        <v>-9.799081529001817E-06</v>
       </c>
       <c r="Q2">
-        <v>-1.179315289386362E-17</v>
+        <v>-2.535473610367748E-12</v>
       </c>
       <c r="R2">
-        <v>-6.051949744269685E-09</v>
+        <v>-6.049956305424457E-09</v>
       </c>
       <c r="S2">
-        <v>-6.068645093730135E-09</v>
+        <v>-6.065894533670928E-09</v>
       </c>
       <c r="T2">
-        <v>0.02659307532955956</v>
+        <v>0.02659307532569877</v>
       </c>
       <c r="U2">
-        <v>-5.652223145659262E-06</v>
+        <v>-5.652224493211096E-06</v>
       </c>
       <c r="V2">
-        <v>-5.668067539159094E-06</v>
+        <v>-5.668067093259482E-06</v>
       </c>
       <c r="W2">
-        <v>1.615279863056732E-15</v>
+        <v>2.391603061792329E-12</v>
       </c>
       <c r="X2">
-        <v>-5.254182889796249E-09</v>
+        <v>-5.25298961084823E-09</v>
       </c>
       <c r="Y2">
-        <v>5.244543721406994E-09</v>
+        <v>5.244871472203577E-09</v>
       </c>
       <c r="Z2">
-        <v>-34.08333644318964</v>
+        <v>-34.08333643952921</v>
       </c>
       <c r="AA2">
-        <v>-90.04629991903678</v>
+        <v>-90.04629115657826</v>
       </c>
       <c r="AB2">
-        <v>-90.04629991893239</v>
+        <v>-90.04629278017691</v>
       </c>
       <c r="AC2">
-        <v>145.9279600744827</v>
+        <v>145.9279600781438</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4783,40 +4783,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.049087166092866</v>
+        <v>1.049087166092982</v>
       </c>
       <c r="AH2">
-        <v>1.050000091762733</v>
+        <v>1.050000091762777</v>
       </c>
       <c r="AI2">
-        <v>1.050000150765694</v>
+        <v>1.050000150765687</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.388322158350399</v>
+        <v>1.388322158404412</v>
       </c>
       <c r="AL2">
-        <v>1.38941495438325</v>
+        <v>1.389414954384012</v>
       </c>
       <c r="AM2">
-        <v>-0.0598843632978054</v>
+        <v>-0.05988436329795214</v>
       </c>
       <c r="AN2">
-        <v>-120.0000168972843</v>
+        <v>-120.0000168972827</v>
       </c>
       <c r="AO2">
-        <v>120.0000150384241</v>
+        <v>120.0000150384275</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1272450071404</v>
+        <v>-139.1272450060646</v>
       </c>
       <c r="AR2">
-        <v>139.0751989924374</v>
+        <v>139.0751989944364</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -4860,40 +4860,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>7.608357526830273E-23</v>
+        <v>-6.462779361820247E-20</v>
       </c>
       <c r="O3">
-        <v>2.017316527910177E-09</v>
+        <v>2.017735794459996E-09</v>
       </c>
       <c r="P3">
-        <v>2.022881669154845E-09</v>
+        <v>2.020925843943029E-09</v>
       </c>
       <c r="Q3">
-        <v>1.421569405189753E-16</v>
+        <v>4.74445818804756E-17</v>
       </c>
       <c r="R3">
-        <v>-2.017316492397866E-09</v>
+        <v>-2.017735806275653E-09</v>
       </c>
       <c r="S3">
-        <v>-2.022881633642535E-09</v>
+        <v>-2.020925855771419E-09</v>
       </c>
       <c r="T3">
-        <v>1.142823350180184E-22</v>
+        <v>2.891692558999471E-19</v>
       </c>
       <c r="U3">
-        <v>1.751394306910338E-09</v>
+        <v>1.751704989810079E-09</v>
       </c>
       <c r="V3">
-        <v>-1.748181188601086E-09</v>
+        <v>-1.747373963958519E-09</v>
       </c>
       <c r="W3">
-        <v>9.604277848143734E-17</v>
+        <v>3.182505808700292E-17</v>
       </c>
       <c r="X3">
-        <v>-1.751394282917818E-09</v>
+        <v>-1.751704997845677E-09</v>
       </c>
       <c r="Y3">
-        <v>1.748181212593605E-09</v>
+        <v>1.747373955916875E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4917,37 +4917,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.388322158350399</v>
+        <v>1.388322158404412</v>
       </c>
       <c r="AI3">
-        <v>1.38941495438325</v>
+        <v>1.389414954384012</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.388322136240584</v>
+        <v>1.388322165777359</v>
       </c>
       <c r="AL3">
-        <v>1.389414948572677</v>
+        <v>1.389414956301959</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1272450071404</v>
+        <v>-139.1272450060646</v>
       </c>
       <c r="AO3">
-        <v>139.0751989924374</v>
+        <v>139.0751989944364</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.127244896389</v>
+        <v>-139.127245042047</v>
       </c>
       <c r="AR3">
-        <v>139.075198105803</v>
+        <v>139.0751992908124</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -4991,40 +4991,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>7.608357590860225E-23</v>
+        <v>-6.461373185422959E-20</v>
       </c>
       <c r="O4">
-        <v>2.017316567694803E-09</v>
+        <v>2.018402931906649E-09</v>
       </c>
       <c r="P4">
-        <v>2.022881671738686E-09</v>
+        <v>2.023726706718687E-09</v>
       </c>
       <c r="Q4">
-        <v>8.529413442637135E-17</v>
+        <v>2.846792289203044E-17</v>
       </c>
       <c r="R4">
-        <v>-2.017316546387416E-09</v>
+        <v>-2.018402939007178E-09</v>
       </c>
       <c r="S4">
-        <v>-2.0228816504313E-09</v>
+        <v>-2.023726713807211E-09</v>
       </c>
       <c r="T4">
-        <v>1.142823353844427E-22</v>
+        <v>2.890528842147457E-19</v>
       </c>
       <c r="U4">
-        <v>1.751394290380388E-09</v>
+        <v>1.750612490597233E-09</v>
       </c>
       <c r="V4">
-        <v>-1.748181224867657E-09</v>
+        <v>-1.74896603700501E-09</v>
       </c>
       <c r="W4">
-        <v>5.762562292626128E-17</v>
+        <v>1.89598214828823E-17</v>
       </c>
       <c r="X4">
-        <v>-1.751394275984876E-09</v>
+        <v>-1.750612495419236E-09</v>
       </c>
       <c r="Y4">
-        <v>1.748181239263169E-09</v>
+        <v>1.748966032183641E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5048,37 +5048,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.388322158350399</v>
+        <v>1.388322158404412</v>
       </c>
       <c r="AI4">
-        <v>1.38941495438325</v>
+        <v>1.389414954384012</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.38832214508451</v>
+        <v>1.388322162833369</v>
       </c>
       <c r="AL4">
-        <v>1.389414950896906</v>
+        <v>1.389414955532315</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1272450071404</v>
+        <v>-139.1272450060646</v>
       </c>
       <c r="AO4">
-        <v>139.0751989924374</v>
+        <v>139.0751989944364</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1272449406896</v>
+        <v>-139.1272450277155</v>
       </c>
       <c r="AR4">
-        <v>139.0751984604568</v>
+        <v>139.0751991718629</v>
       </c>
     </row>
   </sheetData>
@@ -5230,16 +5230,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.2055029044606622</v>
+        <v>0.2055029044507891</v>
       </c>
       <c r="C2">
-        <v>4.89071326321542E-05</v>
+        <v>4.890713095090809E-05</v>
       </c>
       <c r="D2">
-        <v>4.890713263211404E-05</v>
+        <v>4.890713724529205E-05</v>
       </c>
       <c r="E2">
-        <v>0.2054755100020999</v>
+        <v>0.2054755099922268</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5248,16 +5248,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.04745886359103748</v>
+        <v>0.04745886358875738</v>
       </c>
       <c r="I2">
-        <v>1.129461864448972E-05</v>
+        <v>1.129461825622255E-05</v>
       </c>
       <c r="J2">
-        <v>1.129461864448044E-05</v>
+        <v>1.129461970984828E-05</v>
       </c>
       <c r="K2">
-        <v>0.04745253711173311</v>
+        <v>0.04745253710945301</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -5266,52 +5266,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.04322834332378379</v>
+        <v>0.0432283433238681</v>
       </c>
       <c r="O2">
-        <v>1.076458539488558E-05</v>
+        <v>1.076458454056584E-05</v>
       </c>
       <c r="P2">
-        <v>-1.075454672461668E-05</v>
+        <v>-1.075454819638663E-05</v>
       </c>
       <c r="Q2">
-        <v>6.759153734234993E-17</v>
+        <v>-3.540138978117439E-12</v>
       </c>
       <c r="R2">
-        <v>-6.641350888074526E-09</v>
+        <v>-6.640013128697451E-09</v>
       </c>
       <c r="S2">
-        <v>-6.660246341726437E-09</v>
+        <v>-6.658318486604443E-09</v>
       </c>
       <c r="T2">
-        <v>0.02918363702190721</v>
+        <v>0.02918363701731552</v>
       </c>
       <c r="U2">
-        <v>-6.203348080812032E-06</v>
+        <v>-6.203348707916922E-06</v>
       </c>
       <c r="V2">
-        <v>-6.220737018803331E-06</v>
+        <v>-6.220736814908594E-06</v>
       </c>
       <c r="W2">
-        <v>1.780678570741009E-15</v>
+        <v>2.522377988688859E-12</v>
       </c>
       <c r="X2">
-        <v>-5.766422620384267E-09</v>
+        <v>-5.766010140908741E-09</v>
       </c>
       <c r="Y2">
-        <v>5.755513208178505E-09</v>
+        <v>5.755895659099659E-09</v>
       </c>
       <c r="Z2">
-        <v>-34.08618548184842</v>
+        <v>-34.08618547761688</v>
       </c>
       <c r="AA2">
-        <v>-90.04629891840057</v>
+        <v>-90.04629444552131</v>
       </c>
       <c r="AB2">
-        <v>-90.04629891825394</v>
+        <v>-90.04629470590321</v>
       </c>
       <c r="AC2">
-        <v>145.9251111242571</v>
+        <v>145.925111128489</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -5320,40 +5320,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.098998247271365</v>
+        <v>1.098998247271502</v>
       </c>
       <c r="AH2">
-        <v>1.100000176885143</v>
+        <v>1.100000176885164</v>
       </c>
       <c r="AI2">
-        <v>1.100000241641218</v>
+        <v>1.100000241641217</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.454397733334106</v>
+        <v>1.454397733370175</v>
       </c>
       <c r="AL2">
-        <v>1.455578334001392</v>
+        <v>1.455578333982022</v>
       </c>
       <c r="AM2">
-        <v>-0.06273340212525985</v>
+        <v>-0.06273340212609783</v>
       </c>
       <c r="AN2">
-        <v>-120.0000177019167</v>
+        <v>-120.0000177019155</v>
       </c>
       <c r="AO2">
-        <v>120.0000157545396</v>
+        <v>120.0000157545419</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1274707896185</v>
+        <v>-139.1274707880006</v>
       </c>
       <c r="AR2">
-        <v>139.0737992409956</v>
+        <v>139.0737992424376</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -5397,40 +5397,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>8.955798663311129E-23</v>
+        <v>-1.291662968616433E-19</v>
       </c>
       <c r="O3">
-        <v>2.213783571317113E-09</v>
+        <v>2.215109330660837E-09</v>
       </c>
       <c r="P3">
-        <v>2.220082082089812E-09</v>
+        <v>2.219818936527013E-09</v>
       </c>
       <c r="Q3">
-        <v>1.560180628587959E-16</v>
+        <v>5.210192322893964E-17</v>
       </c>
       <c r="R3">
-        <v>-2.213783532345371E-09</v>
+        <v>-2.215109343635503E-09</v>
       </c>
       <c r="S3">
-        <v>-2.22008204311807E-09</v>
+        <v>-2.219818949499971E-09</v>
       </c>
       <c r="T3">
-        <v>1.221475184075948E-22</v>
+        <v>3.461819830211854E-19</v>
       </c>
       <c r="U3">
-        <v>1.922140878842266E-09</v>
+        <v>1.922469176609357E-09</v>
       </c>
       <c r="V3">
-        <v>-1.91850434691727E-09</v>
+        <v>-1.917636382054378E-09</v>
       </c>
       <c r="W3">
-        <v>1.05407511467057E-16</v>
+        <v>3.489475817202433E-17</v>
       </c>
       <c r="X3">
-        <v>-1.922140852512515E-09</v>
+        <v>-1.922469185432136E-09</v>
       </c>
       <c r="Y3">
-        <v>1.918504373247021E-09</v>
+        <v>1.917636373226429E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5454,37 +5454,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.454397733334106</v>
+        <v>1.454397733370175</v>
       </c>
       <c r="AI3">
-        <v>1.455578334001392</v>
+        <v>1.455578333982022</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.454397710172528</v>
+        <v>1.454397741096751</v>
       </c>
       <c r="AL3">
-        <v>1.455578327913806</v>
+        <v>1.455578335989709</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1274707896185</v>
+        <v>-139.1274707880006</v>
       </c>
       <c r="AO3">
-        <v>139.0737992409956</v>
+        <v>139.0737992424376</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.1274706788272</v>
+        <v>-139.127470823966</v>
       </c>
       <c r="AR3">
-        <v>139.0737983544044</v>
+        <v>139.0737995385662</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -5528,40 +5528,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>8.955798913596934E-23</v>
+        <v>-1.292313469444644E-19</v>
       </c>
       <c r="O4">
-        <v>2.213783622485242E-09</v>
+        <v>2.211964366111913E-09</v>
       </c>
       <c r="P4">
-        <v>2.220082142462711E-09</v>
+        <v>2.21969656536392E-09</v>
       </c>
       <c r="Q4">
-        <v>9.361080308409073E-17</v>
+        <v>3.130384407570817E-17</v>
       </c>
       <c r="R4">
-        <v>-2.213783599102196E-09</v>
+        <v>-2.211964373894184E-09</v>
       </c>
       <c r="S4">
-        <v>-2.220082119079665E-09</v>
+        <v>-2.219696573138132E-09</v>
       </c>
       <c r="T4">
-        <v>1.221475182957516E-22</v>
+        <v>3.461577200999505E-19</v>
       </c>
       <c r="U4">
-        <v>1.922140860840598E-09</v>
+        <v>1.920039111852752E-09</v>
       </c>
       <c r="V4">
-        <v>-1.918504390350384E-09</v>
+        <v>-1.918114331459959E-09</v>
       </c>
       <c r="W4">
-        <v>6.324445893563608E-17</v>
+        <v>2.079675895988187E-17</v>
       </c>
       <c r="X4">
-        <v>-1.922140845042747E-09</v>
+        <v>-1.920039117142871E-09</v>
       </c>
       <c r="Y4">
-        <v>1.918504406148236E-09</v>
+        <v>1.918114326170737E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5585,37 +5585,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.454397733334106</v>
+        <v>1.454397733370175</v>
       </c>
       <c r="AI4">
-        <v>1.455578334001392</v>
+        <v>1.455578333982022</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.454397719437159</v>
+        <v>1.454397738010256</v>
       </c>
       <c r="AL4">
-        <v>1.45557833034884</v>
+        <v>1.455578335184723</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1274707896185</v>
+        <v>-139.1274707880006</v>
       </c>
       <c r="AO4">
-        <v>139.0737992409956</v>
+        <v>139.0737992424376</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1274707231437</v>
+        <v>-139.1274708096432</v>
       </c>
       <c r="AR4">
-        <v>139.0737987090409</v>
+        <v>139.0737994198749</v>
       </c>
     </row>
   </sheetData>
@@ -5767,16 +5767,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.02926067670428893</v>
+        <v>0.02926067670397267</v>
       </c>
       <c r="C2">
-        <v>6.963388379408709E-06</v>
+        <v>6.963387923448567E-06</v>
       </c>
       <c r="D2">
-        <v>6.963388379394437E-06</v>
+        <v>6.96338916469672E-06</v>
       </c>
       <c r="E2">
-        <v>0.02925677657332842</v>
+        <v>0.02925677657301176</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5785,16 +5785,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.006757463929450789</v>
+        <v>0.00675746392937775</v>
       </c>
       <c r="I2">
-        <v>1.608125686092352E-06</v>
+        <v>1.608125580792866E-06</v>
       </c>
       <c r="J2">
-        <v>1.608125686089056E-06</v>
+        <v>1.608125867446852E-06</v>
       </c>
       <c r="K2">
-        <v>0.006756563232773398</v>
+        <v>0.006756563232700266</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -5803,52 +5803,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.005155919724109665</v>
+        <v>0.00515591972437203</v>
       </c>
       <c r="O2">
-        <v>1.580087886458694E-06</v>
+        <v>1.580087682689355E-06</v>
       </c>
       <c r="P2">
-        <v>-1.305647146959946E-06</v>
+        <v>-1.30564744661538E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.004279795169875804</v>
+        <v>-0.004279795170136842</v>
       </c>
       <c r="R2">
-        <v>-3.855316918572416E-10</v>
+        <v>-3.853067014560224E-10</v>
       </c>
       <c r="S2">
-        <v>-6.412639179756633E-10</v>
+        <v>-6.4094652365444E-10</v>
       </c>
       <c r="T2">
-        <v>0.004872870770717654</v>
+        <v>0.004872870770328523</v>
       </c>
       <c r="U2">
-        <v>-5.953673639552135E-07</v>
+        <v>-5.953675911793419E-07</v>
       </c>
       <c r="V2">
-        <v>-1.070712696507279E-06</v>
+        <v>-1.070712631406303E-06</v>
       </c>
       <c r="W2">
-        <v>-0.004279796392606942</v>
+        <v>-0.004279796392196462</v>
       </c>
       <c r="X2">
-        <v>-8.463075062948321E-10</v>
+        <v>-8.460887358788481E-10</v>
       </c>
       <c r="Y2">
-        <v>6.986604298175931E-10</v>
+        <v>6.986095707297751E-10</v>
       </c>
       <c r="Z2">
-        <v>-43.39093972089893</v>
+        <v>-43.39093971715987</v>
       </c>
       <c r="AA2">
-        <v>-99.35390319677992</v>
+        <v>-99.35389354375417</v>
       </c>
       <c r="AB2">
-        <v>-99.35390319663745</v>
+        <v>-99.35389504090558</v>
       </c>
       <c r="AC2">
-        <v>136.6203567967735</v>
+        <v>136.620356800513</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -5857,40 +5857,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.049839066787864</v>
+        <v>1.049839066787875</v>
       </c>
       <c r="AH2">
-        <v>1.049999965371924</v>
+        <v>1.049999965371931</v>
       </c>
       <c r="AI2">
-        <v>1.049999988175753</v>
+        <v>1.049999988175752</v>
       </c>
       <c r="AJ2">
-        <v>0.8958023523942295</v>
+        <v>0.8958023523882854</v>
       </c>
       <c r="AK2">
-        <v>1.080031916017599</v>
+        <v>1.080031916029691</v>
       </c>
       <c r="AL2">
-        <v>1.101347223170612</v>
+        <v>1.101347223170466</v>
       </c>
       <c r="AM2">
-        <v>-0.007605892416212932</v>
+        <v>-0.007605892416703676</v>
       </c>
       <c r="AN2">
-        <v>-120.0000026707766</v>
+        <v>-120.0000026707763</v>
       </c>
       <c r="AO2">
-        <v>120.0000019523531</v>
+        <v>120.0000019523536</v>
       </c>
       <c r="AP2">
-        <v>1.620364981437394</v>
+        <v>1.620364980681969</v>
       </c>
       <c r="AQ2">
-        <v>-123.890146889667</v>
+        <v>-123.8901468897449</v>
       </c>
       <c r="AR2">
-        <v>123.1484816068063</v>
+        <v>123.1484816073652</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -5934,40 +5934,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.050996490121963E-10</v>
+        <v>-5.051707681136081E-10</v>
       </c>
       <c r="O3">
-        <v>1.285105578057695E-10</v>
+        <v>1.285489109331763E-10</v>
       </c>
       <c r="P3">
-        <v>2.137546370326052E-10</v>
+        <v>2.136642733329745E-10</v>
       </c>
       <c r="Q3">
-        <v>5.050996521749978E-10</v>
+        <v>5.051707691676082E-10</v>
       </c>
       <c r="R3">
-        <v>-1.285105570156685E-10</v>
+        <v>-1.285489111961209E-10</v>
       </c>
       <c r="S3">
-        <v>-2.137546362425043E-10</v>
+        <v>-2.136642735961431E-10</v>
       </c>
       <c r="T3">
-        <v>-9.752259939199184E-11</v>
+        <v>-9.757866538514643E-11</v>
       </c>
       <c r="U3">
-        <v>2.821024986410788E-10</v>
+        <v>2.822055581971657E-10</v>
       </c>
       <c r="V3">
-        <v>-2.328868033230887E-10</v>
+        <v>-2.327769722297409E-10</v>
       </c>
       <c r="W3">
-        <v>9.752260152881649E-11</v>
+        <v>9.757866609980848E-11</v>
       </c>
       <c r="X3">
-        <v>-2.821024981072776E-10</v>
+        <v>-2.822055583759672E-10</v>
       </c>
       <c r="Y3">
-        <v>2.328868038568899E-10</v>
+        <v>2.327769720506433E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5988,40 +5988,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.8958023523942295</v>
+        <v>0.8958023523882854</v>
       </c>
       <c r="AH3">
-        <v>1.080031916017599</v>
+        <v>1.080031916029691</v>
       </c>
       <c r="AI3">
-        <v>1.101347223170612</v>
+        <v>1.101347223170466</v>
       </c>
       <c r="AJ3">
-        <v>0.8958023585073216</v>
+        <v>0.895802354426066</v>
       </c>
       <c r="AK3">
-        <v>1.080031913183988</v>
+        <v>1.080031916976019</v>
       </c>
       <c r="AL3">
-        <v>1.101347222679357</v>
+        <v>1.101347223330861</v>
       </c>
       <c r="AM3">
-        <v>1.620364981437394</v>
+        <v>1.620364980681969</v>
       </c>
       <c r="AN3">
-        <v>-123.890146889667</v>
+        <v>-123.8901468897449</v>
       </c>
       <c r="AO3">
-        <v>123.1484816068063</v>
+        <v>123.1484816073652</v>
       </c>
       <c r="AP3">
-        <v>1.620365148335489</v>
+        <v>1.620365036562091</v>
       </c>
       <c r="AQ3">
-        <v>-123.8901467976744</v>
+        <v>-123.8901469202621</v>
       </c>
       <c r="AR3">
-        <v>123.1484814358795</v>
+        <v>123.1484816644823</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -6065,40 +6065,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.050996554013541E-10</v>
+        <v>-5.04883774050718E-10</v>
       </c>
       <c r="O4">
-        <v>1.285105633617747E-10</v>
+        <v>1.283939618927819E-10</v>
       </c>
       <c r="P4">
-        <v>2.137546406999061E-10</v>
+        <v>2.136239795604455E-10</v>
       </c>
       <c r="Q4">
-        <v>5.05099657299035E-10</v>
+        <v>5.048837746825814E-10</v>
       </c>
       <c r="R4">
-        <v>-1.285105628877141E-10</v>
+        <v>-1.283939620505281E-10</v>
       </c>
       <c r="S4">
-        <v>-2.137546402258455E-10</v>
+        <v>-2.136239797180228E-10</v>
       </c>
       <c r="T4">
-        <v>-9.752259335436587E-11</v>
+        <v>-9.751960598831522E-11</v>
       </c>
       <c r="U4">
-        <v>2.821025024323285E-10</v>
+        <v>2.81717981147113E-10</v>
       </c>
       <c r="V4">
-        <v>-2.328868077736727E-10</v>
+        <v>-2.327534392152416E-10</v>
       </c>
       <c r="W4">
-        <v>9.752259463646068E-11</v>
+        <v>9.751960641650847E-11</v>
       </c>
       <c r="X4">
-        <v>-2.821025021120478E-10</v>
+        <v>-2.817179812543247E-10</v>
       </c>
       <c r="Y4">
-        <v>2.328868080939534E-10</v>
+        <v>2.327534391081206E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -6119,40 +6119,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.8958023523942295</v>
+        <v>0.8958023523882854</v>
       </c>
       <c r="AH4">
-        <v>1.080031916017599</v>
+        <v>1.080031916029691</v>
       </c>
       <c r="AI4">
-        <v>1.101347223170612</v>
+        <v>1.101347223170466</v>
       </c>
       <c r="AJ4">
-        <v>0.8958023560620848</v>
+        <v>0.8958023536105296</v>
       </c>
       <c r="AK4">
-        <v>1.080031914317433</v>
+        <v>1.080031916598238</v>
       </c>
       <c r="AL4">
-        <v>1.101347222875859</v>
+        <v>1.101347223266792</v>
       </c>
       <c r="AM4">
-        <v>1.620364981437394</v>
+        <v>1.620364980681969</v>
       </c>
       <c r="AN4">
-        <v>-123.890146889667</v>
+        <v>-123.8901468897449</v>
       </c>
       <c r="AO4">
-        <v>123.1484816068063</v>
+        <v>123.1484816073652</v>
       </c>
       <c r="AP4">
-        <v>1.620365081576255</v>
+        <v>1.620365014174947</v>
       </c>
       <c r="AQ4">
-        <v>-123.8901468344715</v>
+        <v>-123.8901469080811</v>
       </c>
       <c r="AR4">
-        <v>123.1484815042502</v>
+        <v>123.1484816415559</v>
       </c>
     </row>
   </sheetData>
@@ -6526,16 +6526,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0306538210440366</v>
+        <v>0.03065382104385409</v>
       </c>
       <c r="C2">
-        <v>7.295227750758578E-06</v>
+        <v>7.295227160294851E-06</v>
       </c>
       <c r="D2">
-        <v>7.295227750744191E-06</v>
+        <v>7.295228331981668E-06</v>
       </c>
       <c r="E2">
-        <v>0.03064973475225124</v>
+        <v>0.03064973475206851</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -6544,16 +6544,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.007079196838074312</v>
+        <v>0.007079196838032162</v>
       </c>
       <c r="I2">
-        <v>1.684760707384928E-06</v>
+        <v>1.684760571023169E-06</v>
       </c>
       <c r="J2">
-        <v>1.684760707381605E-06</v>
+        <v>1.684760841612653E-06</v>
       </c>
       <c r="K2">
-        <v>0.007078253149395343</v>
+        <v>0.007078253149353143</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -6562,52 +6562,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.005658569374458033</v>
+        <v>0.005658569374785873</v>
       </c>
       <c r="O2">
-        <v>1.734186452485131E-06</v>
+        <v>1.734186263078113E-06</v>
       </c>
       <c r="P2">
-        <v>-1.433055266572351E-06</v>
+        <v>-1.43305547262675E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.00469703152293725</v>
+        <v>-0.004697031523268656</v>
       </c>
       <c r="R2">
-        <v>-4.231137992530354E-10</v>
+        <v>-4.229140617772943E-10</v>
       </c>
       <c r="S2">
-        <v>-7.037901003804698E-10</v>
+        <v>-7.035733848422325E-10</v>
       </c>
       <c r="T2">
-        <v>0.005347926041764724</v>
+        <v>0.005347926041350469</v>
       </c>
       <c r="U2">
-        <v>-6.535167497320973E-07</v>
+        <v>-6.535168269839441E-07</v>
       </c>
       <c r="V2">
-        <v>-1.175091295756594E-06</v>
+        <v>-1.175091277333161E-06</v>
       </c>
       <c r="W2">
-        <v>-0.004697032865026467</v>
+        <v>-0.004697032864600205</v>
       </c>
       <c r="X2">
-        <v>-9.288228937826983E-10</v>
+        <v>-9.287570059819153E-10</v>
       </c>
       <c r="Y2">
-        <v>7.66774351337925E-10</v>
+        <v>7.667670204330953E-10</v>
       </c>
       <c r="Z2">
-        <v>-43.39130190312371</v>
+        <v>-43.3913018992516</v>
       </c>
       <c r="AA2">
-        <v>-99.35141533966724</v>
+        <v>-99.35141103975964</v>
       </c>
       <c r="AB2">
-        <v>-99.3514153395862</v>
+        <v>-99.35141085976279</v>
       </c>
       <c r="AC2">
-        <v>136.6199947029818</v>
+        <v>136.6199947068541</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -6616,40 +6616,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.099823451853048</v>
+        <v>1.099823451853059</v>
       </c>
       <c r="AH2">
-        <v>1.100000038173319</v>
+        <v>1.100000038173322</v>
       </c>
       <c r="AI2">
         <v>1.100000063197469</v>
       </c>
       <c r="AJ2">
-        <v>0.938452820410882</v>
+        <v>0.9384528204070008</v>
       </c>
       <c r="AK2">
-        <v>1.131461365027615</v>
+        <v>1.13146136503709</v>
       </c>
       <c r="AL2">
-        <v>1.153792387269966</v>
+        <v>1.15379238726773</v>
       </c>
       <c r="AM2">
-        <v>-0.007968019725887929</v>
+        <v>-0.007968019726462092</v>
       </c>
       <c r="AN2">
-        <v>-120.0000027980197</v>
+        <v>-120.0000027980195</v>
       </c>
       <c r="AO2">
-        <v>120.0000020454813</v>
+        <v>120.0000020454817</v>
       </c>
       <c r="AP2">
-        <v>1.620002888586694</v>
+        <v>1.620002887837867</v>
       </c>
       <c r="AQ2">
-        <v>-123.8901304280121</v>
+        <v>-123.8901304279212</v>
       </c>
       <c r="AR2">
-        <v>123.148442473113</v>
+        <v>123.1484424734919</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -6693,40 +6693,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.543700062056124E-10</v>
+        <v>-5.544181239949471E-10</v>
       </c>
       <c r="O3">
-        <v>1.410379274064129E-10</v>
+        <v>1.409445163151045E-10</v>
       </c>
       <c r="P3">
-        <v>2.345966998796588E-10</v>
+        <v>2.345577332582004E-10</v>
       </c>
       <c r="Q3">
-        <v>5.543700096770426E-10</v>
+        <v>5.544181251514465E-10</v>
       </c>
       <c r="R3">
-        <v>-1.410379265392851E-10</v>
+        <v>-1.409445166035825E-10</v>
       </c>
       <c r="S3">
-        <v>-2.34596699012531E-10</v>
+        <v>-2.345577335469081E-10</v>
       </c>
       <c r="T3">
-        <v>-1.070069309577015E-10</v>
+        <v>-1.070429388006469E-10</v>
       </c>
       <c r="U3">
-        <v>3.09607629163698E-10</v>
+        <v>3.096367549547688E-10</v>
       </c>
       <c r="V3">
-        <v>-2.555914439669584E-10</v>
+        <v>-2.555567919387942E-10</v>
       </c>
       <c r="W3">
-        <v>1.070069333030391E-10</v>
+        <v>1.070429395847497E-10</v>
       </c>
       <c r="X3">
-        <v>-3.096076285778566E-10</v>
+        <v>-3.096367551511254E-10</v>
       </c>
       <c r="Y3">
-        <v>2.555914445527998E-10</v>
+        <v>2.555567917423737E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -6747,40 +6747,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.938452820410882</v>
+        <v>0.9384528204070008</v>
       </c>
       <c r="AH3">
-        <v>1.131461365027615</v>
+        <v>1.13146136503709</v>
       </c>
       <c r="AI3">
-        <v>1.153792387269966</v>
+        <v>1.15379238726773</v>
       </c>
       <c r="AJ3">
-        <v>0.9384528268151571</v>
+        <v>0.9384528225412785</v>
       </c>
       <c r="AK3">
-        <v>1.131461362059104</v>
+        <v>1.131461366028936</v>
       </c>
       <c r="AL3">
-        <v>1.153792386755302</v>
+        <v>1.153792387435746</v>
       </c>
       <c r="AM3">
-        <v>1.620002888586694</v>
+        <v>1.620002887837867</v>
       </c>
       <c r="AN3">
-        <v>-123.8901304280121</v>
+        <v>-123.8901304279212</v>
       </c>
       <c r="AO3">
-        <v>123.148442473113</v>
+        <v>123.1484424734919</v>
       </c>
       <c r="AP3">
-        <v>1.620003055511146</v>
+        <v>1.620002943711855</v>
       </c>
       <c r="AQ3">
-        <v>-123.8901303360192</v>
+        <v>-123.8901304584393</v>
       </c>
       <c r="AR3">
-        <v>123.1484423021877</v>
+        <v>123.1484425305623</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -6824,40 +6824,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.543700086514929E-10</v>
+        <v>-5.542246151191723E-10</v>
       </c>
       <c r="O4">
-        <v>1.410379334052746E-10</v>
+        <v>1.408486122430178E-10</v>
       </c>
       <c r="P4">
-        <v>2.345966994693648E-10</v>
+        <v>2.346477628498728E-10</v>
       </c>
       <c r="Q4">
-        <v>5.543700107343511E-10</v>
+        <v>5.542246158128458E-10</v>
       </c>
       <c r="R4">
-        <v>-1.410379328849979E-10</v>
+        <v>-1.408486124161871E-10</v>
       </c>
       <c r="S4">
-        <v>-2.345966989490881E-10</v>
+        <v>-2.34647763022957E-10</v>
       </c>
       <c r="T4">
-        <v>-1.070069212552332E-10</v>
+        <v>-1.069663110686748E-10</v>
       </c>
       <c r="U4">
-        <v>3.096076322275628E-10</v>
+        <v>3.094170854328273E-10</v>
       </c>
       <c r="V4">
-        <v>-2.555914482191837E-10</v>
+        <v>-2.556546614731239E-10</v>
       </c>
       <c r="W4">
-        <v>1.070069226624358E-10</v>
+        <v>1.06966311538708E-10</v>
       </c>
       <c r="X4">
-        <v>-3.09607631876058E-10</v>
+        <v>-3.094170855506595E-10</v>
       </c>
       <c r="Y4">
-        <v>2.555914485706886E-10</v>
+        <v>2.55654661355435E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -6878,40 +6878,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.938452820410882</v>
+        <v>0.9384528204070008</v>
       </c>
       <c r="AH4">
-        <v>1.131461365027615</v>
+        <v>1.13146136503709</v>
       </c>
       <c r="AI4">
-        <v>1.153792387269966</v>
+        <v>1.15379238726773</v>
       </c>
       <c r="AJ4">
-        <v>0.9384528242534471</v>
+        <v>0.9384528216874897</v>
       </c>
       <c r="AK4">
-        <v>1.131461363246508</v>
+        <v>1.13146136563279</v>
       </c>
       <c r="AL4">
-        <v>1.153792386961167</v>
+        <v>1.153792387368586</v>
       </c>
       <c r="AM4">
-        <v>1.620002888586694</v>
+        <v>1.620002887837867</v>
       </c>
       <c r="AN4">
-        <v>-123.8901304280121</v>
+        <v>-123.8901304279212</v>
       </c>
       <c r="AO4">
-        <v>123.148442473113</v>
+        <v>123.1484424734919</v>
       </c>
       <c r="AP4">
-        <v>1.620002988741369</v>
+        <v>1.620002921341386</v>
       </c>
       <c r="AQ4">
-        <v>-123.8901303728164</v>
+        <v>-123.890130446256</v>
       </c>
       <c r="AR4">
-        <v>123.1484423705578</v>
+        <v>123.1484425076857</v>
       </c>
     </row>
   </sheetData>
@@ -7063,16 +7063,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.1052800862772297</v>
+        <v>0.1052800862749993</v>
       </c>
       <c r="C2">
-        <v>4.223937506329574E-05</v>
+        <v>4.223937587636617E-05</v>
       </c>
       <c r="D2">
-        <v>4.223937506327567E-05</v>
+        <v>4.223937474819869E-05</v>
       </c>
       <c r="E2">
-        <v>0.1052660766178398</v>
+        <v>0.1052660766156088</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7081,16 +7081,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.02431339482328405</v>
+        <v>0.02431339482276895</v>
       </c>
       <c r="I2">
-        <v>9.754765970635482E-06</v>
+        <v>9.754766158406058E-06</v>
       </c>
       <c r="J2">
-        <v>9.754765970630849E-06</v>
+        <v>9.754765897866934E-06</v>
       </c>
       <c r="K2">
-        <v>0.02431015943098784</v>
+        <v>0.02431015943047261</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -7099,52 +7099,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02178342744413441</v>
+        <v>0.02178342744357413</v>
       </c>
       <c r="O2">
-        <v>8.029948881533841E-06</v>
+        <v>8.029948677645567E-06</v>
       </c>
       <c r="P2">
-        <v>-8.021006205635428E-06</v>
+        <v>-8.021006203551136E-06</v>
       </c>
       <c r="Q2">
-        <v>2.003470250986856E-17</v>
+        <v>-3.38643677354371E-15</v>
       </c>
       <c r="R2">
-        <v>-4.957769839009468E-09</v>
+        <v>-4.957206608512854E-09</v>
       </c>
       <c r="S2">
-        <v>-4.972251522291908E-09</v>
+        <v>-4.972196042370526E-09</v>
       </c>
       <c r="T2">
-        <v>0.007653410303112207</v>
+        <v>0.007653410303231041</v>
       </c>
       <c r="U2">
-        <v>-4.625769824510718E-06</v>
+        <v>-4.625770535805607E-06</v>
       </c>
       <c r="V2">
-        <v>-4.641260161986142E-06</v>
+        <v>-4.641260027567354E-06</v>
       </c>
       <c r="W2">
-        <v>4.147077977924127E-16</v>
+        <v>-2.247444888870439E-13</v>
       </c>
       <c r="X2">
-        <v>-4.303637794314662E-09</v>
+        <v>-4.302837644791987E-09</v>
       </c>
       <c r="Y2">
-        <v>4.295276716695392E-09</v>
+        <v>4.295107516736348E-09</v>
       </c>
       <c r="Z2">
-        <v>-19.40578267841806</v>
+        <v>-19.40578267915587</v>
       </c>
       <c r="AA2">
-        <v>-90.05529457161398</v>
+        <v>-90.05529013167765</v>
       </c>
       <c r="AB2">
-        <v>-90.05529457155967</v>
+        <v>-90.0552938586801</v>
       </c>
       <c r="AC2">
-        <v>160.61590516387</v>
+        <v>160.6159051631329</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -7153,28 +7153,28 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9496326612097099</v>
+        <v>0.9496326612097076</v>
       </c>
       <c r="AH2">
-        <v>0.9500001307216147</v>
+        <v>0.950000130721642</v>
       </c>
       <c r="AI2">
-        <v>0.9500001911919729</v>
+        <v>0.9500001911919679</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.256268714655434</v>
+        <v>1.256268714671343</v>
       </c>
       <c r="AL2">
-        <v>1.257316228787097</v>
+        <v>1.257316228793888</v>
       </c>
       <c r="AM2">
-        <v>-0.04731847969705796</v>
+        <v>-0.04731847969576995</v>
       </c>
       <c r="AN2">
-        <v>-120.0000191120075</v>
+        <v>-120.0000191120072</v>
       </c>
       <c r="AO2">
         <v>120.0000170063817</v>
@@ -7183,10 +7183,10 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1365778912919</v>
+        <v>-139.1365778919865</v>
       </c>
       <c r="AR2">
-        <v>139.0814304927868</v>
+        <v>139.081430493029</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -7230,40 +7230,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.243020278205779E-23</v>
+        <v>-1.114251933485498E-20</v>
       </c>
       <c r="O3">
-        <v>1.652589868488836E-09</v>
+        <v>1.65216001370696E-09</v>
       </c>
       <c r="P3">
-        <v>1.657417134178136E-09</v>
+        <v>1.658223096624544E-09</v>
       </c>
       <c r="Q3">
-        <v>2.234282570511017E-16</v>
+        <v>7.443079130283855E-17</v>
       </c>
       <c r="R3">
-        <v>-1.652589812612794E-09</v>
+        <v>-1.652160032305277E-09</v>
       </c>
       <c r="S3">
-        <v>-1.657417078302093E-09</v>
+        <v>-1.658223115221713E-09</v>
       </c>
       <c r="T3">
-        <v>5.510114100722984E-23</v>
+        <v>-3.021955749005001E-20</v>
       </c>
       <c r="U3">
-        <v>1.434545897069834E-09</v>
+        <v>1.43509211763081E-09</v>
       </c>
       <c r="V3">
-        <v>-1.431758842099238E-09</v>
+        <v>-1.432042257949026E-09</v>
       </c>
       <c r="W3">
-        <v>7.86200908461275E-17</v>
+        <v>2.636903556528519E-17</v>
       </c>
       <c r="X3">
-        <v>-1.434545877408121E-09</v>
+        <v>-1.435092124251602E-09</v>
       </c>
       <c r="Y3">
-        <v>1.431758861760951E-09</v>
+        <v>1.432042251331151E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -7287,37 +7287,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.256268714655434</v>
+        <v>1.256268714671343</v>
       </c>
       <c r="AI3">
-        <v>1.257316228787097</v>
+        <v>1.257316228793888</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.256268683033234</v>
+        <v>1.256268725224057</v>
       </c>
       <c r="AL3">
-        <v>1.257316211891947</v>
+        <v>1.257316234388731</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1365778912919</v>
+        <v>-139.1365778919865</v>
       </c>
       <c r="AO3">
-        <v>139.0814304927868</v>
+        <v>139.081430493029</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.136577321035</v>
+        <v>-139.1365780804355</v>
       </c>
       <c r="AR3">
-        <v>139.0814291480081</v>
+        <v>139.0814309418737</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -7361,40 +7361,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.243020376667645E-23</v>
+        <v>-1.114463188189194E-20</v>
       </c>
       <c r="O4">
-        <v>1.652589928240354E-09</v>
+        <v>1.652020014307485E-09</v>
       </c>
       <c r="P4">
-        <v>1.657417165747078E-09</v>
+        <v>1.658568678426469E-09</v>
       </c>
       <c r="Q4">
-        <v>1.340569535564581E-16</v>
+        <v>4.466834102000803E-17</v>
       </c>
       <c r="R4">
-        <v>-1.652589894714727E-09</v>
+        <v>-1.652020025469973E-09</v>
       </c>
       <c r="S4">
-        <v>-1.657417132221451E-09</v>
+        <v>-1.658568689584093E-09</v>
       </c>
       <c r="T4">
-        <v>5.510114248304195E-23</v>
+        <v>-3.022325972559945E-20</v>
       </c>
       <c r="U4">
-        <v>1.434545925708612E-09</v>
+        <v>1.434089706515921E-09</v>
       </c>
       <c r="V4">
-        <v>-1.431758894478645E-09</v>
+        <v>-1.433098463394177E-09</v>
       </c>
       <c r="W4">
-        <v>4.71720354853963E-17</v>
+        <v>1.582497913467215E-17</v>
       </c>
       <c r="X4">
-        <v>-1.434545913911584E-09</v>
+        <v>-1.434089710484608E-09</v>
       </c>
       <c r="Y4">
-        <v>1.431758906275673E-09</v>
+        <v>1.433098459430453E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -7418,37 +7418,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.256268714655434</v>
+        <v>1.256268714671343</v>
       </c>
       <c r="AI4">
-        <v>1.257316228787097</v>
+        <v>1.257316228793888</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.256268695682113</v>
+        <v>1.256268721006024</v>
       </c>
       <c r="AL4">
-        <v>1.257316218650007</v>
+        <v>1.257316232150121</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1365778912919</v>
+        <v>-139.1365778919865</v>
       </c>
       <c r="AO4">
-        <v>139.0814304927868</v>
+        <v>139.081430493029</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1365775491378</v>
+        <v>-139.1365780051425</v>
       </c>
       <c r="AR4">
-        <v>139.0814296859196</v>
+        <v>139.0814307621088</v>
       </c>
     </row>
   </sheetData>
@@ -7600,16 +7600,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.09974105919220888</v>
+        <v>0.09974105919489404</v>
       </c>
       <c r="C2">
-        <v>4.001624948982588E-05</v>
+        <v>4.001624982281317E-05</v>
       </c>
       <c r="D2">
-        <v>4.001624948980457E-05</v>
+        <v>4.001624855350602E-05</v>
       </c>
       <c r="E2">
-        <v>0.09972778852378754</v>
+        <v>0.09972778852647335</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7618,16 +7618,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.02303421129278857</v>
+        <v>0.02303421129340868</v>
       </c>
       <c r="I2">
-        <v>9.241357103671031E-06</v>
+        <v>9.241357180571151E-06</v>
       </c>
       <c r="J2">
-        <v>9.241357103666106E-06</v>
+        <v>9.241356887437216E-06</v>
       </c>
       <c r="K2">
-        <v>0.02303114656314875</v>
+        <v>0.02303114656376901</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -7636,52 +7636,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01955157286660866</v>
+        <v>0.01955157286695428</v>
       </c>
       <c r="O2">
-        <v>7.206934554537329E-06</v>
+        <v>7.20693489030573E-06</v>
       </c>
       <c r="P2">
-        <v>-7.198908386251605E-06</v>
+        <v>-7.198907991558471E-06</v>
       </c>
       <c r="Q2">
-        <v>-2.845546924635243E-18</v>
+        <v>2.759625958893441E-13</v>
       </c>
       <c r="R2">
-        <v>-4.44993612622459E-09</v>
+        <v>-4.450548025870795E-09</v>
       </c>
       <c r="S2">
-        <v>-4.462598422186263E-09</v>
+        <v>-4.46321864928819E-09</v>
       </c>
       <c r="T2">
-        <v>0.006869268374111672</v>
+        <v>0.006869268374809116</v>
       </c>
       <c r="U2">
-        <v>-4.151660155531197E-06</v>
+        <v>-4.151659711316974E-06</v>
       </c>
       <c r="V2">
-        <v>-4.165562880300111E-06</v>
+        <v>-4.16556317384473E-06</v>
       </c>
       <c r="W2">
-        <v>3.933390693592017E-16</v>
+        <v>-5.92047949844306E-13</v>
       </c>
       <c r="X2">
-        <v>-3.862526531212442E-09</v>
+        <v>-3.862935510056401E-09</v>
       </c>
       <c r="Y2">
-        <v>3.855215885122759E-09</v>
+        <v>3.855412175087152E-09</v>
       </c>
       <c r="Z2">
-        <v>-19.40329314493771</v>
+        <v>-19.40329314644089</v>
       </c>
       <c r="AA2">
-        <v>-90.05529473071452</v>
+        <v>-90.05529853691108</v>
       </c>
       <c r="AB2">
-        <v>-90.05529473066437</v>
+        <v>-90.05529784269797</v>
       </c>
       <c r="AC2">
-        <v>160.6183945861123</v>
+        <v>160.6183945846082</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -7690,40 +7690,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8996703063371242</v>
+        <v>0.8996703063370969</v>
       </c>
       <c r="AH2">
-        <v>0.9000001041808048</v>
+        <v>0.9000001041807869</v>
       </c>
       <c r="AI2">
-        <v>0.9000001584533712</v>
+        <v>0.9000001584533808</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.190169016475026</v>
+        <v>1.19016901644547</v>
       </c>
       <c r="AL2">
-        <v>1.191135805290812</v>
+        <v>1.19113580528599</v>
       </c>
       <c r="AM2">
-        <v>-0.044828945929665</v>
+        <v>-0.04482894593032193</v>
       </c>
       <c r="AN2">
-        <v>-120.0000181061122</v>
+        <v>-120.0000181061129</v>
       </c>
       <c r="AO2">
-        <v>120.0000161113089</v>
+        <v>120.0000161113079</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1361552980736</v>
+        <v>-139.1361552982339</v>
       </c>
       <c r="AR2">
-        <v>139.0824298864981</v>
+        <v>139.0824298852958</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -7767,40 +7767,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.8318676930263E-23</v>
+        <v>9.146070694250516E-21</v>
       </c>
       <c r="O3">
-        <v>1.483311973969541E-09</v>
+        <v>1.483356287056076E-09</v>
       </c>
       <c r="P3">
-        <v>1.487532775613708E-09</v>
+        <v>1.486695924232783E-09</v>
       </c>
       <c r="Q3">
-        <v>2.005284047030379E-16</v>
+        <v>6.679765706689108E-17</v>
       </c>
       <c r="R3">
-        <v>-1.48331192381837E-09</v>
+        <v>-1.48335630374247E-09</v>
       </c>
       <c r="S3">
-        <v>-1.487532725462536E-09</v>
+        <v>-1.486695940930508E-09</v>
       </c>
       <c r="T3">
-        <v>5.330066248779035E-23</v>
+        <v>-9.314452293328563E-20</v>
       </c>
       <c r="U3">
-        <v>1.287508811663069E-09</v>
+        <v>1.286983572203391E-09</v>
       </c>
       <c r="V3">
-        <v>-1.285071908638844E-09</v>
+        <v>-1.285149989033466E-09</v>
       </c>
       <c r="W3">
-        <v>7.05620705899858E-17</v>
+        <v>2.37227095119031E-17</v>
       </c>
       <c r="X3">
-        <v>-1.287508794015829E-09</v>
+        <v>-1.286983578134418E-09</v>
       </c>
       <c r="Y3">
-        <v>1.285071926286084E-09</v>
+        <v>1.285149983104206E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -7824,37 +7824,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.190169016475026</v>
+        <v>1.19016901644547</v>
       </c>
       <c r="AI3">
-        <v>1.191135805290812</v>
+        <v>1.19113580528599</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.190168986516117</v>
+        <v>1.190169026439481</v>
       </c>
       <c r="AL3">
-        <v>1.191135789285282</v>
+        <v>1.191135810592438</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1361552980736</v>
+        <v>-139.1361552982339</v>
       </c>
       <c r="AO3">
-        <v>139.0824298864981</v>
+        <v>139.0824298852958</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.1361547278666</v>
+        <v>-139.1361554865712</v>
       </c>
       <c r="AR3">
-        <v>139.0824285416654</v>
+        <v>139.08243033445</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -7898,40 +7898,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.831867785478618E-23</v>
+        <v>9.163146768883414E-21</v>
       </c>
       <c r="O4">
-        <v>1.483312034740708E-09</v>
+        <v>1.482992981290827E-09</v>
       </c>
       <c r="P4">
-        <v>1.487532801358115E-09</v>
+        <v>1.488628816081693E-09</v>
       </c>
       <c r="Q4">
-        <v>1.203170428577036E-16</v>
+        <v>4.007162332436306E-17</v>
       </c>
       <c r="R4">
-        <v>-1.483312004650004E-09</v>
+        <v>-1.482992991310844E-09</v>
       </c>
       <c r="S4">
-        <v>-1.487532771267411E-09</v>
+        <v>-1.488628826095994E-09</v>
       </c>
       <c r="T4">
-        <v>5.330066384088953E-23</v>
+        <v>-9.316444497413079E-20</v>
       </c>
       <c r="U4">
-        <v>1.287508842397549E-09</v>
+        <v>1.287265647456792E-09</v>
       </c>
       <c r="V4">
-        <v>-1.285071954651702E-09</v>
+        <v>-1.286228001436041E-09</v>
       </c>
       <c r="W4">
-        <v>4.233722348397706E-17</v>
+        <v>1.426864450936225E-17</v>
       </c>
       <c r="X4">
-        <v>-1.287508831809205E-09</v>
+        <v>-1.287265651018304E-09</v>
       </c>
       <c r="Y4">
-        <v>1.285071965240047E-09</v>
+        <v>1.286227997879025E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -7955,37 +7955,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.190169016475026</v>
+        <v>1.19016901644547</v>
       </c>
       <c r="AI4">
-        <v>1.191135805290812</v>
+        <v>1.19113580528599</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.19016899849968</v>
+        <v>1.190169022446505</v>
       </c>
       <c r="AL4">
-        <v>1.191135795687494</v>
+        <v>1.191135808465855</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1361552980736</v>
+        <v>-139.1361552982339</v>
       </c>
       <c r="AO4">
-        <v>139.0824298864981</v>
+        <v>139.0824298852958</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1361549559494</v>
+        <v>-139.1361554114004</v>
       </c>
       <c r="AR4">
-        <v>139.0824290795985</v>
+        <v>139.0824301543621</v>
       </c>
     </row>
   </sheetData>
@@ -8137,16 +8137,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.02439206957623863</v>
+        <v>0.02439206957683514</v>
       </c>
       <c r="C2">
-        <v>9.786331032126264E-06</v>
+        <v>9.786331174945902E-06</v>
       </c>
       <c r="D2">
-        <v>9.786331032117612E-06</v>
+        <v>9.78633101572367E-06</v>
       </c>
       <c r="E2">
-        <v>0.02438882371466442</v>
+        <v>0.0243888237152607</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8155,16 +8155,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.005633107258313218</v>
+        <v>0.005633107258450979</v>
       </c>
       <c r="I2">
-        <v>2.260056375988219E-06</v>
+        <v>2.260056408971001E-06</v>
       </c>
       <c r="J2">
-        <v>2.260056375986221E-06</v>
+        <v>2.260056372200202E-06</v>
       </c>
       <c r="K2">
-        <v>0.005632357658680601</v>
+        <v>0.005632357658818306</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -8173,52 +8173,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.004142657814595634</v>
+        <v>0.004142657814708859</v>
       </c>
       <c r="O2">
-        <v>2.113928242908887E-06</v>
+        <v>2.113928249772154E-06</v>
       </c>
       <c r="P2">
-        <v>-1.382324912644163E-06</v>
+        <v>-1.382324931957276E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.0029740743925827</v>
+        <v>-0.002974074392621814</v>
       </c>
       <c r="R2">
-        <v>-3.337249487620048E-10</v>
+        <v>-3.337158144198689E-10</v>
       </c>
       <c r="S2">
-        <v>-1.01393044999675E-09</v>
+        <v>-1.013907954550546E-09</v>
       </c>
       <c r="T2">
-        <v>0.003386424559451164</v>
+        <v>0.003386424559519379</v>
       </c>
       <c r="U2">
-        <v>-3.756944304561924E-07</v>
+        <v>-3.756945709069663E-07</v>
       </c>
       <c r="V2">
-        <v>-1.642868632182139E-06</v>
+        <v>-1.642868611231378E-06</v>
       </c>
       <c r="W2">
-        <v>-0.002974075241208915</v>
+        <v>-0.002974075241247483</v>
       </c>
       <c r="X2">
-        <v>-1.132631917358629E-09</v>
+        <v>-1.132487902182892E-09</v>
       </c>
       <c r="Y2">
-        <v>7.399150811975555E-10</v>
+        <v>7.39893618879745E-10</v>
       </c>
       <c r="Z2">
-        <v>-39.27291736746744</v>
+        <v>-39.27291736726589</v>
       </c>
       <c r="AA2">
-        <v>-109.9224292606829</v>
+        <v>-109.9224256025196</v>
       </c>
       <c r="AB2">
-        <v>-109.9224292606077</v>
+        <v>-109.9224285062947</v>
       </c>
       <c r="AC2">
-        <v>140.7487704748207</v>
+        <v>140.7487704750228</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -8227,40 +8227,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9498581377369323</v>
+        <v>0.9498581377369293</v>
       </c>
       <c r="AH2">
-        <v>0.9499999942098001</v>
+        <v>0.9499999942098053</v>
       </c>
       <c r="AI2">
-        <v>0.9500000545388835</v>
+        <v>0.9500000545388828</v>
       </c>
       <c r="AJ2">
-        <v>0.7467524607717539</v>
+        <v>0.7467524607632491</v>
       </c>
       <c r="AK2">
-        <v>0.9752239721798733</v>
+        <v>0.9752239721836686</v>
       </c>
       <c r="AL2">
-        <v>1.036694517812588</v>
+        <v>1.036694517817192</v>
       </c>
       <c r="AM2">
-        <v>-0.008562029469767338</v>
+        <v>-0.00856202947000685</v>
       </c>
       <c r="AN2">
         <v>-120.0000048418357</v>
       </c>
       <c r="AO2">
-        <v>120.0000027411301</v>
+        <v>120.0000027411302</v>
       </c>
       <c r="AP2">
-        <v>5.748778649250705</v>
+        <v>5.748778649447619</v>
       </c>
       <c r="AQ2">
-        <v>-126.3810027392176</v>
+        <v>-126.3810027397006</v>
       </c>
       <c r="AR2">
-        <v>123.9162975015228</v>
+        <v>123.9162975017938</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -8304,40 +8304,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.434281834039287E-10</v>
+        <v>-5.433910179978018E-10</v>
       </c>
       <c r="O3">
-        <v>1.112416409265642E-10</v>
+        <v>1.11248868887729E-10</v>
       </c>
       <c r="P3">
-        <v>3.379768072569983E-10</v>
+        <v>3.379414502863916E-10</v>
       </c>
       <c r="Q3">
-        <v>5.434281953973467E-10</v>
+        <v>5.433910219923274E-10</v>
       </c>
       <c r="R3">
-        <v>-1.112416379271913E-10</v>
+        <v>-1.112488698860173E-10</v>
       </c>
       <c r="S3">
-        <v>-3.379768042576253E-10</v>
+        <v>-3.379414512844271E-10</v>
       </c>
       <c r="T3">
-        <v>-2.605527793138106E-10</v>
+        <v>-2.604947096916704E-10</v>
       </c>
       <c r="U3">
-        <v>3.775439597468257E-10</v>
+        <v>3.775112194579115E-10</v>
       </c>
       <c r="V3">
-        <v>-2.466383496293418E-10</v>
+        <v>-2.466338482135211E-10</v>
       </c>
       <c r="W3">
-        <v>2.605527835340655E-10</v>
+        <v>2.604947111044742E-10</v>
       </c>
       <c r="X3">
-        <v>-3.775439586914036E-10</v>
+        <v>-3.775112198130052E-10</v>
       </c>
       <c r="Y3">
-        <v>2.466383506847639E-10</v>
+        <v>2.466338478587365E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -8358,40 +8358,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.7467524607717539</v>
+        <v>0.7467524607632491</v>
       </c>
       <c r="AH3">
-        <v>0.9752239721798733</v>
+        <v>0.9752239721836686</v>
       </c>
       <c r="AI3">
-        <v>1.036694517812588</v>
+        <v>1.036694517817192</v>
       </c>
       <c r="AJ3">
-        <v>0.7467524764328305</v>
+        <v>0.7467524659837266</v>
       </c>
       <c r="AK3">
-        <v>0.9752239675709701</v>
+        <v>0.9752239737269304</v>
       </c>
       <c r="AL3">
-        <v>1.036694513350904</v>
+        <v>1.036694519296579</v>
       </c>
       <c r="AM3">
-        <v>5.748778649250705</v>
+        <v>5.748778649447619</v>
       </c>
       <c r="AN3">
-        <v>-126.3810027392176</v>
+        <v>-126.3810027397006</v>
       </c>
       <c r="AO3">
-        <v>123.9162975015228</v>
+        <v>123.9162975017938</v>
       </c>
       <c r="AP3">
-        <v>5.748778518077992</v>
+        <v>5.748778606396987</v>
       </c>
       <c r="AQ3">
-        <v>-126.3810023638191</v>
+        <v>-126.381002864494</v>
       </c>
       <c r="AR3">
-        <v>123.9162971426547</v>
+        <v>123.9162976216164</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -8435,40 +8435,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.434282021346974E-10</v>
+        <v>-5.434909824046946E-10</v>
       </c>
       <c r="O4">
-        <v>1.112416478312778E-10</v>
+        <v>1.11260617713876E-10</v>
       </c>
       <c r="P4">
-        <v>3.379768159365943E-10</v>
+        <v>3.381227175557291E-10</v>
       </c>
       <c r="Q4">
-        <v>5.434282093307486E-10</v>
+        <v>5.434909848016727E-10</v>
       </c>
       <c r="R4">
-        <v>-1.112416460316538E-10</v>
+        <v>-1.112606183130514E-10</v>
       </c>
       <c r="S4">
-        <v>-3.379768141369704E-10</v>
+        <v>-3.381227181548061E-10</v>
       </c>
       <c r="T4">
-        <v>-2.605527829354393E-10</v>
+        <v>-2.604905525831372E-10</v>
       </c>
       <c r="U4">
-        <v>3.77543970069364E-10</v>
+        <v>3.774337077949938E-10</v>
       </c>
       <c r="V4">
-        <v>-2.46638358240665E-10</v>
+        <v>-2.470090482474237E-10</v>
       </c>
       <c r="W4">
-        <v>2.605527854675923E-10</v>
+        <v>2.60490553430611E-10</v>
       </c>
       <c r="X4">
-        <v>-3.775439694361106E-10</v>
+        <v>-3.7743370800813E-10</v>
       </c>
       <c r="Y4">
-        <v>2.466383588739183E-10</v>
+        <v>2.470090480348889E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -8489,40 +8489,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.7467524607717539</v>
+        <v>0.7467524607632491</v>
       </c>
       <c r="AH4">
-        <v>0.9752239721798733</v>
+        <v>0.9752239721836686</v>
       </c>
       <c r="AI4">
-        <v>1.036694517812588</v>
+        <v>1.036694517817192</v>
       </c>
       <c r="AJ4">
-        <v>0.7467524701684002</v>
+        <v>0.7467524638952845</v>
       </c>
       <c r="AK4">
-        <v>0.9752239694145313</v>
+        <v>0.9752239731102325</v>
       </c>
       <c r="AL4">
-        <v>1.036694515135578</v>
+        <v>1.036694518704438</v>
       </c>
       <c r="AM4">
-        <v>5.748778649250705</v>
+        <v>5.748778649447619</v>
       </c>
       <c r="AN4">
-        <v>-126.3810027392176</v>
+        <v>-126.3810027397006</v>
       </c>
       <c r="AO4">
-        <v>123.9162975015228</v>
+        <v>123.9162975017938</v>
       </c>
       <c r="AP4">
-        <v>5.74877857054708</v>
+        <v>5.748778623611087</v>
       </c>
       <c r="AQ4">
-        <v>-126.3810025139785</v>
+        <v>-126.3810028146105</v>
       </c>
       <c r="AR4">
-        <v>123.9162972862019</v>
+        <v>123.9162975736307</v>
       </c>
     </row>
   </sheetData>
@@ -8674,16 +8674,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.02310845738501499</v>
+        <v>0.02310845738518363</v>
       </c>
       <c r="C2">
-        <v>9.271144737508142E-06</v>
+        <v>9.271144976254471E-06</v>
       </c>
       <c r="D2">
-        <v>9.271144737499433E-06</v>
+        <v>9.271144397705774E-06</v>
       </c>
       <c r="E2">
-        <v>0.02310538277684291</v>
+        <v>0.02310538277701174</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8692,16 +8692,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.005336669716240736</v>
+        <v>0.005336669716279679</v>
       </c>
       <c r="I2">
-        <v>2.141079195863089E-06</v>
+        <v>2.141079250999193E-06</v>
       </c>
       <c r="J2">
-        <v>2.141079195861078E-06</v>
+        <v>2.141079117389093E-06</v>
       </c>
       <c r="K2">
-        <v>0.005335959665887833</v>
+        <v>0.005335959665926822</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -8710,52 +8710,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.00371812236094448</v>
+        <v>0.00371812236087141</v>
       </c>
       <c r="O2">
-        <v>1.89725342343159E-06</v>
+        <v>1.897253494564986E-06</v>
       </c>
       <c r="P2">
-        <v>-1.240578132805268E-06</v>
+        <v>-1.240578023266507E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.002669294267925731</v>
+        <v>-0.00266929426785798</v>
       </c>
       <c r="R2">
-        <v>-2.995317075503596E-10</v>
+        <v>-2.996176336631098E-10</v>
       </c>
       <c r="S2">
-        <v>-9.100123668591789E-10</v>
+        <v>-9.101314943158914E-10</v>
       </c>
       <c r="T2">
-        <v>0.003039387137698349</v>
+        <v>0.003039387137843063</v>
       </c>
       <c r="U2">
-        <v>-3.371165903973097E-07</v>
+        <v>-3.371164737107054E-07</v>
       </c>
       <c r="V2">
-        <v>-1.47451161116452E-06</v>
+        <v>-1.474511611028502E-06</v>
       </c>
       <c r="W2">
-        <v>-0.002669295029476009</v>
+        <v>-0.002669295029628793</v>
       </c>
       <c r="X2">
-        <v>-1.01655146120967E-09</v>
+        <v>-1.016662285874915E-09</v>
       </c>
       <c r="Y2">
-        <v>6.640902822717118E-10</v>
+        <v>6.640819762302716E-10</v>
       </c>
       <c r="Z2">
-        <v>-39.27246679667027</v>
+        <v>-39.27246679855858</v>
       </c>
       <c r="AA2">
-        <v>-109.9244683824459</v>
+        <v>-109.9244721684717</v>
       </c>
       <c r="AB2">
-        <v>-109.9244683823996</v>
+        <v>-109.9244708720263</v>
       </c>
       <c r="AC2">
-        <v>140.7492209343798</v>
+        <v>140.7492209324906</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -8764,40 +8764,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8998726639978349</v>
+        <v>0.8998726639978298</v>
       </c>
       <c r="AH2">
-        <v>0.8999999816578801</v>
+        <v>0.8999999816578753</v>
       </c>
       <c r="AI2">
-        <v>0.9000000358069873</v>
+        <v>0.900000035806987</v>
       </c>
       <c r="AJ2">
-        <v>0.707455252762791</v>
+        <v>0.7074552527688903</v>
       </c>
       <c r="AK2">
-        <v>0.9238973984762439</v>
+        <v>0.9238973984683596</v>
       </c>
       <c r="AL2">
-        <v>0.9821318069183326</v>
+        <v>0.9821318069157154</v>
       </c>
       <c r="AM2">
-        <v>-0.008111459964561614</v>
+        <v>-0.00811145996435368</v>
       </c>
       <c r="AN2">
-        <v>-120.000004586957</v>
+        <v>-120.0000045869571</v>
       </c>
       <c r="AO2">
-        <v>120.0000025966922</v>
+        <v>120.000002596692</v>
       </c>
       <c r="AP2">
-        <v>5.749229107633718</v>
+        <v>5.749229108111425</v>
       </c>
       <c r="AQ2">
-        <v>-126.381036657511</v>
+        <v>-126.3810366572702</v>
       </c>
       <c r="AR2">
-        <v>123.9163640964964</v>
+        <v>123.9163640961185</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -8841,40 +8841,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-4.87718110589657E-10</v>
+        <v>-4.877537079234937E-10</v>
       </c>
       <c r="O3">
-        <v>9.984389531535371E-11</v>
+        <v>9.978005889897804E-11</v>
       </c>
       <c r="P3">
-        <v>3.033374472832253E-10</v>
+        <v>3.033893185168658E-10</v>
       </c>
       <c r="Q3">
-        <v>4.877181213535631E-10</v>
+        <v>4.877537115096941E-10</v>
       </c>
       <c r="R3">
-        <v>-9.984389262335383E-11</v>
+        <v>-9.97800597947607E-11</v>
       </c>
       <c r="S3">
-        <v>-3.033374445912255E-10</v>
+        <v>-3.033893194133452E-10</v>
       </c>
       <c r="T3">
-        <v>-2.338680198253855E-10</v>
+        <v>-2.339501980157522E-10</v>
       </c>
       <c r="U3">
-        <v>3.388504753438779E-10</v>
+        <v>3.389257380189608E-10</v>
       </c>
       <c r="V3">
-        <v>-2.213634170611137E-10</v>
+        <v>-2.213576537892196E-10</v>
       </c>
       <c r="W3">
-        <v>2.338680236129986E-10</v>
+        <v>2.339501992849744E-10</v>
       </c>
       <c r="X3">
-        <v>-3.388504743966146E-10</v>
+        <v>-3.389257383378784E-10</v>
       </c>
       <c r="Y3">
-        <v>2.213634180083771E-10</v>
+        <v>2.213576534704181E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -8895,40 +8895,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.707455252762791</v>
+        <v>0.7074552527688903</v>
       </c>
       <c r="AH3">
-        <v>0.9238973984762439</v>
+        <v>0.9238973984683596</v>
       </c>
       <c r="AI3">
-        <v>0.9821318069183326</v>
+        <v>0.9821318069157154</v>
       </c>
       <c r="AJ3">
-        <v>0.707455267599344</v>
+        <v>0.7074552577154267</v>
       </c>
       <c r="AK3">
-        <v>0.9238973941098294</v>
+        <v>0.9238973999299264</v>
       </c>
       <c r="AL3">
-        <v>0.9821318026914828</v>
+        <v>0.9821318083182128</v>
       </c>
       <c r="AM3">
-        <v>5.749229107633718</v>
+        <v>5.749229108111425</v>
       </c>
       <c r="AN3">
-        <v>-126.381036657511</v>
+        <v>-126.3810366572702</v>
       </c>
       <c r="AO3">
-        <v>123.9163640964964</v>
+        <v>123.9163640961185</v>
       </c>
       <c r="AP3">
-        <v>5.749228976411469</v>
+        <v>5.749229065052041</v>
       </c>
       <c r="AQ3">
-        <v>-126.3810362821122</v>
+        <v>-126.381036782019</v>
       </c>
       <c r="AR3">
-        <v>123.9163637376239</v>
+        <v>123.9163642160215</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -8972,40 +8972,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-4.877181284166671E-10</v>
+        <v>-4.876151453767955E-10</v>
       </c>
       <c r="O4">
-        <v>9.984390120011717E-11</v>
+        <v>9.990839645448465E-11</v>
       </c>
       <c r="P4">
-        <v>3.033374544090515E-10</v>
+        <v>3.033483140257915E-10</v>
       </c>
       <c r="Q4">
-        <v>4.877181348750111E-10</v>
+        <v>4.876151475273255E-10</v>
       </c>
       <c r="R4">
-        <v>-9.984389958491713E-11</v>
+        <v>-9.990839699217366E-11</v>
       </c>
       <c r="S4">
-        <v>-3.033374527938514E-10</v>
+        <v>-3.03348314563034E-10</v>
       </c>
       <c r="T4">
-        <v>-2.338680224425245E-10</v>
+        <v>-2.337206874876571E-10</v>
       </c>
       <c r="U4">
-        <v>3.388504869339962E-10</v>
+        <v>3.386572334727327E-10</v>
       </c>
       <c r="V4">
-        <v>-2.213634266411314E-10</v>
+        <v>-2.214300741619084E-10</v>
       </c>
       <c r="W4">
-        <v>2.338680247150925E-10</v>
+        <v>2.33720688247831E-10</v>
       </c>
       <c r="X4">
-        <v>-3.388504863656381E-10</v>
+        <v>-3.386572336638208E-10</v>
       </c>
       <c r="Y4">
-        <v>2.213634272094895E-10</v>
+        <v>2.214300739711315E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -9026,40 +9026,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.707455252762791</v>
+        <v>0.7074552527688903</v>
       </c>
       <c r="AH4">
-        <v>0.9238973984762439</v>
+        <v>0.9238973984683596</v>
       </c>
       <c r="AI4">
-        <v>0.9821318069183326</v>
+        <v>0.9821318069157154</v>
       </c>
       <c r="AJ4">
-        <v>0.7074552616647231</v>
+        <v>0.7074552557359562</v>
       </c>
       <c r="AK4">
-        <v>0.9238973958563951</v>
+        <v>0.9238973993460333</v>
       </c>
       <c r="AL4">
-        <v>0.9821318043822226</v>
+        <v>0.9821318077563349</v>
       </c>
       <c r="AM4">
-        <v>5.749229107633718</v>
+        <v>5.749229108111425</v>
       </c>
       <c r="AN4">
-        <v>-126.381036657511</v>
+        <v>-126.3810366572702</v>
       </c>
       <c r="AO4">
-        <v>123.9163640964964</v>
+        <v>123.9163640961185</v>
       </c>
       <c r="AP4">
-        <v>5.749229028900371</v>
+        <v>5.749229082255076</v>
       </c>
       <c r="AQ4">
-        <v>-126.3810364322717</v>
+        <v>-126.3810367321819</v>
       </c>
       <c r="AR4">
-        <v>123.9163638811729</v>
+        <v>123.9163641679492</v>
       </c>
     </row>
   </sheetData>
@@ -9211,106 +9211,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.112666158615173E-05</v>
+        <v>3.112665297215797E-05</v>
       </c>
       <c r="C2">
-        <v>0.3459535560661574</v>
+        <v>0.3459535560698296</v>
       </c>
       <c r="D2">
-        <v>0.3457320346211745</v>
+        <v>0.3457320346250685</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3459755374753177</v>
+        <v>0.3459755374789877</v>
       </c>
       <c r="G2">
-        <v>0.345703440784071</v>
+        <v>0.3457034407879669</v>
       </c>
       <c r="H2">
-        <v>7.188394685411061E-06</v>
+        <v>7.188392696094385E-06</v>
       </c>
       <c r="I2">
-        <v>0.0798945526792833</v>
+        <v>0.07989455268013136</v>
       </c>
       <c r="J2">
-        <v>0.07984339449216411</v>
+        <v>0.07984339449306339</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.07989962906835731</v>
+        <v>0.07989962906920484</v>
       </c>
       <c r="M2">
-        <v>0.07983679102824617</v>
+        <v>0.0798367910291459</v>
       </c>
       <c r="N2">
-        <v>2.099249628094338E-09</v>
+        <v>2.097360418821175E-09</v>
       </c>
       <c r="O2">
-        <v>0.08098758713525354</v>
+        <v>0.08098758713636653</v>
       </c>
       <c r="P2">
-        <v>0.0501316046819843</v>
+        <v>0.05013160468211987</v>
       </c>
       <c r="Q2">
-        <v>-5.388295887197545E-09</v>
+        <v>-5.385778732205302E-09</v>
       </c>
       <c r="R2">
-        <v>-1.468693860530401E-15</v>
+        <v>1.460098771143564E-12</v>
       </c>
       <c r="S2">
-        <v>-4.172510415752156E-15</v>
+        <v>-1.075259326479518E-12</v>
       </c>
       <c r="T2">
-        <v>-7.547815404560585E-06</v>
+        <v>-7.547813316302439E-06</v>
       </c>
       <c r="U2">
-        <v>0.02159856168971838</v>
+        <v>0.02159856168900336</v>
       </c>
       <c r="V2">
-        <v>0.06698068521582311</v>
+        <v>0.06698068521689543</v>
       </c>
       <c r="W2">
-        <v>-4.285146162283562E-12</v>
+        <v>-7.069753873411603E-12</v>
       </c>
       <c r="X2">
-        <v>9.268547103479285E-16</v>
+        <v>3.373934495168221E-12</v>
       </c>
       <c r="Y2">
-        <v>7.816440103545429E-17</v>
+        <v>-1.501644867034044E-12</v>
       </c>
       <c r="Z2">
-        <v>89.98406327660724</v>
+        <v>89.98407761327053</v>
       </c>
       <c r="AA2">
-        <v>-135.0611648440129</v>
+        <v>-135.0611648433465</v>
       </c>
       <c r="AB2">
-        <v>66.74207476426071</v>
+        <v>66.74207476389496</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.94248496075311</v>
+        <v>44.94248496141964</v>
       </c>
       <c r="AE2">
-        <v>-113.2599635295848</v>
+        <v>-113.2599635299509</v>
       </c>
       <c r="AG2">
-        <v>1.050000177620706</v>
+        <v>1.05000017762065</v>
       </c>
       <c r="AH2">
-        <v>1.04911006102413</v>
+        <v>1.049110061024148</v>
       </c>
       <c r="AI2">
-        <v>1.047845633459333</v>
+        <v>1.0478456334593</v>
       </c>
       <c r="AJ2">
-        <v>1.399911409936931</v>
+        <v>1.399911409933074</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -9319,16 +9319,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.232881459514017E-06</v>
+        <v>-1.232878042019926E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.128511366723</v>
+        <v>-120.1285113667249</v>
       </c>
       <c r="AO2">
-        <v>119.9291057201021</v>
+        <v>119.929105720102</v>
       </c>
       <c r="AP2">
-        <v>-0.01518448050018827</v>
+        <v>-0.01518447796656614</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -9378,40 +9378,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.796098622056878E-09</v>
+        <v>1.796290218855472E-09</v>
       </c>
       <c r="O3">
-        <v>-5.673744569793277E-23</v>
+        <v>1.101711304877877E-19</v>
       </c>
       <c r="P3">
-        <v>-1.17341781759616E-22</v>
+        <v>-8.902579689046942E-20</v>
       </c>
       <c r="Q3">
-        <v>-1.796098606269631E-09</v>
+        <v>-1.796290224108351E-09</v>
       </c>
       <c r="R3">
-        <v>1.421570736811756E-16</v>
+        <v>7.351232562634188E-17</v>
       </c>
       <c r="S3">
-        <v>1.421571341884404E-16</v>
+        <v>1.475556124014263E-16</v>
       </c>
       <c r="T3">
-        <v>1.428406880202372E-12</v>
+        <v>7.971607625615245E-13</v>
       </c>
       <c r="U3">
-        <v>6.151265330274792E-23</v>
+        <v>1.38725908286562E-19</v>
       </c>
       <c r="V3">
-        <v>1.634980185766098E-22</v>
+        <v>-1.773652207420983E-21</v>
       </c>
       <c r="W3">
-        <v>-1.428396214158379E-12</v>
+        <v>-7.971643358554119E-13</v>
       </c>
       <c r="X3">
-        <v>9.604283192551611E-17</v>
+        <v>1.292912636070086E-16</v>
       </c>
       <c r="Y3">
-        <v>9.604272950883181E-17</v>
+        <v>1.99740065546905E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -9432,7 +9432,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.399911409936931</v>
+        <v>1.399911409933074</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -9441,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.399911397625464</v>
+        <v>1.399911414028061</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -9450,7 +9450,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01518448050018827</v>
+        <v>-0.01518447796656614</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01518482034764941</v>
+        <v>-0.0151843640645632</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -9509,40 +9509,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.796098635000937E-09</v>
+        <v>1.79607812933639E-09</v>
       </c>
       <c r="O4">
-        <v>-5.673744548479652E-23</v>
+        <v>1.102098845692813E-19</v>
       </c>
       <c r="P4">
-        <v>-1.17341782909011E-22</v>
+        <v>-8.903554870904186E-20</v>
       </c>
       <c r="Q4">
-        <v>-1.796098625528588E-09</v>
+        <v>-1.796078132487432E-09</v>
       </c>
       <c r="R4">
-        <v>8.529426930900584E-17</v>
+        <v>4.406735418797672E-17</v>
       </c>
       <c r="S4">
-        <v>8.529433134591572E-17</v>
+        <v>8.856884060838792E-17</v>
       </c>
       <c r="T4">
-        <v>1.428377735260679E-12</v>
+        <v>1.221620988676453E-12</v>
       </c>
       <c r="U4">
-        <v>6.151265510285044E-23</v>
+        <v>1.387037148146425E-19</v>
       </c>
       <c r="V4">
-        <v>1.634980230771229E-22</v>
+        <v>-1.730381264052631E-21</v>
       </c>
       <c r="W4">
-        <v>-1.428371335634228E-12</v>
+        <v>-1.221623136931774E-12</v>
       </c>
       <c r="X4">
-        <v>5.762567608009611E-17</v>
+        <v>7.751491580997226E-17</v>
       </c>
       <c r="Y4">
-        <v>5.762557487858609E-17</v>
+        <v>1.19658115085022E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.399911409936931</v>
+        <v>1.399911409933074</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -9572,7 +9572,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.399911402550051</v>
+        <v>1.399911412390218</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -9581,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01518448050018827</v>
+        <v>-0.01518447796656614</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01518468440866947</v>
+        <v>-0.01518440950456159</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -9748,106 +9748,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.260933557600379E-05</v>
+        <v>3.260933116647499E-05</v>
       </c>
       <c r="C2">
-        <v>0.3624026701705976</v>
+        <v>0.3624026701768747</v>
       </c>
       <c r="D2">
-        <v>0.3621617107553519</v>
+        <v>0.3621617107573104</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3624256957769029</v>
+        <v>0.362425695783178</v>
       </c>
       <c r="G2">
-        <v>0.3621317562209156</v>
+        <v>0.3621317562228754</v>
       </c>
       <c r="H2">
-        <v>7.530803581377967E-06</v>
+        <v>7.530802563040896E-06</v>
       </c>
       <c r="I2">
-        <v>0.08369331291834101</v>
+        <v>0.08369331291979062</v>
       </c>
       <c r="J2">
-        <v>0.08363766572420944</v>
+        <v>0.08363766572466173</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.08369863045441969</v>
+        <v>0.08369863045586885</v>
       </c>
       <c r="M2">
-        <v>0.08363074802069827</v>
+        <v>0.08363074802115086</v>
       </c>
       <c r="N2">
-        <v>2.166658766616306E-09</v>
+        <v>2.164074470292048E-09</v>
       </c>
       <c r="O2">
-        <v>0.08887463580194178</v>
+        <v>0.08887463580376741</v>
       </c>
       <c r="P2">
-        <v>0.05500716608658997</v>
+        <v>0.05500716608622416</v>
       </c>
       <c r="Q2">
-        <v>-5.913482128293647E-09</v>
+        <v>-5.9100381621736E-09</v>
       </c>
       <c r="R2">
-        <v>1.971363609534377E-16</v>
+        <v>2.811994317731713E-12</v>
       </c>
       <c r="S2">
-        <v>-2.616734054754981E-15</v>
+        <v>-2.072761336023886E-12</v>
       </c>
       <c r="T2">
-        <v>-8.283885697910367E-06</v>
+        <v>-8.2838845784146E-06</v>
       </c>
       <c r="U2">
-        <v>0.0237020064881647</v>
+        <v>0.02370200648750658</v>
       </c>
       <c r="V2">
-        <v>0.07349918419682462</v>
+        <v>0.0734991841977158</v>
       </c>
       <c r="W2">
-        <v>-4.849978445955197E-12</v>
+        <v>-6.343475672423906E-12</v>
       </c>
       <c r="X2">
-        <v>-1.29224524360461E-17</v>
+        <v>3.770723509261632E-12</v>
       </c>
       <c r="Y2">
-        <v>3.505281462486957E-16</v>
+        <v>-1.561301138924411E-12</v>
       </c>
       <c r="Z2">
-        <v>89.98501293928202</v>
+        <v>89.98503081163636</v>
       </c>
       <c r="AA2">
-        <v>-135.0673049857711</v>
+        <v>-135.0673049850849</v>
       </c>
       <c r="AB2">
-        <v>66.73711005032617</v>
+        <v>66.73711004981082</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.93634557047508</v>
+        <v>44.93634557116155</v>
       </c>
       <c r="AE2">
-        <v>-113.2649289509434</v>
+        <v>-113.2649289514592</v>
       </c>
       <c r="AG2">
-        <v>1.100000271118544</v>
+        <v>1.100000271118519</v>
       </c>
       <c r="AH2">
-        <v>1.099023290949346</v>
+        <v>1.09902329094936</v>
       </c>
       <c r="AI2">
-        <v>1.0976357854028</v>
+        <v>1.097635785402774</v>
       </c>
       <c r="AJ2">
-        <v>1.466563840216172</v>
+        <v>1.466563840232262</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -9856,16 +9856,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.291394423004376E-06</v>
+        <v>-1.2913902307256E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.1346216946706</v>
+        <v>-120.1346216946736</v>
       </c>
       <c r="AO2">
-        <v>119.9257401623237</v>
+        <v>119.9257401623244</v>
       </c>
       <c r="AP2">
-        <v>-0.01565922579150656</v>
+        <v>-0.01565922336989385</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -9915,40 +9915,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.971160693607858E-09</v>
+        <v>1.970959803613529E-09</v>
       </c>
       <c r="O3">
-        <v>9.011484237286729E-24</v>
+        <v>1.780507233497124E-19</v>
       </c>
       <c r="P3">
-        <v>-6.193391875570533E-23</v>
+        <v>-1.201289893471038E-19</v>
       </c>
       <c r="Q3">
-        <v>-1.971160676282217E-09</v>
+        <v>-1.970959809376671E-09</v>
       </c>
       <c r="R3">
-        <v>1.56018143634136E-16</v>
+        <v>8.058405978091256E-17</v>
       </c>
       <c r="S3">
-        <v>1.560182140988197E-16</v>
+        <v>1.619944278124914E-16</v>
       </c>
       <c r="T3">
-        <v>1.616683231082634E-12</v>
+        <v>2.128990990056285E-12</v>
       </c>
       <c r="U3">
-        <v>-3.070229682610716E-24</v>
+        <v>1.403274669576195E-19</v>
       </c>
       <c r="V3">
-        <v>1.112488026103215E-22</v>
+        <v>3.507685836038818E-20</v>
       </c>
       <c r="W3">
-        <v>-1.616671525682846E-12</v>
+        <v>-2.128994917153417E-12</v>
       </c>
       <c r="X3">
-        <v>1.054076367946274E-16</v>
+        <v>1.419505315360284E-16</v>
       </c>
       <c r="Y3">
-        <v>1.054075219193913E-16</v>
+        <v>2.188317324555543E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.466563840216172</v>
+        <v>1.466563840232262</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -9978,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.466563827318583</v>
+        <v>1.466563844523687</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -9987,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01565922579150656</v>
+        <v>-0.01565922336989385</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -9996,7 +9996,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01565956561940253</v>
+        <v>-0.01565910939032468</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -10046,40 +10046,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.971160707167955E-09</v>
+        <v>1.971403928220465E-09</v>
       </c>
       <c r="O4">
-        <v>9.011484326649878E-24</v>
+        <v>1.780895167943133E-19</v>
       </c>
       <c r="P4">
-        <v>-6.19339205871363E-23</v>
+        <v>-1.200855290771182E-19</v>
       </c>
       <c r="Q4">
-        <v>-1.97116069677257E-09</v>
+        <v>-1.971403931680321E-09</v>
       </c>
       <c r="R4">
-        <v>9.361088543249381E-17</v>
+        <v>4.830454760072175E-17</v>
       </c>
       <c r="S4">
-        <v>9.361095745380294E-17</v>
+        <v>9.720648726011722E-17</v>
       </c>
       <c r="T4">
-        <v>1.616652698382779E-12</v>
+        <v>3.504268188165665E-13</v>
       </c>
       <c r="U4">
-        <v>-3.070229851065388E-24</v>
+        <v>1.401781416382983E-19</v>
       </c>
       <c r="V4">
-        <v>1.112488052378035E-22</v>
+        <v>3.509715541910613E-20</v>
       </c>
       <c r="W4">
-        <v>-1.616645675142839E-12</v>
+        <v>-3.504291754412551E-13</v>
       </c>
       <c r="X4">
-        <v>6.32445852676224E-17</v>
+        <v>8.506406201005378E-17</v>
       </c>
       <c r="Y4">
-        <v>6.324447167346348E-17</v>
+        <v>1.310370419942216E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -10100,7 +10100,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.466563840216172</v>
+        <v>1.466563840232262</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -10109,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.466563832477618</v>
+        <v>1.466563842806426</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01565922579150656</v>
+        <v>-0.01565922336989385</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -10127,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01565942968824866</v>
+        <v>-0.01565915489615043</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -10285,130 +10285,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>6.485897477755475E-06</v>
+        <v>6.485895656710858E-06</v>
       </c>
       <c r="C2">
-        <v>0.03084668468181546</v>
+        <v>0.03084668468281365</v>
       </c>
       <c r="D2">
-        <v>0.03025911612833544</v>
+        <v>0.0302591161286619</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.03084976294750837</v>
+        <v>0.03084976294850604</v>
       </c>
       <c r="G2">
-        <v>0.03025270482949052</v>
+        <v>0.0302527048298169</v>
       </c>
       <c r="H2">
-        <v>1.497853884207137E-06</v>
+        <v>1.497853463654891E-06</v>
       </c>
       <c r="I2">
-        <v>0.007123736788013414</v>
+        <v>0.007123736788243936</v>
       </c>
       <c r="J2">
-        <v>0.006988043640983808</v>
+        <v>0.006988043641059201</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007124447683034584</v>
+        <v>0.007124447683264984</v>
       </c>
       <c r="M2">
-        <v>0.006986563014916158</v>
+        <v>0.006986563014991533</v>
       </c>
       <c r="N2">
-        <v>2.380080703188159E-07</v>
+        <v>2.380077190943609E-07</v>
       </c>
       <c r="O2">
-        <v>0.005700747560768053</v>
+        <v>0.005700747561027251</v>
       </c>
       <c r="P2">
-        <v>0.00496911221609733</v>
+        <v>0.004969112216265161</v>
       </c>
       <c r="Q2">
-        <v>-8.908055667019379E-10</v>
+        <v>-8.904345797485238E-10</v>
       </c>
       <c r="R2">
-        <v>-0.00475854025701476</v>
+        <v>-0.00475854025718985</v>
       </c>
       <c r="S2">
-        <v>-0.004576130304534663</v>
+        <v>-0.004576130304744631</v>
       </c>
       <c r="T2">
-        <v>-1.554633059286627E-06</v>
+        <v>-1.554632666332794E-06</v>
       </c>
       <c r="U2">
-        <v>0.00484081746924324</v>
+        <v>0.004840817469311857</v>
       </c>
       <c r="V2">
-        <v>0.005397034853747454</v>
+        <v>0.005397034853700526</v>
       </c>
       <c r="W2">
-        <v>-1.280925150096582E-10</v>
+        <v>-1.285162195920826E-10</v>
       </c>
       <c r="X2">
-        <v>-0.004758540428812053</v>
+        <v>-0.004758540428826199</v>
       </c>
       <c r="Y2">
-        <v>-0.004576131998776537</v>
+        <v>-0.004576131998711652</v>
       </c>
       <c r="Z2">
-        <v>81.29582987153641</v>
+        <v>81.2958403530228</v>
       </c>
       <c r="AA2">
-        <v>-160.344911389557</v>
+        <v>-160.3449113886728</v>
       </c>
       <c r="AB2">
-        <v>72.62891141118693</v>
+        <v>72.62891141239918</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>19.66569194840256</v>
+        <v>19.6656919492873</v>
       </c>
       <c r="AE2">
-        <v>-107.3729461202412</v>
+        <v>-107.3729461190302</v>
       </c>
       <c r="AG2">
-        <v>1.049999998013335</v>
+        <v>1.049999998013324</v>
       </c>
       <c r="AH2">
-        <v>1.049838394737241</v>
+        <v>1.049838394737238</v>
       </c>
       <c r="AI2">
-        <v>1.049823973627608</v>
+        <v>1.049823973627609</v>
       </c>
       <c r="AJ2">
-        <v>1.122117850122293</v>
+        <v>1.122117850126157</v>
       </c>
       <c r="AK2">
-        <v>0.9445774029715749</v>
+        <v>0.9445774029598095</v>
       </c>
       <c r="AL2">
-        <v>0.9262961951466967</v>
+        <v>0.9262961951513873</v>
       </c>
       <c r="AM2">
-        <v>-6.409247659887382E-07</v>
+        <v>-6.409241298695304E-07</v>
       </c>
       <c r="AN2">
-        <v>-120.0084987248653</v>
+        <v>-120.0084987248657</v>
       </c>
       <c r="AO2">
-        <v>119.9927837349447</v>
+        <v>119.9927837349444</v>
       </c>
       <c r="AP2">
-        <v>-0.5662823200432041</v>
+        <v>-0.5662823193219697</v>
       </c>
       <c r="AQ2">
-        <v>-115.3343070173189</v>
+        <v>-115.3343070174031</v>
       </c>
       <c r="AR2">
-        <v>117.6270644861883</v>
+        <v>117.6270644856787</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -10452,40 +10452,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.96935186389349E-10</v>
+        <v>2.971230887065592E-10</v>
       </c>
       <c r="O3">
-        <v>-3.530749758741549E-10</v>
+        <v>-3.530789091185914E-10</v>
       </c>
       <c r="P3">
-        <v>-4.170917717469844E-10</v>
+        <v>-4.170020096498444E-10</v>
       </c>
       <c r="Q3">
-        <v>-2.969351857038899E-10</v>
+        <v>-2.971230889346771E-10</v>
       </c>
       <c r="R3">
-        <v>3.530749781547365E-10</v>
+        <v>3.530789093874217E-10</v>
       </c>
       <c r="S3">
-        <v>4.170917739351904E-10</v>
+        <v>4.170020111060646E-10</v>
       </c>
       <c r="T3">
-        <v>4.269750805617722E-11</v>
+        <v>4.28206432639438E-11</v>
       </c>
       <c r="U3">
-        <v>-2.958092153142444E-10</v>
+        <v>-2.958149167634812E-10</v>
       </c>
       <c r="V3">
-        <v>1.47655519942679E-10</v>
+        <v>1.476943148242122E-10</v>
       </c>
       <c r="W3">
-        <v>-4.269750759307331E-11</v>
+        <v>-4.282064341933366E-11</v>
       </c>
       <c r="X3">
-        <v>2.958092168550312E-10</v>
+        <v>2.958149182822153E-10</v>
       </c>
       <c r="Y3">
-        <v>-1.476555184643023E-10</v>
+        <v>-1.476943151768121E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -10506,40 +10506,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.122117850122293</v>
+        <v>1.122117850126157</v>
       </c>
       <c r="AH3">
-        <v>0.9445774029715749</v>
+        <v>0.9445774029598095</v>
       </c>
       <c r="AI3">
-        <v>0.9262961951466967</v>
+        <v>0.9262961951513873</v>
       </c>
       <c r="AJ3">
-        <v>1.122117847337867</v>
+        <v>1.122117851052994</v>
       </c>
       <c r="AK3">
-        <v>0.9445774085856367</v>
+        <v>0.9445774053824875</v>
       </c>
       <c r="AL3">
-        <v>0.9262961984322891</v>
+        <v>0.9262961982720604</v>
       </c>
       <c r="AM3">
-        <v>-0.5662823200432041</v>
+        <v>-0.5662823193219697</v>
       </c>
       <c r="AN3">
-        <v>-115.3343070173189</v>
+        <v>-115.3343070174031</v>
       </c>
       <c r="AO3">
-        <v>117.6270644861883</v>
+        <v>117.6270644856787</v>
       </c>
       <c r="AP3">
-        <v>-0.5662823889586758</v>
+        <v>-0.5662822961776555</v>
       </c>
       <c r="AQ3">
-        <v>-115.3343070525889</v>
+        <v>-115.3343068940711</v>
       </c>
       <c r="AR3">
-        <v>117.6270647612182</v>
+        <v>117.6270645055987</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -10583,40 +10583,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.969351909054589E-10</v>
+        <v>2.966961949534577E-10</v>
       </c>
       <c r="O4">
-        <v>-3.530749855900423E-10</v>
+        <v>-3.531794058220936E-10</v>
       </c>
       <c r="P4">
-        <v>-4.170917828171026E-10</v>
+        <v>-4.170235163851524E-10</v>
       </c>
       <c r="Q4">
-        <v>-2.969351904941834E-10</v>
+        <v>-2.966961950902005E-10</v>
       </c>
       <c r="R4">
-        <v>3.530749869583913E-10</v>
+        <v>3.531794059833748E-10</v>
       </c>
       <c r="S4">
-        <v>4.170917841300263E-10</v>
+        <v>4.170235172589571E-10</v>
       </c>
       <c r="T4">
-        <v>4.269750541599516E-11</v>
+        <v>4.265476092065464E-11</v>
       </c>
       <c r="U4">
-        <v>-2.958092179661944E-10</v>
+        <v>-2.956089216869621E-10</v>
       </c>
       <c r="V4">
-        <v>1.476555226124101E-10</v>
+        <v>1.475840088579014E-10</v>
       </c>
       <c r="W4">
-        <v>-4.26975051381328E-11</v>
+        <v>-4.265476101380381E-11</v>
       </c>
       <c r="X4">
-        <v>2.958092188906665E-10</v>
+        <v>2.956089225979336E-10</v>
       </c>
       <c r="Y4">
-        <v>-1.476555217253841E-10</v>
+        <v>-1.475840090686143E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -10637,40 +10637,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.122117850122293</v>
+        <v>1.122117850126157</v>
       </c>
       <c r="AH4">
-        <v>0.9445774029715749</v>
+        <v>0.9445774029598095</v>
       </c>
       <c r="AI4">
-        <v>0.9262961951466967</v>
+        <v>0.9262961951513873</v>
       </c>
       <c r="AJ4">
-        <v>1.122117848451638</v>
+        <v>1.122117850682474</v>
       </c>
       <c r="AK4">
-        <v>0.9445774063400121</v>
+        <v>0.9445774044126203</v>
       </c>
       <c r="AL4">
-        <v>0.9262961971180521</v>
+        <v>0.9262961970234609</v>
       </c>
       <c r="AM4">
-        <v>-0.5662823200432041</v>
+        <v>-0.5662823193219697</v>
       </c>
       <c r="AN4">
-        <v>-115.3343070173189</v>
+        <v>-115.3343070174031</v>
       </c>
       <c r="AO4">
-        <v>117.6270644861883</v>
+        <v>117.6270644856787</v>
       </c>
       <c r="AP4">
-        <v>-0.5662823613924883</v>
+        <v>-0.5662823054174653</v>
       </c>
       <c r="AQ4">
-        <v>-115.3343070384809</v>
+        <v>-115.3343069433768</v>
       </c>
       <c r="AR4">
-        <v>117.6270646512062</v>
+        <v>117.6270644977086</v>
       </c>
     </row>
   </sheetData>
@@ -10822,130 +10822,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>6.794985911322041E-06</v>
+        <v>6.794984520784708E-06</v>
       </c>
       <c r="C2">
-        <v>0.03231533714347254</v>
+        <v>0.03231533714426021</v>
       </c>
       <c r="D2">
-        <v>0.03169977413294922</v>
+        <v>0.03169977413291036</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.03231856180154636</v>
+        <v>0.03231856180233356</v>
       </c>
       <c r="G2">
-        <v>0.0316930573517338</v>
+        <v>0.03169305735169497</v>
       </c>
       <c r="H2">
-        <v>1.569234801400019E-06</v>
+        <v>1.569234480269172E-06</v>
       </c>
       <c r="I2">
-        <v>0.007462907550700941</v>
+        <v>0.007462907550882846</v>
       </c>
       <c r="J2">
-        <v>0.007320749360651092</v>
+        <v>0.007320749360642117</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007463652253594823</v>
+        <v>0.007463652253776621</v>
       </c>
       <c r="M2">
-        <v>0.007319198186450854</v>
+        <v>0.007319198186441886</v>
       </c>
       <c r="N2">
-        <v>2.611496035429626E-07</v>
+        <v>2.611492125978398E-07</v>
       </c>
       <c r="O2">
-        <v>0.006256511431689311</v>
+        <v>0.006256511431984195</v>
       </c>
       <c r="P2">
-        <v>0.005453541879818948</v>
+        <v>0.005453541879891622</v>
       </c>
       <c r="Q2">
-        <v>-9.77656496580016E-10</v>
+        <v>-9.772420661225879E-10</v>
       </c>
       <c r="R2">
-        <v>-0.005222448158467363</v>
+        <v>-0.005222448158695383</v>
       </c>
       <c r="S2">
-        <v>-0.005022248935275515</v>
+        <v>-0.005022248935405035</v>
       </c>
       <c r="T2">
-        <v>-1.7062894532806E-06</v>
+        <v>-1.706289155757848E-06</v>
       </c>
       <c r="U2">
-        <v>0.005312746994674445</v>
+        <v>0.005312746994636267</v>
       </c>
       <c r="V2">
-        <v>0.00592318268223971</v>
+        <v>0.0059231826821594</v>
       </c>
       <c r="W2">
-        <v>-1.405867947298716E-10</v>
+        <v>-1.409089130343923E-10</v>
       </c>
       <c r="X2">
-        <v>-0.005222448347185289</v>
+        <v>-0.005222448347095674</v>
       </c>
       <c r="Y2">
-        <v>-0.005022250794852405</v>
+        <v>-0.005022250794776316</v>
       </c>
       <c r="Z2">
-        <v>81.29833822340815</v>
+        <v>81.29834955648167</v>
       </c>
       <c r="AA2">
-        <v>-160.3453156849116</v>
+        <v>-160.3453156833765</v>
       </c>
       <c r="AB2">
-        <v>72.62856413272485</v>
+        <v>72.62856413349229</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>19.66528839025122</v>
+        <v>19.66528839178663</v>
       </c>
       <c r="AE2">
-        <v>-107.3732940830494</v>
+        <v>-107.3732940822832</v>
       </c>
       <c r="AG2">
-        <v>1.100000073996935</v>
+        <v>1.100000073996927</v>
       </c>
       <c r="AH2">
-        <v>1.099822714182373</v>
+        <v>1.099822714182374</v>
       </c>
       <c r="AI2">
-        <v>1.099806887325973</v>
+        <v>1.099806887325975</v>
       </c>
       <c r="AJ2">
-        <v>1.175551542840023</v>
+        <v>1.175551542843638</v>
       </c>
       <c r="AK2">
-        <v>0.9895500080917368</v>
+        <v>0.9895500080807462</v>
       </c>
       <c r="AL2">
-        <v>0.9703978075013853</v>
+        <v>0.970397807507736</v>
       </c>
       <c r="AM2">
-        <v>-6.713539157072585E-07</v>
+        <v>-6.713532615851036E-07</v>
       </c>
       <c r="AN2">
-        <v>-120.0089033601346</v>
+        <v>-120.0089033601351</v>
       </c>
       <c r="AO2">
-        <v>119.9924401645979</v>
+        <v>119.9924401645978</v>
       </c>
       <c r="AP2">
-        <v>-0.5663007758389043</v>
+        <v>-0.566300775188825</v>
       </c>
       <c r="AQ2">
-        <v>-115.3347105745257</v>
+        <v>-115.3347105747327</v>
       </c>
       <c r="AR2">
-        <v>117.6267165243296</v>
+        <v>117.626716523923</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -10989,40 +10989,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.258854958348616E-10</v>
+        <v>3.258825446137171E-10</v>
       </c>
       <c r="O3">
-        <v>-3.875278745829123E-10</v>
+        <v>-3.87580059281037E-10</v>
       </c>
       <c r="P3">
-        <v>-4.577837226167119E-10</v>
+        <v>-4.577246610105457E-10</v>
       </c>
       <c r="Q3">
-        <v>-3.258854950825764E-10</v>
+        <v>-3.258825448640431E-10</v>
       </c>
       <c r="R3">
-        <v>3.875278770859052E-10</v>
+        <v>3.875800595758691E-10</v>
       </c>
       <c r="S3">
-        <v>4.577837250186084E-10</v>
+        <v>4.577246626091942E-10</v>
       </c>
       <c r="T3">
-        <v>4.686226833878556E-11</v>
+        <v>4.69427079789372E-11</v>
       </c>
       <c r="U3">
-        <v>-3.246219090530166E-10</v>
+        <v>-3.247357094513631E-10</v>
       </c>
       <c r="V3">
-        <v>1.620752380546539E-10</v>
+        <v>1.620893240730924E-10</v>
       </c>
       <c r="W3">
-        <v>-4.686226783053313E-11</v>
+        <v>-4.694270814949812E-11</v>
       </c>
       <c r="X3">
-        <v>3.24621910744067E-10</v>
+        <v>3.247357111186694E-10</v>
       </c>
       <c r="Y3">
-        <v>-1.620752364319053E-10</v>
+        <v>-1.620893244595251E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -11043,40 +11043,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.175551542840023</v>
+        <v>1.175551542843638</v>
       </c>
       <c r="AH3">
-        <v>0.9895500080917368</v>
+        <v>0.9895500080807462</v>
       </c>
       <c r="AI3">
-        <v>0.9703978075013853</v>
+        <v>0.970397807507736</v>
       </c>
       <c r="AJ3">
-        <v>1.175551539923017</v>
+        <v>1.175551543815104</v>
       </c>
       <c r="AK3">
-        <v>0.9895500139732319</v>
+        <v>0.9895500106185833</v>
       </c>
       <c r="AL3">
-        <v>0.9703978109435403</v>
+        <v>0.9703978107770819</v>
       </c>
       <c r="AM3">
-        <v>-0.5663007758389043</v>
+        <v>-0.566300775188825</v>
       </c>
       <c r="AN3">
-        <v>-115.3347105745257</v>
+        <v>-115.3347105747327</v>
       </c>
       <c r="AO3">
-        <v>117.6267165243296</v>
+        <v>117.626716523923</v>
       </c>
       <c r="AP3">
-        <v>-0.5663008447531466</v>
+        <v>-0.5663007520217664</v>
       </c>
       <c r="AQ3">
-        <v>-115.3347106097692</v>
+        <v>-115.3347104513724</v>
       </c>
       <c r="AR3">
-        <v>117.626716799386</v>
+        <v>117.6267165439083</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -11120,40 +11120,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.258854978337083E-10</v>
+        <v>3.259502443172876E-10</v>
       </c>
       <c r="O4">
-        <v>-3.875278848163512E-10</v>
+        <v>-3.875880824242028E-10</v>
       </c>
       <c r="P4">
-        <v>-4.577837304968773E-10</v>
+        <v>-4.577137029525269E-10</v>
       </c>
       <c r="Q4">
-        <v>-3.258854973823371E-10</v>
+        <v>-3.259502444674736E-10</v>
       </c>
       <c r="R4">
-        <v>3.87527886318147E-10</v>
+        <v>3.875880826006677E-10</v>
       </c>
       <c r="S4">
-        <v>4.577837319380153E-10</v>
+        <v>4.577137039117779E-10</v>
       </c>
       <c r="T4">
-        <v>4.686226424031576E-11</v>
+        <v>4.703113966967243E-11</v>
       </c>
       <c r="U4">
-        <v>-3.246219092727981E-10</v>
+        <v>-3.247526559626173E-10</v>
       </c>
       <c r="V4">
-        <v>1.620752434302988E-10</v>
+        <v>1.6238560150611E-10</v>
       </c>
       <c r="W4">
-        <v>-4.686226393536429E-11</v>
+        <v>-4.703113977211255E-11</v>
       </c>
       <c r="X4">
-        <v>3.246219102874284E-10</v>
+        <v>3.247526569629696E-10</v>
       </c>
       <c r="Y4">
-        <v>-1.620752424566496E-10</v>
+        <v>-1.623856017381185E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -11174,40 +11174,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.175551542840023</v>
+        <v>1.175551542843638</v>
       </c>
       <c r="AH4">
-        <v>0.9895500080917368</v>
+        <v>0.9895500080807462</v>
       </c>
       <c r="AI4">
-        <v>0.9703978075013853</v>
+        <v>0.970397807507736</v>
       </c>
       <c r="AJ4">
-        <v>1.175551541089819</v>
+        <v>1.175551543426463</v>
       </c>
       <c r="AK4">
-        <v>0.9895500116206339</v>
+        <v>0.9895500096027258</v>
       </c>
       <c r="AL4">
-        <v>0.9703978095666783</v>
+        <v>0.9703978094690828</v>
       </c>
       <c r="AM4">
-        <v>-0.5663007758389043</v>
+        <v>-0.566300775188825</v>
       </c>
       <c r="AN4">
-        <v>-115.3347105745257</v>
+        <v>-115.3347105747327</v>
       </c>
       <c r="AO4">
-        <v>117.6267165243296</v>
+        <v>117.626716523923</v>
       </c>
       <c r="AP4">
-        <v>-0.5663008171874508</v>
+        <v>-0.566300761280594</v>
       </c>
       <c r="AQ4">
-        <v>-115.3347105956718</v>
+        <v>-115.3347105006915</v>
       </c>
       <c r="AR4">
-        <v>117.6267166893635</v>
+        <v>117.6267165359654</v>
       </c>
     </row>
   </sheetData>
@@ -11359,106 +11359,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.815799829980768E-05</v>
+        <v>2.815800147135805E-05</v>
       </c>
       <c r="C2">
-        <v>0.1857545467404366</v>
+        <v>0.1857545467380017</v>
       </c>
       <c r="D2">
-        <v>0.1856519121820666</v>
+        <v>0.185651912182109</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1857788391849013</v>
+        <v>0.1857788391824663</v>
       </c>
       <c r="G2">
-        <v>0.1856240701755072</v>
+        <v>0.1856240701755507</v>
       </c>
       <c r="H2">
-        <v>6.502811256193434E-06</v>
+        <v>6.502811988631629E-06</v>
       </c>
       <c r="I2">
-        <v>0.04289817566474783</v>
+        <v>0.04289817566418549</v>
       </c>
       <c r="J2">
-        <v>0.04287447322843341</v>
+        <v>0.04287447322844318</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.0429037857645718</v>
+        <v>0.04290378576400948</v>
       </c>
       <c r="M2">
-        <v>0.04286804339234485</v>
+        <v>0.04286804339235488</v>
       </c>
       <c r="N2">
-        <v>2.493384798639107E-09</v>
+        <v>2.492913487976058E-09</v>
       </c>
       <c r="O2">
-        <v>0.04074588678960204</v>
+        <v>0.04074588678907138</v>
       </c>
       <c r="P2">
-        <v>0.03183261165468244</v>
+        <v>0.03183261165420587</v>
       </c>
       <c r="Q2">
-        <v>-4.412846012015138E-09</v>
+        <v>-4.412216741596518E-09</v>
       </c>
       <c r="R2">
-        <v>4.519871800285663E-16</v>
+        <v>-1.730326926549705E-12</v>
       </c>
       <c r="S2">
-        <v>-5.291165543385033E-16</v>
+        <v>1.268021566640943E-12</v>
       </c>
       <c r="T2">
-        <v>-6.177671611605192E-06</v>
+        <v>-6.177672307612083E-06</v>
       </c>
       <c r="U2">
-        <v>0.0001989371971629443</v>
+        <v>0.0001989371966399922</v>
       </c>
       <c r="V2">
-        <v>0.02533688277499364</v>
+        <v>0.02533688277560583</v>
       </c>
       <c r="W2">
-        <v>-3.715620344186264E-12</v>
+        <v>-2.787389771112702E-12</v>
       </c>
       <c r="X2">
-        <v>-4.887443807359602E-16</v>
+        <v>3.259888470058415E-13</v>
       </c>
       <c r="Y2">
-        <v>9.339665251671162E-17</v>
+        <v>-1.108504204888074E-12</v>
       </c>
       <c r="Z2">
-        <v>89.97687331892793</v>
+        <v>89.97687769277734</v>
       </c>
       <c r="AA2">
-        <v>-120.3714053657915</v>
+        <v>-120.3714053650587</v>
       </c>
       <c r="AB2">
-        <v>81.41626773202677</v>
+        <v>81.41626773093547</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>59.63298636917383</v>
+        <v>59.63298636990584</v>
       </c>
       <c r="AE2">
-        <v>-98.58503063643305</v>
+        <v>-98.58503063752387</v>
       </c>
       <c r="AG2">
-        <v>0.9500002185826794</v>
+        <v>0.9500002185827071</v>
       </c>
       <c r="AH2">
-        <v>0.9498392833615741</v>
+        <v>0.9498392833615957</v>
       </c>
       <c r="AI2">
-        <v>0.9489339644729822</v>
+        <v>0.9489339644729611</v>
       </c>
       <c r="AJ2">
-        <v>1.26670245020399</v>
+        <v>1.266702450203551</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -11467,16 +11467,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.395865785063789E-06</v>
+        <v>-1.395864881045177E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.0916674065643</v>
+        <v>-120.0916674065632</v>
       </c>
       <c r="AO2">
-        <v>119.9339901159923</v>
+        <v>119.9339901159936</v>
       </c>
       <c r="AP2">
-        <v>-0.01608258479774103</v>
+        <v>-0.01608258626588589</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -11526,40 +11526,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.470948619159509E-09</v>
+        <v>1.47041167470567E-09</v>
       </c>
       <c r="O3">
-        <v>3.644164256459583E-23</v>
+        <v>-1.403271361998119E-19</v>
       </c>
       <c r="P3">
-        <v>-2.887491231250083E-23</v>
+        <v>2.435759485127385E-20</v>
       </c>
       <c r="Q3">
-        <v>-1.470948594328508E-09</v>
+        <v>-1.470411682971107E-09</v>
       </c>
       <c r="R3">
-        <v>2.234282431993338E-16</v>
+        <v>1.437278589789393E-16</v>
       </c>
       <c r="S3">
-        <v>2.234283084242234E-16</v>
+        <v>2.039932782656063E-16</v>
       </c>
       <c r="T3">
-        <v>1.238554778378351E-12</v>
+        <v>3.55303608165335E-13</v>
       </c>
       <c r="U3">
-        <v>-3.991511492478158E-23</v>
+        <v>2.739515573488017E-20</v>
       </c>
       <c r="V3">
-        <v>3.274690399988286E-23</v>
+        <v>-1.346675024647419E-19</v>
       </c>
       <c r="W3">
-        <v>-1.238546040823065E-12</v>
+        <v>-3.553065409913212E-13</v>
       </c>
       <c r="X3">
-        <v>7.862018586884352E-17</v>
+        <v>1.471472740983953E-16</v>
       </c>
       <c r="Y3">
-        <v>7.862011358297108E-17</v>
+        <v>-2.471358778134156E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.26670245020399</v>
+        <v>1.266702450203551</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.266702428814537</v>
+        <v>1.266702457324514</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01608258479774103</v>
+        <v>-0.01608258626588589</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01608292432473087</v>
+        <v>-0.01608247206378129</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -11657,40 +11657,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.470948663104199E-09</v>
+        <v>1.469835968520958E-09</v>
       </c>
       <c r="O4">
-        <v>3.64416434643903E-23</v>
+        <v>-1.403136671171927E-19</v>
       </c>
       <c r="P4">
-        <v>-2.887491278602281E-23</v>
+        <v>2.437210929449926E-20</v>
       </c>
       <c r="Q4">
-        <v>-1.470948648205597E-09</v>
+        <v>-1.469835973476945E-09</v>
       </c>
       <c r="R4">
-        <v>1.340569395290867E-16</v>
+        <v>8.628290277485482E-17</v>
       </c>
       <c r="S4">
-        <v>1.340570040523413E-16</v>
+        <v>1.223891180739029E-16</v>
       </c>
       <c r="T4">
-        <v>1.238544511610039E-12</v>
+        <v>1.507524418056739E-12</v>
       </c>
       <c r="U4">
-        <v>-3.991511634380676E-23</v>
+        <v>2.73916795972132E-20</v>
       </c>
       <c r="V4">
-        <v>3.274690513797906E-23</v>
+        <v>-1.346708200729214E-19</v>
       </c>
       <c r="W4">
-        <v>-1.238539269076544E-12</v>
+        <v>-1.507526183399194E-12</v>
       </c>
       <c r="X4">
-        <v>4.717213055008288E-17</v>
+        <v>8.827280600333895E-17</v>
       </c>
       <c r="Y4">
-        <v>4.717205748377431E-17</v>
+        <v>-1.475622742139845E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -11711,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.26670245020399</v>
+        <v>1.266702450203551</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.266702437370318</v>
+        <v>1.266702454476169</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -11729,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01608258479774103</v>
+        <v>-0.01608258626588589</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01608278851394411</v>
+        <v>-0.01608251764916291</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -12118,106 +12118,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.667581696121961E-05</v>
+        <v>2.667581798880602E-05</v>
       </c>
       <c r="C2">
-        <v>0.1759831158221213</v>
+        <v>0.1759831158217295</v>
       </c>
       <c r="D2">
-        <v>0.1758896612363697</v>
+        <v>0.1758896612358108</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.176006130966592</v>
+        <v>0.1760061309661993</v>
       </c>
       <c r="G2">
-        <v>0.1758632844032374</v>
+        <v>0.1758632844026798</v>
       </c>
       <c r="H2">
-        <v>6.160516133164174E-06</v>
+        <v>6.160516370475094E-06</v>
       </c>
       <c r="I2">
-        <v>0.04064156032269876</v>
+        <v>0.04064156032260827</v>
       </c>
       <c r="J2">
-        <v>0.04061997791028089</v>
+        <v>0.0406199779101518</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.0406468754427202</v>
+        <v>0.0406468754426295</v>
       </c>
       <c r="M2">
-        <v>0.0406138864415064</v>
+        <v>0.04061388644137763</v>
       </c>
       <c r="N2">
-        <v>2.318119225770059E-09</v>
+        <v>2.318364822005402E-09</v>
       </c>
       <c r="O2">
-        <v>0.03657110904887385</v>
+        <v>0.03657110904879374</v>
       </c>
       <c r="P2">
-        <v>0.02857356043760409</v>
+        <v>0.02857356043727723</v>
       </c>
       <c r="Q2">
-        <v>-3.960626794196261E-09</v>
+        <v>-3.960954041082739E-09</v>
       </c>
       <c r="R2">
-        <v>4.413132451631428E-16</v>
+        <v>-6.836551437661884E-13</v>
       </c>
       <c r="S2">
-        <v>-5.340861135412923E-16</v>
+        <v>3.60155977108518E-13</v>
       </c>
       <c r="T2">
-        <v>-5.544465162839658E-06</v>
+        <v>-5.544465376316904E-06</v>
       </c>
       <c r="U2">
-        <v>0.0001783468840068613</v>
+        <v>0.0001783468838038454</v>
       </c>
       <c r="V2">
-        <v>0.02274197521224174</v>
+        <v>0.02274197521246558</v>
       </c>
       <c r="W2">
-        <v>-3.248766675261859E-12</v>
+        <v>-2.963618361934279E-12</v>
       </c>
       <c r="X2">
-        <v>-2.801680493522472E-16</v>
+        <v>6.04518559201211E-13</v>
       </c>
       <c r="Y2">
-        <v>2.454595616122796E-16</v>
+        <v>-9.818502315708245E-13</v>
       </c>
       <c r="Z2">
-        <v>89.97604353721616</v>
+        <v>89.97604100017897</v>
       </c>
       <c r="AA2">
-        <v>-120.3662583688438</v>
+        <v>-120.3662583685262</v>
       </c>
       <c r="AB2">
-        <v>81.42083610512987</v>
+        <v>81.42083610453656</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>59.63813242684066</v>
+        <v>59.63813242715781</v>
       </c>
       <c r="AE2">
-        <v>-98.58046137920341</v>
+        <v>-98.58046137979656</v>
       </c>
       <c r="AG2">
-        <v>0.9000001830350174</v>
+        <v>0.9000001830350245</v>
       </c>
       <c r="AH2">
-        <v>0.8998558035023149</v>
+        <v>0.8998558035023227</v>
       </c>
       <c r="AI2">
-        <v>0.8990432127325103</v>
+        <v>0.8990432127325031</v>
       </c>
       <c r="AJ2">
-        <v>1.200037948165053</v>
+        <v>1.200037948144886</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -12226,16 +12226,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.322580942546491E-06</v>
+        <v>-1.322581576671179E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.0868453840321</v>
+        <v>-120.086845384032</v>
       </c>
       <c r="AO2">
-        <v>119.9374599885295</v>
+        <v>119.9374599885304</v>
       </c>
       <c r="AP2">
-        <v>-0.01566764921647358</v>
+        <v>-0.01566764980126173</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -12285,40 +12285,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.320208883522416E-09</v>
+        <v>1.320173655322206E-09</v>
       </c>
       <c r="O3">
-        <v>3.568454614212563E-23</v>
+        <v>-5.519966735160973E-20</v>
       </c>
       <c r="P3">
-        <v>-2.148662672396103E-23</v>
+        <v>-2.686769232615675E-20</v>
       </c>
       <c r="Q3">
-        <v>-1.320208861235818E-09</v>
+        <v>-1.320173662736827E-09</v>
       </c>
       <c r="R3">
-        <v>2.005283871526667E-16</v>
+        <v>1.288982811453358E-16</v>
       </c>
       <c r="S3">
-        <v>2.005284433666642E-16</v>
+        <v>1.831205239551055E-16</v>
       </c>
       <c r="T3">
-        <v>1.082935191191215E-12</v>
+        <v>1.09423336091353E-12</v>
       </c>
       <c r="U3">
-        <v>-2.297184762255505E-23</v>
+        <v>4.943480441433746E-20</v>
       </c>
       <c r="V3">
-        <v>4.265350877437339E-23</v>
+        <v>-8.061458289552977E-20</v>
       </c>
       <c r="W3">
-        <v>-1.082927348962972E-12</v>
+        <v>-1.094235997857417E-12</v>
       </c>
       <c r="X3">
-        <v>7.056214656282381E-17</v>
+        <v>1.320492807684945E-16</v>
       </c>
       <c r="Y3">
-        <v>7.056208057900764E-17</v>
+        <v>-2.221648218116586E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -12339,7 +12339,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.200037948165053</v>
+        <v>1.200037948144886</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.200037927901241</v>
+        <v>1.200037954886759</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -12357,7 +12357,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01566764921647358</v>
+        <v>-0.01566764980126173</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01566798876793315</v>
+        <v>-0.01566753562421334</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -12416,40 +12416,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.320208925154817E-09</v>
+        <v>1.319901096746757E-09</v>
       </c>
       <c r="O4">
-        <v>3.56845470583547E-23</v>
+        <v>-5.517875275574615E-20</v>
       </c>
       <c r="P4">
-        <v>-2.148662716243108E-23</v>
+        <v>-2.687186361226065E-20</v>
       </c>
       <c r="Q4">
-        <v>-1.320208911782857E-09</v>
+        <v>-1.319901101196164E-09</v>
       </c>
       <c r="R4">
-        <v>1.203170254167409E-16</v>
+        <v>7.733748327654954E-17</v>
       </c>
       <c r="S4">
-        <v>1.203170822402499E-16</v>
+        <v>1.099024501939822E-16</v>
       </c>
       <c r="T4">
-        <v>1.082926852870434E-12</v>
+        <v>2.185736089193992E-12</v>
       </c>
       <c r="U4">
-        <v>-2.297184862301146E-23</v>
+        <v>4.942017262226742E-20</v>
       </c>
       <c r="V4">
-        <v>4.265351030304819E-23</v>
+        <v>-8.062340467444213E-20</v>
       </c>
       <c r="W4">
-        <v>-1.082922147533181E-12</v>
+        <v>-2.18573767692565E-12</v>
       </c>
       <c r="X4">
-        <v>4.233729959339964E-17</v>
+        <v>7.918952376285492E-17</v>
       </c>
       <c r="Y4">
-        <v>4.233723405017668E-17</v>
+        <v>-1.328459184983838E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -12470,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.200037948165053</v>
+        <v>1.200037948144886</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -12479,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.200037936006766</v>
+        <v>1.200037952192612</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -12488,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01566764921647358</v>
+        <v>-0.01566764980126173</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -12497,7 +12497,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.0156678529473585</v>
+        <v>-0.01566758119921979</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -12655,130 +12655,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>8.819641334616266E-06</v>
+        <v>8.819642279069315E-06</v>
       </c>
       <c r="C2">
-        <v>0.02688439965621702</v>
+        <v>0.02688439965680764</v>
       </c>
       <c r="D2">
-        <v>0.02530466707311321</v>
+        <v>0.02530466707326734</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02689030206328891</v>
+        <v>0.0268903020638799</v>
       </c>
       <c r="G2">
-        <v>0.02529585138857301</v>
+        <v>0.02529585138872676</v>
       </c>
       <c r="H2">
-        <v>2.036808949829479E-06</v>
+        <v>2.036809167941571E-06</v>
       </c>
       <c r="I2">
-        <v>0.006208686243923985</v>
+        <v>0.006208686244060382</v>
       </c>
       <c r="J2">
-        <v>0.005843862625646647</v>
+        <v>0.005843862625682241</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.006210049346469026</v>
+        <v>0.00621004934660551</v>
       </c>
       <c r="M2">
-        <v>0.005841826730479359</v>
+        <v>0.005841826730514865</v>
       </c>
       <c r="N2">
-        <v>5.94061671838671E-07</v>
+        <v>5.940615807170564E-07</v>
       </c>
       <c r="O2">
-        <v>0.004780850115175092</v>
+        <v>0.004780850115287156</v>
       </c>
       <c r="P2">
-        <v>0.003847208742554174</v>
+        <v>0.003847208742515909</v>
       </c>
       <c r="Q2">
-        <v>-1.09456334666575E-09</v>
+        <v>-1.094455170484862E-09</v>
       </c>
       <c r="R2">
-        <v>-0.003615443095887362</v>
+        <v>-0.003615443095946794</v>
       </c>
       <c r="S2">
-        <v>-0.003199400327605042</v>
+        <v>-0.003199400327557027</v>
       </c>
       <c r="T2">
-        <v>-1.841519553326331E-06</v>
+        <v>-1.841519800442879E-06</v>
       </c>
       <c r="U2">
-        <v>0.003452839765571285</v>
+        <v>0.003452839765637365</v>
       </c>
       <c r="V2">
-        <v>0.004001174557696117</v>
+        <v>0.004001174557779787</v>
       </c>
       <c r="W2">
-        <v>-3.189639205002925E-10</v>
+        <v>-3.186952573716337E-10</v>
       </c>
       <c r="X2">
-        <v>-0.003615442762496931</v>
+        <v>-0.003615442762587669</v>
       </c>
       <c r="Y2">
-        <v>-0.003199401980798927</v>
+        <v>-0.003199401980851612</v>
       </c>
       <c r="Z2">
-        <v>72.12065050113929</v>
+        <v>72.12065531551482</v>
       </c>
       <c r="AA2">
-        <v>-155.8476646493833</v>
+        <v>-155.8476646492665</v>
       </c>
       <c r="AB2">
-        <v>73.86838421690516</v>
+        <v>73.86838421602192</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>24.16630047508555</v>
+        <v>24.16630047520236</v>
       </c>
       <c r="AE2">
-        <v>-106.131017210296</v>
+        <v>-106.1310172111792</v>
       </c>
       <c r="AG2">
-        <v>0.9500000545766535</v>
+        <v>0.950000054576663</v>
       </c>
       <c r="AH2">
-        <v>0.9498532728913167</v>
+        <v>0.9498532728913138</v>
       </c>
       <c r="AI2">
-        <v>0.9498362963282797</v>
+        <v>0.9498362963282767</v>
       </c>
       <c r="AJ2">
-        <v>1.044830778216592</v>
+        <v>1.044830778223755</v>
       </c>
       <c r="AK2">
-        <v>0.8233442504537678</v>
+        <v>0.8233442504527714</v>
       </c>
       <c r="AL2">
-        <v>0.7745242562806133</v>
+        <v>0.7745242562764713</v>
       </c>
       <c r="AM2">
-        <v>-1.751331689969017E-06</v>
+        <v>-1.751331540518259E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.0099835670892</v>
+        <v>-120.0099835670895</v>
       </c>
       <c r="AO2">
-        <v>119.9922411522931</v>
+        <v>119.9922411522932</v>
       </c>
       <c r="AP2">
-        <v>-1.674031931173209</v>
+        <v>-1.674031931552178</v>
       </c>
       <c r="AQ2">
-        <v>-110.8337021666136</v>
+        <v>-110.8337021662487</v>
       </c>
       <c r="AR2">
-        <v>118.8689975926264</v>
+        <v>118.8689975926449</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -12822,40 +12822,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.648544344347026E-10</v>
+        <v>3.649407735208276E-10</v>
       </c>
       <c r="O3">
-        <v>-3.457408960458002E-10</v>
+        <v>-3.457026971344105E-10</v>
       </c>
       <c r="P3">
-        <v>-4.978117916403798E-10</v>
+        <v>-4.979036576776982E-10</v>
       </c>
       <c r="Q3">
-        <v>-3.648544319986172E-10</v>
+        <v>-3.649407743319878E-10</v>
       </c>
       <c r="R3">
-        <v>3.457409049626955E-10</v>
+        <v>3.457026996813229E-10</v>
       </c>
       <c r="S3">
-        <v>4.978117993343417E-10</v>
+        <v>4.979036619986679E-10</v>
       </c>
       <c r="T3">
-        <v>1.063213077595405E-10</v>
+        <v>1.064256789095103E-10</v>
       </c>
       <c r="U3">
-        <v>-4.568710480404257E-10</v>
+        <v>-4.569215639391241E-10</v>
       </c>
       <c r="V3">
-        <v>5.32528213565647E-11</v>
+        <v>5.335003580385775E-11</v>
       </c>
       <c r="W3">
-        <v>-1.063213069023286E-10</v>
+        <v>-1.064256791982231E-10</v>
       </c>
       <c r="X3">
-        <v>4.568710511781109E-10</v>
+        <v>4.569215687566134E-10</v>
       </c>
       <c r="Y3">
-        <v>-5.325281864920639E-11</v>
+        <v>-5.335003820201892E-11</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -12876,40 +12876,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.044830778216592</v>
+        <v>1.044830778223755</v>
       </c>
       <c r="AH3">
-        <v>0.8233442504537678</v>
+        <v>0.8233442504527714</v>
       </c>
       <c r="AI3">
-        <v>0.7745242562806133</v>
+        <v>0.7745242562764713</v>
       </c>
       <c r="AJ3">
-        <v>1.044830771127078</v>
+        <v>1.044830780586254</v>
       </c>
       <c r="AK3">
-        <v>0.8233442617816964</v>
+        <v>0.8233442581816365</v>
       </c>
       <c r="AL3">
-        <v>0.7745242676703828</v>
+        <v>0.7745242633169344</v>
       </c>
       <c r="AM3">
-        <v>-1.674031931173209</v>
+        <v>-1.674031931552178</v>
       </c>
       <c r="AN3">
-        <v>-110.8337021666136</v>
+        <v>-110.8337021662487</v>
       </c>
       <c r="AO3">
-        <v>118.8689975926264</v>
+        <v>118.8689975926449</v>
       </c>
       <c r="AP3">
-        <v>-1.674031952496938</v>
+        <v>-1.6740319240051</v>
       </c>
       <c r="AQ3">
-        <v>-110.8337026883206</v>
+        <v>-110.833702078691</v>
       </c>
       <c r="AR3">
-        <v>118.8689979943627</v>
+        <v>118.8689973724845</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -12953,40 +12953,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.648544471343846E-10</v>
+        <v>3.649605623226093E-10</v>
       </c>
       <c r="O4">
-        <v>-3.457409105859489E-10</v>
+        <v>-3.45704115996346E-10</v>
       </c>
       <c r="P4">
-        <v>-4.978118069191295E-10</v>
+        <v>-4.979461705267414E-10</v>
       </c>
       <c r="Q4">
-        <v>-3.648544456727333E-10</v>
+        <v>-3.649605628092668E-10</v>
       </c>
       <c r="R4">
-        <v>3.457409159360864E-10</v>
+        <v>3.457041175242089E-10</v>
       </c>
       <c r="S4">
-        <v>4.978118115355069E-10</v>
+        <v>4.979461731194599E-10</v>
       </c>
       <c r="T4">
-        <v>1.063213079928057E-10</v>
+        <v>1.064251005682095E-10</v>
       </c>
       <c r="U4">
-        <v>-4.568710588080777E-10</v>
+        <v>-4.568375642951247E-10</v>
       </c>
       <c r="V4">
-        <v>5.325282495134314E-11</v>
+        <v>5.342714628344653E-11</v>
       </c>
       <c r="W4">
-        <v>-1.063213074784785E-10</v>
+        <v>-1.064251007414339E-10</v>
       </c>
       <c r="X4">
-        <v>4.568710606906889E-10</v>
+        <v>4.568375671852158E-10</v>
       </c>
       <c r="Y4">
-        <v>-5.325282332692805E-11</v>
+        <v>-5.34271477226331E-11</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -13007,40 +13007,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.044830778216592</v>
+        <v>1.044830778223755</v>
       </c>
       <c r="AH4">
-        <v>0.8233442504537678</v>
+        <v>0.8233442504527714</v>
       </c>
       <c r="AI4">
-        <v>0.7745242562806133</v>
+        <v>0.7745242562764713</v>
       </c>
       <c r="AJ4">
-        <v>1.044830773962883</v>
+        <v>1.044830779641078</v>
       </c>
       <c r="AK4">
-        <v>0.8233442572505252</v>
+        <v>0.8233442550898493</v>
       </c>
       <c r="AL4">
-        <v>0.7745242631144751</v>
+        <v>0.7745242605008386</v>
       </c>
       <c r="AM4">
-        <v>-1.674031931173209</v>
+        <v>-1.674031931552178</v>
       </c>
       <c r="AN4">
-        <v>-110.8337021666136</v>
+        <v>-110.8337021662487</v>
       </c>
       <c r="AO4">
-        <v>118.8689975926264</v>
+        <v>118.8689975926449</v>
       </c>
       <c r="AP4">
-        <v>-1.674031943967448</v>
+        <v>-1.674031927021755</v>
       </c>
       <c r="AQ4">
-        <v>-110.8337024796378</v>
+        <v>-110.8337021136804</v>
       </c>
       <c r="AR4">
-        <v>118.8689978336682</v>
+        <v>118.8689974605757</v>
       </c>
     </row>
   </sheetData>
@@ -13192,130 +13192,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>8.355336350723607E-06</v>
+        <v>8.355337188473405E-06</v>
       </c>
       <c r="C2">
-        <v>0.02546964310213707</v>
+        <v>0.0254696431020716</v>
       </c>
       <c r="D2">
-        <v>0.02397306401576239</v>
+        <v>0.02397306401569589</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02547523506064291</v>
+        <v>0.02547523506057757</v>
       </c>
       <c r="G2">
-        <v>0.02396471243897198</v>
+        <v>0.02396471243890582</v>
       </c>
       <c r="H2">
-        <v>1.929582305257073E-06</v>
+        <v>1.929582498727104E-06</v>
       </c>
       <c r="I2">
-        <v>0.00588196220812108</v>
+        <v>0.00588196220810596</v>
       </c>
       <c r="J2">
-        <v>0.005536342067618144</v>
+        <v>0.005536342067602786</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.00588325361563978</v>
+        <v>0.005883253615624691</v>
       </c>
       <c r="M2">
-        <v>0.005534413353546161</v>
+        <v>0.005534413353530883</v>
       </c>
       <c r="N2">
-        <v>5.332269245808313E-07</v>
+        <v>5.332270250579398E-07</v>
       </c>
       <c r="O2">
-        <v>0.004290916274439682</v>
+        <v>0.004290916274472246</v>
       </c>
       <c r="P2">
-        <v>0.00345296021923856</v>
+        <v>0.00345296021914371</v>
       </c>
       <c r="Q2">
-        <v>-9.823875545747418E-10</v>
+        <v>-9.824931198183375E-10</v>
       </c>
       <c r="R2">
-        <v>-0.003244939237188713</v>
+        <v>-0.003244939237263409</v>
       </c>
       <c r="S2">
-        <v>-0.002871537068080113</v>
+        <v>-0.002871537067979098</v>
       </c>
       <c r="T2">
-        <v>-1.652734843834569E-06</v>
+        <v>-1.652734994378491E-06</v>
       </c>
       <c r="U2">
-        <v>0.003098998973980248</v>
+        <v>0.003098998973911946</v>
       </c>
       <c r="V2">
-        <v>0.003591147043464608</v>
+        <v>0.003591147043536619</v>
       </c>
       <c r="W2">
-        <v>-2.862677591107976E-10</v>
+        <v>-2.860989328627122E-10</v>
       </c>
       <c r="X2">
-        <v>-0.003244938937830075</v>
+        <v>-0.003244938937770458</v>
       </c>
       <c r="Y2">
-        <v>-0.00287153855173997</v>
+        <v>-0.002871538551835956</v>
       </c>
       <c r="Z2">
-        <v>72.11858091570839</v>
+        <v>72.11857928589733</v>
       </c>
       <c r="AA2">
-        <v>-155.8471452576395</v>
+        <v>-155.8471452568338</v>
       </c>
       <c r="AB2">
-        <v>73.86880136861825</v>
+        <v>73.86880136725814</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>24.16681899276954</v>
+        <v>24.16681899357397</v>
       </c>
       <c r="AE2">
-        <v>-106.1305992058544</v>
+        <v>-106.1305992072141</v>
       </c>
       <c r="AG2">
-        <v>0.9000000358384317</v>
+        <v>0.900000035838437</v>
       </c>
       <c r="AH2">
-        <v>0.8998682978314761</v>
+        <v>0.8998682978314786</v>
       </c>
       <c r="AI2">
-        <v>0.8998530607498658</v>
+        <v>0.8998530607498636</v>
       </c>
       <c r="AJ2">
-        <v>0.9898404736896618</v>
+        <v>0.9898404736840074</v>
       </c>
       <c r="AK2">
-        <v>0.7800168353155935</v>
+        <v>0.7800168353194068</v>
       </c>
       <c r="AL2">
-        <v>0.7337666083506387</v>
+        <v>0.7337666083520219</v>
       </c>
       <c r="AM2">
-        <v>-1.659271100274987E-06</v>
+        <v>-1.659271374716177E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.009458194112</v>
+        <v>-120.0094581941121</v>
       </c>
       <c r="AO2">
-        <v>119.9926494432283</v>
+        <v>119.9926494432285</v>
       </c>
       <c r="AP2">
-        <v>-1.674003896734075</v>
+        <v>-1.674003897119532</v>
       </c>
       <c r="AQ2">
-        <v>-110.8331836501077</v>
+        <v>-110.833183650489</v>
       </c>
       <c r="AR2">
-        <v>118.8694155958653</v>
+        <v>118.869415596471</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -13359,40 +13359,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.274625047398927E-10</v>
+        <v>3.275630472289105E-10</v>
       </c>
       <c r="O3">
-        <v>-3.102851157813419E-10</v>
+        <v>-3.103021775460753E-10</v>
       </c>
       <c r="P3">
-        <v>-4.467757187533563E-10</v>
+        <v>-4.467886013483856E-10</v>
       </c>
       <c r="Q3">
-        <v>-3.274625025534597E-10</v>
+        <v>-3.275630479567355E-10</v>
       </c>
       <c r="R3">
-        <v>3.102851237844688E-10</v>
+        <v>3.103021798329173E-10</v>
       </c>
       <c r="S3">
-        <v>4.467757256581343E-10</v>
+        <v>4.467886052251567E-10</v>
       </c>
       <c r="T3">
-        <v>9.542258571360747E-11</v>
+        <v>9.542640758096131E-11</v>
       </c>
       <c r="U3">
-        <v>-4.100713333157701E-10</v>
+        <v>-4.101081667816964E-10</v>
       </c>
       <c r="V3">
-        <v>4.777755378554654E-11</v>
+        <v>4.779562618612316E-11</v>
       </c>
       <c r="W3">
-        <v>-9.54225849442434E-11</v>
+        <v>-9.542640783958208E-11</v>
       </c>
       <c r="X3">
-        <v>4.100713361319177E-10</v>
+        <v>4.101081711049174E-10</v>
       </c>
       <c r="Y3">
-        <v>-4.777755135588699E-11</v>
+        <v>-4.779562833850005E-11</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -13413,40 +13413,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9898404736896618</v>
+        <v>0.9898404736840074</v>
       </c>
       <c r="AH3">
-        <v>0.7800168353155935</v>
+        <v>0.7800168353194068</v>
       </c>
       <c r="AI3">
-        <v>0.7337666083506387</v>
+        <v>0.7337666083520219</v>
       </c>
       <c r="AJ3">
-        <v>0.9898404669732375</v>
+        <v>0.9898404759211776</v>
       </c>
       <c r="AK3">
-        <v>0.7800168460469796</v>
+        <v>0.7800168426413148</v>
       </c>
       <c r="AL3">
-        <v>0.7337666191406523</v>
+        <v>0.7337666150207237</v>
       </c>
       <c r="AM3">
-        <v>-1.674003896734075</v>
+        <v>-1.674003897119532</v>
       </c>
       <c r="AN3">
-        <v>-110.8331836501077</v>
+        <v>-110.833183650489</v>
       </c>
       <c r="AO3">
-        <v>118.8694155958653</v>
+        <v>118.869415596471</v>
       </c>
       <c r="AP3">
-        <v>-1.674003918060595</v>
+        <v>-1.674003889607883</v>
       </c>
       <c r="AQ3">
-        <v>-110.8331841718638</v>
+        <v>-110.8331835630423</v>
       </c>
       <c r="AR3">
-        <v>118.869415997551</v>
+        <v>118.8694153761568</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -13490,40 +13490,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.274625156436558E-10</v>
+        <v>3.274296245469385E-10</v>
       </c>
       <c r="O4">
-        <v>-3.10285127759999E-10</v>
+        <v>-3.103482630369151E-10</v>
       </c>
       <c r="P4">
-        <v>-4.467757298197654E-10</v>
+        <v>-4.468263775654742E-10</v>
       </c>
       <c r="Q4">
-        <v>-3.274625143317958E-10</v>
+        <v>-3.274296249835574E-10</v>
       </c>
       <c r="R4">
-        <v>3.102851325618754E-10</v>
+        <v>3.10348264408816E-10</v>
       </c>
       <c r="S4">
-        <v>4.467757339626324E-10</v>
+        <v>4.468263798921278E-10</v>
       </c>
       <c r="T4">
-        <v>9.54225865401646E-11</v>
+        <v>9.535525363135894E-11</v>
       </c>
       <c r="U4">
-        <v>-4.100713432352533E-10</v>
+        <v>-4.099799355205037E-10</v>
       </c>
       <c r="V4">
-        <v>4.777755979695298E-11</v>
+        <v>4.780655157911781E-11</v>
       </c>
       <c r="W4">
-        <v>-9.542258607854614E-11</v>
+        <v>-9.535525378655907E-11</v>
       </c>
       <c r="X4">
-        <v>4.100713449249418E-10</v>
+        <v>4.099799381140299E-10</v>
       </c>
       <c r="Y4">
-        <v>-4.777755833915716E-11</v>
+        <v>-4.780655286996314E-11</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -13544,40 +13544,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9898404736896618</v>
+        <v>0.9898404736840074</v>
       </c>
       <c r="AH4">
-        <v>0.7800168353155935</v>
+        <v>0.7800168353194068</v>
       </c>
       <c r="AI4">
-        <v>0.7337666083506387</v>
+        <v>0.7337666083520219</v>
       </c>
       <c r="AJ4">
-        <v>0.9898404696598071</v>
+        <v>0.9898404750266954</v>
       </c>
       <c r="AK4">
-        <v>0.7800168417544253</v>
+        <v>0.7800168397123501</v>
       </c>
       <c r="AL4">
-        <v>0.733766614824647</v>
+        <v>0.7337666123537822</v>
       </c>
       <c r="AM4">
-        <v>-1.674003896734075</v>
+        <v>-1.674003897119532</v>
       </c>
       <c r="AN4">
-        <v>-110.8331836501077</v>
+        <v>-110.833183650489</v>
       </c>
       <c r="AO4">
-        <v>118.8694155958653</v>
+        <v>118.869415596471</v>
       </c>
       <c r="AP4">
-        <v>-1.674003909529989</v>
+        <v>-1.674003892595486</v>
       </c>
       <c r="AQ4">
-        <v>-110.8331839631614</v>
+        <v>-110.8331835979509</v>
       </c>
       <c r="AR4">
-        <v>118.8694158368767</v>
+        <v>118.8694154643803</v>
       </c>
     </row>
   </sheetData>
@@ -14839,127 +14839,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3396014977798925</v>
+        <v>0.3396014977829826</v>
       </c>
       <c r="D2">
-        <v>0.3396014977798923</v>
+        <v>0.3396014977847441</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3396014977798925</v>
+        <v>0.3396014977829823</v>
       </c>
       <c r="G2">
-        <v>0.3396014977798923</v>
+        <v>0.3396014977847445</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.07842760763283083</v>
+        <v>0.07842760763354445</v>
       </c>
       <c r="J2">
-        <v>0.07842760763283078</v>
+        <v>0.07842760763395126</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.07842760763283083</v>
+        <v>0.07842760763354438</v>
       </c>
       <c r="M2">
-        <v>0.07842760763283077</v>
+        <v>0.07842760763395133</v>
       </c>
       <c r="N2">
-        <v>-2.42861275607684E-18</v>
+        <v>-1.800014916421485E-13</v>
       </c>
       <c r="O2">
-        <v>0.08211242437846838</v>
+        <v>0.08211242437925247</v>
       </c>
       <c r="P2">
-        <v>0.03586932765070251</v>
+        <v>0.03586932765169212</v>
       </c>
       <c r="Q2">
-        <v>2.42861275607684E-18</v>
+        <v>1.79950490779076E-13</v>
       </c>
       <c r="R2">
-        <v>-0.02312154836388518</v>
+        <v>-0.02312154836354323</v>
       </c>
       <c r="S2">
-        <v>0.02312154836388059</v>
+        <v>0.02312154836452414</v>
       </c>
       <c r="T2">
-        <v>-4.990900718775215E-35</v>
+        <v>6.371708426843075E-13</v>
       </c>
       <c r="U2">
-        <v>0.005785376091549832</v>
+        <v>0.005785376091091064</v>
       </c>
       <c r="V2">
-        <v>0.07392443402538297</v>
+        <v>0.07392443402620519</v>
       </c>
       <c r="W2">
-        <v>-2.428612756076838E-18</v>
+        <v>-6.371271276504762E-13</v>
       </c>
       <c r="X2">
-        <v>0.03406952896691683</v>
+        <v>0.034069528968334</v>
       </c>
       <c r="Y2">
-        <v>-0.03406952896691642</v>
+        <v>-0.034069528966833</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-124.163079178916</v>
+        <v>-124.1630791785605</v>
       </c>
       <c r="AB2">
-        <v>55.83692082107669</v>
+        <v>55.83692082144574</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>55.83692082107672</v>
+        <v>55.83692082143227</v>
       </c>
       <c r="AE2">
-        <v>-124.163079178916</v>
+        <v>-124.163079178547</v>
       </c>
       <c r="AF2">
-        <v>1.04999995231631</v>
+        <v>1.049999952316291</v>
       </c>
       <c r="AG2">
-        <v>1.04957914701117</v>
+        <v>1.049579147011182</v>
       </c>
       <c r="AH2">
-        <v>1.047680683785271</v>
+        <v>1.047680683785243</v>
       </c>
       <c r="AI2">
-        <v>1.049999952316309</v>
+        <v>1.049999952311919</v>
       </c>
       <c r="AJ2">
-        <v>0.5249999761581737</v>
+        <v>0.5249999761659004</v>
       </c>
       <c r="AK2">
-        <v>0.5249999761581368</v>
+        <v>0.5249999761543634</v>
       </c>
       <c r="AL2">
-        <v>1.177452216040199E-15</v>
+        <v>3.981699153490761E-13</v>
       </c>
       <c r="AM2">
-        <v>-120.13286376229</v>
+        <v>-120.1328637622913</v>
       </c>
       <c r="AN2">
-        <v>119.9535113661724</v>
+        <v>119.953511366171</v>
       </c>
       <c r="AO2">
-        <v>2.616886448728214E-14</v>
+        <v>4.999062121345718E-10</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999999903</v>
+        <v>179.9999999988495</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999999901</v>
+        <v>-179.9999999988201</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -15003,40 +15003,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>9.692294311873643E-23</v>
+        <v>-3.183231311631726E-13</v>
       </c>
       <c r="O3">
-        <v>-3.885787813128837E-17</v>
+        <v>3.492530161231259E-20</v>
       </c>
       <c r="P3">
-        <v>3.885772562112693E-17</v>
+        <v>1.591616014037735E-13</v>
       </c>
       <c r="Q3">
-        <v>-9.692294311873643E-23</v>
+        <v>3.183231311628396E-13</v>
       </c>
       <c r="R3">
-        <v>1.454756409379394E-16</v>
+        <v>1.065813188655447E-16</v>
       </c>
       <c r="S3">
-        <v>6.776003748137117E-17</v>
+        <v>-1.59054999247111E-13</v>
       </c>
       <c r="T3">
-        <v>-1.846340086368193E-24</v>
+        <v>-2.777372296650053E-24</v>
       </c>
       <c r="U3">
-        <v>1.750453628183988E-09</v>
+        <v>1.750458898299431E-09</v>
       </c>
       <c r="V3">
-        <v>-1.75045363304109E-09</v>
+        <v>-1.75029973669538E-09</v>
       </c>
       <c r="W3">
-        <v>1.846340086368193E-24</v>
+        <v>2.581404108473346E-24</v>
       </c>
       <c r="X3">
-        <v>-1.750453556151818E-09</v>
+        <v>-1.750458826273515E-09</v>
       </c>
       <c r="Y3">
-        <v>1.75045370507326E-09</v>
+        <v>1.750299808720779E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -15057,40 +15057,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.049999952316309</v>
+        <v>1.049999952311919</v>
       </c>
       <c r="AG3">
-        <v>0.5249999761581737</v>
+        <v>0.5249999761659004</v>
       </c>
       <c r="AH3">
-        <v>0.5249999761581368</v>
+        <v>0.5249999761543634</v>
       </c>
       <c r="AI3">
-        <v>1.049999952316309</v>
+        <v>1.049999952310821</v>
       </c>
       <c r="AJ3">
-        <v>0.5249999545541256</v>
+        <v>0.5249999545637923</v>
       </c>
       <c r="AK3">
-        <v>0.5249999977621869</v>
+        <v>0.5249999977553751</v>
       </c>
       <c r="AL3">
-        <v>2.616886448728214E-14</v>
+        <v>4.999062121345718E-10</v>
       </c>
       <c r="AM3">
-        <v>-179.9999999999903</v>
+        <v>179.9999999988495</v>
       </c>
       <c r="AN3">
-        <v>179.9999999999901</v>
+        <v>-179.9999999988201</v>
       </c>
       <c r="AO3">
-        <v>2.616883092971721E-14</v>
+        <v>4.646334059763535E-10</v>
       </c>
       <c r="AP3">
-        <v>-179.9999965101816</v>
+        <v>-179.9999965113875</v>
       </c>
       <c r="AQ3">
-        <v>179.9999965101818</v>
+        <v>179.9999965113467</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -15134,40 +15134,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>9.692294311873643E-23</v>
+        <v>-3.183231311742821E-13</v>
       </c>
       <c r="O4">
-        <v>-2.428620159482864E-17</v>
+        <v>1.591616005035504E-13</v>
       </c>
       <c r="P4">
-        <v>2.428604908466508E-17</v>
+        <v>3.18323166984876E-13</v>
       </c>
       <c r="Q4">
-        <v>-9.692294311873643E-23</v>
+        <v>3.183231311757008E-13</v>
       </c>
       <c r="R4">
-        <v>8.825686249475197E-17</v>
+        <v>-1.590976442676764E-13</v>
       </c>
       <c r="S4">
-        <v>3.968461109007151E-17</v>
+        <v>-3.182592224931634E-13</v>
       </c>
       <c r="T4">
-        <v>-1.846341604925366E-24</v>
+        <v>1.273292524649913E-12</v>
       </c>
       <c r="U4">
-        <v>1.750453671899018E-09</v>
+        <v>1.750140575168258E-09</v>
       </c>
       <c r="V4">
-        <v>-1.750453662184443E-09</v>
+        <v>-1.750299736695376E-09</v>
       </c>
       <c r="W4">
-        <v>1.846341604925366E-24</v>
+        <v>-1.273292524646662E-12</v>
       </c>
       <c r="X4">
-        <v>-1.750453628679713E-09</v>
+        <v>-1.750140531966844E-09</v>
       </c>
       <c r="Y4">
-        <v>1.750453705403747E-09</v>
+        <v>1.750299779910673E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -15188,40 +15188,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.049999952316309</v>
+        <v>1.049999952311919</v>
       </c>
       <c r="AG4">
-        <v>0.5249999761581737</v>
+        <v>0.5249999761659004</v>
       </c>
       <c r="AH4">
-        <v>0.5249999761581368</v>
+        <v>0.5249999761543634</v>
       </c>
       <c r="AI4">
-        <v>1.049999952316309</v>
+        <v>1.049999952309671</v>
       </c>
       <c r="AJ4">
-        <v>0.524999963195744</v>
+        <v>0.5249999632047733</v>
       </c>
       <c r="AK4">
-        <v>0.524999989120567</v>
+        <v>0.5249999891132434</v>
       </c>
       <c r="AL4">
-        <v>2.616886448728214E-14</v>
+        <v>4.999062121345718E-10</v>
       </c>
       <c r="AM4">
-        <v>-179.9999999999903</v>
+        <v>179.9999999988495</v>
       </c>
       <c r="AN4">
-        <v>179.9999999999901</v>
+        <v>-179.9999999988201</v>
       </c>
       <c r="AO4">
-        <v>2.616884435274268E-14</v>
+        <v>5.944083598049341E-10</v>
       </c>
       <c r="AP4">
-        <v>-179.9999979061051</v>
+        <v>-179.999997907477</v>
       </c>
       <c r="AQ4">
-        <v>179.9999979061051</v>
+        <v>179.9999979076956</v>
       </c>
     </row>
   </sheetData>

--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_branch.xlsx
@@ -955,127 +955,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3557435144214025</v>
+        <v>0.3557435144184714</v>
       </c>
       <c r="D2">
-        <v>0.355743514423176</v>
+        <v>0.3557435144184714</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3557435144214032</v>
+        <v>0.3557435144184714</v>
       </c>
       <c r="G2">
-        <v>0.3557435144231753</v>
+        <v>0.3557435144184714</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.08215544674967563</v>
+        <v>0.08215544674899872</v>
       </c>
       <c r="J2">
-        <v>0.08215544675008522</v>
+        <v>0.08215544674899873</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.08215544674967579</v>
+        <v>0.08215544674899872</v>
       </c>
       <c r="M2">
-        <v>0.08215544675008504</v>
+        <v>0.08215544674899873</v>
       </c>
       <c r="N2">
-        <v>-8.112554785401425E-13</v>
+        <v>-2.544261153244686E-18</v>
       </c>
       <c r="O2">
-        <v>0.0901097316350289</v>
+        <v>0.09010973163428015</v>
       </c>
       <c r="P2">
-        <v>0.03935444973556931</v>
+        <v>0.03935444973466317</v>
       </c>
       <c r="Q2">
-        <v>8.112529342919924E-13</v>
+        <v>5.088522306489369E-18</v>
       </c>
       <c r="R2">
-        <v>-0.02537764094899424</v>
+        <v>-0.02537764094980933</v>
       </c>
       <c r="S2">
-        <v>0.02537764095011651</v>
+        <v>0.0253776409498077</v>
       </c>
       <c r="T2">
-        <v>1.423259689123289E-14</v>
+        <v>5.088522306489372E-18</v>
       </c>
       <c r="U2">
-        <v>0.006347849100782066</v>
+        <v>0.006347849100821007</v>
       </c>
       <c r="V2">
-        <v>0.08111962054156635</v>
+        <v>0.08111962054068335</v>
       </c>
       <c r="W2">
-        <v>-1.447175743614143E-14</v>
+        <v>-5.088522306489369E-18</v>
       </c>
       <c r="X2">
-        <v>0.03738588571998035</v>
+        <v>0.03738588571993093</v>
       </c>
       <c r="Y2">
-        <v>-0.03738588571894726</v>
+        <v>-0.03738588571993143</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-124.168767479727</v>
+        <v>-124.1687674797839</v>
       </c>
       <c r="AB2">
-        <v>55.8312325204807</v>
+        <v>55.83123252020882</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>55.83123252026577</v>
+        <v>55.83123252020884</v>
       </c>
       <c r="AE2">
-        <v>-124.1687674795121</v>
+        <v>-124.1687674797839</v>
       </c>
       <c r="AF2">
-        <v>1.100000023841857</v>
+        <v>1.100000023841855</v>
       </c>
       <c r="AG2">
-        <v>1.099538107887549</v>
+        <v>1.099538107887551</v>
       </c>
       <c r="AH2">
-        <v>1.097454749634792</v>
+        <v>1.097454749634821</v>
       </c>
       <c r="AI2">
-        <v>1.100000023859399</v>
+        <v>1.100000023841855</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119113241</v>
+        <v>0.5500000119209313</v>
       </c>
       <c r="AK2">
-        <v>0.5500000119058521</v>
+        <v>0.550000011920925</v>
       </c>
       <c r="AL2">
-        <v>1.264851143932793E-12</v>
+        <v>1.250975106659675E-15</v>
       </c>
       <c r="AM2">
-        <v>-120.1391793376213</v>
+        <v>-120.1391793376201</v>
       </c>
       <c r="AN2">
-        <v>119.9513097268545</v>
+        <v>119.9513097268558</v>
       </c>
       <c r="AO2">
-        <v>2.645052840876529E-10</v>
+        <v>1.181816298246187E-15</v>
       </c>
       <c r="AP2">
-        <v>179.9999999991604</v>
+        <v>-179.9999999999916</v>
       </c>
       <c r="AQ2">
-        <v>-179.9999999986971</v>
+        <v>179.9999999999917</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -1119,40 +1119,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>6.66962795766812E-13</v>
+        <v>-1.124219233306085E-23</v>
       </c>
       <c r="O3">
-        <v>2.791181703351831E-20</v>
+        <v>-4.070821374148507E-17</v>
       </c>
       <c r="P3">
-        <v>4.343628794092517E-20</v>
+        <v>4.579666624442903E-17</v>
       </c>
       <c r="Q3">
-        <v>-6.669627957654743E-13</v>
+        <v>1.124219233306085E-23</v>
       </c>
       <c r="R3">
-        <v>1.169934726769811E-16</v>
+        <v>1.577218284516093E-16</v>
       </c>
       <c r="S3">
-        <v>1.169504879764412E-16</v>
+        <v>7.121694926396706E-17</v>
       </c>
       <c r="T3">
-        <v>3.079025807300905E-24</v>
+        <v>-9.151354021381658E-26</v>
       </c>
       <c r="U3">
-        <v>1.921353073841052E-09</v>
+        <v>1.921133041081558E-09</v>
       </c>
       <c r="V3">
-        <v>-1.920852851725132E-09</v>
+        <v>-1.921133051258581E-09</v>
       </c>
       <c r="W3">
-        <v>-2.557079240098857E-24</v>
+        <v>9.151354021381658E-26</v>
       </c>
       <c r="X3">
-        <v>-1.921352994780761E-09</v>
+        <v>-1.921132962025833E-09</v>
       </c>
       <c r="Y3">
-        <v>1.920852930757135E-09</v>
+        <v>1.921133130314307E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1173,40 +1173,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.100000023859399</v>
+        <v>1.100000023841855</v>
       </c>
       <c r="AG3">
-        <v>0.5500000119113241</v>
+        <v>0.5500000119209313</v>
       </c>
       <c r="AH3">
-        <v>0.5500000119058521</v>
+        <v>0.550000011920925</v>
       </c>
       <c r="AI3">
-        <v>1.100000023857193</v>
+        <v>1.100000023841855</v>
       </c>
       <c r="AJ3">
-        <v>0.5499999892797947</v>
+        <v>0.5499999892881174</v>
       </c>
       <c r="AK3">
-        <v>0.5500000345351774</v>
+        <v>0.5500000345537409</v>
       </c>
       <c r="AL3">
-        <v>2.645052840876529E-10</v>
+        <v>1.181816298246187E-15</v>
       </c>
       <c r="AM3">
-        <v>179.9999999991604</v>
+        <v>-179.9999999999916</v>
       </c>
       <c r="AN3">
-        <v>-179.9999999986971</v>
+        <v>179.9999999999917</v>
       </c>
       <c r="AO3">
-        <v>2.196671977333139E-10</v>
+        <v>1.181819705995724E-15</v>
       </c>
       <c r="AP3">
-        <v>-179.9999965111844</v>
+        <v>-179.9999965101831</v>
       </c>
       <c r="AQ3">
-        <v>179.9999965115584</v>
+        <v>179.9999965101833</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1250,40 +1250,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-3.079025807300905E-24</v>
+        <v>-1.12421924053731E-23</v>
       </c>
       <c r="O4">
-        <v>-3.334813699725587E-13</v>
+        <v>-1.526560220903871E-17</v>
       </c>
       <c r="P4">
-        <v>4.344382896313714E-20</v>
+        <v>4.070814393793904E-17</v>
       </c>
       <c r="Q4">
-        <v>4.17909662934156E-24</v>
+        <v>1.12421924053731E-23</v>
       </c>
       <c r="R4">
-        <v>3.335515398983665E-13</v>
+        <v>8.547377343038407E-17</v>
       </c>
       <c r="S4">
-        <v>7.015274939498083E-17</v>
+        <v>2.950002857833142E-17</v>
       </c>
       <c r="T4">
-        <v>6.66962795766812E-13</v>
+        <v>-9.151343174543977E-26</v>
       </c>
       <c r="U4">
-        <v>1.920519370346376E-09</v>
+        <v>1.921133076701215E-09</v>
       </c>
       <c r="V4">
-        <v>-1.921186333123001E-09</v>
+        <v>-1.921133086878237E-09</v>
       </c>
       <c r="W4">
-        <v>-6.669627957653841E-13</v>
+        <v>9.151343174543977E-26</v>
       </c>
       <c r="X4">
-        <v>-1.920519322920671E-09</v>
+        <v>-1.921133029267777E-09</v>
       </c>
       <c r="Y4">
-        <v>1.921186380544761E-09</v>
+        <v>1.921133134311674E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1304,40 +1304,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.100000023859399</v>
+        <v>1.100000023841855</v>
       </c>
       <c r="AG4">
-        <v>0.5500000119113241</v>
+        <v>0.5500000119209313</v>
       </c>
       <c r="AH4">
-        <v>0.5500000119058521</v>
+        <v>0.550000011920925</v>
       </c>
       <c r="AI4">
-        <v>1.100000023857044</v>
+        <v>1.100000023841855</v>
       </c>
       <c r="AJ4">
-        <v>0.5499999983329995</v>
+        <v>0.5499999983412421</v>
       </c>
       <c r="AK4">
-        <v>0.5500000254818225</v>
+        <v>0.5500000255006147</v>
       </c>
       <c r="AL4">
-        <v>2.645052840876529E-10</v>
+        <v>1.181816298246187E-15</v>
       </c>
       <c r="AM4">
-        <v>179.9999999991604</v>
+        <v>-179.9999999999916</v>
       </c>
       <c r="AN4">
-        <v>-179.9999999986971</v>
+        <v>179.9999999999917</v>
       </c>
       <c r="AO4">
-        <v>3.59007429738013E-10</v>
+        <v>1.181818342895962E-15</v>
       </c>
       <c r="AP4">
-        <v>-179.9999979071662</v>
+        <v>-179.9999979061065</v>
       </c>
       <c r="AQ4">
-        <v>179.9999979078186</v>
+        <v>179.9999979061066</v>
       </c>
     </row>
   </sheetData>
@@ -1489,127 +1489,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.05066944729294589</v>
+        <v>0.05066944729275168</v>
       </c>
       <c r="D2">
-        <v>0.05066944729320973</v>
+        <v>0.05066944729275168</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.05066944729294586</v>
+        <v>0.05066944729275168</v>
       </c>
       <c r="G2">
-        <v>0.05066944729320977</v>
+        <v>0.05066944729275168</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01170160778807629</v>
+        <v>0.01170160778803144</v>
       </c>
       <c r="J2">
-        <v>0.01170160778813722</v>
+        <v>0.01170160778803144</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01170160778807628</v>
+        <v>0.01170160778803144</v>
       </c>
       <c r="M2">
-        <v>0.01170160778813723</v>
+        <v>0.01170160778803144</v>
       </c>
       <c r="N2">
-        <v>-3.47947349563122E-14</v>
+        <v>1.099977162972809E-36</v>
       </c>
       <c r="O2">
-        <v>0.01195213586582431</v>
+        <v>0.01195213586575931</v>
       </c>
       <c r="P2">
-        <v>0.003511272021260142</v>
+        <v>0.003511272021138653</v>
       </c>
       <c r="Q2">
-        <v>3.478866342451929E-14</v>
+        <v>-1.93179787004859E-36</v>
       </c>
       <c r="R2">
-        <v>-0.0106389143624084</v>
+        <v>-0.01063891436235429</v>
       </c>
       <c r="S2">
-        <v>-0.002198050517832185</v>
+        <v>-0.002198050517733626</v>
       </c>
       <c r="T2">
-        <v>8.854813181634305E-14</v>
+        <v>-3.035765945095988E-19</v>
       </c>
       <c r="U2">
-        <v>0.002841561563852629</v>
+        <v>0.002841561563922337</v>
       </c>
       <c r="V2">
-        <v>0.01176985984613227</v>
+        <v>0.01176985984605268</v>
       </c>
       <c r="W2">
-        <v>-8.854357816734298E-14</v>
+        <v>3.035765945095988E-19</v>
       </c>
       <c r="X2">
-        <v>-0.001954334218276918</v>
+        <v>-0.001954334218357825</v>
       </c>
       <c r="Y2">
-        <v>-0.01088263250055613</v>
+        <v>-0.01088263250048817</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-133.392518428136</v>
+        <v>-133.3925184285223</v>
       </c>
       <c r="AB2">
-        <v>46.60748157190714</v>
+        <v>46.60748157147039</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>46.6074815718567</v>
+        <v>46.60748157147042</v>
       </c>
       <c r="AE2">
-        <v>-133.3925184280856</v>
+        <v>-133.3925184285223</v>
       </c>
       <c r="AF2">
-        <v>1.049999952316286</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="AG2">
-        <v>1.049879378451203</v>
+        <v>1.049879378451201</v>
       </c>
       <c r="AH2">
-        <v>1.049638000241886</v>
+        <v>1.049638000241888</v>
       </c>
       <c r="AI2">
-        <v>1.049999952315831</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="AJ2">
-        <v>0.9243966914071265</v>
+        <v>0.9243966914073701</v>
       </c>
       <c r="AK2">
-        <v>0.9487920434332352</v>
+        <v>0.9487920434344531</v>
       </c>
       <c r="AL2">
-        <v>7.130907144390266E-14</v>
+        <v>2.076050991379067E-16</v>
       </c>
       <c r="AM2">
-        <v>-120.0190081334391</v>
+        <v>-120.019008133439</v>
       </c>
       <c r="AN2">
-        <v>119.9961963746863</v>
+        <v>119.9961963746865</v>
       </c>
       <c r="AO2">
-        <v>7.2754296277823E-11</v>
+        <v>3.645994679034516E-16</v>
       </c>
       <c r="AP2">
-        <v>-122.9835155919812</v>
+        <v>-122.9835155918942</v>
       </c>
       <c r="AQ2">
-        <v>125.188627753316</v>
+        <v>125.1886277533084</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -1653,40 +1653,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-7.958078279098861E-14</v>
+        <v>1.449354072788632E-23</v>
       </c>
       <c r="O3">
-        <v>-4.209092355811138E-10</v>
+        <v>-4.209025870336179E-10</v>
       </c>
       <c r="P3">
-        <v>-3.370295330142179E-10</v>
+        <v>-3.371245645935736E-10</v>
       </c>
       <c r="Q3">
-        <v>7.958078279098437E-14</v>
+        <v>-1.449354072788632E-23</v>
       </c>
       <c r="R3">
-        <v>4.209092379547537E-10</v>
+        <v>4.209025894070821E-10</v>
       </c>
       <c r="S3">
-        <v>3.370295353872489E-10</v>
+        <v>3.37124566967038E-10</v>
       </c>
       <c r="T3">
-        <v>-7.958078279119072E-14</v>
+        <v>-2.572397888128923E-26</v>
       </c>
       <c r="U3">
-        <v>1.852618209050096E-10</v>
+        <v>1.852373033288513E-10</v>
       </c>
       <c r="V3">
-        <v>-3.303887849610429E-10</v>
+        <v>-3.303450918265923E-10</v>
       </c>
       <c r="W3">
-        <v>7.958078279117127E-14</v>
+        <v>2.572397888128923E-26</v>
       </c>
       <c r="X3">
-        <v>-1.852618193016929E-10</v>
+        <v>-1.852373017253119E-10</v>
       </c>
       <c r="Y3">
-        <v>3.30388786564702E-10</v>
+        <v>3.303450934301317E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,40 +1707,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.049999952315831</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="AG3">
-        <v>0.9243966914071265</v>
+        <v>0.9243966914073701</v>
       </c>
       <c r="AH3">
-        <v>0.9487920434332352</v>
+        <v>0.9487920434344531</v>
       </c>
       <c r="AI3">
-        <v>1.049999952315675</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="AJ3">
-        <v>0.9243966944757667</v>
+        <v>0.9243966944758226</v>
       </c>
       <c r="AK3">
-        <v>0.9487920490967608</v>
+        <v>0.9487920490981999</v>
       </c>
       <c r="AL3">
-        <v>7.2754296277823E-11</v>
+        <v>3.645994679034516E-16</v>
       </c>
       <c r="AM3">
-        <v>-122.9835155919812</v>
+        <v>-122.9835155918942</v>
       </c>
       <c r="AN3">
-        <v>125.188627753316</v>
+        <v>125.1886277533084</v>
       </c>
       <c r="AO3">
-        <v>6.728118408410087E-11</v>
+        <v>3.64594574603633E-16</v>
       </c>
       <c r="AP3">
-        <v>-122.9835152900158</v>
+        <v>-122.9835152899099</v>
       </c>
       <c r="AQ3">
-        <v>125.1886276906708</v>
+        <v>125.1886276906917</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1784,40 +1784,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-7.958078279124124E-14</v>
+        <v>1.449354079691164E-23</v>
       </c>
       <c r="O4">
-        <v>-4.208107677346515E-10</v>
+        <v>-4.20902593673137E-10</v>
       </c>
       <c r="P4">
-        <v>-3.369707638073338E-10</v>
+        <v>-3.371245759868557E-10</v>
       </c>
       <c r="Q4">
-        <v>7.95807827912427E-14</v>
+        <v>-1.449354079691164E-23</v>
       </c>
       <c r="R4">
-        <v>4.208107691581386E-10</v>
+        <v>4.209025950972156E-10</v>
       </c>
       <c r="S4">
-        <v>3.369707652306346E-10</v>
+        <v>3.371245774109343E-10</v>
       </c>
       <c r="T4">
-        <v>1.193711741865334E-13</v>
+        <v>-2.572415144460441E-26</v>
       </c>
       <c r="U4">
-        <v>1.851561540323438E-10</v>
+        <v>1.852373127357143E-10</v>
       </c>
       <c r="V4">
-        <v>-3.303473453128637E-10</v>
+        <v>-3.303450985176716E-10</v>
       </c>
       <c r="W4">
-        <v>-1.193711741864858E-13</v>
+        <v>2.572415144460441E-26</v>
       </c>
       <c r="X4">
-        <v>-1.851561530704607E-10</v>
+        <v>-1.852373117735906E-10</v>
       </c>
       <c r="Y4">
-        <v>3.303473462748289E-10</v>
+        <v>3.303450994797953E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1838,40 +1838,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.049999952315831</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="AG4">
-        <v>0.9243966914071265</v>
+        <v>0.9243966914073701</v>
       </c>
       <c r="AH4">
-        <v>0.9487920434332352</v>
+        <v>0.9487920434344531</v>
       </c>
       <c r="AI4">
-        <v>1.049999952315547</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="AJ4">
-        <v>0.9243966932480089</v>
+        <v>0.9243966932484416</v>
       </c>
       <c r="AK4">
-        <v>0.9487920468307789</v>
+        <v>0.9487920468327014</v>
       </c>
       <c r="AL4">
-        <v>7.2754296277823E-11</v>
+        <v>3.645994679034516E-16</v>
       </c>
       <c r="AM4">
-        <v>-122.9835155919812</v>
+        <v>-122.9835155918942</v>
       </c>
       <c r="AN4">
-        <v>125.188627753316</v>
+        <v>125.1886277533084</v>
       </c>
       <c r="AO4">
-        <v>8.37806879477124E-11</v>
+        <v>3.645965319234853E-16</v>
       </c>
       <c r="AP4">
-        <v>-122.983515410811</v>
+        <v>-122.9835154107036</v>
       </c>
       <c r="AQ4">
-        <v>125.1886277157422</v>
+        <v>125.1886277157384</v>
       </c>
     </row>
   </sheetData>
@@ -2023,127 +2023,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.05308150717911422</v>
+        <v>0.05308150717890439</v>
       </c>
       <c r="D2">
-        <v>0.05308150717936843</v>
+        <v>0.05308150717890438</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.05308150717911431</v>
+        <v>0.05308150717890441</v>
       </c>
       <c r="G2">
-        <v>0.05308150717936835</v>
+        <v>0.05308150717890437</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01225864916620916</v>
+        <v>0.01225864916616071</v>
       </c>
       <c r="J2">
-        <v>0.01225864916626787</v>
+        <v>0.0122586491661607</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01225864916620919</v>
+        <v>0.01225864916616071</v>
       </c>
       <c r="M2">
-        <v>0.01225864916626785</v>
+        <v>0.0122586491661607</v>
       </c>
       <c r="N2">
-        <v>-1.234593183632662E-13</v>
+        <v>3.180326441555863E-19</v>
       </c>
       <c r="O2">
-        <v>0.0131172853434581</v>
+        <v>0.01311728534338952</v>
       </c>
       <c r="P2">
-        <v>0.00385339951724745</v>
+        <v>0.003853399517110012</v>
       </c>
       <c r="Q2">
-        <v>1.234574101676672E-13</v>
+        <v>-1.589700269777241E-35</v>
       </c>
       <c r="R2">
-        <v>-0.01167605916291939</v>
+        <v>-0.01167605916287374</v>
       </c>
       <c r="S2">
-        <v>-0.002412173336718006</v>
+        <v>-0.002412173336594232</v>
       </c>
       <c r="T2">
-        <v>1.101919505470233E-14</v>
+        <v>-3.180326441555863E-19</v>
       </c>
       <c r="U2">
-        <v>0.003118526389780176</v>
+        <v>0.003118526389838118</v>
       </c>
       <c r="V2">
-        <v>0.01291712564330688</v>
+        <v>0.01291712564322495</v>
       </c>
       <c r="W2">
-        <v>-1.104749995995255E-14</v>
+        <v>3.180326441555863E-19</v>
       </c>
       <c r="X2">
-        <v>-0.00214481763221125</v>
+        <v>-0.002144817632266303</v>
       </c>
       <c r="Y2">
-        <v>-0.01194341688570744</v>
+        <v>-0.01194341688565314</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-133.3932424903436</v>
+        <v>-133.3932424906505</v>
       </c>
       <c r="AB2">
-        <v>46.60675750980228</v>
+        <v>46.60675750934223</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>46.60675750964917</v>
+        <v>46.60675750934224</v>
       </c>
       <c r="AE2">
-        <v>-133.3932424901905</v>
+        <v>-133.3932424906505</v>
       </c>
       <c r="AF2">
         <v>1.100000023841857</v>
       </c>
       <c r="AG2">
-        <v>1.099867693450843</v>
+        <v>1.099867693450841</v>
       </c>
       <c r="AH2">
-        <v>1.099602784311813</v>
+        <v>1.099602784311816</v>
       </c>
       <c r="AI2">
-        <v>1.100000023844145</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="AJ2">
-        <v>0.9684117156654458</v>
+        <v>0.9684117156664244</v>
       </c>
       <c r="AK2">
-        <v>0.9939571251539845</v>
+        <v>0.9939571251563319</v>
       </c>
       <c r="AL2">
-        <v>1.938939491032897E-13</v>
+        <v>2.192535806754925E-16</v>
       </c>
       <c r="AM2">
-        <v>-120.0199130138827</v>
+        <v>-120.0199130138825</v>
       </c>
       <c r="AN2">
-        <v>119.9960155039706</v>
+        <v>119.9960155039708</v>
       </c>
       <c r="AO2">
-        <v>4.781261750552918E-11</v>
+        <v>2.86395493742087E-15</v>
       </c>
       <c r="AP2">
-        <v>-122.9844140436445</v>
+        <v>-122.9844140436503</v>
       </c>
       <c r="AQ2">
-        <v>125.1885126246982</v>
+        <v>125.1885126247582</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -2187,40 +2187,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-8.337034946973016E-14</v>
+        <v>-1.999408649157294E-24</v>
       </c>
       <c r="O3">
-        <v>-4.618283171082641E-10</v>
+        <v>-4.619519336343917E-10</v>
       </c>
       <c r="P3">
-        <v>-3.699888718097138E-10</v>
+        <v>-3.700478120097041E-10</v>
       </c>
       <c r="Q3">
-        <v>8.337034946970324E-14</v>
+        <v>1.999408649157294E-24</v>
       </c>
       <c r="R3">
-        <v>4.618283197134625E-10</v>
+        <v>4.619519362396388E-10</v>
       </c>
       <c r="S3">
-        <v>3.699888744147381E-10</v>
+        <v>3.700478146149512E-10</v>
       </c>
       <c r="T3">
-        <v>4.168517473477812E-14</v>
+        <v>-2.217687983687673E-25</v>
       </c>
       <c r="U3">
-        <v>2.034418634336968E-10</v>
+        <v>2.033593580601177E-10</v>
       </c>
       <c r="V3">
-        <v>-3.626515946175774E-10</v>
+        <v>-3.62541964925171E-10</v>
       </c>
       <c r="W3">
-        <v>-4.168517473477523E-14</v>
+        <v>2.217687983687673E-25</v>
       </c>
       <c r="X3">
-        <v>-2.03441861674629E-10</v>
+        <v>-2.033593562999832E-10</v>
       </c>
       <c r="Y3">
-        <v>3.626515963781447E-10</v>
+        <v>3.625419666853054E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2241,40 +2241,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.100000023844145</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="AG3">
-        <v>0.9684117156654458</v>
+        <v>0.9684117156664244</v>
       </c>
       <c r="AH3">
-        <v>0.9939571251539845</v>
+        <v>0.9939571251563319</v>
       </c>
       <c r="AI3">
-        <v>1.100000023843845</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="AJ3">
-        <v>0.9684117188796934</v>
+        <v>0.9684117188806912</v>
       </c>
       <c r="AK3">
-        <v>0.9939571310875647</v>
+        <v>0.9939571310902834</v>
       </c>
       <c r="AL3">
-        <v>4.781261750552918E-11</v>
+        <v>2.86395493742087E-15</v>
       </c>
       <c r="AM3">
-        <v>-122.9844140436445</v>
+        <v>-122.9844140436503</v>
       </c>
       <c r="AN3">
-        <v>125.1885126246982</v>
+        <v>125.1885126247582</v>
       </c>
       <c r="AO3">
-        <v>4.200137175881051E-11</v>
+        <v>2.863955450163008E-15</v>
       </c>
       <c r="AP3">
-        <v>-122.9844137416368</v>
+        <v>-122.9844137416246</v>
       </c>
       <c r="AQ3">
-        <v>125.1885125620833</v>
+        <v>125.1885125621666</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -2318,40 +2318,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>-1.999408671754873E-24</v>
       </c>
       <c r="O4">
-        <v>-4.617867293325862E-10</v>
+        <v>-4.619519399801827E-10</v>
       </c>
       <c r="P4">
-        <v>-3.699273049415146E-10</v>
+        <v>-3.700478217894609E-10</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.999408671754873E-24</v>
       </c>
       <c r="R4">
-        <v>4.617867308952758E-10</v>
+        <v>4.61951941543331E-10</v>
       </c>
       <c r="S4">
-        <v>3.699273065040236E-10</v>
+        <v>3.700478233526092E-10</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>-2.217687848102202E-25</v>
       </c>
       <c r="U4">
-        <v>2.033711218145542E-10</v>
+        <v>2.033593688544321E-10</v>
       </c>
       <c r="V4">
-        <v>-3.626081824531511E-10</v>
+        <v>-3.625419690080528E-10</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>2.217687848102202E-25</v>
       </c>
       <c r="X4">
-        <v>-2.033711207591422E-10</v>
+        <v>-2.033593677983514E-10</v>
       </c>
       <c r="Y4">
-        <v>3.626081835092544E-10</v>
+        <v>3.625419700641335E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2372,40 +2372,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.100000023844145</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="AG4">
-        <v>0.9684117156654458</v>
+        <v>0.9684117156664244</v>
       </c>
       <c r="AH4">
-        <v>0.9939571251539845</v>
+        <v>0.9939571251563319</v>
       </c>
       <c r="AI4">
-        <v>1.100000023843847</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="AJ4">
-        <v>0.9684117175938077</v>
+        <v>0.9684117175949843</v>
       </c>
       <c r="AK4">
-        <v>0.9939571287136172</v>
+        <v>0.9939571287167029</v>
       </c>
       <c r="AL4">
-        <v>4.781261750552918E-11</v>
+        <v>2.86395493742087E-15</v>
       </c>
       <c r="AM4">
-        <v>-122.9844140436445</v>
+        <v>-122.9844140436503</v>
       </c>
       <c r="AN4">
-        <v>125.1885126246982</v>
+        <v>125.1885126247582</v>
       </c>
       <c r="AO4">
-        <v>5.884150004763327E-11</v>
+        <v>2.863955245066162E-15</v>
       </c>
       <c r="AP4">
-        <v>-122.9844138624495</v>
+        <v>-122.9844138624349</v>
       </c>
       <c r="AQ4">
-        <v>125.1885125871395</v>
+        <v>125.1885125872032</v>
       </c>
     </row>
   </sheetData>
@@ -2557,127 +2557,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.182356680823795</v>
+        <v>0.1823566808252606</v>
       </c>
       <c r="D2">
-        <v>0.1823566808242454</v>
+        <v>0.1823566808252605</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1823566808237947</v>
+        <v>0.1823566808252606</v>
       </c>
       <c r="G2">
-        <v>0.1823566808242458</v>
+        <v>0.1823566808252605</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.04211347213239751</v>
+        <v>0.04211347213273597</v>
       </c>
       <c r="J2">
-        <v>0.04211347213250154</v>
+        <v>0.04211347213273595</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.04211347213239744</v>
+        <v>0.04211347213273597</v>
       </c>
       <c r="M2">
-        <v>0.04211347213250163</v>
+        <v>0.04211347213273595</v>
       </c>
       <c r="N2">
-        <v>-2.093169072431486E-13</v>
+        <v>1.098658187665618E-18</v>
       </c>
       <c r="O2">
-        <v>0.03932910800588477</v>
+        <v>0.03932910800624996</v>
       </c>
       <c r="P2">
-        <v>0.02598699020898061</v>
+        <v>0.02598699020949711</v>
       </c>
       <c r="Q2">
-        <v>2.095240043218687E-13</v>
+        <v>-1.098658187665618E-18</v>
       </c>
       <c r="R2">
-        <v>-0.00667105889906958</v>
+        <v>-0.006671058898376393</v>
       </c>
       <c r="S2">
-        <v>0.00667105889906255</v>
+        <v>0.006671058898376373</v>
       </c>
       <c r="T2">
-        <v>-5.167692597831628E-13</v>
+        <v>-1.098658187665618E-18</v>
       </c>
       <c r="U2">
-        <v>-0.007367019191670315</v>
+        <v>-0.007367019191465275</v>
       </c>
       <c r="V2">
-        <v>0.0303505071781597</v>
+        <v>0.03035050717801045</v>
       </c>
       <c r="W2">
-        <v>5.169252692413449E-13</v>
+        <v>1.098658187665618E-18</v>
       </c>
       <c r="X2">
-        <v>0.01885876318492715</v>
+        <v>0.0188587631847376</v>
       </c>
       <c r="Y2">
-        <v>-0.0188587631851847</v>
+        <v>-0.01885876318473813</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-109.4806160305616</v>
+        <v>-109.4806160309473</v>
       </c>
       <c r="AB2">
-        <v>70.51938396834485</v>
+        <v>70.51938396904544</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>70.51938396943071</v>
+        <v>70.51938396904544</v>
       </c>
       <c r="AE2">
-        <v>-109.4806160316475</v>
+        <v>-109.4806160309473</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880790769</v>
+        <v>0.9499999880790568</v>
       </c>
       <c r="AG2">
-        <v>0.9501269348783421</v>
+        <v>0.9501269348783331</v>
       </c>
       <c r="AH2">
-        <v>0.9487685420882864</v>
+        <v>0.9487685420882901</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880786455</v>
+        <v>0.9499999880790571</v>
       </c>
       <c r="AJ2">
-        <v>0.4749999940530728</v>
+        <v>0.4749999940395219</v>
       </c>
       <c r="AK2">
-        <v>0.4749999940576076</v>
+        <v>0.474999994039534</v>
       </c>
       <c r="AL2">
-        <v>3.552890384816676E-13</v>
+        <v>5.243448782065525E-16</v>
       </c>
       <c r="AM2">
-        <v>-120.090154140878</v>
+        <v>-120.0901541408788</v>
       </c>
       <c r="AN2">
-        <v>119.9482807313199</v>
+        <v>119.9482807313187</v>
       </c>
       <c r="AO2">
-        <v>-1.1568458813415E-09</v>
+        <v>2.992290340933839E-14</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999979165</v>
+        <v>-179.9999999999925</v>
       </c>
       <c r="AQ2">
-        <v>-179.999999999267</v>
+        <v>179.9999999999924</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -2721,40 +2721,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.440033259678304E-13</v>
+        <v>-4.871303872876352E-23</v>
       </c>
       <c r="O3">
-        <v>3.60007795735809E-14</v>
+        <v>-3.405840850645732E-17</v>
       </c>
       <c r="P3">
-        <v>1.81526688788354E-20</v>
+        <v>3.405839477490325E-17</v>
       </c>
       <c r="Q3">
-        <v>1.440033259677207E-13</v>
+        <v>4.871303872876352E-23</v>
       </c>
       <c r="R3">
-        <v>-3.58332073992297E-14</v>
+        <v>2.016296178400791E-16</v>
       </c>
       <c r="S3">
-        <v>1.675985154426536E-16</v>
+        <v>1.335128148156829E-16</v>
       </c>
       <c r="T3">
-        <v>2.880066519501986E-13</v>
+        <v>-1.728223793184694E-24</v>
       </c>
       <c r="U3">
-        <v>1.432833093479251E-09</v>
+        <v>1.432911065209952E-09</v>
       </c>
       <c r="V3">
-        <v>-1.433193101807877E-09</v>
+        <v>-1.432911067407305E-09</v>
       </c>
       <c r="W3">
-        <v>-2.880066519509516E-13</v>
+        <v>1.728223793184694E-24</v>
       </c>
       <c r="X3">
-        <v>-1.432833034520377E-09</v>
+        <v>-1.432911006244843E-09</v>
       </c>
       <c r="Y3">
-        <v>1.433193160791336E-09</v>
+        <v>1.432911126372415E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2775,40 +2775,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9499999880786455</v>
+        <v>0.9499999880790571</v>
       </c>
       <c r="AG3">
-        <v>0.4749999940530728</v>
+        <v>0.4749999940395219</v>
       </c>
       <c r="AH3">
-        <v>0.4749999940576076</v>
+        <v>0.474999994039534</v>
       </c>
       <c r="AI3">
-        <v>0.9499999880804879</v>
+        <v>0.9499999880790571</v>
       </c>
       <c r="AJ3">
-        <v>0.4749999745061622</v>
+        <v>0.4749999744930052</v>
       </c>
       <c r="AK3">
-        <v>0.4750000136063672</v>
+        <v>0.4750000135860572</v>
       </c>
       <c r="AL3">
-        <v>-1.1568458813415E-09</v>
+        <v>2.992290340933839E-14</v>
       </c>
       <c r="AM3">
-        <v>-179.9999999979165</v>
+        <v>-179.9999999999925</v>
       </c>
       <c r="AN3">
-        <v>-179.999999999267</v>
+        <v>179.9999999999924</v>
       </c>
       <c r="AO3">
-        <v>-1.234230370059394E-09</v>
+        <v>2.992292142746984E-14</v>
       </c>
       <c r="AP3">
-        <v>-179.9999932971403</v>
+        <v>-179.9999932995603</v>
       </c>
       <c r="AQ3">
-        <v>179.999993299788</v>
+        <v>179.9999932995606</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -2852,40 +2852,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.440033259736455E-13</v>
+        <v>-4.871304035250219E-23</v>
       </c>
       <c r="O4">
-        <v>-1.440033779143412E-13</v>
+        <v>-1.977585206680462E-17</v>
       </c>
       <c r="P4">
-        <v>-1.440033078274319E-13</v>
+        <v>2.417047108591226E-17</v>
       </c>
       <c r="Q4">
-        <v>-1.440033259738012E-13</v>
+        <v>4.871304035250219E-23</v>
       </c>
       <c r="R4">
-        <v>1.441039484872089E-13</v>
+        <v>1.20318583762306E-16</v>
       </c>
       <c r="S4">
-        <v>1.441038748118746E-13</v>
+        <v>7.637226145271441E-17</v>
       </c>
       <c r="T4">
-        <v>-2.907537971694035E-24</v>
+        <v>-1.728223574604487E-24</v>
       </c>
       <c r="U4">
-        <v>1.433265103457178E-09</v>
+        <v>1.432911106958963E-09</v>
       </c>
       <c r="V4">
-        <v>-1.433121100144889E-09</v>
+        <v>-1.432911115748266E-09</v>
       </c>
       <c r="W4">
-        <v>2.877640643519706E-24</v>
+        <v>1.728223574604487E-24</v>
       </c>
       <c r="X4">
-        <v>-1.43326506805718E-09</v>
+        <v>-1.432911071579896E-09</v>
       </c>
       <c r="Y4">
-        <v>1.433121135524223E-09</v>
+        <v>1.432911151127334E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9499999880786455</v>
+        <v>0.9499999880790571</v>
       </c>
       <c r="AG4">
-        <v>0.4749999940530728</v>
+        <v>0.4749999940395219</v>
       </c>
       <c r="AH4">
-        <v>0.4749999940576076</v>
+        <v>0.474999994039534</v>
       </c>
       <c r="AI4">
-        <v>0.949999988079673</v>
+        <v>0.9499999880790571</v>
       </c>
       <c r="AJ4">
-        <v>0.4749999823244697</v>
+        <v>0.4749999823116104</v>
       </c>
       <c r="AK4">
-        <v>0.4750000057872406</v>
+        <v>0.4750000057674478</v>
       </c>
       <c r="AL4">
-        <v>-1.1568458813415E-09</v>
+        <v>2.992290340933839E-14</v>
       </c>
       <c r="AM4">
-        <v>-179.9999999979165</v>
+        <v>-179.9999999999925</v>
       </c>
       <c r="AN4">
-        <v>-179.999999999267</v>
+        <v>179.9999999999924</v>
       </c>
       <c r="AO4">
-        <v>-1.144950387180494E-09</v>
+        <v>2.992291422021784E-14</v>
       </c>
       <c r="AP4">
-        <v>-179.9999959773949</v>
+        <v>-179.9999959797331</v>
       </c>
       <c r="AQ4">
-        <v>179.9999959802209</v>
+        <v>179.9999959797331</v>
       </c>
     </row>
   </sheetData>
@@ -3091,127 +3091,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1727660155210032</v>
+        <v>0.1727660155207067</v>
       </c>
       <c r="D2">
-        <v>0.1727660155203913</v>
+        <v>0.1727660155207066</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1727660155210027</v>
+        <v>0.1727660155207067</v>
       </c>
       <c r="G2">
-        <v>0.1727660155203917</v>
+        <v>0.1727660155207066</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.03989860282168359</v>
+        <v>0.03989860282161513</v>
       </c>
       <c r="J2">
-        <v>0.03989860282154229</v>
+        <v>0.03989860282161511</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.03989860282168349</v>
+        <v>0.03989860282161513</v>
       </c>
       <c r="M2">
-        <v>0.03989860282154239</v>
+        <v>0.03989860282161511</v>
       </c>
       <c r="N2">
-        <v>-6.595869509036617E-14</v>
+        <v>-5.204170290066909E-19</v>
       </c>
       <c r="O2">
-        <v>0.03529931497988932</v>
+        <v>0.03529931497983594</v>
       </c>
       <c r="P2">
-        <v>0.02332712330998936</v>
+        <v>0.02332712331029338</v>
       </c>
       <c r="Q2">
-        <v>6.596806259743581E-14</v>
+        <v>5.204170290066906E-19</v>
       </c>
       <c r="R2">
-        <v>-0.005986095834817829</v>
+        <v>-0.005986095834771259</v>
       </c>
       <c r="S2">
-        <v>0.005986095835062072</v>
+        <v>0.005986095834771261</v>
       </c>
       <c r="T2">
-        <v>-1.82974464062522E-13</v>
+        <v>-1.040834058013382E-18</v>
       </c>
       <c r="U2">
-        <v>-0.00661231928843742</v>
+        <v>-0.006612319288387273</v>
       </c>
       <c r="V2">
-        <v>0.02724184366223613</v>
+        <v>0.02724184366206226</v>
       </c>
       <c r="W2">
-        <v>1.830785474674413E-13</v>
+        <v>1.040834058013382E-18</v>
       </c>
       <c r="X2">
-        <v>0.01692708147551594</v>
+        <v>0.01692708147522465</v>
       </c>
       <c r="Y2">
-        <v>-0.01692708147564225</v>
+        <v>-0.01692708147522488</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-109.4756397444171</v>
+        <v>-109.4756397444799</v>
       </c>
       <c r="AB2">
-        <v>70.52436025496397</v>
+        <v>70.52436025551279</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>70.52436025557553</v>
+        <v>70.52436025551278</v>
       </c>
       <c r="AE2">
-        <v>-109.4756397450287</v>
+        <v>-109.4756397444799</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761581358</v>
+        <v>0.8999999761581288</v>
       </c>
       <c r="AG2">
-        <v>0.9001139774548361</v>
+        <v>0.9001139774548345</v>
       </c>
       <c r="AH2">
-        <v>0.8988947482999331</v>
+        <v>0.8988947482999384</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761551563</v>
+        <v>0.8999999761581289</v>
       </c>
       <c r="AJ2">
-        <v>0.4499999880855623</v>
+        <v>0.4499999880790613</v>
       </c>
       <c r="AK2">
-        <v>0.4499999880921794</v>
+        <v>0.4499999880790669</v>
       </c>
       <c r="AL2">
-        <v>1.137305199592748E-13</v>
+        <v>5.095719068657533E-16</v>
       </c>
       <c r="AM2">
-        <v>-120.0854126414232</v>
+        <v>-120.085412641423</v>
       </c>
       <c r="AN2">
-        <v>119.9509980239257</v>
+        <v>119.9509980239249</v>
       </c>
       <c r="AO2">
-        <v>-2.395860923618548E-10</v>
+        <v>1.670260853488846E-14</v>
       </c>
       <c r="AP2">
-        <v>179.9999999998857</v>
+        <v>-179.9999999999926</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999998747</v>
+        <v>179.9999999999926</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -3255,40 +3255,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.364242016509089E-13</v>
+        <v>-4.360346831831073E-23</v>
       </c>
       <c r="O3">
-        <v>-6.821209842534727E-14</v>
+        <v>-3.12250233268453E-17</v>
       </c>
       <c r="P3">
-        <v>-6.821210347753951E-14</v>
+        <v>3.018418419221129E-17</v>
       </c>
       <c r="Q3">
-        <v>-1.364242016508455E-13</v>
+        <v>4.360346831831073E-23</v>
       </c>
       <c r="R3">
-        <v>6.836249643144399E-14</v>
+        <v>1.816213406807545E-16</v>
       </c>
       <c r="S3">
-        <v>6.836249896980611E-14</v>
+        <v>1.202121326438002E-16</v>
       </c>
       <c r="T3">
-        <v>-1.364242016520499E-13</v>
+        <v>-8.658019573592802E-25</v>
       </c>
       <c r="U3">
-        <v>1.286070948991314E-09</v>
+        <v>1.286047571839792E-09</v>
       </c>
       <c r="V3">
-        <v>-1.286002736909398E-09</v>
+        <v>-1.28604756975814E-09</v>
       </c>
       <c r="W3">
-        <v>1.364242016519705E-13</v>
+        <v>8.658019573592802E-25</v>
       </c>
       <c r="X3">
-        <v>-1.28607089605942E-09</v>
+        <v>-1.286047518918199E-09</v>
       </c>
       <c r="Y3">
-        <v>1.286002789821185E-09</v>
+        <v>1.286047622679733E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3309,40 +3309,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8999999761551563</v>
+        <v>0.8999999761581289</v>
       </c>
       <c r="AG3">
-        <v>0.4499999880855623</v>
+        <v>0.4499999880790613</v>
       </c>
       <c r="AH3">
-        <v>0.4499999880921794</v>
+        <v>0.4499999880790669</v>
       </c>
       <c r="AI3">
-        <v>0.8999999761546853</v>
+        <v>0.8999999761581289</v>
       </c>
       <c r="AJ3">
-        <v>0.4499999695673319</v>
+        <v>0.4499999695613089</v>
       </c>
       <c r="AK3">
-        <v>0.4500000066099451</v>
+        <v>0.4500000065968255</v>
       </c>
       <c r="AL3">
-        <v>-2.395860923618548E-10</v>
+        <v>1.670260853488846E-14</v>
       </c>
       <c r="AM3">
-        <v>179.9999999998857</v>
+        <v>-179.9999999999926</v>
       </c>
       <c r="AN3">
-        <v>179.9999999998747</v>
+        <v>179.9999999999926</v>
       </c>
       <c r="AO3">
-        <v>-2.362350423465078E-10</v>
+        <v>1.670262739208523E-14</v>
       </c>
       <c r="AP3">
-        <v>-179.999993299589</v>
+        <v>-179.9999932995604</v>
       </c>
       <c r="AQ3">
-        <v>179.9999932993712</v>
+        <v>179.9999932995608</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -3386,40 +3386,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.728484033006769E-13</v>
+        <v>-4.360346973826032E-23</v>
       </c>
       <c r="O4">
-        <v>-6.821209842509251E-14</v>
+        <v>-2.081668274671161E-17</v>
       </c>
       <c r="P4">
-        <v>-1.364242043053519E-13</v>
+        <v>2.081667767009068E-17</v>
       </c>
       <c r="Q4">
-        <v>-2.728484033010853E-13</v>
+        <v>4.360346973826032E-23</v>
       </c>
       <c r="R4">
-        <v>6.830235163282717E-14</v>
+        <v>1.110544786469613E-16</v>
       </c>
       <c r="S4">
-        <v>1.365144428858153E-13</v>
+        <v>6.942111852228678E-17</v>
       </c>
       <c r="T4">
-        <v>-5.456968066070585E-13</v>
+        <v>-8.658016023718823E-25</v>
       </c>
       <c r="U4">
-        <v>1.286207373192969E-09</v>
+        <v>1.286047609309818E-09</v>
       </c>
       <c r="V4">
-        <v>-1.28593452480857E-09</v>
+        <v>-1.28604761347317E-09</v>
       </c>
       <c r="W4">
-        <v>5.456968066075921E-13</v>
+        <v>8.658016023718823E-25</v>
       </c>
       <c r="X4">
-        <v>-1.286207341429408E-09</v>
+        <v>-1.286047577556861E-09</v>
       </c>
       <c r="Y4">
-        <v>1.285934556553815E-09</v>
+        <v>1.286047645226128E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3440,40 +3440,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.8999999761551563</v>
+        <v>0.8999999761581289</v>
       </c>
       <c r="AG4">
-        <v>0.4499999880855623</v>
+        <v>0.4499999880790613</v>
       </c>
       <c r="AH4">
-        <v>0.4499999880921794</v>
+        <v>0.4499999880790669</v>
       </c>
       <c r="AI4">
-        <v>0.8999999761561297</v>
+        <v>0.8999999761581289</v>
       </c>
       <c r="AJ4">
-        <v>0.4499999769742542</v>
+        <v>0.4499999769684085</v>
       </c>
       <c r="AK4">
-        <v>0.4499999992044632</v>
+        <v>0.4499999991897219</v>
       </c>
       <c r="AL4">
-        <v>-2.395860923618548E-10</v>
+        <v>1.670260853488846E-14</v>
       </c>
       <c r="AM4">
-        <v>179.9999999998857</v>
+        <v>-179.9999999999926</v>
       </c>
       <c r="AN4">
-        <v>179.9999999998747</v>
+        <v>179.9999999999926</v>
       </c>
       <c r="AO4">
-        <v>-2.276905978372536E-10</v>
+        <v>1.670261984920712E-14</v>
       </c>
       <c r="AP4">
-        <v>-179.9999959795781</v>
+        <v>-179.9999959797332</v>
       </c>
       <c r="AQ4">
-        <v>179.9999959793771</v>
+        <v>179.9999959797333</v>
       </c>
     </row>
   </sheetData>
@@ -3625,127 +3625,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.04223863540422783</v>
+        <v>0.04223863540419828</v>
       </c>
       <c r="D2">
-        <v>0.04223863540440475</v>
+        <v>0.04223863540419828</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.04223863540422796</v>
+        <v>0.04223863540419828</v>
       </c>
       <c r="G2">
-        <v>0.04223863540440462</v>
+        <v>0.04223863540419828</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.00975459515368815</v>
+        <v>0.009754595153681328</v>
       </c>
       <c r="J2">
-        <v>0.009754595153729008</v>
+        <v>0.009754595153681328</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.009754595153688182</v>
+        <v>0.009754595153681326</v>
       </c>
       <c r="M2">
-        <v>0.009754595153728979</v>
+        <v>0.009754595153681328</v>
       </c>
       <c r="N2">
-        <v>-5.094148418749238E-14</v>
+        <v>2.746645469164075E-19</v>
       </c>
       <c r="O2">
-        <v>0.009145426051986837</v>
+        <v>0.009145426051980472</v>
       </c>
       <c r="P2">
-        <v>0.003279349242978402</v>
+        <v>0.003279349243070329</v>
       </c>
       <c r="Q2">
-        <v>5.099614243339696E-14</v>
+        <v>-2.746645469164075E-19</v>
       </c>
       <c r="R2">
-        <v>-0.007393294790477599</v>
+        <v>-0.007393294790450208</v>
       </c>
       <c r="S2">
-        <v>-0.001527217981407577</v>
+        <v>-0.001527217981540056</v>
       </c>
       <c r="T2">
-        <v>-1.645921804105645E-13</v>
+        <v>9.736126157428184E-37</v>
       </c>
       <c r="U2">
-        <v>0.001489880146369924</v>
+        <v>0.001489880146368682</v>
       </c>
       <c r="V2">
-        <v>0.008663716984875506</v>
+        <v>0.008663716984792322</v>
       </c>
       <c r="W2">
-        <v>1.645993216887803E-13</v>
+        <v>-2.746645469164075E-19</v>
       </c>
       <c r="X2">
-        <v>-0.0008733386060848104</v>
+        <v>-0.0008733386060701011</v>
       </c>
       <c r="Y2">
-        <v>-0.008047175444556588</v>
+        <v>-0.008047175444493753</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-129.2730122327434</v>
+        <v>-129.2730122327422</v>
       </c>
       <c r="AB2">
-        <v>50.72698776653687</v>
+        <v>50.72698776725052</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>50.72698776724896</v>
+        <v>50.72698776725052</v>
       </c>
       <c r="AE2">
-        <v>-129.2730122334556</v>
+        <v>-129.2730122327422</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880790737</v>
+        <v>0.9499999880790674</v>
       </c>
       <c r="AG2">
-        <v>0.9499102019017731</v>
+        <v>0.9499102019017732</v>
       </c>
       <c r="AH2">
-        <v>0.9496643516854965</v>
+        <v>0.9496643516854993</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880807952</v>
+        <v>0.9499999880790674</v>
       </c>
       <c r="AJ2">
-        <v>0.7631990742699961</v>
+        <v>0.7631990742675668</v>
       </c>
       <c r="AK2">
-        <v>0.8396877029726389</v>
+        <v>0.8396877029729445</v>
       </c>
       <c r="AL2">
-        <v>7.780433048820096E-14</v>
+        <v>2.030982680110189E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0202479590293</v>
       </c>
       <c r="AN2">
-        <v>119.9945677925553</v>
+        <v>119.9945677925551</v>
       </c>
       <c r="AO2">
-        <v>-3.395880090024672E-10</v>
+        <v>2.132484936059895E-16</v>
       </c>
       <c r="AP2">
-        <v>-122.5361235041184</v>
+        <v>-122.5361235042045</v>
       </c>
       <c r="AQ2">
-        <v>129.9810150648715</v>
+        <v>129.9810150645925</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -3789,40 +3789,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-6.401231012059596E-25</v>
+        <v>-1.288846870899803E-23</v>
       </c>
       <c r="O3">
-        <v>-5.20172227952566E-10</v>
+        <v>-5.201390904855484E-10</v>
       </c>
       <c r="P3">
-        <v>-2.954659654021549E-10</v>
+        <v>-2.953676383197859E-10</v>
       </c>
       <c r="Q3">
-        <v>6.773868157876789E-25</v>
+        <v>1.288846870899803E-23</v>
       </c>
       <c r="R3">
-        <v>5.201722369431974E-10</v>
+        <v>5.201390994758819E-10</v>
       </c>
       <c r="S3">
-        <v>2.954659743943405E-10</v>
+        <v>2.953676473101193E-10</v>
       </c>
       <c r="T3">
-        <v>-1.080024944804785E-13</v>
+        <v>-1.231665114814419E-26</v>
       </c>
       <c r="U3">
-        <v>1.175712132713588E-10</v>
+        <v>1.176355892276271E-10</v>
       </c>
       <c r="V3">
-        <v>-5.069710187941089E-10</v>
+        <v>-5.069511604102293E-10</v>
       </c>
       <c r="W3">
-        <v>1.080024944805734E-13</v>
+        <v>1.231665114814419E-26</v>
       </c>
       <c r="X3">
-        <v>-1.175712101064159E-10</v>
+        <v>-1.176355860641003E-10</v>
       </c>
       <c r="Y3">
-        <v>5.069710219575997E-10</v>
+        <v>5.069511635737561E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3843,40 +3843,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9499999880807952</v>
+        <v>0.9499999880790674</v>
       </c>
       <c r="AG3">
-        <v>0.7631990742699961</v>
+        <v>0.7631990742675668</v>
       </c>
       <c r="AH3">
-        <v>0.8396877029726389</v>
+        <v>0.8396877029729445</v>
       </c>
       <c r="AI3">
-        <v>0.94999998808163</v>
+        <v>0.9499999880790674</v>
       </c>
       <c r="AJ3">
-        <v>0.7631990858214011</v>
+        <v>0.7631990858184422</v>
       </c>
       <c r="AK3">
-        <v>0.8396877133631061</v>
+        <v>0.8396877133621731</v>
       </c>
       <c r="AL3">
-        <v>-3.395880090024672E-10</v>
+        <v>2.132484936059895E-16</v>
       </c>
       <c r="AM3">
-        <v>-122.5361235041184</v>
+        <v>-122.5361235042045</v>
       </c>
       <c r="AN3">
-        <v>129.9810150648715</v>
+        <v>129.9810150645925</v>
       </c>
       <c r="AO3">
-        <v>-3.593565669857676E-10</v>
+        <v>2.132537809740354E-16</v>
       </c>
       <c r="AP3">
-        <v>-122.5361229594993</v>
+        <v>-122.5361229596084</v>
       </c>
       <c r="AQ3">
-        <v>129.9810144618154</v>
+        <v>129.9810144615353</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -3920,40 +3920,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.440033259735446E-13</v>
+        <v>-1.288846902125547E-23</v>
       </c>
       <c r="O4">
-        <v>-5.200856248772989E-10</v>
+        <v>-5.201391082798662E-10</v>
       </c>
       <c r="P4">
-        <v>-2.954250739378964E-10</v>
+        <v>-2.953676541861837E-10</v>
       </c>
       <c r="Q4">
-        <v>1.440033259735589E-13</v>
+        <v>1.288846902125547E-23</v>
       </c>
       <c r="R4">
-        <v>5.200856302713825E-10</v>
+        <v>5.201391136740668E-10</v>
       </c>
       <c r="S4">
-        <v>2.954250793332278E-10</v>
+        <v>2.953676595803842E-10</v>
       </c>
       <c r="T4">
-        <v>7.200166298783919E-14</v>
+        <v>-1.231654185804099E-26</v>
       </c>
       <c r="U4">
-        <v>1.176531888832339E-10</v>
+        <v>1.176355974388134E-10</v>
       </c>
       <c r="V4">
-        <v>-5.070197841497282E-10</v>
+        <v>-5.069511762493771E-10</v>
       </c>
       <c r="W4">
-        <v>-7.200166298785517E-14</v>
+        <v>1.231654185804099E-26</v>
       </c>
       <c r="X4">
-        <v>-1.176531869852059E-10</v>
+        <v>-1.176355955406972E-10</v>
       </c>
       <c r="Y4">
-        <v>5.070197860484561E-10</v>
+        <v>5.069511781474933E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3974,40 +3974,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9499999880807952</v>
+        <v>0.9499999880790674</v>
       </c>
       <c r="AG4">
-        <v>0.7631990742699961</v>
+        <v>0.7631990742675668</v>
       </c>
       <c r="AH4">
-        <v>0.8396877029726389</v>
+        <v>0.8396877029729445</v>
       </c>
       <c r="AI4">
-        <v>0.9499999880809129</v>
+        <v>0.9499999880790674</v>
       </c>
       <c r="AJ4">
-        <v>0.7631990812007773</v>
+        <v>0.7631990811980922</v>
       </c>
       <c r="AK4">
-        <v>0.8396877092069469</v>
+        <v>0.8396877092064819</v>
       </c>
       <c r="AL4">
-        <v>-3.395880090024672E-10</v>
+        <v>2.132484936059895E-16</v>
       </c>
       <c r="AM4">
-        <v>-122.5361235041184</v>
+        <v>-122.5361235042045</v>
       </c>
       <c r="AN4">
-        <v>129.9810150648715</v>
+        <v>129.9810150645925</v>
       </c>
       <c r="AO4">
-        <v>-3.423982909531318E-10</v>
+        <v>2.132516660269813E-16</v>
       </c>
       <c r="AP4">
-        <v>-122.5361231773148</v>
+        <v>-122.5361231774468</v>
       </c>
       <c r="AQ4">
-        <v>129.9810147030372</v>
+        <v>129.9810147027582</v>
       </c>
     </row>
   </sheetData>
@@ -4159,127 +4159,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.04001617762586085</v>
+        <v>0.04001617762540317</v>
       </c>
       <c r="D2">
-        <v>0.0400161776258431</v>
+        <v>0.04001617762540315</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.04001617762586087</v>
+        <v>0.04001617762540317</v>
       </c>
       <c r="G2">
-        <v>0.04001617762584307</v>
+        <v>0.04001617762540315</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.009241340507398959</v>
+        <v>0.009241340507293264</v>
       </c>
       <c r="J2">
-        <v>0.009241340507394861</v>
+        <v>0.009241340507293258</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.009241340507398966</v>
+        <v>0.009241340507293264</v>
       </c>
       <c r="M2">
-        <v>0.009241340507394854</v>
+        <v>0.009241340507293258</v>
       </c>
       <c r="N2">
-        <v>2.441796700099391E-15</v>
+        <v>-2.602085145033483E-19</v>
       </c>
       <c r="O2">
-        <v>0.008208248980527336</v>
+        <v>0.008208248980439439</v>
       </c>
       <c r="P2">
-        <v>0.002943423073778492</v>
+        <v>0.002943423073839462</v>
       </c>
       <c r="Q2">
-        <v>-2.419418767564721E-15</v>
+        <v>4.095122551746376E-35</v>
       </c>
       <c r="R2">
-        <v>-0.006635649656944657</v>
+        <v>-0.006635649656879884</v>
       </c>
       <c r="S2">
-        <v>-0.001370823750171524</v>
+        <v>-0.001370823750279901</v>
       </c>
       <c r="T2">
-        <v>-8.58245743386397E-14</v>
+        <v>-8.884439216273526E-37</v>
       </c>
       <c r="U2">
-        <v>0.001337228939329231</v>
+        <v>0.001337228939277349</v>
       </c>
       <c r="V2">
-        <v>0.007775980972923708</v>
+        <v>0.007775980972802931</v>
       </c>
       <c r="W2">
-        <v>8.583706434733287E-14</v>
+        <v>-2.602085145033484E-19</v>
       </c>
       <c r="X2">
-        <v>-0.0007838612604767001</v>
+        <v>-0.0007838612604351147</v>
       </c>
       <c r="Y2">
-        <v>-0.007222613294066976</v>
+        <v>-0.007222613293960712</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-129.27211129394</v>
+        <v>-129.2721112936844</v>
       </c>
       <c r="AB2">
-        <v>50.72788870562088</v>
+        <v>50.7278887063083</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>50.72788870605252</v>
+        <v>50.72788870630832</v>
       </c>
       <c r="AE2">
-        <v>-129.2721112943717</v>
+        <v>-129.2721112936844</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761581421</v>
+        <v>0.8999999761581389</v>
       </c>
       <c r="AG2">
-        <v>0.8999193931135874</v>
+        <v>0.8999193931135896</v>
       </c>
       <c r="AH2">
-        <v>0.8996987365102919</v>
+        <v>0.8996987365102961</v>
       </c>
       <c r="AI2">
-        <v>0.899999976158026</v>
+        <v>0.899999976158139</v>
       </c>
       <c r="AJ2">
-        <v>0.7230322855550202</v>
+        <v>0.7230322855558015</v>
       </c>
       <c r="AK2">
-        <v>0.7955069817299606</v>
+        <v>0.7955069817295959</v>
       </c>
       <c r="AL2">
-        <v>-2.5991852122724E-14</v>
+        <v>1.956280605976938E-16</v>
       </c>
       <c r="AM2">
-        <v>-120.0191825636723</v>
+        <v>-120.0191825636721</v>
       </c>
       <c r="AN2">
-        <v>119.9948534113833</v>
+        <v>119.9948534113831</v>
       </c>
       <c r="AO2">
-        <v>-1.916429492746603E-10</v>
+        <v>9.017123795957977E-15</v>
       </c>
       <c r="AP2">
-        <v>-122.5350516915676</v>
+        <v>-122.5350516916008</v>
       </c>
       <c r="AQ2">
-        <v>129.9811982500723</v>
+        <v>129.9811982497753</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -4323,40 +4323,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-2.28155865747889E-25</v>
+        <v>-1.043678752815433E-23</v>
       </c>
       <c r="O3">
-        <v>-4.66859726940392E-10</v>
+        <v>-4.668272015194709E-10</v>
       </c>
       <c r="P3">
-        <v>-2.650735966853063E-10</v>
+        <v>-2.650584706291991E-10</v>
       </c>
       <c r="Q3">
-        <v>2.392952378823636E-25</v>
+        <v>1.043678752815433E-23</v>
       </c>
       <c r="R3">
-        <v>4.66859735009228E-10</v>
+        <v>4.668272095879518E-10</v>
       </c>
       <c r="S3">
-        <v>2.650736047541914E-10</v>
+        <v>2.650584786976799E-10</v>
       </c>
       <c r="T3">
-        <v>-6.82121008259572E-14</v>
+        <v>-4.674143252264891E-25</v>
       </c>
       <c r="U3">
-        <v>1.055201058679385E-10</v>
+        <v>1.055343962454156E-10</v>
       </c>
       <c r="V3">
-        <v>-4.55023839015811E-10</v>
+        <v>-4.55008083986829E-10</v>
       </c>
       <c r="W3">
-        <v>6.821210082597039E-14</v>
+        <v>4.674143252264891E-25</v>
       </c>
       <c r="X3">
-        <v>-1.055201030282822E-10</v>
+        <v>-1.055343934062713E-10</v>
       </c>
       <c r="Y3">
-        <v>4.55023841855119E-10</v>
+        <v>4.550080868259734E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4377,40 +4377,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.899999976158026</v>
+        <v>0.899999976158139</v>
       </c>
       <c r="AG3">
-        <v>0.7230322855550202</v>
+        <v>0.7230322855558015</v>
       </c>
       <c r="AH3">
-        <v>0.7955069817299606</v>
+        <v>0.7955069817295959</v>
       </c>
       <c r="AI3">
-        <v>0.8999999761582</v>
+        <v>0.899999976158139</v>
       </c>
       <c r="AJ3">
-        <v>0.7230322964982995</v>
+        <v>0.7230322964990781</v>
       </c>
       <c r="AK3">
-        <v>0.7955069915717237</v>
+        <v>0.7955069915711531</v>
       </c>
       <c r="AL3">
-        <v>-1.916429492746603E-10</v>
+        <v>9.017123795957977E-15</v>
       </c>
       <c r="AM3">
-        <v>-122.5350516915676</v>
+        <v>-122.5350516916008</v>
       </c>
       <c r="AN3">
-        <v>129.9811982500723</v>
+        <v>129.9811982497753</v>
       </c>
       <c r="AO3">
-        <v>-2.009996323558165E-10</v>
+        <v>9.017127970667553E-15</v>
       </c>
       <c r="AP3">
-        <v>-122.535051147066</v>
+        <v>-122.5350511470975</v>
       </c>
       <c r="AQ3">
-        <v>129.98119764699</v>
+        <v>129.9811976466908</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -4454,40 +4454,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.364242016515722E-13</v>
+        <v>-1.043678782397716E-23</v>
       </c>
       <c r="O4">
-        <v>-4.668449909303072E-10</v>
+        <v>-4.668272169675341E-10</v>
       </c>
       <c r="P4">
-        <v>-2.65142895801016E-10</v>
+        <v>-2.650584833182462E-10</v>
       </c>
       <c r="Q4">
-        <v>1.36424201651584E-13</v>
+        <v>1.043678782397716E-23</v>
       </c>
       <c r="R4">
-        <v>4.668449957718487E-10</v>
+        <v>4.668272218086229E-10</v>
       </c>
       <c r="S4">
-        <v>2.651429006434413E-10</v>
+        <v>2.65058488159335E-10</v>
       </c>
       <c r="T4">
-        <v>1.023181512393921E-13</v>
+        <v>-4.67414258666352E-25</v>
       </c>
       <c r="U4">
-        <v>1.05543205573175E-10</v>
+        <v>1.055344031247212E-10</v>
       </c>
       <c r="V4">
-        <v>-4.550819491367961E-10</v>
+        <v>-4.550080946271099E-10</v>
       </c>
       <c r="W4">
-        <v>-1.023181512394115E-13</v>
+        <v>4.67414258666352E-25</v>
       </c>
       <c r="X4">
-        <v>-1.055432038693288E-10</v>
+        <v>-1.055344014212344E-10</v>
       </c>
       <c r="Y4">
-        <v>4.550819508407154E-10</v>
+        <v>4.550080963305966E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -4508,40 +4508,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.899999976158026</v>
+        <v>0.899999976158139</v>
       </c>
       <c r="AG4">
-        <v>0.7230322855550202</v>
+        <v>0.7230322855558015</v>
       </c>
       <c r="AH4">
-        <v>0.7955069817299606</v>
+        <v>0.7955069817295959</v>
       </c>
       <c r="AI4">
-        <v>0.8999999761581374</v>
+        <v>0.899999976158139</v>
       </c>
       <c r="AJ4">
-        <v>0.7230322921212288</v>
+        <v>0.7230322921217676</v>
       </c>
       <c r="AK4">
-        <v>0.7955069876356251</v>
+        <v>0.7955069876345304</v>
       </c>
       <c r="AL4">
-        <v>-1.916429492746603E-10</v>
+        <v>9.017123795957977E-15</v>
       </c>
       <c r="AM4">
-        <v>-122.5350516915676</v>
+        <v>-122.5350516916008</v>
       </c>
       <c r="AN4">
-        <v>129.9811982500723</v>
+        <v>129.9811982497753</v>
       </c>
       <c r="AO4">
-        <v>-1.944542947341415E-10</v>
+        <v>9.017126300783862E-15</v>
       </c>
       <c r="AP4">
-        <v>-122.5350513648198</v>
+        <v>-122.5350513648988</v>
       </c>
       <c r="AQ4">
-        <v>129.9811978882215</v>
+        <v>129.9811978879246</v>
       </c>
     </row>
   </sheetData>
@@ -4693,16 +4693,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.1961699758751887</v>
+        <v>0.1961699758851258</v>
       </c>
       <c r="C2">
-        <v>4.668407731738846E-05</v>
+        <v>4.668407857659386E-05</v>
       </c>
       <c r="D2">
-        <v>4.668408495978257E-05</v>
+        <v>4.668407857650866E-05</v>
       </c>
       <c r="E2">
-        <v>0.1961438285442765</v>
+        <v>0.1961438285542146</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4711,16 +4711,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.04530351602646002</v>
+        <v>0.04530351602875489</v>
       </c>
       <c r="I2">
-        <v>1.07812260030782E-05</v>
+        <v>1.078122629387923E-05</v>
       </c>
       <c r="J2">
-        <v>1.078122776801354E-05</v>
+        <v>1.078122629385956E-05</v>
       </c>
       <c r="K2">
-        <v>0.04529747755895373</v>
+        <v>0.04529747756124886</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4729,52 +4729,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.03939106662759952</v>
+        <v>0.03939106662789152</v>
       </c>
       <c r="O2">
-        <v>9.808225390188018E-06</v>
+        <v>9.808226519159631E-06</v>
       </c>
       <c r="P2">
-        <v>-9.799081529001817E-06</v>
+        <v>-9.799079482928837E-06</v>
       </c>
       <c r="Q2">
-        <v>-2.535473610367748E-12</v>
+        <v>-1.179315289386362E-17</v>
       </c>
       <c r="R2">
-        <v>-6.049956305424457E-09</v>
+        <v>-6.051949744269685E-09</v>
       </c>
       <c r="S2">
-        <v>-6.065894533670928E-09</v>
+        <v>-6.068645093730135E-09</v>
       </c>
       <c r="T2">
-        <v>0.02659307532569877</v>
+        <v>0.02659307532955956</v>
       </c>
       <c r="U2">
-        <v>-5.652224493211096E-06</v>
+        <v>-5.652223145659262E-06</v>
       </c>
       <c r="V2">
-        <v>-5.668067093259482E-06</v>
+        <v>-5.668067539159094E-06</v>
       </c>
       <c r="W2">
-        <v>2.391603061792329E-12</v>
+        <v>1.615279863056732E-15</v>
       </c>
       <c r="X2">
-        <v>-5.25298961084823E-09</v>
+        <v>-5.254182889796249E-09</v>
       </c>
       <c r="Y2">
-        <v>5.244871472203577E-09</v>
+        <v>5.244543721406994E-09</v>
       </c>
       <c r="Z2">
-        <v>-34.08333643952921</v>
+        <v>-34.08333644318964</v>
       </c>
       <c r="AA2">
-        <v>-90.04629115657826</v>
+        <v>-90.04629991903678</v>
       </c>
       <c r="AB2">
-        <v>-90.04629278017691</v>
+        <v>-90.04629991893239</v>
       </c>
       <c r="AC2">
-        <v>145.9279600781438</v>
+        <v>145.9279600744827</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4783,40 +4783,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.049087166092982</v>
+        <v>1.049087166092866</v>
       </c>
       <c r="AH2">
-        <v>1.050000091762777</v>
+        <v>1.050000091762733</v>
       </c>
       <c r="AI2">
-        <v>1.050000150765687</v>
+        <v>1.050000150765694</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.388322158404412</v>
+        <v>1.388322158350399</v>
       </c>
       <c r="AL2">
-        <v>1.389414954384012</v>
+        <v>1.38941495438325</v>
       </c>
       <c r="AM2">
-        <v>-0.05988436329795214</v>
+        <v>-0.0598843632978054</v>
       </c>
       <c r="AN2">
-        <v>-120.0000168972827</v>
+        <v>-120.0000168972843</v>
       </c>
       <c r="AO2">
-        <v>120.0000150384275</v>
+        <v>120.0000150384241</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1272450060646</v>
+        <v>-139.1272450071404</v>
       </c>
       <c r="AR2">
-        <v>139.0751989944364</v>
+        <v>139.0751989924374</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -4860,40 +4860,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-6.462779361820247E-20</v>
+        <v>7.608357526830273E-23</v>
       </c>
       <c r="O3">
-        <v>2.017735794459996E-09</v>
+        <v>2.017316527910177E-09</v>
       </c>
       <c r="P3">
-        <v>2.020925843943029E-09</v>
+        <v>2.022881669154845E-09</v>
       </c>
       <c r="Q3">
-        <v>4.74445818804756E-17</v>
+        <v>1.421569405189753E-16</v>
       </c>
       <c r="R3">
-        <v>-2.017735806275653E-09</v>
+        <v>-2.017316492397866E-09</v>
       </c>
       <c r="S3">
-        <v>-2.020925855771419E-09</v>
+        <v>-2.022881633642535E-09</v>
       </c>
       <c r="T3">
-        <v>2.891692558999471E-19</v>
+        <v>1.142823350180184E-22</v>
       </c>
       <c r="U3">
-        <v>1.751704989810079E-09</v>
+        <v>1.751394306910338E-09</v>
       </c>
       <c r="V3">
-        <v>-1.747373963958519E-09</v>
+        <v>-1.748181188601086E-09</v>
       </c>
       <c r="W3">
-        <v>3.182505808700292E-17</v>
+        <v>9.604277848143734E-17</v>
       </c>
       <c r="X3">
-        <v>-1.751704997845677E-09</v>
+        <v>-1.751394282917818E-09</v>
       </c>
       <c r="Y3">
-        <v>1.747373955916875E-09</v>
+        <v>1.748181212593605E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4917,37 +4917,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.388322158404412</v>
+        <v>1.388322158350399</v>
       </c>
       <c r="AI3">
-        <v>1.389414954384012</v>
+        <v>1.38941495438325</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.388322165777359</v>
+        <v>1.388322136240584</v>
       </c>
       <c r="AL3">
-        <v>1.389414956301959</v>
+        <v>1.389414948572677</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1272450060646</v>
+        <v>-139.1272450071404</v>
       </c>
       <c r="AO3">
-        <v>139.0751989944364</v>
+        <v>139.0751989924374</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.127245042047</v>
+        <v>-139.127244896389</v>
       </c>
       <c r="AR3">
-        <v>139.0751992908124</v>
+        <v>139.075198105803</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -4991,40 +4991,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-6.461373185422959E-20</v>
+        <v>7.608357590860225E-23</v>
       </c>
       <c r="O4">
-        <v>2.018402931906649E-09</v>
+        <v>2.017316567694803E-09</v>
       </c>
       <c r="P4">
-        <v>2.023726706718687E-09</v>
+        <v>2.022881671738686E-09</v>
       </c>
       <c r="Q4">
-        <v>2.846792289203044E-17</v>
+        <v>8.529413442637135E-17</v>
       </c>
       <c r="R4">
-        <v>-2.018402939007178E-09</v>
+        <v>-2.017316546387416E-09</v>
       </c>
       <c r="S4">
-        <v>-2.023726713807211E-09</v>
+        <v>-2.0228816504313E-09</v>
       </c>
       <c r="T4">
-        <v>2.890528842147457E-19</v>
+        <v>1.142823353844427E-22</v>
       </c>
       <c r="U4">
-        <v>1.750612490597233E-09</v>
+        <v>1.751394290380388E-09</v>
       </c>
       <c r="V4">
-        <v>-1.74896603700501E-09</v>
+        <v>-1.748181224867657E-09</v>
       </c>
       <c r="W4">
-        <v>1.89598214828823E-17</v>
+        <v>5.762562292626128E-17</v>
       </c>
       <c r="X4">
-        <v>-1.750612495419236E-09</v>
+        <v>-1.751394275984876E-09</v>
       </c>
       <c r="Y4">
-        <v>1.748966032183641E-09</v>
+        <v>1.748181239263169E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5048,37 +5048,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.388322158404412</v>
+        <v>1.388322158350399</v>
       </c>
       <c r="AI4">
-        <v>1.389414954384012</v>
+        <v>1.38941495438325</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.388322162833369</v>
+        <v>1.38832214508451</v>
       </c>
       <c r="AL4">
-        <v>1.389414955532315</v>
+        <v>1.389414950896906</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1272450060646</v>
+        <v>-139.1272450071404</v>
       </c>
       <c r="AO4">
-        <v>139.0751989944364</v>
+        <v>139.0751989924374</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1272450277155</v>
+        <v>-139.1272449406896</v>
       </c>
       <c r="AR4">
-        <v>139.0751991718629</v>
+        <v>139.0751984604568</v>
       </c>
     </row>
   </sheetData>
@@ -5230,16 +5230,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.2055029044507891</v>
+        <v>0.2055029044606622</v>
       </c>
       <c r="C2">
-        <v>4.890713095090809E-05</v>
+        <v>4.89071326321542E-05</v>
       </c>
       <c r="D2">
-        <v>4.890713724529205E-05</v>
+        <v>4.890713263211404E-05</v>
       </c>
       <c r="E2">
-        <v>0.2054755099922268</v>
+        <v>0.2054755100020999</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5248,16 +5248,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.04745886358875738</v>
+        <v>0.04745886359103748</v>
       </c>
       <c r="I2">
-        <v>1.129461825622255E-05</v>
+        <v>1.129461864448972E-05</v>
       </c>
       <c r="J2">
-        <v>1.129461970984828E-05</v>
+        <v>1.129461864448044E-05</v>
       </c>
       <c r="K2">
-        <v>0.04745253710945301</v>
+        <v>0.04745253711173311</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -5266,52 +5266,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0432283433238681</v>
+        <v>0.04322834332378379</v>
       </c>
       <c r="O2">
-        <v>1.076458454056584E-05</v>
+        <v>1.076458539488558E-05</v>
       </c>
       <c r="P2">
-        <v>-1.075454819638663E-05</v>
+        <v>-1.075454672461668E-05</v>
       </c>
       <c r="Q2">
-        <v>-3.540138978117439E-12</v>
+        <v>6.759153734234993E-17</v>
       </c>
       <c r="R2">
-        <v>-6.640013128697451E-09</v>
+        <v>-6.641350888074526E-09</v>
       </c>
       <c r="S2">
-        <v>-6.658318486604443E-09</v>
+        <v>-6.660246341726437E-09</v>
       </c>
       <c r="T2">
-        <v>0.02918363701731552</v>
+        <v>0.02918363702190721</v>
       </c>
       <c r="U2">
-        <v>-6.203348707916922E-06</v>
+        <v>-6.203348080812032E-06</v>
       </c>
       <c r="V2">
-        <v>-6.220736814908594E-06</v>
+        <v>-6.220737018803331E-06</v>
       </c>
       <c r="W2">
-        <v>2.522377988688859E-12</v>
+        <v>1.780678570741009E-15</v>
       </c>
       <c r="X2">
-        <v>-5.766010140908741E-09</v>
+        <v>-5.766422620384267E-09</v>
       </c>
       <c r="Y2">
-        <v>5.755895659099659E-09</v>
+        <v>5.755513208178505E-09</v>
       </c>
       <c r="Z2">
-        <v>-34.08618547761688</v>
+        <v>-34.08618548184842</v>
       </c>
       <c r="AA2">
-        <v>-90.04629444552131</v>
+        <v>-90.04629891840057</v>
       </c>
       <c r="AB2">
-        <v>-90.04629470590321</v>
+        <v>-90.04629891825394</v>
       </c>
       <c r="AC2">
-        <v>145.925111128489</v>
+        <v>145.9251111242571</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -5320,40 +5320,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.098998247271502</v>
+        <v>1.098998247271365</v>
       </c>
       <c r="AH2">
-        <v>1.100000176885164</v>
+        <v>1.100000176885143</v>
       </c>
       <c r="AI2">
-        <v>1.100000241641217</v>
+        <v>1.100000241641218</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.454397733370175</v>
+        <v>1.454397733334106</v>
       </c>
       <c r="AL2">
-        <v>1.455578333982022</v>
+        <v>1.455578334001392</v>
       </c>
       <c r="AM2">
-        <v>-0.06273340212609783</v>
+        <v>-0.06273340212525985</v>
       </c>
       <c r="AN2">
-        <v>-120.0000177019155</v>
+        <v>-120.0000177019167</v>
       </c>
       <c r="AO2">
-        <v>120.0000157545419</v>
+        <v>120.0000157545396</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1274707880006</v>
+        <v>-139.1274707896185</v>
       </c>
       <c r="AR2">
-        <v>139.0737992424376</v>
+        <v>139.0737992409956</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -5397,40 +5397,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.291662968616433E-19</v>
+        <v>8.955798663311129E-23</v>
       </c>
       <c r="O3">
-        <v>2.215109330660837E-09</v>
+        <v>2.213783571317113E-09</v>
       </c>
       <c r="P3">
-        <v>2.219818936527013E-09</v>
+        <v>2.220082082089812E-09</v>
       </c>
       <c r="Q3">
-        <v>5.210192322893964E-17</v>
+        <v>1.560180628587959E-16</v>
       </c>
       <c r="R3">
-        <v>-2.215109343635503E-09</v>
+        <v>-2.213783532345371E-09</v>
       </c>
       <c r="S3">
-        <v>-2.219818949499971E-09</v>
+        <v>-2.22008204311807E-09</v>
       </c>
       <c r="T3">
-        <v>3.461819830211854E-19</v>
+        <v>1.221475184075948E-22</v>
       </c>
       <c r="U3">
-        <v>1.922469176609357E-09</v>
+        <v>1.922140878842266E-09</v>
       </c>
       <c r="V3">
-        <v>-1.917636382054378E-09</v>
+        <v>-1.91850434691727E-09</v>
       </c>
       <c r="W3">
-        <v>3.489475817202433E-17</v>
+        <v>1.05407511467057E-16</v>
       </c>
       <c r="X3">
-        <v>-1.922469185432136E-09</v>
+        <v>-1.922140852512515E-09</v>
       </c>
       <c r="Y3">
-        <v>1.917636373226429E-09</v>
+        <v>1.918504373247021E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5454,37 +5454,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.454397733370175</v>
+        <v>1.454397733334106</v>
       </c>
       <c r="AI3">
-        <v>1.455578333982022</v>
+        <v>1.455578334001392</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.454397741096751</v>
+        <v>1.454397710172528</v>
       </c>
       <c r="AL3">
-        <v>1.455578335989709</v>
+        <v>1.455578327913806</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1274707880006</v>
+        <v>-139.1274707896185</v>
       </c>
       <c r="AO3">
-        <v>139.0737992424376</v>
+        <v>139.0737992409956</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.127470823966</v>
+        <v>-139.1274706788272</v>
       </c>
       <c r="AR3">
-        <v>139.0737995385662</v>
+        <v>139.0737983544044</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -5528,40 +5528,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.292313469444644E-19</v>
+        <v>8.955798913596934E-23</v>
       </c>
       <c r="O4">
-        <v>2.211964366111913E-09</v>
+        <v>2.213783622485242E-09</v>
       </c>
       <c r="P4">
-        <v>2.21969656536392E-09</v>
+        <v>2.220082142462711E-09</v>
       </c>
       <c r="Q4">
-        <v>3.130384407570817E-17</v>
+        <v>9.361080308409073E-17</v>
       </c>
       <c r="R4">
-        <v>-2.211964373894184E-09</v>
+        <v>-2.213783599102196E-09</v>
       </c>
       <c r="S4">
-        <v>-2.219696573138132E-09</v>
+        <v>-2.220082119079665E-09</v>
       </c>
       <c r="T4">
-        <v>3.461577200999505E-19</v>
+        <v>1.221475182957516E-22</v>
       </c>
       <c r="U4">
-        <v>1.920039111852752E-09</v>
+        <v>1.922140860840598E-09</v>
       </c>
       <c r="V4">
-        <v>-1.918114331459959E-09</v>
+        <v>-1.918504390350384E-09</v>
       </c>
       <c r="W4">
-        <v>2.079675895988187E-17</v>
+        <v>6.324445893563608E-17</v>
       </c>
       <c r="X4">
-        <v>-1.920039117142871E-09</v>
+        <v>-1.922140845042747E-09</v>
       </c>
       <c r="Y4">
-        <v>1.918114326170737E-09</v>
+        <v>1.918504406148236E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5585,37 +5585,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.454397733370175</v>
+        <v>1.454397733334106</v>
       </c>
       <c r="AI4">
-        <v>1.455578333982022</v>
+        <v>1.455578334001392</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.454397738010256</v>
+        <v>1.454397719437159</v>
       </c>
       <c r="AL4">
-        <v>1.455578335184723</v>
+        <v>1.45557833034884</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1274707880006</v>
+        <v>-139.1274707896185</v>
       </c>
       <c r="AO4">
-        <v>139.0737992424376</v>
+        <v>139.0737992409956</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1274708096432</v>
+        <v>-139.1274707231437</v>
       </c>
       <c r="AR4">
-        <v>139.0737994198749</v>
+        <v>139.0737987090409</v>
       </c>
     </row>
   </sheetData>
@@ -5767,16 +5767,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.02926067670397267</v>
+        <v>0.02926067670428893</v>
       </c>
       <c r="C2">
-        <v>6.963387923448567E-06</v>
+        <v>6.963388379408709E-06</v>
       </c>
       <c r="D2">
-        <v>6.96338916469672E-06</v>
+        <v>6.963388379394437E-06</v>
       </c>
       <c r="E2">
-        <v>0.02925677657301176</v>
+        <v>0.02925677657332842</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5785,16 +5785,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.00675746392937775</v>
+        <v>0.006757463929450789</v>
       </c>
       <c r="I2">
-        <v>1.608125580792866E-06</v>
+        <v>1.608125686092352E-06</v>
       </c>
       <c r="J2">
-        <v>1.608125867446852E-06</v>
+        <v>1.608125686089056E-06</v>
       </c>
       <c r="K2">
-        <v>0.006756563232700266</v>
+        <v>0.006756563232773398</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -5803,52 +5803,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.00515591972437203</v>
+        <v>0.005155919724109665</v>
       </c>
       <c r="O2">
-        <v>1.580087682689355E-06</v>
+        <v>1.580087886458694E-06</v>
       </c>
       <c r="P2">
-        <v>-1.30564744661538E-06</v>
+        <v>-1.305647146959946E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.004279795170136842</v>
+        <v>-0.004279795169875804</v>
       </c>
       <c r="R2">
-        <v>-3.853067014560224E-10</v>
+        <v>-3.855316918572416E-10</v>
       </c>
       <c r="S2">
-        <v>-6.4094652365444E-10</v>
+        <v>-6.412639179756633E-10</v>
       </c>
       <c r="T2">
-        <v>0.004872870770328523</v>
+        <v>0.004872870770717654</v>
       </c>
       <c r="U2">
-        <v>-5.953675911793419E-07</v>
+        <v>-5.953673639552135E-07</v>
       </c>
       <c r="V2">
-        <v>-1.070712631406303E-06</v>
+        <v>-1.070712696507279E-06</v>
       </c>
       <c r="W2">
-        <v>-0.004279796392196462</v>
+        <v>-0.004279796392606942</v>
       </c>
       <c r="X2">
-        <v>-8.460887358788481E-10</v>
+        <v>-8.463075062948321E-10</v>
       </c>
       <c r="Y2">
-        <v>6.986095707297751E-10</v>
+        <v>6.986604298175931E-10</v>
       </c>
       <c r="Z2">
-        <v>-43.39093971715987</v>
+        <v>-43.39093972089893</v>
       </c>
       <c r="AA2">
-        <v>-99.35389354375417</v>
+        <v>-99.35390319677992</v>
       </c>
       <c r="AB2">
-        <v>-99.35389504090558</v>
+        <v>-99.35390319663745</v>
       </c>
       <c r="AC2">
-        <v>136.620356800513</v>
+        <v>136.6203567967735</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -5857,40 +5857,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.049839066787875</v>
+        <v>1.049839066787864</v>
       </c>
       <c r="AH2">
-        <v>1.049999965371931</v>
+        <v>1.049999965371924</v>
       </c>
       <c r="AI2">
-        <v>1.049999988175752</v>
+        <v>1.049999988175753</v>
       </c>
       <c r="AJ2">
-        <v>0.8958023523882854</v>
+        <v>0.8958023523942295</v>
       </c>
       <c r="AK2">
-        <v>1.080031916029691</v>
+        <v>1.080031916017599</v>
       </c>
       <c r="AL2">
-        <v>1.101347223170466</v>
+        <v>1.101347223170612</v>
       </c>
       <c r="AM2">
-        <v>-0.007605892416703676</v>
+        <v>-0.007605892416212932</v>
       </c>
       <c r="AN2">
-        <v>-120.0000026707763</v>
+        <v>-120.0000026707766</v>
       </c>
       <c r="AO2">
-        <v>120.0000019523536</v>
+        <v>120.0000019523531</v>
       </c>
       <c r="AP2">
-        <v>1.620364980681969</v>
+        <v>1.620364981437394</v>
       </c>
       <c r="AQ2">
-        <v>-123.8901468897449</v>
+        <v>-123.890146889667</v>
       </c>
       <c r="AR2">
-        <v>123.1484816073652</v>
+        <v>123.1484816068063</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -5934,40 +5934,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.051707681136081E-10</v>
+        <v>-5.050996490121963E-10</v>
       </c>
       <c r="O3">
-        <v>1.285489109331763E-10</v>
+        <v>1.285105578057695E-10</v>
       </c>
       <c r="P3">
-        <v>2.136642733329745E-10</v>
+        <v>2.137546370326052E-10</v>
       </c>
       <c r="Q3">
-        <v>5.051707691676082E-10</v>
+        <v>5.050996521749978E-10</v>
       </c>
       <c r="R3">
-        <v>-1.285489111961209E-10</v>
+        <v>-1.285105570156685E-10</v>
       </c>
       <c r="S3">
-        <v>-2.136642735961431E-10</v>
+        <v>-2.137546362425043E-10</v>
       </c>
       <c r="T3">
-        <v>-9.757866538514643E-11</v>
+        <v>-9.752259939199184E-11</v>
       </c>
       <c r="U3">
-        <v>2.822055581971657E-10</v>
+        <v>2.821024986410788E-10</v>
       </c>
       <c r="V3">
-        <v>-2.327769722297409E-10</v>
+        <v>-2.328868033230887E-10</v>
       </c>
       <c r="W3">
-        <v>9.757866609980848E-11</v>
+        <v>9.752260152881649E-11</v>
       </c>
       <c r="X3">
-        <v>-2.822055583759672E-10</v>
+        <v>-2.821024981072776E-10</v>
       </c>
       <c r="Y3">
-        <v>2.327769720506433E-10</v>
+        <v>2.328868038568899E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5988,40 +5988,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.8958023523882854</v>
+        <v>0.8958023523942295</v>
       </c>
       <c r="AH3">
-        <v>1.080031916029691</v>
+        <v>1.080031916017599</v>
       </c>
       <c r="AI3">
-        <v>1.101347223170466</v>
+        <v>1.101347223170612</v>
       </c>
       <c r="AJ3">
-        <v>0.895802354426066</v>
+        <v>0.8958023585073216</v>
       </c>
       <c r="AK3">
-        <v>1.080031916976019</v>
+        <v>1.080031913183988</v>
       </c>
       <c r="AL3">
-        <v>1.101347223330861</v>
+        <v>1.101347222679357</v>
       </c>
       <c r="AM3">
-        <v>1.620364980681969</v>
+        <v>1.620364981437394</v>
       </c>
       <c r="AN3">
-        <v>-123.8901468897449</v>
+        <v>-123.890146889667</v>
       </c>
       <c r="AO3">
-        <v>123.1484816073652</v>
+        <v>123.1484816068063</v>
       </c>
       <c r="AP3">
-        <v>1.620365036562091</v>
+        <v>1.620365148335489</v>
       </c>
       <c r="AQ3">
-        <v>-123.8901469202621</v>
+        <v>-123.8901467976744</v>
       </c>
       <c r="AR3">
-        <v>123.1484816644823</v>
+        <v>123.1484814358795</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -6065,40 +6065,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.04883774050718E-10</v>
+        <v>-5.050996554013541E-10</v>
       </c>
       <c r="O4">
-        <v>1.283939618927819E-10</v>
+        <v>1.285105633617747E-10</v>
       </c>
       <c r="P4">
-        <v>2.136239795604455E-10</v>
+        <v>2.137546406999061E-10</v>
       </c>
       <c r="Q4">
-        <v>5.048837746825814E-10</v>
+        <v>5.05099657299035E-10</v>
       </c>
       <c r="R4">
-        <v>-1.283939620505281E-10</v>
+        <v>-1.285105628877141E-10</v>
       </c>
       <c r="S4">
-        <v>-2.136239797180228E-10</v>
+        <v>-2.137546402258455E-10</v>
       </c>
       <c r="T4">
-        <v>-9.751960598831522E-11</v>
+        <v>-9.752259335436587E-11</v>
       </c>
       <c r="U4">
-        <v>2.81717981147113E-10</v>
+        <v>2.821025024323285E-10</v>
       </c>
       <c r="V4">
-        <v>-2.327534392152416E-10</v>
+        <v>-2.328868077736727E-10</v>
       </c>
       <c r="W4">
-        <v>9.751960641650847E-11</v>
+        <v>9.752259463646068E-11</v>
       </c>
       <c r="X4">
-        <v>-2.817179812543247E-10</v>
+        <v>-2.821025021120478E-10</v>
       </c>
       <c r="Y4">
-        <v>2.327534391081206E-10</v>
+        <v>2.328868080939534E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -6119,40 +6119,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.8958023523882854</v>
+        <v>0.8958023523942295</v>
       </c>
       <c r="AH4">
-        <v>1.080031916029691</v>
+        <v>1.080031916017599</v>
       </c>
       <c r="AI4">
-        <v>1.101347223170466</v>
+        <v>1.101347223170612</v>
       </c>
       <c r="AJ4">
-        <v>0.8958023536105296</v>
+        <v>0.8958023560620848</v>
       </c>
       <c r="AK4">
-        <v>1.080031916598238</v>
+        <v>1.080031914317433</v>
       </c>
       <c r="AL4">
-        <v>1.101347223266792</v>
+        <v>1.101347222875859</v>
       </c>
       <c r="AM4">
-        <v>1.620364980681969</v>
+        <v>1.620364981437394</v>
       </c>
       <c r="AN4">
-        <v>-123.8901468897449</v>
+        <v>-123.890146889667</v>
       </c>
       <c r="AO4">
-        <v>123.1484816073652</v>
+        <v>123.1484816068063</v>
       </c>
       <c r="AP4">
-        <v>1.620365014174947</v>
+        <v>1.620365081576255</v>
       </c>
       <c r="AQ4">
-        <v>-123.8901469080811</v>
+        <v>-123.8901468344715</v>
       </c>
       <c r="AR4">
-        <v>123.1484816415559</v>
+        <v>123.1484815042502</v>
       </c>
     </row>
   </sheetData>
@@ -6526,16 +6526,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.03065382104385409</v>
+        <v>0.0306538210440366</v>
       </c>
       <c r="C2">
-        <v>7.295227160294851E-06</v>
+        <v>7.295227750758578E-06</v>
       </c>
       <c r="D2">
-        <v>7.295228331981668E-06</v>
+        <v>7.295227750744191E-06</v>
       </c>
       <c r="E2">
-        <v>0.03064973475206851</v>
+        <v>0.03064973475225124</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -6544,16 +6544,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.007079196838032162</v>
+        <v>0.007079196838074312</v>
       </c>
       <c r="I2">
-        <v>1.684760571023169E-06</v>
+        <v>1.684760707384928E-06</v>
       </c>
       <c r="J2">
-        <v>1.684760841612653E-06</v>
+        <v>1.684760707381605E-06</v>
       </c>
       <c r="K2">
-        <v>0.007078253149353143</v>
+        <v>0.007078253149395343</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -6562,52 +6562,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.005658569374785873</v>
+        <v>0.005658569374458033</v>
       </c>
       <c r="O2">
-        <v>1.734186263078113E-06</v>
+        <v>1.734186452485131E-06</v>
       </c>
       <c r="P2">
-        <v>-1.43305547262675E-06</v>
+        <v>-1.433055266572351E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.004697031523268656</v>
+        <v>-0.00469703152293725</v>
       </c>
       <c r="R2">
-        <v>-4.229140617772943E-10</v>
+        <v>-4.231137992530354E-10</v>
       </c>
       <c r="S2">
-        <v>-7.035733848422325E-10</v>
+        <v>-7.037901003804698E-10</v>
       </c>
       <c r="T2">
-        <v>0.005347926041350469</v>
+        <v>0.005347926041764724</v>
       </c>
       <c r="U2">
-        <v>-6.535168269839441E-07</v>
+        <v>-6.535167497320973E-07</v>
       </c>
       <c r="V2">
-        <v>-1.175091277333161E-06</v>
+        <v>-1.175091295756594E-06</v>
       </c>
       <c r="W2">
-        <v>-0.004697032864600205</v>
+        <v>-0.004697032865026467</v>
       </c>
       <c r="X2">
-        <v>-9.287570059819153E-10</v>
+        <v>-9.288228937826983E-10</v>
       </c>
       <c r="Y2">
-        <v>7.667670204330953E-10</v>
+        <v>7.66774351337925E-10</v>
       </c>
       <c r="Z2">
-        <v>-43.3913018992516</v>
+        <v>-43.39130190312371</v>
       </c>
       <c r="AA2">
-        <v>-99.35141103975964</v>
+        <v>-99.35141533966724</v>
       </c>
       <c r="AB2">
-        <v>-99.35141085976279</v>
+        <v>-99.3514153395862</v>
       </c>
       <c r="AC2">
-        <v>136.6199947068541</v>
+        <v>136.6199947029818</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -6616,40 +6616,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.099823451853059</v>
+        <v>1.099823451853048</v>
       </c>
       <c r="AH2">
-        <v>1.100000038173322</v>
+        <v>1.100000038173319</v>
       </c>
       <c r="AI2">
         <v>1.100000063197469</v>
       </c>
       <c r="AJ2">
-        <v>0.9384528204070008</v>
+        <v>0.938452820410882</v>
       </c>
       <c r="AK2">
-        <v>1.13146136503709</v>
+        <v>1.131461365027615</v>
       </c>
       <c r="AL2">
-        <v>1.15379238726773</v>
+        <v>1.153792387269966</v>
       </c>
       <c r="AM2">
-        <v>-0.007968019726462092</v>
+        <v>-0.007968019725887929</v>
       </c>
       <c r="AN2">
-        <v>-120.0000027980195</v>
+        <v>-120.0000027980197</v>
       </c>
       <c r="AO2">
-        <v>120.0000020454817</v>
+        <v>120.0000020454813</v>
       </c>
       <c r="AP2">
-        <v>1.620002887837867</v>
+        <v>1.620002888586694</v>
       </c>
       <c r="AQ2">
-        <v>-123.8901304279212</v>
+        <v>-123.8901304280121</v>
       </c>
       <c r="AR2">
-        <v>123.1484424734919</v>
+        <v>123.148442473113</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -6693,40 +6693,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.544181239949471E-10</v>
+        <v>-5.543700062056124E-10</v>
       </c>
       <c r="O3">
-        <v>1.409445163151045E-10</v>
+        <v>1.410379274064129E-10</v>
       </c>
       <c r="P3">
-        <v>2.345577332582004E-10</v>
+        <v>2.345966998796588E-10</v>
       </c>
       <c r="Q3">
-        <v>5.544181251514465E-10</v>
+        <v>5.543700096770426E-10</v>
       </c>
       <c r="R3">
-        <v>-1.409445166035825E-10</v>
+        <v>-1.410379265392851E-10</v>
       </c>
       <c r="S3">
-        <v>-2.345577335469081E-10</v>
+        <v>-2.34596699012531E-10</v>
       </c>
       <c r="T3">
-        <v>-1.070429388006469E-10</v>
+        <v>-1.070069309577015E-10</v>
       </c>
       <c r="U3">
-        <v>3.096367549547688E-10</v>
+        <v>3.09607629163698E-10</v>
       </c>
       <c r="V3">
-        <v>-2.555567919387942E-10</v>
+        <v>-2.555914439669584E-10</v>
       </c>
       <c r="W3">
-        <v>1.070429395847497E-10</v>
+        <v>1.070069333030391E-10</v>
       </c>
       <c r="X3">
-        <v>-3.096367551511254E-10</v>
+        <v>-3.096076285778566E-10</v>
       </c>
       <c r="Y3">
-        <v>2.555567917423737E-10</v>
+        <v>2.555914445527998E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -6747,40 +6747,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9384528204070008</v>
+        <v>0.938452820410882</v>
       </c>
       <c r="AH3">
-        <v>1.13146136503709</v>
+        <v>1.131461365027615</v>
       </c>
       <c r="AI3">
-        <v>1.15379238726773</v>
+        <v>1.153792387269966</v>
       </c>
       <c r="AJ3">
-        <v>0.9384528225412785</v>
+        <v>0.9384528268151571</v>
       </c>
       <c r="AK3">
-        <v>1.131461366028936</v>
+        <v>1.131461362059104</v>
       </c>
       <c r="AL3">
-        <v>1.153792387435746</v>
+        <v>1.153792386755302</v>
       </c>
       <c r="AM3">
-        <v>1.620002887837867</v>
+        <v>1.620002888586694</v>
       </c>
       <c r="AN3">
-        <v>-123.8901304279212</v>
+        <v>-123.8901304280121</v>
       </c>
       <c r="AO3">
-        <v>123.1484424734919</v>
+        <v>123.148442473113</v>
       </c>
       <c r="AP3">
-        <v>1.620002943711855</v>
+        <v>1.620003055511146</v>
       </c>
       <c r="AQ3">
-        <v>-123.8901304584393</v>
+        <v>-123.8901303360192</v>
       </c>
       <c r="AR3">
-        <v>123.1484425305623</v>
+        <v>123.1484423021877</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -6824,40 +6824,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.542246151191723E-10</v>
+        <v>-5.543700086514929E-10</v>
       </c>
       <c r="O4">
-        <v>1.408486122430178E-10</v>
+        <v>1.410379334052746E-10</v>
       </c>
       <c r="P4">
-        <v>2.346477628498728E-10</v>
+        <v>2.345966994693648E-10</v>
       </c>
       <c r="Q4">
-        <v>5.542246158128458E-10</v>
+        <v>5.543700107343511E-10</v>
       </c>
       <c r="R4">
-        <v>-1.408486124161871E-10</v>
+        <v>-1.410379328849979E-10</v>
       </c>
       <c r="S4">
-        <v>-2.34647763022957E-10</v>
+        <v>-2.345966989490881E-10</v>
       </c>
       <c r="T4">
-        <v>-1.069663110686748E-10</v>
+        <v>-1.070069212552332E-10</v>
       </c>
       <c r="U4">
-        <v>3.094170854328273E-10</v>
+        <v>3.096076322275628E-10</v>
       </c>
       <c r="V4">
-        <v>-2.556546614731239E-10</v>
+        <v>-2.555914482191837E-10</v>
       </c>
       <c r="W4">
-        <v>1.06966311538708E-10</v>
+        <v>1.070069226624358E-10</v>
       </c>
       <c r="X4">
-        <v>-3.094170855506595E-10</v>
+        <v>-3.09607631876058E-10</v>
       </c>
       <c r="Y4">
-        <v>2.55654661355435E-10</v>
+        <v>2.555914485706886E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -6878,40 +6878,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9384528204070008</v>
+        <v>0.938452820410882</v>
       </c>
       <c r="AH4">
-        <v>1.13146136503709</v>
+        <v>1.131461365027615</v>
       </c>
       <c r="AI4">
-        <v>1.15379238726773</v>
+        <v>1.153792387269966</v>
       </c>
       <c r="AJ4">
-        <v>0.9384528216874897</v>
+        <v>0.9384528242534471</v>
       </c>
       <c r="AK4">
-        <v>1.13146136563279</v>
+        <v>1.131461363246508</v>
       </c>
       <c r="AL4">
-        <v>1.153792387368586</v>
+        <v>1.153792386961167</v>
       </c>
       <c r="AM4">
-        <v>1.620002887837867</v>
+        <v>1.620002888586694</v>
       </c>
       <c r="AN4">
-        <v>-123.8901304279212</v>
+        <v>-123.8901304280121</v>
       </c>
       <c r="AO4">
-        <v>123.1484424734919</v>
+        <v>123.148442473113</v>
       </c>
       <c r="AP4">
-        <v>1.620002921341386</v>
+        <v>1.620002988741369</v>
       </c>
       <c r="AQ4">
-        <v>-123.890130446256</v>
+        <v>-123.8901303728164</v>
       </c>
       <c r="AR4">
-        <v>123.1484425076857</v>
+        <v>123.1484423705578</v>
       </c>
     </row>
   </sheetData>
@@ -7063,16 +7063,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.1052800862749993</v>
+        <v>0.1052800862772297</v>
       </c>
       <c r="C2">
-        <v>4.223937587636617E-05</v>
+        <v>4.223937506329574E-05</v>
       </c>
       <c r="D2">
-        <v>4.223937474819869E-05</v>
+        <v>4.223937506327567E-05</v>
       </c>
       <c r="E2">
-        <v>0.1052660766156088</v>
+        <v>0.1052660766178398</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7081,16 +7081,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.02431339482276895</v>
+        <v>0.02431339482328405</v>
       </c>
       <c r="I2">
-        <v>9.754766158406058E-06</v>
+        <v>9.754765970635482E-06</v>
       </c>
       <c r="J2">
-        <v>9.754765897866934E-06</v>
+        <v>9.754765970630849E-06</v>
       </c>
       <c r="K2">
-        <v>0.02431015943047261</v>
+        <v>0.02431015943098784</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -7099,52 +7099,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02178342744357413</v>
+        <v>0.02178342744413441</v>
       </c>
       <c r="O2">
-        <v>8.029948677645567E-06</v>
+        <v>8.029948881533841E-06</v>
       </c>
       <c r="P2">
-        <v>-8.021006203551136E-06</v>
+        <v>-8.021006205635428E-06</v>
       </c>
       <c r="Q2">
-        <v>-3.38643677354371E-15</v>
+        <v>2.003470250986856E-17</v>
       </c>
       <c r="R2">
-        <v>-4.957206608512854E-09</v>
+        <v>-4.957769839009468E-09</v>
       </c>
       <c r="S2">
-        <v>-4.972196042370526E-09</v>
+        <v>-4.972251522291908E-09</v>
       </c>
       <c r="T2">
-        <v>0.007653410303231041</v>
+        <v>0.007653410303112207</v>
       </c>
       <c r="U2">
-        <v>-4.625770535805607E-06</v>
+        <v>-4.625769824510718E-06</v>
       </c>
       <c r="V2">
-        <v>-4.641260027567354E-06</v>
+        <v>-4.641260161986142E-06</v>
       </c>
       <c r="W2">
-        <v>-2.247444888870439E-13</v>
+        <v>4.147077977924127E-16</v>
       </c>
       <c r="X2">
-        <v>-4.302837644791987E-09</v>
+        <v>-4.303637794314662E-09</v>
       </c>
       <c r="Y2">
-        <v>4.295107516736348E-09</v>
+        <v>4.295276716695392E-09</v>
       </c>
       <c r="Z2">
-        <v>-19.40578267915587</v>
+        <v>-19.40578267841806</v>
       </c>
       <c r="AA2">
-        <v>-90.05529013167765</v>
+        <v>-90.05529457161398</v>
       </c>
       <c r="AB2">
-        <v>-90.0552938586801</v>
+        <v>-90.05529457155967</v>
       </c>
       <c r="AC2">
-        <v>160.6159051631329</v>
+        <v>160.61590516387</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -7153,28 +7153,28 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9496326612097076</v>
+        <v>0.9496326612097099</v>
       </c>
       <c r="AH2">
-        <v>0.950000130721642</v>
+        <v>0.9500001307216147</v>
       </c>
       <c r="AI2">
-        <v>0.9500001911919679</v>
+        <v>0.9500001911919729</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.256268714671343</v>
+        <v>1.256268714655434</v>
       </c>
       <c r="AL2">
-        <v>1.257316228793888</v>
+        <v>1.257316228787097</v>
       </c>
       <c r="AM2">
-        <v>-0.04731847969576995</v>
+        <v>-0.04731847969705796</v>
       </c>
       <c r="AN2">
-        <v>-120.0000191120072</v>
+        <v>-120.0000191120075</v>
       </c>
       <c r="AO2">
         <v>120.0000170063817</v>
@@ -7183,10 +7183,10 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1365778919865</v>
+        <v>-139.1365778912919</v>
       </c>
       <c r="AR2">
-        <v>139.081430493029</v>
+        <v>139.0814304927868</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -7230,40 +7230,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.114251933485498E-20</v>
+        <v>2.243020278205779E-23</v>
       </c>
       <c r="O3">
-        <v>1.65216001370696E-09</v>
+        <v>1.652589868488836E-09</v>
       </c>
       <c r="P3">
-        <v>1.658223096624544E-09</v>
+        <v>1.657417134178136E-09</v>
       </c>
       <c r="Q3">
-        <v>7.443079130283855E-17</v>
+        <v>2.234282570511017E-16</v>
       </c>
       <c r="R3">
-        <v>-1.652160032305277E-09</v>
+        <v>-1.652589812612794E-09</v>
       </c>
       <c r="S3">
-        <v>-1.658223115221713E-09</v>
+        <v>-1.657417078302093E-09</v>
       </c>
       <c r="T3">
-        <v>-3.021955749005001E-20</v>
+        <v>5.510114100722984E-23</v>
       </c>
       <c r="U3">
-        <v>1.43509211763081E-09</v>
+        <v>1.434545897069834E-09</v>
       </c>
       <c r="V3">
-        <v>-1.432042257949026E-09</v>
+        <v>-1.431758842099238E-09</v>
       </c>
       <c r="W3">
-        <v>2.636903556528519E-17</v>
+        <v>7.86200908461275E-17</v>
       </c>
       <c r="X3">
-        <v>-1.435092124251602E-09</v>
+        <v>-1.434545877408121E-09</v>
       </c>
       <c r="Y3">
-        <v>1.432042251331151E-09</v>
+        <v>1.431758861760951E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -7287,37 +7287,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.256268714671343</v>
+        <v>1.256268714655434</v>
       </c>
       <c r="AI3">
-        <v>1.257316228793888</v>
+        <v>1.257316228787097</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.256268725224057</v>
+        <v>1.256268683033234</v>
       </c>
       <c r="AL3">
-        <v>1.257316234388731</v>
+        <v>1.257316211891947</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1365778919865</v>
+        <v>-139.1365778912919</v>
       </c>
       <c r="AO3">
-        <v>139.081430493029</v>
+        <v>139.0814304927868</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.1365780804355</v>
+        <v>-139.136577321035</v>
       </c>
       <c r="AR3">
-        <v>139.0814309418737</v>
+        <v>139.0814291480081</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -7361,40 +7361,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.114463188189194E-20</v>
+        <v>2.243020376667645E-23</v>
       </c>
       <c r="O4">
-        <v>1.652020014307485E-09</v>
+        <v>1.652589928240354E-09</v>
       </c>
       <c r="P4">
-        <v>1.658568678426469E-09</v>
+        <v>1.657417165747078E-09</v>
       </c>
       <c r="Q4">
-        <v>4.466834102000803E-17</v>
+        <v>1.340569535564581E-16</v>
       </c>
       <c r="R4">
-        <v>-1.652020025469973E-09</v>
+        <v>-1.652589894714727E-09</v>
       </c>
       <c r="S4">
-        <v>-1.658568689584093E-09</v>
+        <v>-1.657417132221451E-09</v>
       </c>
       <c r="T4">
-        <v>-3.022325972559945E-20</v>
+        <v>5.510114248304195E-23</v>
       </c>
       <c r="U4">
-        <v>1.434089706515921E-09</v>
+        <v>1.434545925708612E-09</v>
       </c>
       <c r="V4">
-        <v>-1.433098463394177E-09</v>
+        <v>-1.431758894478645E-09</v>
       </c>
       <c r="W4">
-        <v>1.582497913467215E-17</v>
+        <v>4.71720354853963E-17</v>
       </c>
       <c r="X4">
-        <v>-1.434089710484608E-09</v>
+        <v>-1.434545913911584E-09</v>
       </c>
       <c r="Y4">
-        <v>1.433098459430453E-09</v>
+        <v>1.431758906275673E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -7418,37 +7418,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.256268714671343</v>
+        <v>1.256268714655434</v>
       </c>
       <c r="AI4">
-        <v>1.257316228793888</v>
+        <v>1.257316228787097</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.256268721006024</v>
+        <v>1.256268695682113</v>
       </c>
       <c r="AL4">
-        <v>1.257316232150121</v>
+        <v>1.257316218650007</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1365778919865</v>
+        <v>-139.1365778912919</v>
       </c>
       <c r="AO4">
-        <v>139.081430493029</v>
+        <v>139.0814304927868</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1365780051425</v>
+        <v>-139.1365775491378</v>
       </c>
       <c r="AR4">
-        <v>139.0814307621088</v>
+        <v>139.0814296859196</v>
       </c>
     </row>
   </sheetData>
@@ -7600,16 +7600,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.09974105919489404</v>
+        <v>0.09974105919220888</v>
       </c>
       <c r="C2">
-        <v>4.001624982281317E-05</v>
+        <v>4.001624948982588E-05</v>
       </c>
       <c r="D2">
-        <v>4.001624855350602E-05</v>
+        <v>4.001624948980457E-05</v>
       </c>
       <c r="E2">
-        <v>0.09972778852647335</v>
+        <v>0.09972778852378754</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7618,16 +7618,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.02303421129340868</v>
+        <v>0.02303421129278857</v>
       </c>
       <c r="I2">
-        <v>9.241357180571151E-06</v>
+        <v>9.241357103671031E-06</v>
       </c>
       <c r="J2">
-        <v>9.241356887437216E-06</v>
+        <v>9.241357103666106E-06</v>
       </c>
       <c r="K2">
-        <v>0.02303114656376901</v>
+        <v>0.02303114656314875</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -7636,52 +7636,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01955157286695428</v>
+        <v>0.01955157286660866</v>
       </c>
       <c r="O2">
-        <v>7.20693489030573E-06</v>
+        <v>7.206934554537329E-06</v>
       </c>
       <c r="P2">
-        <v>-7.198907991558471E-06</v>
+        <v>-7.198908386251605E-06</v>
       </c>
       <c r="Q2">
-        <v>2.759625958893441E-13</v>
+        <v>-2.845546924635243E-18</v>
       </c>
       <c r="R2">
-        <v>-4.450548025870795E-09</v>
+        <v>-4.44993612622459E-09</v>
       </c>
       <c r="S2">
-        <v>-4.46321864928819E-09</v>
+        <v>-4.462598422186263E-09</v>
       </c>
       <c r="T2">
-        <v>0.006869268374809116</v>
+        <v>0.006869268374111672</v>
       </c>
       <c r="U2">
-        <v>-4.151659711316974E-06</v>
+        <v>-4.151660155531197E-06</v>
       </c>
       <c r="V2">
-        <v>-4.16556317384473E-06</v>
+        <v>-4.165562880300111E-06</v>
       </c>
       <c r="W2">
-        <v>-5.92047949844306E-13</v>
+        <v>3.933390693592017E-16</v>
       </c>
       <c r="X2">
-        <v>-3.862935510056401E-09</v>
+        <v>-3.862526531212442E-09</v>
       </c>
       <c r="Y2">
-        <v>3.855412175087152E-09</v>
+        <v>3.855215885122759E-09</v>
       </c>
       <c r="Z2">
-        <v>-19.40329314644089</v>
+        <v>-19.40329314493771</v>
       </c>
       <c r="AA2">
-        <v>-90.05529853691108</v>
+        <v>-90.05529473071452</v>
       </c>
       <c r="AB2">
-        <v>-90.05529784269797</v>
+        <v>-90.05529473066437</v>
       </c>
       <c r="AC2">
-        <v>160.6183945846082</v>
+        <v>160.6183945861123</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -7690,40 +7690,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8996703063370969</v>
+        <v>0.8996703063371242</v>
       </c>
       <c r="AH2">
-        <v>0.9000001041807869</v>
+        <v>0.9000001041808048</v>
       </c>
       <c r="AI2">
-        <v>0.9000001584533808</v>
+        <v>0.9000001584533712</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.19016901644547</v>
+        <v>1.190169016475026</v>
       </c>
       <c r="AL2">
-        <v>1.19113580528599</v>
+        <v>1.191135805290812</v>
       </c>
       <c r="AM2">
-        <v>-0.04482894593032193</v>
+        <v>-0.044828945929665</v>
       </c>
       <c r="AN2">
-        <v>-120.0000181061129</v>
+        <v>-120.0000181061122</v>
       </c>
       <c r="AO2">
-        <v>120.0000161113079</v>
+        <v>120.0000161113089</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-139.1361552982339</v>
+        <v>-139.1361552980736</v>
       </c>
       <c r="AR2">
-        <v>139.0824298852958</v>
+        <v>139.0824298864981</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -7767,40 +7767,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>9.146070694250516E-21</v>
+        <v>1.8318676930263E-23</v>
       </c>
       <c r="O3">
-        <v>1.483356287056076E-09</v>
+        <v>1.483311973969541E-09</v>
       </c>
       <c r="P3">
-        <v>1.486695924232783E-09</v>
+        <v>1.487532775613708E-09</v>
       </c>
       <c r="Q3">
-        <v>6.679765706689108E-17</v>
+        <v>2.005284047030379E-16</v>
       </c>
       <c r="R3">
-        <v>-1.48335630374247E-09</v>
+        <v>-1.48331192381837E-09</v>
       </c>
       <c r="S3">
-        <v>-1.486695940930508E-09</v>
+        <v>-1.487532725462536E-09</v>
       </c>
       <c r="T3">
-        <v>-9.314452293328563E-20</v>
+        <v>5.330066248779035E-23</v>
       </c>
       <c r="U3">
-        <v>1.286983572203391E-09</v>
+        <v>1.287508811663069E-09</v>
       </c>
       <c r="V3">
-        <v>-1.285149989033466E-09</v>
+        <v>-1.285071908638844E-09</v>
       </c>
       <c r="W3">
-        <v>2.37227095119031E-17</v>
+        <v>7.05620705899858E-17</v>
       </c>
       <c r="X3">
-        <v>-1.286983578134418E-09</v>
+        <v>-1.287508794015829E-09</v>
       </c>
       <c r="Y3">
-        <v>1.285149983104206E-09</v>
+        <v>1.285071926286084E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -7824,37 +7824,37 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.19016901644547</v>
+        <v>1.190169016475026</v>
       </c>
       <c r="AI3">
-        <v>1.19113580528599</v>
+        <v>1.191135805290812</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.190169026439481</v>
+        <v>1.190168986516117</v>
       </c>
       <c r="AL3">
-        <v>1.191135810592438</v>
+        <v>1.191135789285282</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-139.1361552982339</v>
+        <v>-139.1361552980736</v>
       </c>
       <c r="AO3">
-        <v>139.0824298852958</v>
+        <v>139.0824298864981</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-139.1361554865712</v>
+        <v>-139.1361547278666</v>
       </c>
       <c r="AR3">
-        <v>139.08243033445</v>
+        <v>139.0824285416654</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -7898,40 +7898,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>9.163146768883414E-21</v>
+        <v>1.831867785478618E-23</v>
       </c>
       <c r="O4">
-        <v>1.482992981290827E-09</v>
+        <v>1.483312034740708E-09</v>
       </c>
       <c r="P4">
-        <v>1.488628816081693E-09</v>
+        <v>1.487532801358115E-09</v>
       </c>
       <c r="Q4">
-        <v>4.007162332436306E-17</v>
+        <v>1.203170428577036E-16</v>
       </c>
       <c r="R4">
-        <v>-1.482992991310844E-09</v>
+        <v>-1.483312004650004E-09</v>
       </c>
       <c r="S4">
-        <v>-1.488628826095994E-09</v>
+        <v>-1.487532771267411E-09</v>
       </c>
       <c r="T4">
-        <v>-9.316444497413079E-20</v>
+        <v>5.330066384088953E-23</v>
       </c>
       <c r="U4">
-        <v>1.287265647456792E-09</v>
+        <v>1.287508842397549E-09</v>
       </c>
       <c r="V4">
-        <v>-1.286228001436041E-09</v>
+        <v>-1.285071954651702E-09</v>
       </c>
       <c r="W4">
-        <v>1.426864450936225E-17</v>
+        <v>4.233722348397706E-17</v>
       </c>
       <c r="X4">
-        <v>-1.287265651018304E-09</v>
+        <v>-1.287508831809205E-09</v>
       </c>
       <c r="Y4">
-        <v>1.286227997879025E-09</v>
+        <v>1.285071965240047E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -7955,37 +7955,37 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.19016901644547</v>
+        <v>1.190169016475026</v>
       </c>
       <c r="AI4">
-        <v>1.19113580528599</v>
+        <v>1.191135805290812</v>
       </c>
       <c r="AJ4">
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.190169022446505</v>
+        <v>1.19016899849968</v>
       </c>
       <c r="AL4">
-        <v>1.191135808465855</v>
+        <v>1.191135795687494</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-139.1361552982339</v>
+        <v>-139.1361552980736</v>
       </c>
       <c r="AO4">
-        <v>139.0824298852958</v>
+        <v>139.0824298864981</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>-139.1361554114004</v>
+        <v>-139.1361549559494</v>
       </c>
       <c r="AR4">
-        <v>139.0824301543621</v>
+        <v>139.0824290795985</v>
       </c>
     </row>
   </sheetData>
@@ -8137,16 +8137,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.02439206957683514</v>
+        <v>0.02439206957623863</v>
       </c>
       <c r="C2">
-        <v>9.786331174945902E-06</v>
+        <v>9.786331032126264E-06</v>
       </c>
       <c r="D2">
-        <v>9.78633101572367E-06</v>
+        <v>9.786331032117612E-06</v>
       </c>
       <c r="E2">
-        <v>0.0243888237152607</v>
+        <v>0.02438882371466442</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8155,16 +8155,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.005633107258450979</v>
+        <v>0.005633107258313218</v>
       </c>
       <c r="I2">
-        <v>2.260056408971001E-06</v>
+        <v>2.260056375988219E-06</v>
       </c>
       <c r="J2">
-        <v>2.260056372200202E-06</v>
+        <v>2.260056375986221E-06</v>
       </c>
       <c r="K2">
-        <v>0.005632357658818306</v>
+        <v>0.005632357658680601</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -8173,52 +8173,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.004142657814708859</v>
+        <v>0.004142657814595634</v>
       </c>
       <c r="O2">
-        <v>2.113928249772154E-06</v>
+        <v>2.113928242908887E-06</v>
       </c>
       <c r="P2">
-        <v>-1.382324931957276E-06</v>
+        <v>-1.382324912644163E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.002974074392621814</v>
+        <v>-0.0029740743925827</v>
       </c>
       <c r="R2">
-        <v>-3.337158144198689E-10</v>
+        <v>-3.337249487620048E-10</v>
       </c>
       <c r="S2">
-        <v>-1.013907954550546E-09</v>
+        <v>-1.01393044999675E-09</v>
       </c>
       <c r="T2">
-        <v>0.003386424559519379</v>
+        <v>0.003386424559451164</v>
       </c>
       <c r="U2">
-        <v>-3.756945709069663E-07</v>
+        <v>-3.756944304561924E-07</v>
       </c>
       <c r="V2">
-        <v>-1.642868611231378E-06</v>
+        <v>-1.642868632182139E-06</v>
       </c>
       <c r="W2">
-        <v>-0.002974075241247483</v>
+        <v>-0.002974075241208915</v>
       </c>
       <c r="X2">
-        <v>-1.132487902182892E-09</v>
+        <v>-1.132631917358629E-09</v>
       </c>
       <c r="Y2">
-        <v>7.39893618879745E-10</v>
+        <v>7.399150811975555E-10</v>
       </c>
       <c r="Z2">
-        <v>-39.27291736726589</v>
+        <v>-39.27291736746744</v>
       </c>
       <c r="AA2">
-        <v>-109.9224256025196</v>
+        <v>-109.9224292606829</v>
       </c>
       <c r="AB2">
-        <v>-109.9224285062947</v>
+        <v>-109.9224292606077</v>
       </c>
       <c r="AC2">
-        <v>140.7487704750228</v>
+        <v>140.7487704748207</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -8227,40 +8227,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9498581377369293</v>
+        <v>0.9498581377369323</v>
       </c>
       <c r="AH2">
-        <v>0.9499999942098053</v>
+        <v>0.9499999942098001</v>
       </c>
       <c r="AI2">
-        <v>0.9500000545388828</v>
+        <v>0.9500000545388835</v>
       </c>
       <c r="AJ2">
-        <v>0.7467524607632491</v>
+        <v>0.7467524607717539</v>
       </c>
       <c r="AK2">
-        <v>0.9752239721836686</v>
+        <v>0.9752239721798733</v>
       </c>
       <c r="AL2">
-        <v>1.036694517817192</v>
+        <v>1.036694517812588</v>
       </c>
       <c r="AM2">
-        <v>-0.00856202947000685</v>
+        <v>-0.008562029469767338</v>
       </c>
       <c r="AN2">
         <v>-120.0000048418357</v>
       </c>
       <c r="AO2">
-        <v>120.0000027411302</v>
+        <v>120.0000027411301</v>
       </c>
       <c r="AP2">
-        <v>5.748778649447619</v>
+        <v>5.748778649250705</v>
       </c>
       <c r="AQ2">
-        <v>-126.3810027397006</v>
+        <v>-126.3810027392176</v>
       </c>
       <c r="AR2">
-        <v>123.9162975017938</v>
+        <v>123.9162975015228</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -8304,40 +8304,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.433910179978018E-10</v>
+        <v>-5.434281834039287E-10</v>
       </c>
       <c r="O3">
-        <v>1.11248868887729E-10</v>
+        <v>1.112416409265642E-10</v>
       </c>
       <c r="P3">
-        <v>3.379414502863916E-10</v>
+        <v>3.379768072569983E-10</v>
       </c>
       <c r="Q3">
-        <v>5.433910219923274E-10</v>
+        <v>5.434281953973467E-10</v>
       </c>
       <c r="R3">
-        <v>-1.112488698860173E-10</v>
+        <v>-1.112416379271913E-10</v>
       </c>
       <c r="S3">
-        <v>-3.379414512844271E-10</v>
+        <v>-3.379768042576253E-10</v>
       </c>
       <c r="T3">
-        <v>-2.604947096916704E-10</v>
+        <v>-2.605527793138106E-10</v>
       </c>
       <c r="U3">
-        <v>3.775112194579115E-10</v>
+        <v>3.775439597468257E-10</v>
       </c>
       <c r="V3">
-        <v>-2.466338482135211E-10</v>
+        <v>-2.466383496293418E-10</v>
       </c>
       <c r="W3">
-        <v>2.604947111044742E-10</v>
+        <v>2.605527835340655E-10</v>
       </c>
       <c r="X3">
-        <v>-3.775112198130052E-10</v>
+        <v>-3.775439586914036E-10</v>
       </c>
       <c r="Y3">
-        <v>2.466338478587365E-10</v>
+        <v>2.466383506847639E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -8358,40 +8358,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.7467524607632491</v>
+        <v>0.7467524607717539</v>
       </c>
       <c r="AH3">
-        <v>0.9752239721836686</v>
+        <v>0.9752239721798733</v>
       </c>
       <c r="AI3">
-        <v>1.036694517817192</v>
+        <v>1.036694517812588</v>
       </c>
       <c r="AJ3">
-        <v>0.7467524659837266</v>
+        <v>0.7467524764328305</v>
       </c>
       <c r="AK3">
-        <v>0.9752239737269304</v>
+        <v>0.9752239675709701</v>
       </c>
       <c r="AL3">
-        <v>1.036694519296579</v>
+        <v>1.036694513350904</v>
       </c>
       <c r="AM3">
-        <v>5.748778649447619</v>
+        <v>5.748778649250705</v>
       </c>
       <c r="AN3">
-        <v>-126.3810027397006</v>
+        <v>-126.3810027392176</v>
       </c>
       <c r="AO3">
-        <v>123.9162975017938</v>
+        <v>123.9162975015228</v>
       </c>
       <c r="AP3">
-        <v>5.748778606396987</v>
+        <v>5.748778518077992</v>
       </c>
       <c r="AQ3">
-        <v>-126.381002864494</v>
+        <v>-126.3810023638191</v>
       </c>
       <c r="AR3">
-        <v>123.9162976216164</v>
+        <v>123.9162971426547</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -8435,40 +8435,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.434909824046946E-10</v>
+        <v>-5.434282021346974E-10</v>
       </c>
       <c r="O4">
-        <v>1.11260617713876E-10</v>
+        <v>1.112416478312778E-10</v>
       </c>
       <c r="P4">
-        <v>3.381227175557291E-10</v>
+        <v>3.379768159365943E-10</v>
       </c>
       <c r="Q4">
-        <v>5.434909848016727E-10</v>
+        <v>5.434282093307486E-10</v>
       </c>
       <c r="R4">
-        <v>-1.112606183130514E-10</v>
+        <v>-1.112416460316538E-10</v>
       </c>
       <c r="S4">
-        <v>-3.381227181548061E-10</v>
+        <v>-3.379768141369704E-10</v>
       </c>
       <c r="T4">
-        <v>-2.604905525831372E-10</v>
+        <v>-2.605527829354393E-10</v>
       </c>
       <c r="U4">
-        <v>3.774337077949938E-10</v>
+        <v>3.77543970069364E-10</v>
       </c>
       <c r="V4">
-        <v>-2.470090482474237E-10</v>
+        <v>-2.46638358240665E-10</v>
       </c>
       <c r="W4">
-        <v>2.60490553430611E-10</v>
+        <v>2.605527854675923E-10</v>
       </c>
       <c r="X4">
-        <v>-3.7743370800813E-10</v>
+        <v>-3.775439694361106E-10</v>
       </c>
       <c r="Y4">
-        <v>2.470090480348889E-10</v>
+        <v>2.466383588739183E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -8489,40 +8489,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.7467524607632491</v>
+        <v>0.7467524607717539</v>
       </c>
       <c r="AH4">
-        <v>0.9752239721836686</v>
+        <v>0.9752239721798733</v>
       </c>
       <c r="AI4">
-        <v>1.036694517817192</v>
+        <v>1.036694517812588</v>
       </c>
       <c r="AJ4">
-        <v>0.7467524638952845</v>
+        <v>0.7467524701684002</v>
       </c>
       <c r="AK4">
-        <v>0.9752239731102325</v>
+        <v>0.9752239694145313</v>
       </c>
       <c r="AL4">
-        <v>1.036694518704438</v>
+        <v>1.036694515135578</v>
       </c>
       <c r="AM4">
-        <v>5.748778649447619</v>
+        <v>5.748778649250705</v>
       </c>
       <c r="AN4">
-        <v>-126.3810027397006</v>
+        <v>-126.3810027392176</v>
       </c>
       <c r="AO4">
-        <v>123.9162975017938</v>
+        <v>123.9162975015228</v>
       </c>
       <c r="AP4">
-        <v>5.748778623611087</v>
+        <v>5.74877857054708</v>
       </c>
       <c r="AQ4">
-        <v>-126.3810028146105</v>
+        <v>-126.3810025139785</v>
       </c>
       <c r="AR4">
-        <v>123.9162975736307</v>
+        <v>123.9162972862019</v>
       </c>
     </row>
   </sheetData>
@@ -8674,16 +8674,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.02310845738518363</v>
+        <v>0.02310845738501499</v>
       </c>
       <c r="C2">
-        <v>9.271144976254471E-06</v>
+        <v>9.271144737508142E-06</v>
       </c>
       <c r="D2">
-        <v>9.271144397705774E-06</v>
+        <v>9.271144737499433E-06</v>
       </c>
       <c r="E2">
-        <v>0.02310538277701174</v>
+        <v>0.02310538277684291</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8692,16 +8692,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.005336669716279679</v>
+        <v>0.005336669716240736</v>
       </c>
       <c r="I2">
-        <v>2.141079250999193E-06</v>
+        <v>2.141079195863089E-06</v>
       </c>
       <c r="J2">
-        <v>2.141079117389093E-06</v>
+        <v>2.141079195861078E-06</v>
       </c>
       <c r="K2">
-        <v>0.005335959665926822</v>
+        <v>0.005335959665887833</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -8710,52 +8710,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.00371812236087141</v>
+        <v>0.00371812236094448</v>
       </c>
       <c r="O2">
-        <v>1.897253494564986E-06</v>
+        <v>1.89725342343159E-06</v>
       </c>
       <c r="P2">
-        <v>-1.240578023266507E-06</v>
+        <v>-1.240578132805268E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.00266929426785798</v>
+        <v>-0.002669294267925731</v>
       </c>
       <c r="R2">
-        <v>-2.996176336631098E-10</v>
+        <v>-2.995317075503596E-10</v>
       </c>
       <c r="S2">
-        <v>-9.101314943158914E-10</v>
+        <v>-9.100123668591789E-10</v>
       </c>
       <c r="T2">
-        <v>0.003039387137843063</v>
+        <v>0.003039387137698349</v>
       </c>
       <c r="U2">
-        <v>-3.371164737107054E-07</v>
+        <v>-3.371165903973097E-07</v>
       </c>
       <c r="V2">
-        <v>-1.474511611028502E-06</v>
+        <v>-1.47451161116452E-06</v>
       </c>
       <c r="W2">
-        <v>-0.002669295029628793</v>
+        <v>-0.002669295029476009</v>
       </c>
       <c r="X2">
-        <v>-1.016662285874915E-09</v>
+        <v>-1.01655146120967E-09</v>
       </c>
       <c r="Y2">
-        <v>6.640819762302716E-10</v>
+        <v>6.640902822717118E-10</v>
       </c>
       <c r="Z2">
-        <v>-39.27246679855858</v>
+        <v>-39.27246679667027</v>
       </c>
       <c r="AA2">
-        <v>-109.9244721684717</v>
+        <v>-109.9244683824459</v>
       </c>
       <c r="AB2">
-        <v>-109.9244708720263</v>
+        <v>-109.9244683823996</v>
       </c>
       <c r="AC2">
-        <v>140.7492209324906</v>
+        <v>140.7492209343798</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -8764,40 +8764,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8998726639978298</v>
+        <v>0.8998726639978349</v>
       </c>
       <c r="AH2">
-        <v>0.8999999816578753</v>
+        <v>0.8999999816578801</v>
       </c>
       <c r="AI2">
-        <v>0.900000035806987</v>
+        <v>0.9000000358069873</v>
       </c>
       <c r="AJ2">
-        <v>0.7074552527688903</v>
+        <v>0.707455252762791</v>
       </c>
       <c r="AK2">
-        <v>0.9238973984683596</v>
+        <v>0.9238973984762439</v>
       </c>
       <c r="AL2">
-        <v>0.9821318069157154</v>
+        <v>0.9821318069183326</v>
       </c>
       <c r="AM2">
-        <v>-0.00811145996435368</v>
+        <v>-0.008111459964561614</v>
       </c>
       <c r="AN2">
-        <v>-120.0000045869571</v>
+        <v>-120.000004586957</v>
       </c>
       <c r="AO2">
-        <v>120.000002596692</v>
+        <v>120.0000025966922</v>
       </c>
       <c r="AP2">
-        <v>5.749229108111425</v>
+        <v>5.749229107633718</v>
       </c>
       <c r="AQ2">
-        <v>-126.3810366572702</v>
+        <v>-126.381036657511</v>
       </c>
       <c r="AR2">
-        <v>123.9163640961185</v>
+        <v>123.9163640964964</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -8841,40 +8841,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-4.877537079234937E-10</v>
+        <v>-4.87718110589657E-10</v>
       </c>
       <c r="O3">
-        <v>9.978005889897804E-11</v>
+        <v>9.984389531535371E-11</v>
       </c>
       <c r="P3">
-        <v>3.033893185168658E-10</v>
+        <v>3.033374472832253E-10</v>
       </c>
       <c r="Q3">
-        <v>4.877537115096941E-10</v>
+        <v>4.877181213535631E-10</v>
       </c>
       <c r="R3">
-        <v>-9.97800597947607E-11</v>
+        <v>-9.984389262335383E-11</v>
       </c>
       <c r="S3">
-        <v>-3.033893194133452E-10</v>
+        <v>-3.033374445912255E-10</v>
       </c>
       <c r="T3">
-        <v>-2.339501980157522E-10</v>
+        <v>-2.338680198253855E-10</v>
       </c>
       <c r="U3">
-        <v>3.389257380189608E-10</v>
+        <v>3.388504753438779E-10</v>
       </c>
       <c r="V3">
-        <v>-2.213576537892196E-10</v>
+        <v>-2.213634170611137E-10</v>
       </c>
       <c r="W3">
-        <v>2.339501992849744E-10</v>
+        <v>2.338680236129986E-10</v>
       </c>
       <c r="X3">
-        <v>-3.389257383378784E-10</v>
+        <v>-3.388504743966146E-10</v>
       </c>
       <c r="Y3">
-        <v>2.213576534704181E-10</v>
+        <v>2.213634180083771E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -8895,40 +8895,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.7074552527688903</v>
+        <v>0.707455252762791</v>
       </c>
       <c r="AH3">
-        <v>0.9238973984683596</v>
+        <v>0.9238973984762439</v>
       </c>
       <c r="AI3">
-        <v>0.9821318069157154</v>
+        <v>0.9821318069183326</v>
       </c>
       <c r="AJ3">
-        <v>0.7074552577154267</v>
+        <v>0.707455267599344</v>
       </c>
       <c r="AK3">
-        <v>0.9238973999299264</v>
+        <v>0.9238973941098294</v>
       </c>
       <c r="AL3">
-        <v>0.9821318083182128</v>
+        <v>0.9821318026914828</v>
       </c>
       <c r="AM3">
-        <v>5.749229108111425</v>
+        <v>5.749229107633718</v>
       </c>
       <c r="AN3">
-        <v>-126.3810366572702</v>
+        <v>-126.381036657511</v>
       </c>
       <c r="AO3">
-        <v>123.9163640961185</v>
+        <v>123.9163640964964</v>
       </c>
       <c r="AP3">
-        <v>5.749229065052041</v>
+        <v>5.749228976411469</v>
       </c>
       <c r="AQ3">
-        <v>-126.381036782019</v>
+        <v>-126.3810362821122</v>
       </c>
       <c r="AR3">
-        <v>123.9163642160215</v>
+        <v>123.9163637376239</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -8972,40 +8972,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-4.876151453767955E-10</v>
+        <v>-4.877181284166671E-10</v>
       </c>
       <c r="O4">
-        <v>9.990839645448465E-11</v>
+        <v>9.984390120011717E-11</v>
       </c>
       <c r="P4">
-        <v>3.033483140257915E-10</v>
+        <v>3.033374544090515E-10</v>
       </c>
       <c r="Q4">
-        <v>4.876151475273255E-10</v>
+        <v>4.877181348750111E-10</v>
       </c>
       <c r="R4">
-        <v>-9.990839699217366E-11</v>
+        <v>-9.984389958491713E-11</v>
       </c>
       <c r="S4">
-        <v>-3.03348314563034E-10</v>
+        <v>-3.033374527938514E-10</v>
       </c>
       <c r="T4">
-        <v>-2.337206874876571E-10</v>
+        <v>-2.338680224425245E-10</v>
       </c>
       <c r="U4">
-        <v>3.386572334727327E-10</v>
+        <v>3.388504869339962E-10</v>
       </c>
       <c r="V4">
-        <v>-2.214300741619084E-10</v>
+        <v>-2.213634266411314E-10</v>
       </c>
       <c r="W4">
-        <v>2.33720688247831E-10</v>
+        <v>2.338680247150925E-10</v>
       </c>
       <c r="X4">
-        <v>-3.386572336638208E-10</v>
+        <v>-3.388504863656381E-10</v>
       </c>
       <c r="Y4">
-        <v>2.214300739711315E-10</v>
+        <v>2.213634272094895E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -9026,40 +9026,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.7074552527688903</v>
+        <v>0.707455252762791</v>
       </c>
       <c r="AH4">
-        <v>0.9238973984683596</v>
+        <v>0.9238973984762439</v>
       </c>
       <c r="AI4">
-        <v>0.9821318069157154</v>
+        <v>0.9821318069183326</v>
       </c>
       <c r="AJ4">
-        <v>0.7074552557359562</v>
+        <v>0.7074552616647231</v>
       </c>
       <c r="AK4">
-        <v>0.9238973993460333</v>
+        <v>0.9238973958563951</v>
       </c>
       <c r="AL4">
-        <v>0.9821318077563349</v>
+        <v>0.9821318043822226</v>
       </c>
       <c r="AM4">
-        <v>5.749229108111425</v>
+        <v>5.749229107633718</v>
       </c>
       <c r="AN4">
-        <v>-126.3810366572702</v>
+        <v>-126.381036657511</v>
       </c>
       <c r="AO4">
-        <v>123.9163640961185</v>
+        <v>123.9163640964964</v>
       </c>
       <c r="AP4">
-        <v>5.749229082255076</v>
+        <v>5.749229028900371</v>
       </c>
       <c r="AQ4">
-        <v>-126.3810367321819</v>
+        <v>-126.3810364322717</v>
       </c>
       <c r="AR4">
-        <v>123.9163641679492</v>
+        <v>123.9163638811729</v>
       </c>
     </row>
   </sheetData>
@@ -9211,106 +9211,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.112665297215797E-05</v>
+        <v>3.112666158615173E-05</v>
       </c>
       <c r="C2">
-        <v>0.3459535560698296</v>
+        <v>0.3459535560661574</v>
       </c>
       <c r="D2">
-        <v>0.3457320346250685</v>
+        <v>0.3457320346211745</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3459755374789877</v>
+        <v>0.3459755374753177</v>
       </c>
       <c r="G2">
-        <v>0.3457034407879669</v>
+        <v>0.345703440784071</v>
       </c>
       <c r="H2">
-        <v>7.188392696094385E-06</v>
+        <v>7.188394685411061E-06</v>
       </c>
       <c r="I2">
-        <v>0.07989455268013136</v>
+        <v>0.0798945526792833</v>
       </c>
       <c r="J2">
-        <v>0.07984339449306339</v>
+        <v>0.07984339449216411</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.07989962906920484</v>
+        <v>0.07989962906835731</v>
       </c>
       <c r="M2">
-        <v>0.0798367910291459</v>
+        <v>0.07983679102824617</v>
       </c>
       <c r="N2">
-        <v>2.097360418821175E-09</v>
+        <v>2.099249628094338E-09</v>
       </c>
       <c r="O2">
-        <v>0.08098758713636653</v>
+        <v>0.08098758713525354</v>
       </c>
       <c r="P2">
-        <v>0.05013160468211987</v>
+        <v>0.0501316046819843</v>
       </c>
       <c r="Q2">
-        <v>-5.385778732205302E-09</v>
+        <v>-5.388295887197545E-09</v>
       </c>
       <c r="R2">
-        <v>1.460098771143564E-12</v>
+        <v>-1.468693860530401E-15</v>
       </c>
       <c r="S2">
-        <v>-1.075259326479518E-12</v>
+        <v>-4.172510415752156E-15</v>
       </c>
       <c r="T2">
-        <v>-7.547813316302439E-06</v>
+        <v>-7.547815404560585E-06</v>
       </c>
       <c r="U2">
-        <v>0.02159856168900336</v>
+        <v>0.02159856168971838</v>
       </c>
       <c r="V2">
-        <v>0.06698068521689543</v>
+        <v>0.06698068521582311</v>
       </c>
       <c r="W2">
-        <v>-7.069753873411603E-12</v>
+        <v>-4.285146162283562E-12</v>
       </c>
       <c r="X2">
-        <v>3.373934495168221E-12</v>
+        <v>9.268547103479285E-16</v>
       </c>
       <c r="Y2">
-        <v>-1.501644867034044E-12</v>
+        <v>7.816440103545429E-17</v>
       </c>
       <c r="Z2">
-        <v>89.98407761327053</v>
+        <v>89.98406327660724</v>
       </c>
       <c r="AA2">
-        <v>-135.0611648433465</v>
+        <v>-135.0611648440129</v>
       </c>
       <c r="AB2">
-        <v>66.74207476389496</v>
+        <v>66.74207476426071</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.94248496141964</v>
+        <v>44.94248496075311</v>
       </c>
       <c r="AE2">
-        <v>-113.2599635299509</v>
+        <v>-113.2599635295848</v>
       </c>
       <c r="AG2">
-        <v>1.05000017762065</v>
+        <v>1.050000177620706</v>
       </c>
       <c r="AH2">
-        <v>1.049110061024148</v>
+        <v>1.04911006102413</v>
       </c>
       <c r="AI2">
-        <v>1.0478456334593</v>
+        <v>1.047845633459333</v>
       </c>
       <c r="AJ2">
-        <v>1.399911409933074</v>
+        <v>1.399911409936931</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -9319,16 +9319,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.232878042019926E-06</v>
+        <v>-1.232881459514017E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.1285113667249</v>
+        <v>-120.128511366723</v>
       </c>
       <c r="AO2">
-        <v>119.929105720102</v>
+        <v>119.9291057201021</v>
       </c>
       <c r="AP2">
-        <v>-0.01518447796656614</v>
+        <v>-0.01518448050018827</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -9378,40 +9378,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.796290218855472E-09</v>
+        <v>1.796098622056878E-09</v>
       </c>
       <c r="O3">
-        <v>1.101711304877877E-19</v>
+        <v>-5.673744569793277E-23</v>
       </c>
       <c r="P3">
-        <v>-8.902579689046942E-20</v>
+        <v>-1.17341781759616E-22</v>
       </c>
       <c r="Q3">
-        <v>-1.796290224108351E-09</v>
+        <v>-1.796098606269631E-09</v>
       </c>
       <c r="R3">
-        <v>7.351232562634188E-17</v>
+        <v>1.421570736811756E-16</v>
       </c>
       <c r="S3">
-        <v>1.475556124014263E-16</v>
+        <v>1.421571341884404E-16</v>
       </c>
       <c r="T3">
-        <v>7.971607625615245E-13</v>
+        <v>1.428406880202372E-12</v>
       </c>
       <c r="U3">
-        <v>1.38725908286562E-19</v>
+        <v>6.151265330274792E-23</v>
       </c>
       <c r="V3">
-        <v>-1.773652207420983E-21</v>
+        <v>1.634980185766098E-22</v>
       </c>
       <c r="W3">
-        <v>-7.971643358554119E-13</v>
+        <v>-1.428396214158379E-12</v>
       </c>
       <c r="X3">
-        <v>1.292912636070086E-16</v>
+        <v>9.604283192551611E-17</v>
       </c>
       <c r="Y3">
-        <v>1.99740065546905E-17</v>
+        <v>9.604272950883181E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -9432,7 +9432,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.399911409933074</v>
+        <v>1.399911409936931</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -9441,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.399911414028061</v>
+        <v>1.399911397625464</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -9450,7 +9450,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01518447796656614</v>
+        <v>-0.01518448050018827</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.0151843640645632</v>
+        <v>-0.01518482034764941</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -9509,40 +9509,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.79607812933639E-09</v>
+        <v>1.796098635000937E-09</v>
       </c>
       <c r="O4">
-        <v>1.102098845692813E-19</v>
+        <v>-5.673744548479652E-23</v>
       </c>
       <c r="P4">
-        <v>-8.903554870904186E-20</v>
+        <v>-1.17341782909011E-22</v>
       </c>
       <c r="Q4">
-        <v>-1.796078132487432E-09</v>
+        <v>-1.796098625528588E-09</v>
       </c>
       <c r="R4">
-        <v>4.406735418797672E-17</v>
+        <v>8.529426930900584E-17</v>
       </c>
       <c r="S4">
-        <v>8.856884060838792E-17</v>
+        <v>8.529433134591572E-17</v>
       </c>
       <c r="T4">
-        <v>1.221620988676453E-12</v>
+        <v>1.428377735260679E-12</v>
       </c>
       <c r="U4">
-        <v>1.387037148146425E-19</v>
+        <v>6.151265510285044E-23</v>
       </c>
       <c r="V4">
-        <v>-1.730381264052631E-21</v>
+        <v>1.634980230771229E-22</v>
       </c>
       <c r="W4">
-        <v>-1.221623136931774E-12</v>
+        <v>-1.428371335634228E-12</v>
       </c>
       <c r="X4">
-        <v>7.751491580997226E-17</v>
+        <v>5.762567608009611E-17</v>
       </c>
       <c r="Y4">
-        <v>1.19658115085022E-17</v>
+        <v>5.762557487858609E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.399911409933074</v>
+        <v>1.399911409936931</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -9572,7 +9572,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.399911412390218</v>
+        <v>1.399911402550051</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -9581,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01518447796656614</v>
+        <v>-0.01518448050018827</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01518440950456159</v>
+        <v>-0.01518468440866947</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -9748,106 +9748,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.260933116647499E-05</v>
+        <v>3.260933557600379E-05</v>
       </c>
       <c r="C2">
-        <v>0.3624026701768747</v>
+        <v>0.3624026701705976</v>
       </c>
       <c r="D2">
-        <v>0.3621617107573104</v>
+        <v>0.3621617107553519</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.362425695783178</v>
+        <v>0.3624256957769029</v>
       </c>
       <c r="G2">
-        <v>0.3621317562228754</v>
+        <v>0.3621317562209156</v>
       </c>
       <c r="H2">
-        <v>7.530802563040896E-06</v>
+        <v>7.530803581377967E-06</v>
       </c>
       <c r="I2">
-        <v>0.08369331291979062</v>
+        <v>0.08369331291834101</v>
       </c>
       <c r="J2">
-        <v>0.08363766572466173</v>
+        <v>0.08363766572420944</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.08369863045586885</v>
+        <v>0.08369863045441969</v>
       </c>
       <c r="M2">
-        <v>0.08363074802115086</v>
+        <v>0.08363074802069827</v>
       </c>
       <c r="N2">
-        <v>2.164074470292048E-09</v>
+        <v>2.166658766616306E-09</v>
       </c>
       <c r="O2">
-        <v>0.08887463580376741</v>
+        <v>0.08887463580194178</v>
       </c>
       <c r="P2">
-        <v>0.05500716608622416</v>
+        <v>0.05500716608658997</v>
       </c>
       <c r="Q2">
-        <v>-5.9100381621736E-09</v>
+        <v>-5.913482128293647E-09</v>
       </c>
       <c r="R2">
-        <v>2.811994317731713E-12</v>
+        <v>1.971363609534377E-16</v>
       </c>
       <c r="S2">
-        <v>-2.072761336023886E-12</v>
+        <v>-2.616734054754981E-15</v>
       </c>
       <c r="T2">
-        <v>-8.2838845784146E-06</v>
+        <v>-8.283885697910367E-06</v>
       </c>
       <c r="U2">
-        <v>0.02370200648750658</v>
+        <v>0.0237020064881647</v>
       </c>
       <c r="V2">
-        <v>0.0734991841977158</v>
+        <v>0.07349918419682462</v>
       </c>
       <c r="W2">
-        <v>-6.343475672423906E-12</v>
+        <v>-4.849978445955197E-12</v>
       </c>
       <c r="X2">
-        <v>3.770723509261632E-12</v>
+        <v>-1.29224524360461E-17</v>
       </c>
       <c r="Y2">
-        <v>-1.561301138924411E-12</v>
+        <v>3.505281462486957E-16</v>
       </c>
       <c r="Z2">
-        <v>89.98503081163636</v>
+        <v>89.98501293928202</v>
       </c>
       <c r="AA2">
-        <v>-135.0673049850849</v>
+        <v>-135.0673049857711</v>
       </c>
       <c r="AB2">
-        <v>66.73711004981082</v>
+        <v>66.73711005032617</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.93634557116155</v>
+        <v>44.93634557047508</v>
       </c>
       <c r="AE2">
-        <v>-113.2649289514592</v>
+        <v>-113.2649289509434</v>
       </c>
       <c r="AG2">
-        <v>1.100000271118519</v>
+        <v>1.100000271118544</v>
       </c>
       <c r="AH2">
-        <v>1.09902329094936</v>
+        <v>1.099023290949346</v>
       </c>
       <c r="AI2">
-        <v>1.097635785402774</v>
+        <v>1.0976357854028</v>
       </c>
       <c r="AJ2">
-        <v>1.466563840232262</v>
+        <v>1.466563840216172</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -9856,16 +9856,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.2913902307256E-06</v>
+        <v>-1.291394423004376E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.1346216946736</v>
+        <v>-120.1346216946706</v>
       </c>
       <c r="AO2">
-        <v>119.9257401623244</v>
+        <v>119.9257401623237</v>
       </c>
       <c r="AP2">
-        <v>-0.01565922336989385</v>
+        <v>-0.01565922579150656</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -9915,40 +9915,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.970959803613529E-09</v>
+        <v>1.971160693607858E-09</v>
       </c>
       <c r="O3">
-        <v>1.780507233497124E-19</v>
+        <v>9.011484237286729E-24</v>
       </c>
       <c r="P3">
-        <v>-1.201289893471038E-19</v>
+        <v>-6.193391875570533E-23</v>
       </c>
       <c r="Q3">
-        <v>-1.970959809376671E-09</v>
+        <v>-1.971160676282217E-09</v>
       </c>
       <c r="R3">
-        <v>8.058405978091256E-17</v>
+        <v>1.56018143634136E-16</v>
       </c>
       <c r="S3">
-        <v>1.619944278124914E-16</v>
+        <v>1.560182140988197E-16</v>
       </c>
       <c r="T3">
-        <v>2.128990990056285E-12</v>
+        <v>1.616683231082634E-12</v>
       </c>
       <c r="U3">
-        <v>1.403274669576195E-19</v>
+        <v>-3.070229682610716E-24</v>
       </c>
       <c r="V3">
-        <v>3.507685836038818E-20</v>
+        <v>1.112488026103215E-22</v>
       </c>
       <c r="W3">
-        <v>-2.128994917153417E-12</v>
+        <v>-1.616671525682846E-12</v>
       </c>
       <c r="X3">
-        <v>1.419505315360284E-16</v>
+        <v>1.054076367946274E-16</v>
       </c>
       <c r="Y3">
-        <v>2.188317324555543E-17</v>
+        <v>1.054075219193913E-16</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.466563840232262</v>
+        <v>1.466563840216172</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -9978,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.466563844523687</v>
+        <v>1.466563827318583</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -9987,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01565922336989385</v>
+        <v>-0.01565922579150656</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -9996,7 +9996,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01565910939032468</v>
+        <v>-0.01565956561940253</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -10046,40 +10046,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.971403928220465E-09</v>
+        <v>1.971160707167955E-09</v>
       </c>
       <c r="O4">
-        <v>1.780895167943133E-19</v>
+        <v>9.011484326649878E-24</v>
       </c>
       <c r="P4">
-        <v>-1.200855290771182E-19</v>
+        <v>-6.19339205871363E-23</v>
       </c>
       <c r="Q4">
-        <v>-1.971403931680321E-09</v>
+        <v>-1.97116069677257E-09</v>
       </c>
       <c r="R4">
-        <v>4.830454760072175E-17</v>
+        <v>9.361088543249381E-17</v>
       </c>
       <c r="S4">
-        <v>9.720648726011722E-17</v>
+        <v>9.361095745380294E-17</v>
       </c>
       <c r="T4">
-        <v>3.504268188165665E-13</v>
+        <v>1.616652698382779E-12</v>
       </c>
       <c r="U4">
-        <v>1.401781416382983E-19</v>
+        <v>-3.070229851065388E-24</v>
       </c>
       <c r="V4">
-        <v>3.509715541910613E-20</v>
+        <v>1.112488052378035E-22</v>
       </c>
       <c r="W4">
-        <v>-3.504291754412551E-13</v>
+        <v>-1.616645675142839E-12</v>
       </c>
       <c r="X4">
-        <v>8.506406201005378E-17</v>
+        <v>6.32445852676224E-17</v>
       </c>
       <c r="Y4">
-        <v>1.310370419942216E-17</v>
+        <v>6.324447167346348E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -10100,7 +10100,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.466563840232262</v>
+        <v>1.466563840216172</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -10109,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.466563842806426</v>
+        <v>1.466563832477618</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01565922336989385</v>
+        <v>-0.01565922579150656</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -10127,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01565915489615043</v>
+        <v>-0.01565942968824866</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -10285,130 +10285,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>6.485895656710858E-06</v>
+        <v>6.485897477755475E-06</v>
       </c>
       <c r="C2">
-        <v>0.03084668468281365</v>
+        <v>0.03084668468181546</v>
       </c>
       <c r="D2">
-        <v>0.0302591161286619</v>
+        <v>0.03025911612833544</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.03084976294850604</v>
+        <v>0.03084976294750837</v>
       </c>
       <c r="G2">
-        <v>0.0302527048298169</v>
+        <v>0.03025270482949052</v>
       </c>
       <c r="H2">
-        <v>1.497853463654891E-06</v>
+        <v>1.497853884207137E-06</v>
       </c>
       <c r="I2">
-        <v>0.007123736788243936</v>
+        <v>0.007123736788013414</v>
       </c>
       <c r="J2">
-        <v>0.006988043641059201</v>
+        <v>0.006988043640983808</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007124447683264984</v>
+        <v>0.007124447683034584</v>
       </c>
       <c r="M2">
-        <v>0.006986563014991533</v>
+        <v>0.006986563014916158</v>
       </c>
       <c r="N2">
-        <v>2.380077190943609E-07</v>
+        <v>2.380080703188159E-07</v>
       </c>
       <c r="O2">
-        <v>0.005700747561027251</v>
+        <v>0.005700747560768053</v>
       </c>
       <c r="P2">
-        <v>0.004969112216265161</v>
+        <v>0.00496911221609733</v>
       </c>
       <c r="Q2">
-        <v>-8.904345797485238E-10</v>
+        <v>-8.908055667019379E-10</v>
       </c>
       <c r="R2">
-        <v>-0.00475854025718985</v>
+        <v>-0.00475854025701476</v>
       </c>
       <c r="S2">
-        <v>-0.004576130304744631</v>
+        <v>-0.004576130304534663</v>
       </c>
       <c r="T2">
-        <v>-1.554632666332794E-06</v>
+        <v>-1.554633059286627E-06</v>
       </c>
       <c r="U2">
-        <v>0.004840817469311857</v>
+        <v>0.00484081746924324</v>
       </c>
       <c r="V2">
-        <v>0.005397034853700526</v>
+        <v>0.005397034853747454</v>
       </c>
       <c r="W2">
-        <v>-1.285162195920826E-10</v>
+        <v>-1.280925150096582E-10</v>
       </c>
       <c r="X2">
-        <v>-0.004758540428826199</v>
+        <v>-0.004758540428812053</v>
       </c>
       <c r="Y2">
-        <v>-0.004576131998711652</v>
+        <v>-0.004576131998776537</v>
       </c>
       <c r="Z2">
-        <v>81.2958403530228</v>
+        <v>81.29582987153641</v>
       </c>
       <c r="AA2">
-        <v>-160.3449113886728</v>
+        <v>-160.344911389557</v>
       </c>
       <c r="AB2">
-        <v>72.62891141239918</v>
+        <v>72.62891141118693</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>19.6656919492873</v>
+        <v>19.66569194840256</v>
       </c>
       <c r="AE2">
-        <v>-107.3729461190302</v>
+        <v>-107.3729461202412</v>
       </c>
       <c r="AG2">
-        <v>1.049999998013324</v>
+        <v>1.049999998013335</v>
       </c>
       <c r="AH2">
-        <v>1.049838394737238</v>
+        <v>1.049838394737241</v>
       </c>
       <c r="AI2">
-        <v>1.049823973627609</v>
+        <v>1.049823973627608</v>
       </c>
       <c r="AJ2">
-        <v>1.122117850126157</v>
+        <v>1.122117850122293</v>
       </c>
       <c r="AK2">
-        <v>0.9445774029598095</v>
+        <v>0.9445774029715749</v>
       </c>
       <c r="AL2">
-        <v>0.9262961951513873</v>
+        <v>0.9262961951466967</v>
       </c>
       <c r="AM2">
-        <v>-6.409241298695304E-07</v>
+        <v>-6.409247659887382E-07</v>
       </c>
       <c r="AN2">
-        <v>-120.0084987248657</v>
+        <v>-120.0084987248653</v>
       </c>
       <c r="AO2">
-        <v>119.9927837349444</v>
+        <v>119.9927837349447</v>
       </c>
       <c r="AP2">
-        <v>-0.5662823193219697</v>
+        <v>-0.5662823200432041</v>
       </c>
       <c r="AQ2">
-        <v>-115.3343070174031</v>
+        <v>-115.3343070173189</v>
       </c>
       <c r="AR2">
-        <v>117.6270644856787</v>
+        <v>117.6270644861883</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -10452,40 +10452,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.971230887065592E-10</v>
+        <v>2.96935186389349E-10</v>
       </c>
       <c r="O3">
-        <v>-3.530789091185914E-10</v>
+        <v>-3.530749758741549E-10</v>
       </c>
       <c r="P3">
-        <v>-4.170020096498444E-10</v>
+        <v>-4.170917717469844E-10</v>
       </c>
       <c r="Q3">
-        <v>-2.971230889346771E-10</v>
+        <v>-2.969351857038899E-10</v>
       </c>
       <c r="R3">
-        <v>3.530789093874217E-10</v>
+        <v>3.530749781547365E-10</v>
       </c>
       <c r="S3">
-        <v>4.170020111060646E-10</v>
+        <v>4.170917739351904E-10</v>
       </c>
       <c r="T3">
-        <v>4.28206432639438E-11</v>
+        <v>4.269750805617722E-11</v>
       </c>
       <c r="U3">
-        <v>-2.958149167634812E-10</v>
+        <v>-2.958092153142444E-10</v>
       </c>
       <c r="V3">
-        <v>1.476943148242122E-10</v>
+        <v>1.47655519942679E-10</v>
       </c>
       <c r="W3">
-        <v>-4.282064341933366E-11</v>
+        <v>-4.269750759307331E-11</v>
       </c>
       <c r="X3">
-        <v>2.958149182822153E-10</v>
+        <v>2.958092168550312E-10</v>
       </c>
       <c r="Y3">
-        <v>-1.476943151768121E-10</v>
+        <v>-1.476555184643023E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -10506,40 +10506,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.122117850126157</v>
+        <v>1.122117850122293</v>
       </c>
       <c r="AH3">
-        <v>0.9445774029598095</v>
+        <v>0.9445774029715749</v>
       </c>
       <c r="AI3">
-        <v>0.9262961951513873</v>
+        <v>0.9262961951466967</v>
       </c>
       <c r="AJ3">
-        <v>1.122117851052994</v>
+        <v>1.122117847337867</v>
       </c>
       <c r="AK3">
-        <v>0.9445774053824875</v>
+        <v>0.9445774085856367</v>
       </c>
       <c r="AL3">
-        <v>0.9262961982720604</v>
+        <v>0.9262961984322891</v>
       </c>
       <c r="AM3">
-        <v>-0.5662823193219697</v>
+        <v>-0.5662823200432041</v>
       </c>
       <c r="AN3">
-        <v>-115.3343070174031</v>
+        <v>-115.3343070173189</v>
       </c>
       <c r="AO3">
-        <v>117.6270644856787</v>
+        <v>117.6270644861883</v>
       </c>
       <c r="AP3">
-        <v>-0.5662822961776555</v>
+        <v>-0.5662823889586758</v>
       </c>
       <c r="AQ3">
-        <v>-115.3343068940711</v>
+        <v>-115.3343070525889</v>
       </c>
       <c r="AR3">
-        <v>117.6270645055987</v>
+        <v>117.6270647612182</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -10583,40 +10583,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.966961949534577E-10</v>
+        <v>2.969351909054589E-10</v>
       </c>
       <c r="O4">
-        <v>-3.531794058220936E-10</v>
+        <v>-3.530749855900423E-10</v>
       </c>
       <c r="P4">
-        <v>-4.170235163851524E-10</v>
+        <v>-4.170917828171026E-10</v>
       </c>
       <c r="Q4">
-        <v>-2.966961950902005E-10</v>
+        <v>-2.969351904941834E-10</v>
       </c>
       <c r="R4">
-        <v>3.531794059833748E-10</v>
+        <v>3.530749869583913E-10</v>
       </c>
       <c r="S4">
-        <v>4.170235172589571E-10</v>
+        <v>4.170917841300263E-10</v>
       </c>
       <c r="T4">
-        <v>4.265476092065464E-11</v>
+        <v>4.269750541599516E-11</v>
       </c>
       <c r="U4">
-        <v>-2.956089216869621E-10</v>
+        <v>-2.958092179661944E-10</v>
       </c>
       <c r="V4">
-        <v>1.475840088579014E-10</v>
+        <v>1.476555226124101E-10</v>
       </c>
       <c r="W4">
-        <v>-4.265476101380381E-11</v>
+        <v>-4.26975051381328E-11</v>
       </c>
       <c r="X4">
-        <v>2.956089225979336E-10</v>
+        <v>2.958092188906665E-10</v>
       </c>
       <c r="Y4">
-        <v>-1.475840090686143E-10</v>
+        <v>-1.476555217253841E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -10637,40 +10637,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.122117850126157</v>
+        <v>1.122117850122293</v>
       </c>
       <c r="AH4">
-        <v>0.9445774029598095</v>
+        <v>0.9445774029715749</v>
       </c>
       <c r="AI4">
-        <v>0.9262961951513873</v>
+        <v>0.9262961951466967</v>
       </c>
       <c r="AJ4">
-        <v>1.122117850682474</v>
+        <v>1.122117848451638</v>
       </c>
       <c r="AK4">
-        <v>0.9445774044126203</v>
+        <v>0.9445774063400121</v>
       </c>
       <c r="AL4">
-        <v>0.9262961970234609</v>
+        <v>0.9262961971180521</v>
       </c>
       <c r="AM4">
-        <v>-0.5662823193219697</v>
+        <v>-0.5662823200432041</v>
       </c>
       <c r="AN4">
-        <v>-115.3343070174031</v>
+        <v>-115.3343070173189</v>
       </c>
       <c r="AO4">
-        <v>117.6270644856787</v>
+        <v>117.6270644861883</v>
       </c>
       <c r="AP4">
-        <v>-0.5662823054174653</v>
+        <v>-0.5662823613924883</v>
       </c>
       <c r="AQ4">
-        <v>-115.3343069433768</v>
+        <v>-115.3343070384809</v>
       </c>
       <c r="AR4">
-        <v>117.6270644977086</v>
+        <v>117.6270646512062</v>
       </c>
     </row>
   </sheetData>
@@ -10822,130 +10822,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>6.794984520784708E-06</v>
+        <v>6.794985911322041E-06</v>
       </c>
       <c r="C2">
-        <v>0.03231533714426021</v>
+        <v>0.03231533714347254</v>
       </c>
       <c r="D2">
-        <v>0.03169977413291036</v>
+        <v>0.03169977413294922</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.03231856180233356</v>
+        <v>0.03231856180154636</v>
       </c>
       <c r="G2">
-        <v>0.03169305735169497</v>
+        <v>0.0316930573517338</v>
       </c>
       <c r="H2">
-        <v>1.569234480269172E-06</v>
+        <v>1.569234801400019E-06</v>
       </c>
       <c r="I2">
-        <v>0.007462907550882846</v>
+        <v>0.007462907550700941</v>
       </c>
       <c r="J2">
-        <v>0.007320749360642117</v>
+        <v>0.007320749360651092</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007463652253776621</v>
+        <v>0.007463652253594823</v>
       </c>
       <c r="M2">
-        <v>0.007319198186441886</v>
+        <v>0.007319198186450854</v>
       </c>
       <c r="N2">
-        <v>2.611492125978398E-07</v>
+        <v>2.611496035429626E-07</v>
       </c>
       <c r="O2">
-        <v>0.006256511431984195</v>
+        <v>0.006256511431689311</v>
       </c>
       <c r="P2">
-        <v>0.005453541879891622</v>
+        <v>0.005453541879818948</v>
       </c>
       <c r="Q2">
-        <v>-9.772420661225879E-10</v>
+        <v>-9.77656496580016E-10</v>
       </c>
       <c r="R2">
-        <v>-0.005222448158695383</v>
+        <v>-0.005222448158467363</v>
       </c>
       <c r="S2">
-        <v>-0.005022248935405035</v>
+        <v>-0.005022248935275515</v>
       </c>
       <c r="T2">
-        <v>-1.706289155757848E-06</v>
+        <v>-1.7062894532806E-06</v>
       </c>
       <c r="U2">
-        <v>0.005312746994636267</v>
+        <v>0.005312746994674445</v>
       </c>
       <c r="V2">
-        <v>0.0059231826821594</v>
+        <v>0.00592318268223971</v>
       </c>
       <c r="W2">
-        <v>-1.409089130343923E-10</v>
+        <v>-1.405867947298716E-10</v>
       </c>
       <c r="X2">
-        <v>-0.005222448347095674</v>
+        <v>-0.005222448347185289</v>
       </c>
       <c r="Y2">
-        <v>-0.005022250794776316</v>
+        <v>-0.005022250794852405</v>
       </c>
       <c r="Z2">
-        <v>81.29834955648167</v>
+        <v>81.29833822340815</v>
       </c>
       <c r="AA2">
-        <v>-160.3453156833765</v>
+        <v>-160.3453156849116</v>
       </c>
       <c r="AB2">
-        <v>72.62856413349229</v>
+        <v>72.62856413272485</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>19.66528839178663</v>
+        <v>19.66528839025122</v>
       </c>
       <c r="AE2">
-        <v>-107.3732940822832</v>
+        <v>-107.3732940830494</v>
       </c>
       <c r="AG2">
-        <v>1.100000073996927</v>
+        <v>1.100000073996935</v>
       </c>
       <c r="AH2">
-        <v>1.099822714182374</v>
+        <v>1.099822714182373</v>
       </c>
       <c r="AI2">
-        <v>1.099806887325975</v>
+        <v>1.099806887325973</v>
       </c>
       <c r="AJ2">
-        <v>1.175551542843638</v>
+        <v>1.175551542840023</v>
       </c>
       <c r="AK2">
-        <v>0.9895500080807462</v>
+        <v>0.9895500080917368</v>
       </c>
       <c r="AL2">
-        <v>0.970397807507736</v>
+        <v>0.9703978075013853</v>
       </c>
       <c r="AM2">
-        <v>-6.713532615851036E-07</v>
+        <v>-6.713539157072585E-07</v>
       </c>
       <c r="AN2">
-        <v>-120.0089033601351</v>
+        <v>-120.0089033601346</v>
       </c>
       <c r="AO2">
-        <v>119.9924401645978</v>
+        <v>119.9924401645979</v>
       </c>
       <c r="AP2">
-        <v>-0.566300775188825</v>
+        <v>-0.5663007758389043</v>
       </c>
       <c r="AQ2">
-        <v>-115.3347105747327</v>
+        <v>-115.3347105745257</v>
       </c>
       <c r="AR2">
-        <v>117.626716523923</v>
+        <v>117.6267165243296</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -10989,40 +10989,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.258825446137171E-10</v>
+        <v>3.258854958348616E-10</v>
       </c>
       <c r="O3">
-        <v>-3.87580059281037E-10</v>
+        <v>-3.875278745829123E-10</v>
       </c>
       <c r="P3">
-        <v>-4.577246610105457E-10</v>
+        <v>-4.577837226167119E-10</v>
       </c>
       <c r="Q3">
-        <v>-3.258825448640431E-10</v>
+        <v>-3.258854950825764E-10</v>
       </c>
       <c r="R3">
-        <v>3.875800595758691E-10</v>
+        <v>3.875278770859052E-10</v>
       </c>
       <c r="S3">
-        <v>4.577246626091942E-10</v>
+        <v>4.577837250186084E-10</v>
       </c>
       <c r="T3">
-        <v>4.69427079789372E-11</v>
+        <v>4.686226833878556E-11</v>
       </c>
       <c r="U3">
-        <v>-3.247357094513631E-10</v>
+        <v>-3.246219090530166E-10</v>
       </c>
       <c r="V3">
-        <v>1.620893240730924E-10</v>
+        <v>1.620752380546539E-10</v>
       </c>
       <c r="W3">
-        <v>-4.694270814949812E-11</v>
+        <v>-4.686226783053313E-11</v>
       </c>
       <c r="X3">
-        <v>3.247357111186694E-10</v>
+        <v>3.24621910744067E-10</v>
       </c>
       <c r="Y3">
-        <v>-1.620893244595251E-10</v>
+        <v>-1.620752364319053E-10</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -11043,40 +11043,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.175551542843638</v>
+        <v>1.175551542840023</v>
       </c>
       <c r="AH3">
-        <v>0.9895500080807462</v>
+        <v>0.9895500080917368</v>
       </c>
       <c r="AI3">
-        <v>0.970397807507736</v>
+        <v>0.9703978075013853</v>
       </c>
       <c r="AJ3">
-        <v>1.175551543815104</v>
+        <v>1.175551539923017</v>
       </c>
       <c r="AK3">
-        <v>0.9895500106185833</v>
+        <v>0.9895500139732319</v>
       </c>
       <c r="AL3">
-        <v>0.9703978107770819</v>
+        <v>0.9703978109435403</v>
       </c>
       <c r="AM3">
-        <v>-0.566300775188825</v>
+        <v>-0.5663007758389043</v>
       </c>
       <c r="AN3">
-        <v>-115.3347105747327</v>
+        <v>-115.3347105745257</v>
       </c>
       <c r="AO3">
-        <v>117.626716523923</v>
+        <v>117.6267165243296</v>
       </c>
       <c r="AP3">
-        <v>-0.5663007520217664</v>
+        <v>-0.5663008447531466</v>
       </c>
       <c r="AQ3">
-        <v>-115.3347104513724</v>
+        <v>-115.3347106097692</v>
       </c>
       <c r="AR3">
-        <v>117.6267165439083</v>
+        <v>117.626716799386</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -11120,40 +11120,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.259502443172876E-10</v>
+        <v>3.258854978337083E-10</v>
       </c>
       <c r="O4">
-        <v>-3.875880824242028E-10</v>
+        <v>-3.875278848163512E-10</v>
       </c>
       <c r="P4">
-        <v>-4.577137029525269E-10</v>
+        <v>-4.577837304968773E-10</v>
       </c>
       <c r="Q4">
-        <v>-3.259502444674736E-10</v>
+        <v>-3.258854973823371E-10</v>
       </c>
       <c r="R4">
-        <v>3.875880826006677E-10</v>
+        <v>3.87527886318147E-10</v>
       </c>
       <c r="S4">
-        <v>4.577137039117779E-10</v>
+        <v>4.577837319380153E-10</v>
       </c>
       <c r="T4">
-        <v>4.703113966967243E-11</v>
+        <v>4.686226424031576E-11</v>
       </c>
       <c r="U4">
-        <v>-3.247526559626173E-10</v>
+        <v>-3.246219092727981E-10</v>
       </c>
       <c r="V4">
-        <v>1.6238560150611E-10</v>
+        <v>1.620752434302988E-10</v>
       </c>
       <c r="W4">
-        <v>-4.703113977211255E-11</v>
+        <v>-4.686226393536429E-11</v>
       </c>
       <c r="X4">
-        <v>3.247526569629696E-10</v>
+        <v>3.246219102874284E-10</v>
       </c>
       <c r="Y4">
-        <v>-1.623856017381185E-10</v>
+        <v>-1.620752424566496E-10</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -11174,40 +11174,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.175551542843638</v>
+        <v>1.175551542840023</v>
       </c>
       <c r="AH4">
-        <v>0.9895500080807462</v>
+        <v>0.9895500080917368</v>
       </c>
       <c r="AI4">
-        <v>0.970397807507736</v>
+        <v>0.9703978075013853</v>
       </c>
       <c r="AJ4">
-        <v>1.175551543426463</v>
+        <v>1.175551541089819</v>
       </c>
       <c r="AK4">
-        <v>0.9895500096027258</v>
+        <v>0.9895500116206339</v>
       </c>
       <c r="AL4">
-        <v>0.9703978094690828</v>
+        <v>0.9703978095666783</v>
       </c>
       <c r="AM4">
-        <v>-0.566300775188825</v>
+        <v>-0.5663007758389043</v>
       </c>
       <c r="AN4">
-        <v>-115.3347105747327</v>
+        <v>-115.3347105745257</v>
       </c>
       <c r="AO4">
-        <v>117.626716523923</v>
+        <v>117.6267165243296</v>
       </c>
       <c r="AP4">
-        <v>-0.566300761280594</v>
+        <v>-0.5663008171874508</v>
       </c>
       <c r="AQ4">
-        <v>-115.3347105006915</v>
+        <v>-115.3347105956718</v>
       </c>
       <c r="AR4">
-        <v>117.6267165359654</v>
+        <v>117.6267166893635</v>
       </c>
     </row>
   </sheetData>
@@ -11359,106 +11359,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.815800147135805E-05</v>
+        <v>2.815799829980768E-05</v>
       </c>
       <c r="C2">
-        <v>0.1857545467380017</v>
+        <v>0.1857545467404366</v>
       </c>
       <c r="D2">
-        <v>0.185651912182109</v>
+        <v>0.1856519121820666</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1857788391824663</v>
+        <v>0.1857788391849013</v>
       </c>
       <c r="G2">
-        <v>0.1856240701755507</v>
+        <v>0.1856240701755072</v>
       </c>
       <c r="H2">
-        <v>6.502811988631629E-06</v>
+        <v>6.502811256193434E-06</v>
       </c>
       <c r="I2">
-        <v>0.04289817566418549</v>
+        <v>0.04289817566474783</v>
       </c>
       <c r="J2">
-        <v>0.04287447322844318</v>
+        <v>0.04287447322843341</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.04290378576400948</v>
+        <v>0.0429037857645718</v>
       </c>
       <c r="M2">
-        <v>0.04286804339235488</v>
+        <v>0.04286804339234485</v>
       </c>
       <c r="N2">
-        <v>2.492913487976058E-09</v>
+        <v>2.493384798639107E-09</v>
       </c>
       <c r="O2">
-        <v>0.04074588678907138</v>
+        <v>0.04074588678960204</v>
       </c>
       <c r="P2">
-        <v>0.03183261165420587</v>
+        <v>0.03183261165468244</v>
       </c>
       <c r="Q2">
-        <v>-4.412216741596518E-09</v>
+        <v>-4.412846012015138E-09</v>
       </c>
       <c r="R2">
-        <v>-1.730326926549705E-12</v>
+        <v>4.519871800285663E-16</v>
       </c>
       <c r="S2">
-        <v>1.268021566640943E-12</v>
+        <v>-5.291165543385033E-16</v>
       </c>
       <c r="T2">
-        <v>-6.177672307612083E-06</v>
+        <v>-6.177671611605192E-06</v>
       </c>
       <c r="U2">
-        <v>0.0001989371966399922</v>
+        <v>0.0001989371971629443</v>
       </c>
       <c r="V2">
-        <v>0.02533688277560583</v>
+        <v>0.02533688277499364</v>
       </c>
       <c r="W2">
-        <v>-2.787389771112702E-12</v>
+        <v>-3.715620344186264E-12</v>
       </c>
       <c r="X2">
-        <v>3.259888470058415E-13</v>
+        <v>-4.887443807359602E-16</v>
       </c>
       <c r="Y2">
-        <v>-1.108504204888074E-12</v>
+        <v>9.339665251671162E-17</v>
       </c>
       <c r="Z2">
-        <v>89.97687769277734</v>
+        <v>89.97687331892793</v>
       </c>
       <c r="AA2">
-        <v>-120.3714053650587</v>
+        <v>-120.3714053657915</v>
       </c>
       <c r="AB2">
-        <v>81.41626773093547</v>
+        <v>81.41626773202677</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>59.63298636990584</v>
+        <v>59.63298636917383</v>
       </c>
       <c r="AE2">
-        <v>-98.58503063752387</v>
+        <v>-98.58503063643305</v>
       </c>
       <c r="AG2">
-        <v>0.9500002185827071</v>
+        <v>0.9500002185826794</v>
       </c>
       <c r="AH2">
-        <v>0.9498392833615957</v>
+        <v>0.9498392833615741</v>
       </c>
       <c r="AI2">
-        <v>0.9489339644729611</v>
+        <v>0.9489339644729822</v>
       </c>
       <c r="AJ2">
-        <v>1.266702450203551</v>
+        <v>1.26670245020399</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -11467,16 +11467,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.395864881045177E-06</v>
+        <v>-1.395865785063789E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.0916674065632</v>
+        <v>-120.0916674065643</v>
       </c>
       <c r="AO2">
-        <v>119.9339901159936</v>
+        <v>119.9339901159923</v>
       </c>
       <c r="AP2">
-        <v>-0.01608258626588589</v>
+        <v>-0.01608258479774103</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -11526,40 +11526,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.47041167470567E-09</v>
+        <v>1.470948619159509E-09</v>
       </c>
       <c r="O3">
-        <v>-1.403271361998119E-19</v>
+        <v>3.644164256459583E-23</v>
       </c>
       <c r="P3">
-        <v>2.435759485127385E-20</v>
+        <v>-2.887491231250083E-23</v>
       </c>
       <c r="Q3">
-        <v>-1.470411682971107E-09</v>
+        <v>-1.470948594328508E-09</v>
       </c>
       <c r="R3">
-        <v>1.437278589789393E-16</v>
+        <v>2.234282431993338E-16</v>
       </c>
       <c r="S3">
-        <v>2.039932782656063E-16</v>
+        <v>2.234283084242234E-16</v>
       </c>
       <c r="T3">
-        <v>3.55303608165335E-13</v>
+        <v>1.238554778378351E-12</v>
       </c>
       <c r="U3">
-        <v>2.739515573488017E-20</v>
+        <v>-3.991511492478158E-23</v>
       </c>
       <c r="V3">
-        <v>-1.346675024647419E-19</v>
+        <v>3.274690399988286E-23</v>
       </c>
       <c r="W3">
-        <v>-3.553065409913212E-13</v>
+        <v>-1.238546040823065E-12</v>
       </c>
       <c r="X3">
-        <v>1.471472740983953E-16</v>
+        <v>7.862018586884352E-17</v>
       </c>
       <c r="Y3">
-        <v>-2.471358778134156E-17</v>
+        <v>7.862011358297108E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.266702450203551</v>
+        <v>1.26670245020399</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -11589,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.266702457324514</v>
+        <v>1.266702428814537</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01608258626588589</v>
+        <v>-0.01608258479774103</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01608247206378129</v>
+        <v>-0.01608292432473087</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -11657,40 +11657,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.469835968520958E-09</v>
+        <v>1.470948663104199E-09</v>
       </c>
       <c r="O4">
-        <v>-1.403136671171927E-19</v>
+        <v>3.64416434643903E-23</v>
       </c>
       <c r="P4">
-        <v>2.437210929449926E-20</v>
+        <v>-2.887491278602281E-23</v>
       </c>
       <c r="Q4">
-        <v>-1.469835973476945E-09</v>
+        <v>-1.470948648205597E-09</v>
       </c>
       <c r="R4">
-        <v>8.628290277485482E-17</v>
+        <v>1.340569395290867E-16</v>
       </c>
       <c r="S4">
-        <v>1.223891180739029E-16</v>
+        <v>1.340570040523413E-16</v>
       </c>
       <c r="T4">
-        <v>1.507524418056739E-12</v>
+        <v>1.238544511610039E-12</v>
       </c>
       <c r="U4">
-        <v>2.73916795972132E-20</v>
+        <v>-3.991511634380676E-23</v>
       </c>
       <c r="V4">
-        <v>-1.346708200729214E-19</v>
+        <v>3.274690513797906E-23</v>
       </c>
       <c r="W4">
-        <v>-1.507526183399194E-12</v>
+        <v>-1.238539269076544E-12</v>
       </c>
       <c r="X4">
-        <v>8.827280600333895E-17</v>
+        <v>4.717213055008288E-17</v>
       </c>
       <c r="Y4">
-        <v>-1.475622742139845E-17</v>
+        <v>4.717205748377431E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -11711,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.266702450203551</v>
+        <v>1.26670245020399</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.266702454476169</v>
+        <v>1.266702437370318</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -11729,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01608258626588589</v>
+        <v>-0.01608258479774103</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01608251764916291</v>
+        <v>-0.01608278851394411</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -12118,106 +12118,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.667581798880602E-05</v>
+        <v>2.667581696121961E-05</v>
       </c>
       <c r="C2">
-        <v>0.1759831158217295</v>
+        <v>0.1759831158221213</v>
       </c>
       <c r="D2">
-        <v>0.1758896612358108</v>
+        <v>0.1758896612363697</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.1760061309661993</v>
+        <v>0.176006130966592</v>
       </c>
       <c r="G2">
-        <v>0.1758632844026798</v>
+        <v>0.1758632844032374</v>
       </c>
       <c r="H2">
-        <v>6.160516370475094E-06</v>
+        <v>6.160516133164174E-06</v>
       </c>
       <c r="I2">
-        <v>0.04064156032260827</v>
+        <v>0.04064156032269876</v>
       </c>
       <c r="J2">
-        <v>0.0406199779101518</v>
+        <v>0.04061997791028089</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.0406468754426295</v>
+        <v>0.0406468754427202</v>
       </c>
       <c r="M2">
-        <v>0.04061388644137763</v>
+        <v>0.0406138864415064</v>
       </c>
       <c r="N2">
-        <v>2.318364822005402E-09</v>
+        <v>2.318119225770059E-09</v>
       </c>
       <c r="O2">
-        <v>0.03657110904879374</v>
+        <v>0.03657110904887385</v>
       </c>
       <c r="P2">
-        <v>0.02857356043727723</v>
+        <v>0.02857356043760409</v>
       </c>
       <c r="Q2">
-        <v>-3.960954041082739E-09</v>
+        <v>-3.960626794196261E-09</v>
       </c>
       <c r="R2">
-        <v>-6.836551437661884E-13</v>
+        <v>4.413132451631428E-16</v>
       </c>
       <c r="S2">
-        <v>3.60155977108518E-13</v>
+        <v>-5.340861135412923E-16</v>
       </c>
       <c r="T2">
-        <v>-5.544465376316904E-06</v>
+        <v>-5.544465162839658E-06</v>
       </c>
       <c r="U2">
-        <v>0.0001783468838038454</v>
+        <v>0.0001783468840068613</v>
       </c>
       <c r="V2">
-        <v>0.02274197521246558</v>
+        <v>0.02274197521224174</v>
       </c>
       <c r="W2">
-        <v>-2.963618361934279E-12</v>
+        <v>-3.248766675261859E-12</v>
       </c>
       <c r="X2">
-        <v>6.04518559201211E-13</v>
+        <v>-2.801680493522472E-16</v>
       </c>
       <c r="Y2">
-        <v>-9.818502315708245E-13</v>
+        <v>2.454595616122796E-16</v>
       </c>
       <c r="Z2">
-        <v>89.97604100017897</v>
+        <v>89.97604353721616</v>
       </c>
       <c r="AA2">
-        <v>-120.3662583685262</v>
+        <v>-120.3662583688438</v>
       </c>
       <c r="AB2">
-        <v>81.42083610453656</v>
+        <v>81.42083610512987</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>59.63813242715781</v>
+        <v>59.63813242684066</v>
       </c>
       <c r="AE2">
-        <v>-98.58046137979656</v>
+        <v>-98.58046137920341</v>
       </c>
       <c r="AG2">
-        <v>0.9000001830350245</v>
+        <v>0.9000001830350174</v>
       </c>
       <c r="AH2">
-        <v>0.8998558035023227</v>
+        <v>0.8998558035023149</v>
       </c>
       <c r="AI2">
-        <v>0.8990432127325031</v>
+        <v>0.8990432127325103</v>
       </c>
       <c r="AJ2">
-        <v>1.200037948144886</v>
+        <v>1.200037948165053</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -12226,16 +12226,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.322581576671179E-06</v>
+        <v>-1.322580942546491E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.086845384032</v>
+        <v>-120.0868453840321</v>
       </c>
       <c r="AO2">
-        <v>119.9374599885304</v>
+        <v>119.9374599885295</v>
       </c>
       <c r="AP2">
-        <v>-0.01566764980126173</v>
+        <v>-0.01566764921647358</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -12285,40 +12285,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.320173655322206E-09</v>
+        <v>1.320208883522416E-09</v>
       </c>
       <c r="O3">
-        <v>-5.519966735160973E-20</v>
+        <v>3.568454614212563E-23</v>
       </c>
       <c r="P3">
-        <v>-2.686769232615675E-20</v>
+        <v>-2.148662672396103E-23</v>
       </c>
       <c r="Q3">
-        <v>-1.320173662736827E-09</v>
+        <v>-1.320208861235818E-09</v>
       </c>
       <c r="R3">
-        <v>1.288982811453358E-16</v>
+        <v>2.005283871526667E-16</v>
       </c>
       <c r="S3">
-        <v>1.831205239551055E-16</v>
+        <v>2.005284433666642E-16</v>
       </c>
       <c r="T3">
-        <v>1.09423336091353E-12</v>
+        <v>1.082935191191215E-12</v>
       </c>
       <c r="U3">
-        <v>4.943480441433746E-20</v>
+        <v>-2.297184762255505E-23</v>
       </c>
       <c r="V3">
-        <v>-8.061458289552977E-20</v>
+        <v>4.265350877437339E-23</v>
       </c>
       <c r="W3">
-        <v>-1.094235997857417E-12</v>
+        <v>-1.082927348962972E-12</v>
       </c>
       <c r="X3">
-        <v>1.320492807684945E-16</v>
+        <v>7.056214656282381E-17</v>
       </c>
       <c r="Y3">
-        <v>-2.221648218116586E-17</v>
+        <v>7.056208057900764E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -12339,7 +12339,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.200037948144886</v>
+        <v>1.200037948165053</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.200037954886759</v>
+        <v>1.200037927901241</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -12357,7 +12357,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.01566764980126173</v>
+        <v>-0.01566764921647358</v>
       </c>
       <c r="AN3">
         <v>0</v>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01566753562421334</v>
+        <v>-0.01566798876793315</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -12416,40 +12416,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.319901096746757E-09</v>
+        <v>1.320208925154817E-09</v>
       </c>
       <c r="O4">
-        <v>-5.517875275574615E-20</v>
+        <v>3.56845470583547E-23</v>
       </c>
       <c r="P4">
-        <v>-2.687186361226065E-20</v>
+        <v>-2.148662716243108E-23</v>
       </c>
       <c r="Q4">
-        <v>-1.319901101196164E-09</v>
+        <v>-1.320208911782857E-09</v>
       </c>
       <c r="R4">
-        <v>7.733748327654954E-17</v>
+        <v>1.203170254167409E-16</v>
       </c>
       <c r="S4">
-        <v>1.099024501939822E-16</v>
+        <v>1.203170822402499E-16</v>
       </c>
       <c r="T4">
-        <v>2.185736089193992E-12</v>
+        <v>1.082926852870434E-12</v>
       </c>
       <c r="U4">
-        <v>4.942017262226742E-20</v>
+        <v>-2.297184862301146E-23</v>
       </c>
       <c r="V4">
-        <v>-8.062340467444213E-20</v>
+        <v>4.265351030304819E-23</v>
       </c>
       <c r="W4">
-        <v>-2.18573767692565E-12</v>
+        <v>-1.082922147533181E-12</v>
       </c>
       <c r="X4">
-        <v>7.918952376285492E-17</v>
+        <v>4.233729959339964E-17</v>
       </c>
       <c r="Y4">
-        <v>-1.328459184983838E-17</v>
+        <v>4.233723405017668E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -12470,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.200037948144886</v>
+        <v>1.200037948165053</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -12479,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.200037952192612</v>
+        <v>1.200037936006766</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -12488,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.01566764980126173</v>
+        <v>-0.01566764921647358</v>
       </c>
       <c r="AN4">
         <v>0</v>
@@ -12497,7 +12497,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.01566758119921979</v>
+        <v>-0.0156678529473585</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -12655,130 +12655,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>8.819642279069315E-06</v>
+        <v>8.819641334616266E-06</v>
       </c>
       <c r="C2">
-        <v>0.02688439965680764</v>
+        <v>0.02688439965621702</v>
       </c>
       <c r="D2">
-        <v>0.02530466707326734</v>
+        <v>0.02530466707311321</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0268903020638799</v>
+        <v>0.02689030206328891</v>
       </c>
       <c r="G2">
-        <v>0.02529585138872676</v>
+        <v>0.02529585138857301</v>
       </c>
       <c r="H2">
-        <v>2.036809167941571E-06</v>
+        <v>2.036808949829479E-06</v>
       </c>
       <c r="I2">
-        <v>0.006208686244060382</v>
+        <v>0.006208686243923985</v>
       </c>
       <c r="J2">
-        <v>0.005843862625682241</v>
+        <v>0.005843862625646647</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.00621004934660551</v>
+        <v>0.006210049346469026</v>
       </c>
       <c r="M2">
-        <v>0.005841826730514865</v>
+        <v>0.005841826730479359</v>
       </c>
       <c r="N2">
-        <v>5.940615807170564E-07</v>
+        <v>5.94061671838671E-07</v>
       </c>
       <c r="O2">
-        <v>0.004780850115287156</v>
+        <v>0.004780850115175092</v>
       </c>
       <c r="P2">
-        <v>0.003847208742515909</v>
+        <v>0.003847208742554174</v>
       </c>
       <c r="Q2">
-        <v>-1.094455170484862E-09</v>
+        <v>-1.09456334666575E-09</v>
       </c>
       <c r="R2">
-        <v>-0.003615443095946794</v>
+        <v>-0.003615443095887362</v>
       </c>
       <c r="S2">
-        <v>-0.003199400327557027</v>
+        <v>-0.003199400327605042</v>
       </c>
       <c r="T2">
-        <v>-1.841519800442879E-06</v>
+        <v>-1.841519553326331E-06</v>
       </c>
       <c r="U2">
-        <v>0.003452839765637365</v>
+        <v>0.003452839765571285</v>
       </c>
       <c r="V2">
-        <v>0.004001174557779787</v>
+        <v>0.004001174557696117</v>
       </c>
       <c r="W2">
-        <v>-3.186952573716337E-10</v>
+        <v>-3.189639205002925E-10</v>
       </c>
       <c r="X2">
-        <v>-0.003615442762587669</v>
+        <v>-0.003615442762496931</v>
       </c>
       <c r="Y2">
-        <v>-0.003199401980851612</v>
+        <v>-0.003199401980798927</v>
       </c>
       <c r="Z2">
-        <v>72.12065531551482</v>
+        <v>72.12065050113929</v>
       </c>
       <c r="AA2">
-        <v>-155.8476646492665</v>
+        <v>-155.8476646493833</v>
       </c>
       <c r="AB2">
-        <v>73.86838421602192</v>
+        <v>73.86838421690516</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>24.16630047520236</v>
+        <v>24.16630047508555</v>
       </c>
       <c r="AE2">
-        <v>-106.1310172111792</v>
+        <v>-106.131017210296</v>
       </c>
       <c r="AG2">
-        <v>0.950000054576663</v>
+        <v>0.9500000545766535</v>
       </c>
       <c r="AH2">
-        <v>0.9498532728913138</v>
+        <v>0.9498532728913167</v>
       </c>
       <c r="AI2">
-        <v>0.9498362963282767</v>
+        <v>0.9498362963282797</v>
       </c>
       <c r="AJ2">
-        <v>1.044830778223755</v>
+        <v>1.044830778216592</v>
       </c>
       <c r="AK2">
-        <v>0.8233442504527714</v>
+        <v>0.8233442504537678</v>
       </c>
       <c r="AL2">
-        <v>0.7745242562764713</v>
+        <v>0.7745242562806133</v>
       </c>
       <c r="AM2">
-        <v>-1.751331540518259E-06</v>
+        <v>-1.751331689969017E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.0099835670895</v>
+        <v>-120.0099835670892</v>
       </c>
       <c r="AO2">
-        <v>119.9922411522932</v>
+        <v>119.9922411522931</v>
       </c>
       <c r="AP2">
-        <v>-1.674031931552178</v>
+        <v>-1.674031931173209</v>
       </c>
       <c r="AQ2">
-        <v>-110.8337021662487</v>
+        <v>-110.8337021666136</v>
       </c>
       <c r="AR2">
-        <v>118.8689975926449</v>
+        <v>118.8689975926264</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -12822,40 +12822,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.649407735208276E-10</v>
+        <v>3.648544344347026E-10</v>
       </c>
       <c r="O3">
-        <v>-3.457026971344105E-10</v>
+        <v>-3.457408960458002E-10</v>
       </c>
       <c r="P3">
-        <v>-4.979036576776982E-10</v>
+        <v>-4.978117916403798E-10</v>
       </c>
       <c r="Q3">
-        <v>-3.649407743319878E-10</v>
+        <v>-3.648544319986172E-10</v>
       </c>
       <c r="R3">
-        <v>3.457026996813229E-10</v>
+        <v>3.457409049626955E-10</v>
       </c>
       <c r="S3">
-        <v>4.979036619986679E-10</v>
+        <v>4.978117993343417E-10</v>
       </c>
       <c r="T3">
-        <v>1.064256789095103E-10</v>
+        <v>1.063213077595405E-10</v>
       </c>
       <c r="U3">
-        <v>-4.569215639391241E-10</v>
+        <v>-4.568710480404257E-10</v>
       </c>
       <c r="V3">
-        <v>5.335003580385775E-11</v>
+        <v>5.32528213565647E-11</v>
       </c>
       <c r="W3">
-        <v>-1.064256791982231E-10</v>
+        <v>-1.063213069023286E-10</v>
       </c>
       <c r="X3">
-        <v>4.569215687566134E-10</v>
+        <v>4.568710511781109E-10</v>
       </c>
       <c r="Y3">
-        <v>-5.335003820201892E-11</v>
+        <v>-5.325281864920639E-11</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -12876,40 +12876,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.044830778223755</v>
+        <v>1.044830778216592</v>
       </c>
       <c r="AH3">
-        <v>0.8233442504527714</v>
+        <v>0.8233442504537678</v>
       </c>
       <c r="AI3">
-        <v>0.7745242562764713</v>
+        <v>0.7745242562806133</v>
       </c>
       <c r="AJ3">
-        <v>1.044830780586254</v>
+        <v>1.044830771127078</v>
       </c>
       <c r="AK3">
-        <v>0.8233442581816365</v>
+        <v>0.8233442617816964</v>
       </c>
       <c r="AL3">
-        <v>0.7745242633169344</v>
+        <v>0.7745242676703828</v>
       </c>
       <c r="AM3">
-        <v>-1.674031931552178</v>
+        <v>-1.674031931173209</v>
       </c>
       <c r="AN3">
-        <v>-110.8337021662487</v>
+        <v>-110.8337021666136</v>
       </c>
       <c r="AO3">
-        <v>118.8689975926449</v>
+        <v>118.8689975926264</v>
       </c>
       <c r="AP3">
-        <v>-1.6740319240051</v>
+        <v>-1.674031952496938</v>
       </c>
       <c r="AQ3">
-        <v>-110.833702078691</v>
+        <v>-110.8337026883206</v>
       </c>
       <c r="AR3">
-        <v>118.8689973724845</v>
+        <v>118.8689979943627</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -12953,40 +12953,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.649605623226093E-10</v>
+        <v>3.648544471343846E-10</v>
       </c>
       <c r="O4">
-        <v>-3.45704115996346E-10</v>
+        <v>-3.457409105859489E-10</v>
       </c>
       <c r="P4">
-        <v>-4.979461705267414E-10</v>
+        <v>-4.978118069191295E-10</v>
       </c>
       <c r="Q4">
-        <v>-3.649605628092668E-10</v>
+        <v>-3.648544456727333E-10</v>
       </c>
       <c r="R4">
-        <v>3.457041175242089E-10</v>
+        <v>3.457409159360864E-10</v>
       </c>
       <c r="S4">
-        <v>4.979461731194599E-10</v>
+        <v>4.978118115355069E-10</v>
       </c>
       <c r="T4">
-        <v>1.064251005682095E-10</v>
+        <v>1.063213079928057E-10</v>
       </c>
       <c r="U4">
-        <v>-4.568375642951247E-10</v>
+        <v>-4.568710588080777E-10</v>
       </c>
       <c r="V4">
-        <v>5.342714628344653E-11</v>
+        <v>5.325282495134314E-11</v>
       </c>
       <c r="W4">
-        <v>-1.064251007414339E-10</v>
+        <v>-1.063213074784785E-10</v>
       </c>
       <c r="X4">
-        <v>4.568375671852158E-10</v>
+        <v>4.568710606906889E-10</v>
       </c>
       <c r="Y4">
-        <v>-5.34271477226331E-11</v>
+        <v>-5.325282332692805E-11</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -13007,40 +13007,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.044830778223755</v>
+        <v>1.044830778216592</v>
       </c>
       <c r="AH4">
-        <v>0.8233442504527714</v>
+        <v>0.8233442504537678</v>
       </c>
       <c r="AI4">
-        <v>0.7745242562764713</v>
+        <v>0.7745242562806133</v>
       </c>
       <c r="AJ4">
-        <v>1.044830779641078</v>
+        <v>1.044830773962883</v>
       </c>
       <c r="AK4">
-        <v>0.8233442550898493</v>
+        <v>0.8233442572505252</v>
       </c>
       <c r="AL4">
-        <v>0.7745242605008386</v>
+        <v>0.7745242631144751</v>
       </c>
       <c r="AM4">
-        <v>-1.674031931552178</v>
+        <v>-1.674031931173209</v>
       </c>
       <c r="AN4">
-        <v>-110.8337021662487</v>
+        <v>-110.8337021666136</v>
       </c>
       <c r="AO4">
-        <v>118.8689975926449</v>
+        <v>118.8689975926264</v>
       </c>
       <c r="AP4">
-        <v>-1.674031927021755</v>
+        <v>-1.674031943967448</v>
       </c>
       <c r="AQ4">
-        <v>-110.8337021136804</v>
+        <v>-110.8337024796378</v>
       </c>
       <c r="AR4">
-        <v>118.8689974605757</v>
+        <v>118.8689978336682</v>
       </c>
     </row>
   </sheetData>
@@ -13192,130 +13192,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>8.355337188473405E-06</v>
+        <v>8.355336350723607E-06</v>
       </c>
       <c r="C2">
-        <v>0.0254696431020716</v>
+        <v>0.02546964310213707</v>
       </c>
       <c r="D2">
-        <v>0.02397306401569589</v>
+        <v>0.02397306401576239</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02547523506057757</v>
+        <v>0.02547523506064291</v>
       </c>
       <c r="G2">
-        <v>0.02396471243890582</v>
+        <v>0.02396471243897198</v>
       </c>
       <c r="H2">
-        <v>1.929582498727104E-06</v>
+        <v>1.929582305257073E-06</v>
       </c>
       <c r="I2">
-        <v>0.00588196220810596</v>
+        <v>0.00588196220812108</v>
       </c>
       <c r="J2">
-        <v>0.005536342067602786</v>
+        <v>0.005536342067618144</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.005883253615624691</v>
+        <v>0.00588325361563978</v>
       </c>
       <c r="M2">
-        <v>0.005534413353530883</v>
+        <v>0.005534413353546161</v>
       </c>
       <c r="N2">
-        <v>5.332270250579398E-07</v>
+        <v>5.332269245808313E-07</v>
       </c>
       <c r="O2">
-        <v>0.004290916274472246</v>
+        <v>0.004290916274439682</v>
       </c>
       <c r="P2">
-        <v>0.00345296021914371</v>
+        <v>0.00345296021923856</v>
       </c>
       <c r="Q2">
-        <v>-9.824931198183375E-10</v>
+        <v>-9.823875545747418E-10</v>
       </c>
       <c r="R2">
-        <v>-0.003244939237263409</v>
+        <v>-0.003244939237188713</v>
       </c>
       <c r="S2">
-        <v>-0.002871537067979098</v>
+        <v>-0.002871537068080113</v>
       </c>
       <c r="T2">
-        <v>-1.652734994378491E-06</v>
+        <v>-1.652734843834569E-06</v>
       </c>
       <c r="U2">
-        <v>0.003098998973911946</v>
+        <v>0.003098998973980248</v>
       </c>
       <c r="V2">
-        <v>0.003591147043536619</v>
+        <v>0.003591147043464608</v>
       </c>
       <c r="W2">
-        <v>-2.860989328627122E-10</v>
+        <v>-2.862677591107976E-10</v>
       </c>
       <c r="X2">
-        <v>-0.003244938937770458</v>
+        <v>-0.003244938937830075</v>
       </c>
       <c r="Y2">
-        <v>-0.002871538551835956</v>
+        <v>-0.00287153855173997</v>
       </c>
       <c r="Z2">
-        <v>72.11857928589733</v>
+        <v>72.11858091570839</v>
       </c>
       <c r="AA2">
-        <v>-155.8471452568338</v>
+        <v>-155.8471452576395</v>
       </c>
       <c r="AB2">
-        <v>73.86880136725814</v>
+        <v>73.86880136861825</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>24.16681899357397</v>
+        <v>24.16681899276954</v>
       </c>
       <c r="AE2">
-        <v>-106.1305992072141</v>
+        <v>-106.1305992058544</v>
       </c>
       <c r="AG2">
-        <v>0.900000035838437</v>
+        <v>0.9000000358384317</v>
       </c>
       <c r="AH2">
-        <v>0.8998682978314786</v>
+        <v>0.8998682978314761</v>
       </c>
       <c r="AI2">
-        <v>0.8998530607498636</v>
+        <v>0.8998530607498658</v>
       </c>
       <c r="AJ2">
-        <v>0.9898404736840074</v>
+        <v>0.9898404736896618</v>
       </c>
       <c r="AK2">
-        <v>0.7800168353194068</v>
+        <v>0.7800168353155935</v>
       </c>
       <c r="AL2">
-        <v>0.7337666083520219</v>
+        <v>0.7337666083506387</v>
       </c>
       <c r="AM2">
-        <v>-1.659271374716177E-06</v>
+        <v>-1.659271100274987E-06</v>
       </c>
       <c r="AN2">
-        <v>-120.0094581941121</v>
+        <v>-120.009458194112</v>
       </c>
       <c r="AO2">
-        <v>119.9926494432285</v>
+        <v>119.9926494432283</v>
       </c>
       <c r="AP2">
-        <v>-1.674003897119532</v>
+        <v>-1.674003896734075</v>
       </c>
       <c r="AQ2">
-        <v>-110.833183650489</v>
+        <v>-110.8331836501077</v>
       </c>
       <c r="AR2">
-        <v>118.869415596471</v>
+        <v>118.8694155958653</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -13359,40 +13359,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.275630472289105E-10</v>
+        <v>3.274625047398927E-10</v>
       </c>
       <c r="O3">
-        <v>-3.103021775460753E-10</v>
+        <v>-3.102851157813419E-10</v>
       </c>
       <c r="P3">
-        <v>-4.467886013483856E-10</v>
+        <v>-4.467757187533563E-10</v>
       </c>
       <c r="Q3">
-        <v>-3.275630479567355E-10</v>
+        <v>-3.274625025534597E-10</v>
       </c>
       <c r="R3">
-        <v>3.103021798329173E-10</v>
+        <v>3.102851237844688E-10</v>
       </c>
       <c r="S3">
-        <v>4.467886052251567E-10</v>
+        <v>4.467757256581343E-10</v>
       </c>
       <c r="T3">
-        <v>9.542640758096131E-11</v>
+        <v>9.542258571360747E-11</v>
       </c>
       <c r="U3">
-        <v>-4.101081667816964E-10</v>
+        <v>-4.100713333157701E-10</v>
       </c>
       <c r="V3">
-        <v>4.779562618612316E-11</v>
+        <v>4.777755378554654E-11</v>
       </c>
       <c r="W3">
-        <v>-9.542640783958208E-11</v>
+        <v>-9.54225849442434E-11</v>
       </c>
       <c r="X3">
-        <v>4.101081711049174E-10</v>
+        <v>4.100713361319177E-10</v>
       </c>
       <c r="Y3">
-        <v>-4.779562833850005E-11</v>
+        <v>-4.777755135588699E-11</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -13413,40 +13413,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9898404736840074</v>
+        <v>0.9898404736896618</v>
       </c>
       <c r="AH3">
-        <v>0.7800168353194068</v>
+        <v>0.7800168353155935</v>
       </c>
       <c r="AI3">
-        <v>0.7337666083520219</v>
+        <v>0.7337666083506387</v>
       </c>
       <c r="AJ3">
-        <v>0.9898404759211776</v>
+        <v>0.9898404669732375</v>
       </c>
       <c r="AK3">
-        <v>0.7800168426413148</v>
+        <v>0.7800168460469796</v>
       </c>
       <c r="AL3">
-        <v>0.7337666150207237</v>
+        <v>0.7337666191406523</v>
       </c>
       <c r="AM3">
-        <v>-1.674003897119532</v>
+        <v>-1.674003896734075</v>
       </c>
       <c r="AN3">
-        <v>-110.833183650489</v>
+        <v>-110.8331836501077</v>
       </c>
       <c r="AO3">
-        <v>118.869415596471</v>
+        <v>118.8694155958653</v>
       </c>
       <c r="AP3">
-        <v>-1.674003889607883</v>
+        <v>-1.674003918060595</v>
       </c>
       <c r="AQ3">
-        <v>-110.8331835630423</v>
+        <v>-110.8331841718638</v>
       </c>
       <c r="AR3">
-        <v>118.8694153761568</v>
+        <v>118.869415997551</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -13490,40 +13490,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.274296245469385E-10</v>
+        <v>3.274625156436558E-10</v>
       </c>
       <c r="O4">
-        <v>-3.103482630369151E-10</v>
+        <v>-3.10285127759999E-10</v>
       </c>
       <c r="P4">
-        <v>-4.468263775654742E-10</v>
+        <v>-4.467757298197654E-10</v>
       </c>
       <c r="Q4">
-        <v>-3.274296249835574E-10</v>
+        <v>-3.274625143317958E-10</v>
       </c>
       <c r="R4">
-        <v>3.10348264408816E-10</v>
+        <v>3.102851325618754E-10</v>
       </c>
       <c r="S4">
-        <v>4.468263798921278E-10</v>
+        <v>4.467757339626324E-10</v>
       </c>
       <c r="T4">
-        <v>9.535525363135894E-11</v>
+        <v>9.54225865401646E-11</v>
       </c>
       <c r="U4">
-        <v>-4.099799355205037E-10</v>
+        <v>-4.100713432352533E-10</v>
       </c>
       <c r="V4">
-        <v>4.780655157911781E-11</v>
+        <v>4.777755979695298E-11</v>
       </c>
       <c r="W4">
-        <v>-9.535525378655907E-11</v>
+        <v>-9.542258607854614E-11</v>
       </c>
       <c r="X4">
-        <v>4.099799381140299E-10</v>
+        <v>4.100713449249418E-10</v>
       </c>
       <c r="Y4">
-        <v>-4.780655286996314E-11</v>
+        <v>-4.777755833915716E-11</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -13544,40 +13544,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9898404736840074</v>
+        <v>0.9898404736896618</v>
       </c>
       <c r="AH4">
-        <v>0.7800168353194068</v>
+        <v>0.7800168353155935</v>
       </c>
       <c r="AI4">
-        <v>0.7337666083520219</v>
+        <v>0.7337666083506387</v>
       </c>
       <c r="AJ4">
-        <v>0.9898404750266954</v>
+        <v>0.9898404696598071</v>
       </c>
       <c r="AK4">
-        <v>0.7800168397123501</v>
+        <v>0.7800168417544253</v>
       </c>
       <c r="AL4">
-        <v>0.7337666123537822</v>
+        <v>0.733766614824647</v>
       </c>
       <c r="AM4">
-        <v>-1.674003897119532</v>
+        <v>-1.674003896734075</v>
       </c>
       <c r="AN4">
-        <v>-110.833183650489</v>
+        <v>-110.8331836501077</v>
       </c>
       <c r="AO4">
-        <v>118.869415596471</v>
+        <v>118.8694155958653</v>
       </c>
       <c r="AP4">
-        <v>-1.674003892595486</v>
+        <v>-1.674003909529989</v>
       </c>
       <c r="AQ4">
-        <v>-110.8331835979509</v>
+        <v>-110.8331839631614</v>
       </c>
       <c r="AR4">
-        <v>118.8694154643803</v>
+        <v>118.8694158368767</v>
       </c>
     </row>
   </sheetData>
@@ -14839,127 +14839,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3396014977829826</v>
+        <v>0.3396014977798925</v>
       </c>
       <c r="D2">
-        <v>0.3396014977847441</v>
+        <v>0.3396014977798923</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3396014977829823</v>
+        <v>0.3396014977798925</v>
       </c>
       <c r="G2">
-        <v>0.3396014977847445</v>
+        <v>0.3396014977798923</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.07842760763354445</v>
+        <v>0.07842760763283083</v>
       </c>
       <c r="J2">
-        <v>0.07842760763395126</v>
+        <v>0.07842760763283078</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.07842760763354438</v>
+        <v>0.07842760763283083</v>
       </c>
       <c r="M2">
-        <v>0.07842760763395133</v>
+        <v>0.07842760763283077</v>
       </c>
       <c r="N2">
-        <v>-1.800014916421485E-13</v>
+        <v>-2.42861275607684E-18</v>
       </c>
       <c r="O2">
-        <v>0.08211242437925247</v>
+        <v>0.08211242437846838</v>
       </c>
       <c r="P2">
-        <v>0.03586932765169212</v>
+        <v>0.03586932765070251</v>
       </c>
       <c r="Q2">
-        <v>1.79950490779076E-13</v>
+        <v>2.42861275607684E-18</v>
       </c>
       <c r="R2">
-        <v>-0.02312154836354323</v>
+        <v>-0.02312154836388518</v>
       </c>
       <c r="S2">
-        <v>0.02312154836452414</v>
+        <v>0.02312154836388059</v>
       </c>
       <c r="T2">
-        <v>6.371708426843075E-13</v>
+        <v>-4.990900718775215E-35</v>
       </c>
       <c r="U2">
-        <v>0.005785376091091064</v>
+        <v>0.005785376091549832</v>
       </c>
       <c r="V2">
-        <v>0.07392443402620519</v>
+        <v>0.07392443402538297</v>
       </c>
       <c r="W2">
-        <v>-6.371271276504762E-13</v>
+        <v>-2.428612756076838E-18</v>
       </c>
       <c r="X2">
-        <v>0.034069528968334</v>
+        <v>0.03406952896691683</v>
       </c>
       <c r="Y2">
-        <v>-0.034069528966833</v>
+        <v>-0.03406952896691642</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-124.1630791785605</v>
+        <v>-124.163079178916</v>
       </c>
       <c r="AB2">
-        <v>55.83692082144574</v>
+        <v>55.83692082107669</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>55.83692082143227</v>
+        <v>55.83692082107672</v>
       </c>
       <c r="AE2">
-        <v>-124.163079178547</v>
+        <v>-124.163079178916</v>
       </c>
       <c r="AF2">
-        <v>1.049999952316291</v>
+        <v>1.04999995231631</v>
       </c>
       <c r="AG2">
-        <v>1.049579147011182</v>
+        <v>1.04957914701117</v>
       </c>
       <c r="AH2">
-        <v>1.047680683785243</v>
+        <v>1.047680683785271</v>
       </c>
       <c r="AI2">
-        <v>1.049999952311919</v>
+        <v>1.049999952316309</v>
       </c>
       <c r="AJ2">
-        <v>0.5249999761659004</v>
+        <v>0.5249999761581737</v>
       </c>
       <c r="AK2">
-        <v>0.5249999761543634</v>
+        <v>0.5249999761581368</v>
       </c>
       <c r="AL2">
-        <v>3.981699153490761E-13</v>
+        <v>1.177452216040199E-15</v>
       </c>
       <c r="AM2">
-        <v>-120.1328637622913</v>
+        <v>-120.13286376229</v>
       </c>
       <c r="AN2">
-        <v>119.953511366171</v>
+        <v>119.9535113661724</v>
       </c>
       <c r="AO2">
-        <v>4.999062121345718E-10</v>
+        <v>2.616886448728214E-14</v>
       </c>
       <c r="AP2">
-        <v>179.9999999988495</v>
+        <v>-179.9999999999903</v>
       </c>
       <c r="AQ2">
-        <v>-179.9999999988201</v>
+        <v>179.9999999999901</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -15003,40 +15003,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-3.183231311631726E-13</v>
+        <v>9.692294311873643E-23</v>
       </c>
       <c r="O3">
-        <v>3.492530161231259E-20</v>
+        <v>-3.885787813128837E-17</v>
       </c>
       <c r="P3">
-        <v>1.591616014037735E-13</v>
+        <v>3.885772562112693E-17</v>
       </c>
       <c r="Q3">
-        <v>3.183231311628396E-13</v>
+        <v>-9.692294311873643E-23</v>
       </c>
       <c r="R3">
-        <v>1.065813188655447E-16</v>
+        <v>1.454756409379394E-16</v>
       </c>
       <c r="S3">
-        <v>-1.59054999247111E-13</v>
+        <v>6.776003748137117E-17</v>
       </c>
       <c r="T3">
-        <v>-2.777372296650053E-24</v>
+        <v>-1.846340086368193E-24</v>
       </c>
       <c r="U3">
-        <v>1.750458898299431E-09</v>
+        <v>1.750453628183988E-09</v>
       </c>
       <c r="V3">
-        <v>-1.75029973669538E-09</v>
+        <v>-1.75045363304109E-09</v>
       </c>
       <c r="W3">
-        <v>2.581404108473346E-24</v>
+        <v>1.846340086368193E-24</v>
       </c>
       <c r="X3">
-        <v>-1.750458826273515E-09</v>
+        <v>-1.750453556151818E-09</v>
       </c>
       <c r="Y3">
-        <v>1.750299808720779E-09</v>
+        <v>1.75045370507326E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -15057,40 +15057,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.049999952311919</v>
+        <v>1.049999952316309</v>
       </c>
       <c r="AG3">
-        <v>0.5249999761659004</v>
+        <v>0.5249999761581737</v>
       </c>
       <c r="AH3">
-        <v>0.5249999761543634</v>
+        <v>0.5249999761581368</v>
       </c>
       <c r="AI3">
-        <v>1.049999952310821</v>
+        <v>1.049999952316309</v>
       </c>
       <c r="AJ3">
-        <v>0.5249999545637923</v>
+        <v>0.5249999545541256</v>
       </c>
       <c r="AK3">
-        <v>0.5249999977553751</v>
+        <v>0.5249999977621869</v>
       </c>
       <c r="AL3">
-        <v>4.999062121345718E-10</v>
+        <v>2.616886448728214E-14</v>
       </c>
       <c r="AM3">
-        <v>179.9999999988495</v>
+        <v>-179.9999999999903</v>
       </c>
       <c r="AN3">
-        <v>-179.9999999988201</v>
+        <v>179.9999999999901</v>
       </c>
       <c r="AO3">
-        <v>4.646334059763535E-10</v>
+        <v>2.616883092971721E-14</v>
       </c>
       <c r="AP3">
-        <v>-179.9999965113875</v>
+        <v>-179.9999965101816</v>
       </c>
       <c r="AQ3">
-        <v>179.9999965113467</v>
+        <v>179.9999965101818</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -15134,40 +15134,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-3.183231311742821E-13</v>
+        <v>9.692294311873643E-23</v>
       </c>
       <c r="O4">
-        <v>1.591616005035504E-13</v>
+        <v>-2.428620159482864E-17</v>
       </c>
       <c r="P4">
-        <v>3.18323166984876E-13</v>
+        <v>2.428604908466508E-17</v>
       </c>
       <c r="Q4">
-        <v>3.183231311757008E-13</v>
+        <v>-9.692294311873643E-23</v>
       </c>
       <c r="R4">
-        <v>-1.590976442676764E-13</v>
+        <v>8.825686249475197E-17</v>
       </c>
       <c r="S4">
-        <v>-3.182592224931634E-13</v>
+        <v>3.968461109007151E-17</v>
       </c>
       <c r="T4">
-        <v>1.273292524649913E-12</v>
+        <v>-1.846341604925366E-24</v>
       </c>
       <c r="U4">
-        <v>1.750140575168258E-09</v>
+        <v>1.750453671899018E-09</v>
       </c>
       <c r="V4">
-        <v>-1.750299736695376E-09</v>
+        <v>-1.750453662184443E-09</v>
       </c>
       <c r="W4">
-        <v>-1.273292524646662E-12</v>
+        <v>1.846341604925366E-24</v>
       </c>
       <c r="X4">
-        <v>-1.750140531966844E-09</v>
+        <v>-1.750453628679713E-09</v>
       </c>
       <c r="Y4">
-        <v>1.750299779910673E-09</v>
+        <v>1.750453705403747E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -15188,40 +15188,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.049999952311919</v>
+        <v>1.049999952316309</v>
       </c>
       <c r="AG4">
-        <v>0.5249999761659004</v>
+        <v>0.5249999761581737</v>
       </c>
       <c r="AH4">
-        <v>0.5249999761543634</v>
+        <v>0.5249999761581368</v>
       </c>
       <c r="AI4">
-        <v>1.049999952309671</v>
+        <v>1.049999952316309</v>
       </c>
       <c r="AJ4">
-        <v>0.5249999632047733</v>
+        <v>0.524999963195744</v>
       </c>
       <c r="AK4">
-        <v>0.5249999891132434</v>
+        <v>0.524999989120567</v>
       </c>
       <c r="AL4">
-        <v>4.999062121345718E-10</v>
+        <v>2.616886448728214E-14</v>
       </c>
       <c r="AM4">
-        <v>179.9999999988495</v>
+        <v>-179.9999999999903</v>
       </c>
       <c r="AN4">
-        <v>-179.9999999988201</v>
+        <v>179.9999999999901</v>
       </c>
       <c r="AO4">
-        <v>5.944083598049341E-10</v>
+        <v>2.616884435274268E-14</v>
       </c>
       <c r="AP4">
-        <v>-179.999997907477</v>
+        <v>-179.9999979061051</v>
       </c>
       <c r="AQ4">
-        <v>179.9999979076956</v>
+        <v>179.9999979061051</v>
       </c>
     </row>
   </sheetData>
